--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" updateLinks="never"/>
   <bookViews>
-    <workbookView windowWidth="18340" windowHeight="8720" activeTab="1"/>
+    <workbookView windowHeight="7070" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TechSelection" sheetId="21" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="181">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -439,9 +439,6 @@
   </si>
   <si>
     <t>Saudi Arabia</t>
-  </si>
-  <si>
-    <t>XXXX</t>
   </si>
   <si>
     <t>\I:</t>
@@ -11896,40 +11893,40 @@
         <v>134</v>
       </c>
       <c r="AO66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AP66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AR66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AS66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AT66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AU66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AV66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AW66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AX66" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="AP66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AQ66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AR66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AT66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AU66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AV66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AW66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AX66" s="11" t="s">
+      <c r="AY66" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AY66" s="2" t="s">
+      <c r="AZ66" s="16" t="s">
         <v>137</v>
-      </c>
-      <c r="AZ66" s="16" t="s">
-        <v>138</v>
       </c>
       <c r="BE66" s="11"/>
       <c r="BF66" s="11"/>
@@ -11945,7 +11942,7 @@
         <v>68</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D67" s="2">
         <f t="shared" ref="D67:AK67" si="2">D77/1000</f>
@@ -12083,19 +12080,17 @@
         <v>0</v>
       </c>
       <c r="AL67" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AN67" s="15"/>
+      <c r="AX67" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="AN67" s="15">
-        <v>1000</v>
-      </c>
-      <c r="AX67" s="1" t="s">
+      <c r="AY67" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="AY67" s="1" t="s">
+      <c r="AZ67" s="16" t="s">
         <v>142</v>
-      </c>
-      <c r="AZ67" s="16" t="s">
-        <v>143</v>
       </c>
       <c r="BD67" s="17"/>
       <c r="BE67" s="11"/>
@@ -12246,17 +12241,15 @@
         <v>0</v>
       </c>
       <c r="AL68" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AN68" s="15">
-        <v>0</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AN68" s="15"/>
       <c r="AX68" s="1"/>
       <c r="AY68" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AZ68" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" ht="16" spans="3:52">
@@ -12398,17 +12391,15 @@
         <v>0</v>
       </c>
       <c r="AL69" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AN69" s="15">
-        <v>0</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AN69" s="15"/>
       <c r="AX69" s="1"/>
       <c r="AY69" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AZ69" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" ht="16" spans="3:52">
@@ -12550,17 +12541,15 @@
         <v>140000</v>
       </c>
       <c r="AL70" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AN70" s="15">
-        <v>0</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="AN70" s="15"/>
       <c r="AX70" s="1"/>
       <c r="AY70" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AZ70" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" ht="16" spans="3:52">
@@ -12702,15 +12691,15 @@
         <v>0</v>
       </c>
       <c r="AL71" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AN71" s="15"/>
       <c r="AX71" s="1"/>
       <c r="AY71" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AZ71" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" ht="16" spans="3:52">
@@ -12852,15 +12841,15 @@
         <v>0</v>
       </c>
       <c r="AL72" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AN72" s="15"/>
       <c r="AX72" s="1"/>
       <c r="AY72" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AZ72" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="16" spans="2:52">
@@ -13003,7 +12992,7 @@
         <v>0</v>
       </c>
       <c r="AL73" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AM73" s="2"/>
       <c r="AN73" s="15"/>
@@ -13017,16 +13006,16 @@
       <c r="AV73" s="2"/>
       <c r="AW73" s="2"/>
       <c r="AY73" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AZ73" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
@@ -14023,7 +14012,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -14035,25 +14024,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" t="s">
         <v>152</v>
-      </c>
-      <c r="F1" t="s">
-        <v>153</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I1" t="s">
         <v>154</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>155</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>156</v>
-      </c>
-      <c r="K1" t="s">
-        <v>157</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -14175,28 +14164,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G2" t="s">
         <v>159</v>
       </c>
-      <c r="G2" t="s">
-        <v>160</v>
-      </c>
       <c r="H2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -14304,7 +14293,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -14315,31 +14304,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G3" t="s">
         <v>159</v>
       </c>
-      <c r="G3" t="s">
-        <v>160</v>
-      </c>
       <c r="H3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -14447,7 +14436,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -14458,31 +14447,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G4" t="s">
         <v>159</v>
       </c>
-      <c r="G4" t="s">
-        <v>160</v>
-      </c>
       <c r="H4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -14590,7 +14579,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -14604,28 +14593,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" t="s">
         <v>159</v>
       </c>
-      <c r="G5" t="s">
-        <v>160</v>
-      </c>
       <c r="H5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -14733,7 +14722,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -14744,31 +14733,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G6" t="s">
         <v>159</v>
       </c>
-      <c r="G6" t="s">
-        <v>160</v>
-      </c>
       <c r="H6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -14876,7 +14865,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -14890,28 +14879,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G7" t="s">
         <v>159</v>
       </c>
-      <c r="G7" t="s">
-        <v>160</v>
-      </c>
       <c r="H7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -15019,7 +15008,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -15030,31 +15019,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
+        <v>158</v>
+      </c>
+      <c r="G8" t="s">
         <v>159</v>
       </c>
-      <c r="G8" t="s">
-        <v>160</v>
-      </c>
       <c r="H8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -15162,7 +15151,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -15173,31 +15162,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
+        <v>158</v>
+      </c>
+      <c r="G9" t="s">
         <v>159</v>
       </c>
-      <c r="G9" t="s">
-        <v>160</v>
-      </c>
       <c r="H9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -15305,7 +15294,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -15316,31 +15305,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" t="s">
         <v>159</v>
       </c>
-      <c r="G10" t="s">
-        <v>160</v>
-      </c>
       <c r="H10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -15448,7 +15437,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -15459,31 +15448,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" t="s">
         <v>159</v>
       </c>
-      <c r="G11" t="s">
-        <v>160</v>
-      </c>
       <c r="H11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -15591,7 +15580,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -15602,31 +15591,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
+        <v>158</v>
+      </c>
+      <c r="G12" t="s">
         <v>159</v>
       </c>
-      <c r="G12" t="s">
-        <v>160</v>
-      </c>
       <c r="H12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -15734,7 +15723,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -15745,31 +15734,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
+        <v>158</v>
+      </c>
+      <c r="G13" t="s">
         <v>159</v>
       </c>
-      <c r="G13" t="s">
-        <v>160</v>
-      </c>
       <c r="H13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -15877,7 +15866,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -15888,31 +15877,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
+        <v>158</v>
+      </c>
+      <c r="G14" t="s">
         <v>159</v>
       </c>
-      <c r="G14" t="s">
-        <v>160</v>
-      </c>
       <c r="H14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -16020,7 +16009,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -16031,31 +16020,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" t="s">
         <v>159</v>
       </c>
-      <c r="G15" t="s">
-        <v>160</v>
-      </c>
       <c r="H15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -16163,7 +16152,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -16174,31 +16163,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
+        <v>158</v>
+      </c>
+      <c r="G16" t="s">
         <v>159</v>
       </c>
-      <c r="G16" t="s">
-        <v>160</v>
-      </c>
       <c r="H16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -16306,7 +16295,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -16320,28 +16309,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
+        <v>158</v>
+      </c>
+      <c r="G17" t="s">
         <v>159</v>
       </c>
-      <c r="G17" t="s">
-        <v>160</v>
-      </c>
       <c r="H17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -16449,7 +16438,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -16460,31 +16449,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
+        <v>158</v>
+      </c>
+      <c r="G18" t="s">
         <v>159</v>
       </c>
-      <c r="G18" t="s">
-        <v>160</v>
-      </c>
       <c r="H18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -16592,7 +16581,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -16603,31 +16592,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
+        <v>158</v>
+      </c>
+      <c r="G19" t="s">
         <v>159</v>
       </c>
-      <c r="G19" t="s">
-        <v>160</v>
-      </c>
       <c r="H19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -16735,7 +16724,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -16746,31 +16735,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G20" t="s">
         <v>159</v>
       </c>
-      <c r="G20" t="s">
-        <v>160</v>
-      </c>
       <c r="H20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -16878,7 +16867,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -16892,28 +16881,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
+        <v>158</v>
+      </c>
+      <c r="G21" t="s">
         <v>159</v>
       </c>
-      <c r="G21" t="s">
-        <v>160</v>
-      </c>
       <c r="H21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -17021,7 +17010,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -17032,31 +17021,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
+        <v>158</v>
+      </c>
+      <c r="G22" t="s">
         <v>159</v>
       </c>
-      <c r="G22" t="s">
-        <v>160</v>
-      </c>
       <c r="H22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -17164,7 +17153,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -17175,31 +17164,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
+        <v>158</v>
+      </c>
+      <c r="G23" t="s">
         <v>159</v>
       </c>
-      <c r="G23" t="s">
-        <v>160</v>
-      </c>
       <c r="H23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -17307,7 +17296,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -17321,28 +17310,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
+        <v>158</v>
+      </c>
+      <c r="G24" t="s">
         <v>159</v>
       </c>
-      <c r="G24" t="s">
-        <v>160</v>
-      </c>
       <c r="H24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -17450,7 +17439,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -17461,31 +17450,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
+        <v>158</v>
+      </c>
+      <c r="G25" t="s">
         <v>159</v>
       </c>
-      <c r="G25" t="s">
-        <v>160</v>
-      </c>
       <c r="H25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -17593,7 +17582,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -17604,31 +17593,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
+        <v>158</v>
+      </c>
+      <c r="G26" t="s">
         <v>159</v>
       </c>
-      <c r="G26" t="s">
-        <v>160</v>
-      </c>
       <c r="H26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -17736,7 +17725,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -17747,31 +17736,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
+        <v>158</v>
+      </c>
+      <c r="G27" t="s">
         <v>159</v>
       </c>
-      <c r="G27" t="s">
-        <v>160</v>
-      </c>
       <c r="H27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -17879,7 +17868,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -17890,31 +17879,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
+        <v>158</v>
+      </c>
+      <c r="G28" t="s">
         <v>159</v>
       </c>
-      <c r="G28" t="s">
-        <v>160</v>
-      </c>
       <c r="H28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -18022,7 +18011,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -18036,28 +18025,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
+        <v>157</v>
+      </c>
+      <c r="E29" t="s">
+        <v>157</v>
+      </c>
+      <c r="F29" t="s">
         <v>158</v>
       </c>
-      <c r="E29" t="s">
-        <v>158</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>159</v>
       </c>
-      <c r="G29" t="s">
-        <v>160</v>
-      </c>
       <c r="H29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -18165,7 +18154,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -18176,31 +18165,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D30" t="s">
+        <v>157</v>
+      </c>
+      <c r="E30" t="s">
+        <v>157</v>
+      </c>
+      <c r="F30" t="s">
         <v>158</v>
       </c>
-      <c r="E30" t="s">
-        <v>158</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>159</v>
       </c>
-      <c r="G30" t="s">
-        <v>160</v>
-      </c>
       <c r="H30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -18308,7 +18297,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -18319,31 +18308,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D31" t="s">
+        <v>157</v>
+      </c>
+      <c r="E31" t="s">
+        <v>157</v>
+      </c>
+      <c r="F31" t="s">
         <v>158</v>
       </c>
-      <c r="E31" t="s">
-        <v>158</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>159</v>
       </c>
-      <c r="G31" t="s">
-        <v>160</v>
-      </c>
       <c r="H31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -18451,7 +18440,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -18465,28 +18454,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
+        <v>157</v>
+      </c>
+      <c r="E32" t="s">
+        <v>157</v>
+      </c>
+      <c r="F32" t="s">
         <v>158</v>
       </c>
-      <c r="E32" t="s">
-        <v>158</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>159</v>
       </c>
-      <c r="G32" t="s">
-        <v>160</v>
-      </c>
       <c r="H32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -18594,7 +18583,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -18605,31 +18594,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D33" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" t="s">
+        <v>157</v>
+      </c>
+      <c r="F33" t="s">
         <v>158</v>
       </c>
-      <c r="E33" t="s">
-        <v>158</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>159</v>
       </c>
-      <c r="G33" t="s">
-        <v>160</v>
-      </c>
       <c r="H33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -18737,7 +18726,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -18751,28 +18740,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
+        <v>157</v>
+      </c>
+      <c r="E34" t="s">
+        <v>157</v>
+      </c>
+      <c r="F34" t="s">
         <v>158</v>
       </c>
-      <c r="E34" t="s">
-        <v>158</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>159</v>
       </c>
-      <c r="G34" t="s">
-        <v>160</v>
-      </c>
       <c r="H34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -18880,7 +18869,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -18891,31 +18880,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D35" t="s">
+        <v>157</v>
+      </c>
+      <c r="E35" t="s">
+        <v>157</v>
+      </c>
+      <c r="F35" t="s">
         <v>158</v>
       </c>
-      <c r="E35" t="s">
-        <v>158</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>159</v>
       </c>
-      <c r="G35" t="s">
-        <v>160</v>
-      </c>
       <c r="H35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -19023,7 +19012,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -19034,31 +19023,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D36" t="s">
+        <v>157</v>
+      </c>
+      <c r="E36" t="s">
+        <v>157</v>
+      </c>
+      <c r="F36" t="s">
         <v>158</v>
       </c>
-      <c r="E36" t="s">
-        <v>158</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>159</v>
       </c>
-      <c r="G36" t="s">
-        <v>160</v>
-      </c>
       <c r="H36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -19166,7 +19155,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -19177,31 +19166,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D37" t="s">
+        <v>157</v>
+      </c>
+      <c r="E37" t="s">
+        <v>157</v>
+      </c>
+      <c r="F37" t="s">
         <v>158</v>
       </c>
-      <c r="E37" t="s">
-        <v>158</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>159</v>
       </c>
-      <c r="G37" t="s">
-        <v>160</v>
-      </c>
       <c r="H37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -19309,7 +19298,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -19320,31 +19309,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D38" t="s">
+        <v>157</v>
+      </c>
+      <c r="E38" t="s">
+        <v>157</v>
+      </c>
+      <c r="F38" t="s">
         <v>158</v>
       </c>
-      <c r="E38" t="s">
-        <v>158</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>159</v>
       </c>
-      <c r="G38" t="s">
-        <v>160</v>
-      </c>
       <c r="H38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -19452,7 +19441,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -19463,31 +19452,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D39" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" t="s">
+        <v>157</v>
+      </c>
+      <c r="F39" t="s">
         <v>158</v>
       </c>
-      <c r="E39" t="s">
-        <v>158</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>159</v>
       </c>
-      <c r="G39" t="s">
-        <v>160</v>
-      </c>
       <c r="H39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -19595,7 +19584,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -19606,31 +19595,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D40" t="s">
+        <v>157</v>
+      </c>
+      <c r="E40" t="s">
+        <v>157</v>
+      </c>
+      <c r="F40" t="s">
         <v>158</v>
       </c>
-      <c r="E40" t="s">
-        <v>158</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>159</v>
       </c>
-      <c r="G40" t="s">
-        <v>160</v>
-      </c>
       <c r="H40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -19738,7 +19727,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -19749,31 +19738,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D41" t="s">
+        <v>157</v>
+      </c>
+      <c r="E41" t="s">
+        <v>157</v>
+      </c>
+      <c r="F41" t="s">
         <v>158</v>
       </c>
-      <c r="E41" t="s">
-        <v>158</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>159</v>
       </c>
-      <c r="G41" t="s">
-        <v>160</v>
-      </c>
       <c r="H41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -19881,7 +19870,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -19892,31 +19881,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E42" t="s">
+        <v>157</v>
+      </c>
+      <c r="F42" t="s">
         <v>158</v>
       </c>
-      <c r="E42" t="s">
-        <v>158</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>159</v>
       </c>
-      <c r="G42" t="s">
-        <v>160</v>
-      </c>
       <c r="H42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -20024,7 +20013,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -20035,31 +20024,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D43" t="s">
+        <v>157</v>
+      </c>
+      <c r="E43" t="s">
+        <v>157</v>
+      </c>
+      <c r="F43" t="s">
         <v>158</v>
       </c>
-      <c r="E43" t="s">
-        <v>158</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>159</v>
       </c>
-      <c r="G43" t="s">
-        <v>160</v>
-      </c>
       <c r="H43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -20167,7 +20156,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -20181,28 +20170,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
+        <v>157</v>
+      </c>
+      <c r="E44" t="s">
+        <v>157</v>
+      </c>
+      <c r="F44" t="s">
         <v>158</v>
       </c>
-      <c r="E44" t="s">
-        <v>158</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>159</v>
       </c>
-      <c r="G44" t="s">
-        <v>160</v>
-      </c>
       <c r="H44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -20310,7 +20299,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -20321,31 +20310,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D45" t="s">
+        <v>157</v>
+      </c>
+      <c r="E45" t="s">
+        <v>157</v>
+      </c>
+      <c r="F45" t="s">
         <v>158</v>
       </c>
-      <c r="E45" t="s">
-        <v>158</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>159</v>
       </c>
-      <c r="G45" t="s">
-        <v>160</v>
-      </c>
       <c r="H45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -20453,7 +20442,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -20464,31 +20453,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D46" t="s">
+        <v>157</v>
+      </c>
+      <c r="E46" t="s">
+        <v>157</v>
+      </c>
+      <c r="F46" t="s">
         <v>158</v>
       </c>
-      <c r="E46" t="s">
-        <v>158</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>159</v>
       </c>
-      <c r="G46" t="s">
-        <v>160</v>
-      </c>
       <c r="H46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -20596,7 +20585,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -20607,31 +20596,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D47" t="s">
+        <v>157</v>
+      </c>
+      <c r="E47" t="s">
+        <v>157</v>
+      </c>
+      <c r="F47" t="s">
         <v>158</v>
       </c>
-      <c r="E47" t="s">
-        <v>158</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>159</v>
       </c>
-      <c r="G47" t="s">
-        <v>160</v>
-      </c>
       <c r="H47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -20739,7 +20728,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -20753,28 +20742,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
+        <v>157</v>
+      </c>
+      <c r="E48" t="s">
+        <v>157</v>
+      </c>
+      <c r="F48" t="s">
         <v>158</v>
       </c>
-      <c r="E48" t="s">
-        <v>158</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>159</v>
       </c>
-      <c r="G48" t="s">
-        <v>160</v>
-      </c>
       <c r="H48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -20882,7 +20871,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -20893,31 +20882,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D49" t="s">
+        <v>157</v>
+      </c>
+      <c r="E49" t="s">
+        <v>157</v>
+      </c>
+      <c r="F49" t="s">
         <v>158</v>
       </c>
-      <c r="E49" t="s">
-        <v>158</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>159</v>
       </c>
-      <c r="G49" t="s">
-        <v>160</v>
-      </c>
       <c r="H49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -21025,7 +21014,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -21036,31 +21025,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D50" t="s">
+        <v>157</v>
+      </c>
+      <c r="E50" t="s">
+        <v>157</v>
+      </c>
+      <c r="F50" t="s">
         <v>158</v>
       </c>
-      <c r="E50" t="s">
-        <v>158</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>159</v>
       </c>
-      <c r="G50" t="s">
-        <v>160</v>
-      </c>
       <c r="H50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -21168,7 +21157,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -21182,28 +21171,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
+        <v>157</v>
+      </c>
+      <c r="E51" t="s">
+        <v>157</v>
+      </c>
+      <c r="F51" t="s">
         <v>158</v>
       </c>
-      <c r="E51" t="s">
-        <v>158</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>159</v>
       </c>
-      <c r="G51" t="s">
-        <v>160</v>
-      </c>
       <c r="H51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -21311,7 +21300,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -21322,31 +21311,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D52" t="s">
+        <v>157</v>
+      </c>
+      <c r="E52" t="s">
+        <v>157</v>
+      </c>
+      <c r="F52" t="s">
         <v>158</v>
       </c>
-      <c r="E52" t="s">
-        <v>158</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>159</v>
       </c>
-      <c r="G52" t="s">
-        <v>160</v>
-      </c>
       <c r="H52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -21454,7 +21443,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -21465,31 +21454,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D53" t="s">
+        <v>157</v>
+      </c>
+      <c r="E53" t="s">
+        <v>157</v>
+      </c>
+      <c r="F53" t="s">
         <v>158</v>
       </c>
-      <c r="E53" t="s">
-        <v>158</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>159</v>
       </c>
-      <c r="G53" t="s">
-        <v>160</v>
-      </c>
       <c r="H53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -21597,7 +21586,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -21608,31 +21597,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D54" t="s">
+        <v>157</v>
+      </c>
+      <c r="E54" t="s">
+        <v>157</v>
+      </c>
+      <c r="F54" t="s">
         <v>158</v>
       </c>
-      <c r="E54" t="s">
-        <v>158</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>159</v>
       </c>
-      <c r="G54" t="s">
-        <v>160</v>
-      </c>
       <c r="H54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -21740,7 +21729,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -21751,31 +21740,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D55" t="s">
+        <v>157</v>
+      </c>
+      <c r="E55" t="s">
+        <v>157</v>
+      </c>
+      <c r="F55" t="s">
         <v>158</v>
       </c>
-      <c r="E55" t="s">
-        <v>158</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>159</v>
       </c>
-      <c r="G55" t="s">
-        <v>160</v>
-      </c>
       <c r="H55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -21883,7 +21872,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" updateLinks="never"/>
   <bookViews>
-    <workbookView windowHeight="7070" activeTab="1"/>
+    <workbookView windowWidth="13920" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TechSelection" sheetId="21" r:id="rId1"/>
@@ -36,8 +36,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>xli9</author>
+  </authors>
+  <commentList>
+    <comment ref="D99" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+Total refurbishment cost ~5times of direct recycling costs [https://www.nature.com/articles/s41467-024-52030-0]</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="196">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -432,9 +464,6 @@
     <t>5. what does that mean list every country??</t>
   </si>
   <si>
-    <t>~FI_T</t>
-  </si>
-  <si>
     <t>Limtype</t>
   </si>
   <si>
@@ -487,6 +516,54 @@
   </si>
   <si>
     <t>ktonne</t>
+  </si>
+  <si>
+    <t>*According to BloomBerg that ~2.5times more demand in 2024 vs. 2017 [means that 2.5 times higher demand every seven years] [https://about.bnef.com/blog/lithium-ion-battery-pack-prices-see-largest-drop-since-2017-falling-to-115-per-kilowatt-hour-bloombergnef/]; and a 18% learning rate also from Bloomberg</t>
+  </si>
+  <si>
+    <t>*0.313</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-LFP</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-LMO</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NCA</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NMC 111</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NMC532</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NMC 622</t>
+  </si>
+  <si>
+    <t>Tra_EV_Batt-NMC 811</t>
+  </si>
+  <si>
+    <t>Util_Rep_Batt-LFP</t>
+  </si>
+  <si>
+    <t>Util_Rep_Batt-LMO</t>
+  </si>
+  <si>
+    <t>Util_Rep_Batt-NCA</t>
+  </si>
+  <si>
+    <t>Util_Rep_Batt-NMC 111</t>
+  </si>
+  <si>
+    <t>Util_Rep_Batt-NMC532</t>
+  </si>
+  <si>
+    <t>Util_Rep_Batt-NMC 622</t>
+  </si>
+  <si>
+    <t>Util_Rep_Batt-NMC 811</t>
   </si>
   <si>
     <t>scenario</t>
@@ -593,7 +670,7 @@
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="0.0"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -624,13 +701,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.2"/>
       <color rgb="FF212529"/>
       <name val="Segoe UI"/>
@@ -647,6 +717,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -792,8 +869,19 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -809,6 +897,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1005,12 +1099,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1114,19 +1223,19 @@
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1135,7 +1244,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1147,122 +1256,122 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1276,16 +1385,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="51" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="51" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
@@ -1773,29 +1879,29 @@
   <dimension ref="A1:AA281"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="19" customWidth="1"/>
-    <col min="2" max="2" width="8.85454545454546" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.70909090909091" style="19" customWidth="1"/>
-    <col min="4" max="4" width="8.85454545454546" style="19" customWidth="1"/>
-    <col min="5" max="5" width="4.42727272727273" style="19" customWidth="1"/>
-    <col min="6" max="6" width="4.28181818181818" style="19" customWidth="1"/>
-    <col min="7" max="7" width="4.42727272727273" style="19" customWidth="1"/>
-    <col min="8" max="8" width="4.57272727272727" style="19" customWidth="1"/>
-    <col min="9" max="9" width="4" style="19" customWidth="1"/>
-    <col min="10" max="10" width="4.42727272727273" style="19" customWidth="1"/>
-    <col min="11" max="11" width="4.57272727272727" style="19" customWidth="1"/>
-    <col min="12" max="12" width="4.42727272727273" style="19" customWidth="1"/>
-    <col min="13" max="13" width="4" style="19" customWidth="1"/>
-    <col min="14" max="14" width="4.28181818181818" style="19" customWidth="1"/>
-    <col min="15" max="16" width="4.42727272727273" style="19" customWidth="1"/>
-    <col min="17" max="18" width="4.57272727272727" style="19" customWidth="1"/>
-    <col min="19" max="19" width="4.42727272727273" style="19" customWidth="1"/>
-    <col min="20" max="20" width="5" style="19" customWidth="1"/>
-    <col min="21" max="21" width="11.7090909090909" style="19" customWidth="1"/>
-    <col min="22" max="22" width="10.7090909090909" style="19" customWidth="1"/>
-    <col min="23" max="23" width="13.1363636363636" style="19" customWidth="1"/>
-    <col min="24" max="259" width="11.4272727272727" style="19" customWidth="1"/>
-    <col min="260" max="16384" width="9.13636363636364" style="19"/>
+    <col min="1" max="1" width="15" style="20" customWidth="1"/>
+    <col min="2" max="2" width="8.85454545454546" style="20" customWidth="1"/>
+    <col min="3" max="3" width="4.70909090909091" style="20" customWidth="1"/>
+    <col min="4" max="4" width="8.85454545454546" style="20" customWidth="1"/>
+    <col min="5" max="5" width="4.42727272727273" style="20" customWidth="1"/>
+    <col min="6" max="6" width="4.28181818181818" style="20" customWidth="1"/>
+    <col min="7" max="7" width="4.42727272727273" style="20" customWidth="1"/>
+    <col min="8" max="8" width="4.57272727272727" style="20" customWidth="1"/>
+    <col min="9" max="9" width="4" style="20" customWidth="1"/>
+    <col min="10" max="10" width="4.42727272727273" style="20" customWidth="1"/>
+    <col min="11" max="11" width="4.57272727272727" style="20" customWidth="1"/>
+    <col min="12" max="12" width="4.42727272727273" style="20" customWidth="1"/>
+    <col min="13" max="13" width="4" style="20" customWidth="1"/>
+    <col min="14" max="14" width="4.28181818181818" style="20" customWidth="1"/>
+    <col min="15" max="16" width="4.42727272727273" style="20" customWidth="1"/>
+    <col min="17" max="18" width="4.57272727272727" style="20" customWidth="1"/>
+    <col min="19" max="19" width="4.42727272727273" style="20" customWidth="1"/>
+    <col min="20" max="20" width="5" style="20" customWidth="1"/>
+    <col min="21" max="21" width="11.7090909090909" style="20" customWidth="1"/>
+    <col min="22" max="22" width="10.7090909090909" style="20" customWidth="1"/>
+    <col min="23" max="23" width="13.1363636363636" style="20" customWidth="1"/>
+    <col min="24" max="259" width="11.4272727272727" style="20" customWidth="1"/>
+    <col min="260" max="16384" width="9.13636363636364" style="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.5" spans="1:21">
@@ -2874,7 +2980,7 @@
       <c r="AA34" s="4"/>
     </row>
     <row r="35" ht="12.5" spans="1:27">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="20" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -2902,7 +3008,7 @@
       <c r="AA35" s="4"/>
     </row>
     <row r="36" ht="12.5" spans="1:27">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="20" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -2930,7 +3036,7 @@
       <c r="AA36" s="4"/>
     </row>
     <row r="37" ht="12.5" spans="1:27">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="20" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -2958,7 +3064,7 @@
       <c r="AA37" s="4"/>
     </row>
     <row r="38" ht="12.5" spans="1:27">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="20" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -2986,7 +3092,7 @@
       <c r="AA38" s="4"/>
     </row>
     <row r="39" ht="12.5" spans="1:27">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="20" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -8347,16 +8453,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:BL99"/>
+  <dimension ref="A2:BL105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
+    <col min="2" max="2" width="255.636363636364" customWidth="1"/>
     <col min="4" max="4" width="11.6363636363636" customWidth="1"/>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
     <col min="6" max="9" width="7.13636363636364" customWidth="1"/>
     <col min="10" max="10" width="10.6363636363636" customWidth="1"/>
     <col min="11" max="11" width="11.2818181818182" customWidth="1"/>
     <col min="12" max="12" width="6" customWidth="1"/>
-    <col min="13" max="33" width="7.13636363636364" customWidth="1"/>
+    <col min="13" max="24" width="7.13636363636364" customWidth="1"/>
+    <col min="25" max="25" width="9.54545454545454" customWidth="1"/>
+    <col min="26" max="33" width="7.13636363636364" customWidth="1"/>
     <col min="34" max="49" width="6" customWidth="1"/>
     <col min="50" max="50" width="12.2818181818182" customWidth="1"/>
     <col min="51" max="51" width="13.6363636363636" customWidth="1"/>
@@ -8642,7 +8751,7 @@
       <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="21" t="s">
         <v>92</v>
       </c>
       <c r="F14">
@@ -8701,7 +8810,7 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>92</v>
       </c>
       <c r="C18">
@@ -8710,7 +8819,7 @@
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="21" t="s">
         <v>100</v>
       </c>
       <c r="F18" t="s">
@@ -11498,7 +11607,7 @@
       <c r="D45">
         <v>2020</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="E45" s="22" t="s">
         <v>119</v>
       </c>
       <c r="F45" t="s">
@@ -11582,7 +11691,7 @@
       <c r="D55" t="s">
         <v>126</v>
       </c>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="21" t="s">
         <v>127</v>
       </c>
     </row>
@@ -11720,8 +11829,8 @@
     <row r="65" s="1" customFormat="1" spans="1:53">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
-      <c r="C65" s="2" t="s">
-        <v>131</v>
+      <c r="C65" t="s">
+        <v>73</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
@@ -11776,7 +11885,7 @@
     </row>
     <row r="66" s="2" customFormat="1" ht="16" spans="2:64">
       <c r="B66" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>56</v>
@@ -11860,7 +11969,7 @@
         <v>29</v>
       </c>
       <c r="AD66" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AE66" s="2" t="s">
         <v>31</v>
@@ -11890,43 +11999,43 @@
         <v>116</v>
       </c>
       <c r="AN66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AO66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AP66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AQ66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AR66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AS66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AU66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AV66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AW66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AX66" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="AO66" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AP66" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AQ66" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR66" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AS66" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AT66" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AU66" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AV66" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AW66" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AX66" s="11" t="s">
+      <c r="AY66" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AY66" s="2" t="s">
+      <c r="AZ66" s="17" t="s">
         <v>136</v>
-      </c>
-      <c r="AZ66" s="16" t="s">
-        <v>137</v>
       </c>
       <c r="BE66" s="11"/>
       <c r="BF66" s="11"/>
@@ -11942,7 +12051,7 @@
         <v>68</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D67" s="2">
         <f t="shared" ref="D67:AK67" si="2">D77/1000</f>
@@ -12080,22 +12189,22 @@
         <v>0</v>
       </c>
       <c r="AL67" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="AN67" s="16"/>
+      <c r="AX67" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AN67" s="15"/>
-      <c r="AX67" s="1" t="s">
+      <c r="AY67" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="AY67" s="1" t="s">
+      <c r="AZ67" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="AZ67" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="BD67" s="17"/>
+      <c r="BD67" s="18"/>
       <c r="BE67" s="11"/>
       <c r="BF67" s="11"/>
-      <c r="BG67" s="18"/>
+      <c r="BG67" s="19"/>
       <c r="BH67" s="11"/>
       <c r="BI67" s="11"/>
       <c r="BJ67" s="11"/>
@@ -12241,15 +12350,15 @@
         <v>0</v>
       </c>
       <c r="AL68" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AN68" s="15"/>
+        <v>138</v>
+      </c>
+      <c r="AN68" s="16"/>
       <c r="AX68" s="1"/>
       <c r="AY68" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="AZ68" s="16" t="s">
         <v>142</v>
+      </c>
+      <c r="AZ68" s="17" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" ht="16" spans="3:52">
@@ -12391,15 +12500,15 @@
         <v>0</v>
       </c>
       <c r="AL69" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AN69" s="15"/>
+        <v>138</v>
+      </c>
+      <c r="AN69" s="16"/>
       <c r="AX69" s="1"/>
       <c r="AY69" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AZ69" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="AZ69" s="17" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" ht="16" spans="3:52">
@@ -12541,15 +12650,15 @@
         <v>140000</v>
       </c>
       <c r="AL70" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AN70" s="15"/>
+        <v>138</v>
+      </c>
+      <c r="AN70" s="16"/>
       <c r="AX70" s="1"/>
       <c r="AY70" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="AZ70" s="16" t="s">
-        <v>142</v>
+        <v>144</v>
+      </c>
+      <c r="AZ70" s="17" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" ht="16" spans="3:52">
@@ -12691,15 +12800,15 @@
         <v>0</v>
       </c>
       <c r="AL71" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AN71" s="15"/>
+        <v>138</v>
+      </c>
+      <c r="AN71" s="16"/>
       <c r="AX71" s="1"/>
       <c r="AY71" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AZ71" s="16" t="s">
-        <v>142</v>
+        <v>145</v>
+      </c>
+      <c r="AZ71" s="17" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" ht="16" spans="3:52">
@@ -12841,15 +12950,15 @@
         <v>0</v>
       </c>
       <c r="AL72" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AN72" s="15"/>
+        <v>138</v>
+      </c>
+      <c r="AN72" s="16"/>
       <c r="AX72" s="1"/>
       <c r="AY72" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AZ72" s="16" t="s">
-        <v>142</v>
+        <v>146</v>
+      </c>
+      <c r="AZ72" s="17" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="16" spans="2:52">
@@ -12992,10 +13101,10 @@
         <v>0</v>
       </c>
       <c r="AL73" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AM73" s="2"/>
-      <c r="AN73" s="15"/>
+      <c r="AN73" s="16"/>
       <c r="AO73" s="2"/>
       <c r="AP73" s="2"/>
       <c r="AQ73" s="2"/>
@@ -13006,16 +13115,16 @@
       <c r="AV73" s="2"/>
       <c r="AW73" s="2"/>
       <c r="AY73" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AZ73" s="16" t="s">
-        <v>142</v>
+        <v>147</v>
+      </c>
+      <c r="AZ73" s="17" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
@@ -13668,7 +13777,9 @@
       <c r="Z87" s="8"/>
     </row>
     <row r="88" spans="2:26">
-      <c r="B88" s="8"/>
+      <c r="B88" s="8" t="s">
+        <v>149</v>
+      </c>
       <c r="C88" s="8"/>
       <c r="D88" s="8"/>
       <c r="E88" s="8"/>
@@ -13722,10 +13833,12 @@
       <c r="Z89" s="8"/>
     </row>
     <row r="90" spans="2:26">
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
+      <c r="B90" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C90" s="13"/>
+      <c r="D90" s="13"/>
+      <c r="E90"/>
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
@@ -13748,11 +13861,17 @@
       <c r="Y90" s="8"/>
       <c r="Z90" s="8"/>
     </row>
-    <row r="91" ht="14.5" spans="2:26">
-      <c r="B91" s="8"/>
-      <c r="C91" s="9"/>
-      <c r="D91" s="13"/>
-      <c r="E91" s="9"/>
+    <row r="91" spans="2:26">
+      <c r="B91" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C91" s="13">
+        <v>2050</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E91"/>
       <c r="F91" s="9"/>
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
@@ -13775,11 +13894,17 @@
       <c r="Y91" s="8"/>
       <c r="Z91" s="8"/>
     </row>
-    <row r="92" ht="14.5" spans="2:26">
-      <c r="B92" s="8"/>
-      <c r="C92" s="9"/>
-      <c r="D92" s="14"/>
-      <c r="E92" s="9"/>
+    <row r="92" spans="2:26">
+      <c r="B92" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D92" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E92"/>
       <c r="F92" s="9"/>
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
@@ -13802,10 +13927,17 @@
       <c r="Y92" s="8"/>
       <c r="Z92" s="8"/>
     </row>
-    <row r="93" ht="14.5" spans="2:26">
-      <c r="B93" s="8"/>
-      <c r="C93" s="9"/>
-      <c r="D93" s="14"/>
+    <row r="93" spans="2:26">
+      <c r="B93" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C93" s="15" t="str">
+        <f>C92</f>
+        <v>*0.313</v>
+      </c>
+      <c r="D93" s="14" t="s">
+        <v>152</v>
+      </c>
       <c r="E93" s="9"/>
       <c r="F93" s="9"/>
       <c r="G93" s="9"/>
@@ -13829,10 +13961,17 @@
       <c r="Y93" s="8"/>
       <c r="Z93" s="8"/>
     </row>
-    <row r="94" ht="14.5" spans="2:26">
-      <c r="B94" s="8"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="14"/>
+    <row r="94" spans="2:26">
+      <c r="B94" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C94" s="15" t="str">
+        <f t="shared" ref="C94:C105" si="9">C93</f>
+        <v>*0.313</v>
+      </c>
+      <c r="D94" s="14" t="s">
+        <v>153</v>
+      </c>
       <c r="E94" s="9"/>
       <c r="F94" s="9"/>
       <c r="G94" s="9"/>
@@ -13856,10 +13995,17 @@
       <c r="Y94" s="8"/>
       <c r="Z94" s="8"/>
     </row>
-    <row r="95" ht="14.5" spans="2:26">
-      <c r="B95" s="8"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="14"/>
+    <row r="95" spans="2:26">
+      <c r="B95" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C95" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v>*0.313</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="E95" s="9"/>
       <c r="F95" s="9"/>
       <c r="G95" s="9"/>
@@ -13883,10 +14029,17 @@
       <c r="Y95" s="8"/>
       <c r="Z95" s="8"/>
     </row>
-    <row r="96" ht="14.5" spans="2:26">
-      <c r="B96" s="8"/>
-      <c r="C96" s="9"/>
-      <c r="D96" s="14"/>
+    <row r="96" spans="2:26">
+      <c r="B96" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C96" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v>*0.313</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>155</v>
+      </c>
       <c r="E96" s="9"/>
       <c r="F96" s="9"/>
       <c r="G96" s="9"/>
@@ -13910,10 +14063,17 @@
       <c r="Y96" s="8"/>
       <c r="Z96" s="8"/>
     </row>
-    <row r="97" ht="14.5" spans="2:26">
-      <c r="B97" s="8"/>
-      <c r="C97" s="9"/>
-      <c r="D97" s="14"/>
+    <row r="97" spans="2:26">
+      <c r="B97" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C97" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v>*0.313</v>
+      </c>
+      <c r="D97" s="14" t="s">
+        <v>156</v>
+      </c>
       <c r="E97" s="9"/>
       <c r="F97" s="9"/>
       <c r="G97" s="9"/>
@@ -13937,10 +14097,17 @@
       <c r="Y97" s="8"/>
       <c r="Z97" s="8"/>
     </row>
-    <row r="98" ht="14.5" spans="2:26">
-      <c r="B98" s="8"/>
-      <c r="C98" s="9"/>
-      <c r="D98" s="14"/>
+    <row r="98" spans="2:26">
+      <c r="B98" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C98" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v>*0.313</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>157</v>
+      </c>
       <c r="E98" s="9"/>
       <c r="F98" s="9"/>
       <c r="G98" s="9"/>
@@ -13965,9 +14132,16 @@
       <c r="Z98" s="8"/>
     </row>
     <row r="99" spans="2:26">
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
+      <c r="B99" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C99" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v>*0.313</v>
+      </c>
+      <c r="D99" s="15" t="s">
+        <v>158</v>
+      </c>
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
@@ -13991,12 +14165,85 @@
       <c r="Y99" s="8"/>
       <c r="Z99" s="8"/>
     </row>
+    <row r="100" spans="2:4">
+      <c r="B100" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C100" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v>*0.313</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C101" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v>*0.313</v>
+      </c>
+      <c r="D101" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="B102" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C102" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v>*0.313</v>
+      </c>
+      <c r="D102" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C103" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v>*0.313</v>
+      </c>
+      <c r="D103" s="15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="B104" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C104" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v>*0.313</v>
+      </c>
+      <c r="D104" s="15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="B105" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C105" s="15" t="str">
+        <f t="shared" si="9"/>
+        <v>*0.313</v>
+      </c>
+      <c r="D105" s="15" t="s">
+        <v>164</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="AZ33:BA38">
     <sortCondition ref="AZ33:AZ38"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -14012,7 +14259,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -14024,25 +14271,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="F1" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="I1" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="J1" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="K1" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -14164,28 +14411,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -14293,7 +14540,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -14304,31 +14551,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G3" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H3" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I3" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J3" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K3" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -14436,7 +14683,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -14447,31 +14694,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G4" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H4" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I4" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J4" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K4" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -14579,7 +14826,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -14593,28 +14840,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G5" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H5" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I5" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J5" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K5" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -14722,7 +14969,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -14733,31 +14980,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G6" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H6" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I6" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J6" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K6" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -14865,7 +15112,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -14879,28 +15126,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G7" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H7" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I7" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J7" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K7" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -15008,7 +15255,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -15019,31 +15266,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G8" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H8" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I8" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J8" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K8" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -15151,7 +15398,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -15162,31 +15409,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G9" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H9" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I9" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J9" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K9" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -15294,7 +15541,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -15305,31 +15552,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="D10" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G10" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H10" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I10" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J10" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K10" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -15437,7 +15684,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -15448,31 +15695,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G11" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H11" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I11" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J11" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K11" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -15580,7 +15827,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -15591,31 +15838,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G12" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H12" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I12" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J12" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K12" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -15723,7 +15970,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -15734,31 +15981,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G13" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H13" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I13" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J13" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -15866,7 +16113,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -15877,31 +16124,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G14" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H14" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I14" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J14" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K14" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -16009,7 +16256,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -16020,31 +16267,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G15" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H15" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I15" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J15" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K15" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -16152,7 +16399,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -16163,31 +16410,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G16" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H16" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I16" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J16" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K16" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -16295,7 +16542,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -16309,28 +16556,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G17" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H17" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I17" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J17" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K17" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -16438,7 +16685,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -16449,31 +16696,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G18" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H18" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I18" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J18" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K18" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -16581,7 +16828,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -16592,31 +16839,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G19" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H19" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I19" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J19" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K19" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -16724,7 +16971,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -16735,31 +16982,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G20" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H20" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I20" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J20" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K20" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -16867,7 +17114,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -16881,28 +17128,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G21" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H21" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I21" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J21" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K21" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -17010,7 +17257,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -17021,31 +17268,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="D22" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G22" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H22" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I22" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J22" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K22" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -17153,7 +17400,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -17164,31 +17411,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G23" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H23" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I23" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J23" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K23" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -17296,7 +17543,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -17310,28 +17557,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G24" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H24" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I24" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J24" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K24" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -17439,7 +17686,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -17450,31 +17697,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G25" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H25" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I25" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J25" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K25" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -17582,7 +17829,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -17593,31 +17840,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G26" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H26" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I26" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J26" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K26" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -17725,7 +17972,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -17736,31 +17983,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G27" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H27" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I27" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J27" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -17868,7 +18115,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -17879,31 +18126,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="D28" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G28" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I28" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J28" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K28" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -18011,7 +18258,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -18025,28 +18272,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E29" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F29" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G29" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H29" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I29" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J29" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K29" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -18154,7 +18401,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -18165,31 +18412,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D30" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E30" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F30" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G30" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H30" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I30" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J30" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K30" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -18297,7 +18544,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -18308,31 +18555,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D31" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E31" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F31" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G31" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H31" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I31" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J31" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K31" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -18440,7 +18687,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -18454,28 +18701,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E32" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F32" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G32" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H32" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I32" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J32" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K32" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -18583,7 +18830,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -18594,31 +18841,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="D33" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E33" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F33" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G33" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H33" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I33" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J33" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K33" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -18726,7 +18973,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -18740,28 +18987,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E34" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F34" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G34" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H34" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I34" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J34" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K34" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -18869,7 +19116,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -18880,31 +19127,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E35" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F35" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G35" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H35" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I35" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J35" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K35" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -19012,7 +19259,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -19023,31 +19270,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="D36" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E36" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F36" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G36" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H36" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I36" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J36" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K36" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -19155,7 +19402,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -19166,31 +19413,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E37" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F37" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G37" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H37" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I37" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J37" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K37" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -19298,7 +19545,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -19309,31 +19556,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E38" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F38" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G38" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H38" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I38" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J38" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K38" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -19441,7 +19688,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -19452,31 +19699,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="D39" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E39" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F39" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G39" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H39" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I39" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J39" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K39" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -19584,7 +19831,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -19595,31 +19842,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="D40" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E40" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F40" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G40" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H40" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I40" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J40" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K40" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -19727,7 +19974,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -19738,31 +19985,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="D41" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E41" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F41" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G41" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H41" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I41" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J41" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K41" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -19870,7 +20117,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -19881,31 +20128,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="D42" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E42" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F42" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G42" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H42" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I42" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J42" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K42" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -20013,7 +20260,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -20024,31 +20271,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D43" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E43" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F43" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G43" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H43" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I43" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J43" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K43" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -20156,7 +20403,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -20170,28 +20417,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E44" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F44" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G44" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H44" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I44" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J44" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K44" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -20299,7 +20546,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -20310,31 +20557,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="D45" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E45" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F45" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G45" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H45" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I45" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J45" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K45" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -20442,7 +20689,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -20453,31 +20700,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
+        <v>188</v>
+      </c>
+      <c r="D46" t="s">
+        <v>172</v>
+      </c>
+      <c r="E46" t="s">
+        <v>172</v>
+      </c>
+      <c r="F46" t="s">
         <v>173</v>
       </c>
-      <c r="D46" t="s">
-        <v>157</v>
-      </c>
-      <c r="E46" t="s">
-        <v>157</v>
-      </c>
-      <c r="F46" t="s">
-        <v>158</v>
-      </c>
       <c r="G46" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H46" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I46" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J46" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K46" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -20585,7 +20832,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -20596,31 +20843,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" t="s">
+        <v>172</v>
+      </c>
+      <c r="E47" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" t="s">
+        <v>173</v>
+      </c>
+      <c r="G47" t="s">
         <v>174</v>
       </c>
-      <c r="D47" t="s">
-        <v>157</v>
-      </c>
-      <c r="E47" t="s">
-        <v>157</v>
-      </c>
-      <c r="F47" t="s">
-        <v>158</v>
-      </c>
-      <c r="G47" t="s">
-        <v>159</v>
-      </c>
       <c r="H47" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I47" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J47" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K47" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -20728,7 +20975,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -20742,28 +20989,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E48" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F48" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G48" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H48" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I48" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J48" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K48" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -20871,7 +21118,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -20882,31 +21129,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="D49" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E49" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F49" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G49" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H49" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I49" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J49" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K49" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -21014,7 +21261,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -21025,31 +21272,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="D50" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E50" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F50" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G50" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H50" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I50" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J50" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K50" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -21157,7 +21404,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -21171,28 +21418,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E51" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F51" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G51" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H51" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I51" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J51" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K51" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -21300,7 +21547,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -21311,31 +21558,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="D52" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E52" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F52" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G52" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H52" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I52" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J52" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K52" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -21443,7 +21690,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -21454,31 +21701,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D53" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E53" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F53" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G53" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H53" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I53" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J53" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K53" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -21586,7 +21833,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -21597,31 +21844,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D54" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E54" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F54" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G54" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H54" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I54" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J54" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K54" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -21729,7 +21976,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -21740,31 +21987,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="D55" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E55" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F55" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G55" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="H55" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I55" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="J55" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="K55" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -21872,7 +22119,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" updateLinks="never"/>
   <bookViews>
-    <workbookView windowWidth="13920" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="18350" windowHeight="8710" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TechSelection" sheetId="21" r:id="rId1"/>
@@ -870,12 +870,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -13834,11 +13834,10 @@
     </row>
     <row r="90" spans="2:26">
       <c r="B90" s="13" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="C90" s="13"/>
       <c r="D90" s="13"/>
-      <c r="E90"/>
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
@@ -13871,7 +13870,6 @@
       <c r="D91" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="E91"/>
       <c r="F91" s="9"/>
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
@@ -13904,7 +13902,6 @@
       <c r="D92" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="E92"/>
       <c r="F92" s="9"/>
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="193">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -470,22 +470,13 @@
     <t>Saudi Arabia</t>
   </si>
   <si>
-    <t>\I:</t>
-  </si>
-  <si>
     <t>Pset_PN</t>
   </si>
   <si>
-    <t>C_out</t>
-  </si>
-  <si>
-    <t>PCG</t>
+    <t>pset_cg</t>
   </si>
   <si>
     <t>Flow_BND</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>MINBatMaterials</t>
@@ -881,7 +872,7 @@
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -902,13 +893,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1244,7 +1229,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1268,16 +1253,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1286,85 +1271,85 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1386,9 +1371,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="51" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -8456,7 +8441,8 @@
   <dimension ref="A2:BL105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
-    <col min="2" max="2" width="255.636363636364" customWidth="1"/>
+    <col min="2" max="2" width="21.3727272727273" customWidth="1"/>
+    <col min="3" max="3" width="12.7272727272727" customWidth="1"/>
     <col min="4" max="4" width="11.6363636363636" customWidth="1"/>
     <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
     <col min="6" max="9" width="7.13636363636364" customWidth="1"/>
@@ -8466,7 +8452,10 @@
     <col min="13" max="24" width="7.13636363636364" customWidth="1"/>
     <col min="25" max="25" width="9.54545454545454" customWidth="1"/>
     <col min="26" max="33" width="7.13636363636364" customWidth="1"/>
-    <col min="34" max="49" width="6" customWidth="1"/>
+    <col min="34" max="37" width="6" customWidth="1"/>
+    <col min="38" max="38" width="15.5454545454545" customWidth="1"/>
+    <col min="39" max="39" width="13.6363636363636" customWidth="1"/>
+    <col min="40" max="49" width="6" customWidth="1"/>
     <col min="50" max="50" width="12.2818181818182" customWidth="1"/>
     <col min="51" max="51" width="13.6363636363636" customWidth="1"/>
   </cols>
@@ -11883,7 +11872,7 @@
       <c r="AZ65" s="2"/>
       <c r="BA65" s="2"/>
     </row>
-    <row r="66" s="2" customFormat="1" ht="16" spans="2:64">
+    <row r="66" s="2" customFormat="1" ht="14.5" spans="2:64">
       <c r="B66" s="2" t="s">
         <v>131</v>
       </c>
@@ -11992,51 +11981,24 @@
       <c r="AK66" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AL66" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AM66" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AN66" s="2" t="s">
+      <c r="AL66" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="AO66" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AP66" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AQ66" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AR66" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AS66" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AT66" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AU66" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AV66" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AW66" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AX66" s="11" t="s">
+      <c r="AM66" t="s">
+        <v>58</v>
+      </c>
+      <c r="AN66" t="s">
         <v>134</v>
       </c>
-      <c r="AY66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AZ66" s="17" t="s">
-        <v>136</v>
-      </c>
+      <c r="AO66" s="2"/>
+      <c r="AP66" s="2"/>
+      <c r="AQ66" s="2"/>
+      <c r="AR66" s="2"/>
+      <c r="AS66" s="2"/>
+      <c r="AT66" s="2"/>
+      <c r="AU66" s="2"/>
+      <c r="AV66" s="2"/>
+      <c r="AW66" s="2"/>
       <c r="BE66" s="11"/>
       <c r="BF66" s="11"/>
       <c r="BG66" s="11"/>
@@ -12051,7 +12013,7 @@
         <v>68</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D67" s="2">
         <f t="shared" ref="D67:AK67" si="2">D77/1000</f>
@@ -12188,18 +12150,14 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AL67" s="2" t="s">
+      <c r="AL67" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM67" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AN67" s="17" t="s">
         <v>138</v>
-      </c>
-      <c r="AN67" s="16"/>
-      <c r="AX67" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="AY67" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="AZ67" s="17" t="s">
-        <v>141</v>
       </c>
       <c r="BD67" s="18"/>
       <c r="BE67" s="11"/>
@@ -12211,8 +12169,13 @@
       <c r="BK67" s="11"/>
       <c r="BL67" s="11"/>
     </row>
-    <row r="68" s="2" customFormat="1" ht="16" spans="3:52">
-      <c r="C68" s="11"/>
+    <row r="68" s="2" customFormat="1" ht="16" spans="2:40">
+      <c r="B68" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="D68" s="2">
         <f t="shared" ref="D68:AK68" si="3">D78/1000</f>
         <v>0</v>
@@ -12349,20 +12312,23 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AL68" s="2" t="s">
+      <c r="AL68" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM68" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AN68" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="AN68" s="16"/>
-      <c r="AX68" s="1"/>
-      <c r="AY68" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AZ68" s="17" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" ht="16" spans="3:52">
-      <c r="C69" s="11"/>
+    </row>
+    <row r="69" s="2" customFormat="1" ht="16" spans="2:40">
+      <c r="B69" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="D69" s="2">
         <f t="shared" ref="D69:AK69" si="4">D79/1000</f>
         <v>13</v>
@@ -12499,20 +12465,23 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AL69" s="2" t="s">
+      <c r="AL69" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM69" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AN69" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="AN69" s="16"/>
-      <c r="AX69" s="1"/>
-      <c r="AY69" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="AZ69" s="17" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" ht="16" spans="3:52">
-      <c r="C70" s="11"/>
+    </row>
+    <row r="70" s="2" customFormat="1" ht="16" spans="2:40">
+      <c r="B70" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="D70" s="2">
         <f t="shared" ref="D70:AK70" si="5">D80/1000</f>
         <v>0</v>
@@ -12649,20 +12618,23 @@
         <f t="shared" si="5"/>
         <v>140000</v>
       </c>
-      <c r="AL70" s="2" t="s">
+      <c r="AL70" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM70" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AN70" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="AN70" s="16"/>
-      <c r="AX70" s="1"/>
-      <c r="AY70" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AZ70" s="17" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" ht="16" spans="3:52">
-      <c r="C71" s="11"/>
+    </row>
+    <row r="71" s="2" customFormat="1" ht="16" spans="2:40">
+      <c r="B71" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="D71" s="2">
         <f t="shared" ref="D71:AK71" si="6">D81/1000</f>
         <v>0</v>
@@ -12799,20 +12771,23 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AL71" s="2" t="s">
+      <c r="AL71" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM71" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="AN71" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="AN71" s="16"/>
-      <c r="AX71" s="1"/>
-      <c r="AY71" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="AZ71" s="17" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" ht="16" spans="3:52">
-      <c r="C72" s="11"/>
+    </row>
+    <row r="72" s="2" customFormat="1" ht="16" spans="2:40">
+      <c r="B72" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="D72" s="2">
         <f t="shared" ref="D72:AK72" si="7">D82/1000</f>
         <v>0</v>
@@ -12949,21 +12924,23 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL72" s="2" t="s">
+      <c r="AL72" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM72" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AN72" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="AN72" s="16"/>
-      <c r="AX72" s="1"/>
-      <c r="AY72" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AZ72" s="17" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" ht="16" spans="2:52">
-      <c r="B73" s="2"/>
-      <c r="C73" s="11"/>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="16" spans="2:49">
+      <c r="B73" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="D73" s="2">
         <f t="shared" ref="D73:AK73" si="8">D83/1000</f>
         <v>0</v>
@@ -13100,11 +13077,15 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL73" s="2" t="s">
+      <c r="AL73" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM73" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AN73" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="AM73" s="2"/>
-      <c r="AN73" s="16"/>
       <c r="AO73" s="2"/>
       <c r="AP73" s="2"/>
       <c r="AQ73" s="2"/>
@@ -13114,17 +13095,11 @@
       <c r="AU73" s="2"/>
       <c r="AV73" s="2"/>
       <c r="AW73" s="2"/>
-      <c r="AY73" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AZ73" s="17" t="s">
-        <v>141</v>
-      </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
@@ -13778,7 +13753,7 @@
     </row>
     <row r="88" spans="2:26">
       <c r="B88" s="8" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="8"/>
@@ -13832,7 +13807,8 @@
       <c r="Y89" s="8"/>
       <c r="Z89" s="8"/>
     </row>
-    <row r="90" spans="2:26">
+    <row r="90" spans="1:26">
+      <c r="A90" s="13"/>
       <c r="B90" s="13" t="s">
         <v>108</v>
       </c>
@@ -13860,7 +13836,10 @@
       <c r="Y90" s="8"/>
       <c r="Z90" s="8"/>
     </row>
-    <row r="91" spans="2:26">
+    <row r="91" spans="1:26">
+      <c r="A91" s="14" t="s">
+        <v>131</v>
+      </c>
       <c r="B91" s="13" t="s">
         <v>56</v>
       </c>
@@ -13892,15 +13871,18 @@
       <c r="Y91" s="8"/>
       <c r="Z91" s="8"/>
     </row>
-    <row r="92" spans="2:26">
+    <row r="92" spans="1:26">
+      <c r="A92" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B92" s="13" t="s">
         <v>118</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D92" s="14" t="s">
-        <v>151</v>
+        <v>147</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>148</v>
       </c>
       <c r="F92" s="9"/>
       <c r="G92" s="9"/>
@@ -13924,16 +13906,19 @@
       <c r="Y92" s="8"/>
       <c r="Z92" s="8"/>
     </row>
-    <row r="93" spans="2:26">
+    <row r="93" spans="1:26">
+      <c r="A93" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B93" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C93" s="15" t="str">
+      <c r="C93" s="16" t="str">
         <f>C92</f>
         <v>*0.313</v>
       </c>
-      <c r="D93" s="14" t="s">
-        <v>152</v>
+      <c r="D93" s="15" t="s">
+        <v>149</v>
       </c>
       <c r="E93" s="9"/>
       <c r="F93" s="9"/>
@@ -13958,16 +13943,19 @@
       <c r="Y93" s="8"/>
       <c r="Z93" s="8"/>
     </row>
-    <row r="94" spans="2:26">
+    <row r="94" spans="1:26">
+      <c r="A94" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B94" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C94" s="15" t="str">
+      <c r="C94" s="16" t="str">
         <f t="shared" ref="C94:C105" si="9">C93</f>
         <v>*0.313</v>
       </c>
-      <c r="D94" s="14" t="s">
-        <v>153</v>
+      <c r="D94" s="15" t="s">
+        <v>150</v>
       </c>
       <c r="E94" s="9"/>
       <c r="F94" s="9"/>
@@ -13992,16 +13980,19 @@
       <c r="Y94" s="8"/>
       <c r="Z94" s="8"/>
     </row>
-    <row r="95" spans="2:26">
+    <row r="95" spans="1:26">
+      <c r="A95" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B95" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C95" s="15" t="str">
+      <c r="C95" s="16" t="str">
         <f t="shared" si="9"/>
         <v>*0.313</v>
       </c>
-      <c r="D95" s="14" t="s">
-        <v>154</v>
+      <c r="D95" s="15" t="s">
+        <v>151</v>
       </c>
       <c r="E95" s="9"/>
       <c r="F95" s="9"/>
@@ -14026,16 +14017,19 @@
       <c r="Y95" s="8"/>
       <c r="Z95" s="8"/>
     </row>
-    <row r="96" spans="2:26">
+    <row r="96" spans="1:26">
+      <c r="A96" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B96" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C96" s="15" t="str">
+      <c r="C96" s="16" t="str">
         <f t="shared" si="9"/>
         <v>*0.313</v>
       </c>
-      <c r="D96" s="14" t="s">
-        <v>155</v>
+      <c r="D96" s="15" t="s">
+        <v>152</v>
       </c>
       <c r="E96" s="9"/>
       <c r="F96" s="9"/>
@@ -14060,16 +14054,19 @@
       <c r="Y96" s="8"/>
       <c r="Z96" s="8"/>
     </row>
-    <row r="97" spans="2:26">
+    <row r="97" spans="1:26">
+      <c r="A97" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B97" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C97" s="15" t="str">
+      <c r="C97" s="16" t="str">
         <f t="shared" si="9"/>
         <v>*0.313</v>
       </c>
-      <c r="D97" s="14" t="s">
-        <v>156</v>
+      <c r="D97" s="15" t="s">
+        <v>153</v>
       </c>
       <c r="E97" s="9"/>
       <c r="F97" s="9"/>
@@ -14094,16 +14091,19 @@
       <c r="Y97" s="8"/>
       <c r="Z97" s="8"/>
     </row>
-    <row r="98" spans="2:26">
+    <row r="98" spans="1:26">
+      <c r="A98" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B98" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C98" s="15" t="str">
+      <c r="C98" s="16" t="str">
         <f t="shared" si="9"/>
         <v>*0.313</v>
       </c>
-      <c r="D98" s="14" t="s">
-        <v>157</v>
+      <c r="D98" s="15" t="s">
+        <v>154</v>
       </c>
       <c r="E98" s="9"/>
       <c r="F98" s="9"/>
@@ -14128,16 +14128,19 @@
       <c r="Y98" s="8"/>
       <c r="Z98" s="8"/>
     </row>
-    <row r="99" spans="2:26">
+    <row r="99" spans="1:26">
+      <c r="A99" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B99" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C99" s="15" t="str">
+      <c r="C99" s="16" t="str">
         <f t="shared" si="9"/>
         <v>*0.313</v>
       </c>
-      <c r="D99" s="15" t="s">
-        <v>158</v>
+      <c r="D99" s="16" t="s">
+        <v>155</v>
       </c>
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
@@ -14162,76 +14165,94 @@
       <c r="Y99" s="8"/>
       <c r="Z99" s="8"/>
     </row>
-    <row r="100" spans="2:4">
+    <row r="100" spans="1:4">
+      <c r="A100" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B100" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C100" s="15" t="str">
+      <c r="C100" s="16" t="str">
         <f t="shared" si="9"/>
         <v>*0.313</v>
       </c>
-      <c r="D100" s="15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4">
+      <c r="D100" s="16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B101" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C101" s="15" t="str">
+      <c r="C101" s="16" t="str">
         <f t="shared" si="9"/>
         <v>*0.313</v>
       </c>
-      <c r="D101" s="15" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4">
+      <c r="D101" s="16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B102" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C102" s="15" t="str">
+      <c r="C102" s="16" t="str">
         <f t="shared" si="9"/>
         <v>*0.313</v>
       </c>
-      <c r="D102" s="15" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4">
+      <c r="D102" s="16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B103" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C103" s="15" t="str">
+      <c r="C103" s="16" t="str">
         <f t="shared" si="9"/>
         <v>*0.313</v>
       </c>
-      <c r="D103" s="15" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="104" spans="2:4">
+      <c r="D103" s="16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B104" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C104" s="15" t="str">
+      <c r="C104" s="16" t="str">
         <f t="shared" si="9"/>
         <v>*0.313</v>
       </c>
-      <c r="D104" s="15" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="105" spans="2:4">
+      <c r="D104" s="16" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B105" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C105" s="15" t="str">
+      <c r="C105" s="16" t="str">
         <f t="shared" si="9"/>
         <v>*0.313</v>
       </c>
-      <c r="D105" s="15" t="s">
-        <v>164</v>
+      <c r="D105" s="16" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -14256,7 +14277,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -14268,25 +14289,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I1" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K1" t="s">
         <v>168</v>
-      </c>
-      <c r="I1" t="s">
-        <v>169</v>
-      </c>
-      <c r="J1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K1" t="s">
-        <v>171</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -14408,28 +14429,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -14537,7 +14558,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -14548,31 +14569,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -14680,7 +14701,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -14691,31 +14712,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -14823,7 +14844,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -14837,28 +14858,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -14966,7 +14987,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -14977,31 +14998,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -15109,7 +15130,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -15123,28 +15144,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -15252,7 +15273,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -15263,31 +15284,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -15395,7 +15416,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -15406,31 +15427,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -15538,7 +15559,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -15549,31 +15570,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G10" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -15681,7 +15702,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -15692,31 +15713,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -15824,7 +15845,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -15835,31 +15856,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G12" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -15967,7 +15988,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -15978,31 +15999,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -16110,7 +16131,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -16121,31 +16142,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -16253,7 +16274,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -16264,31 +16285,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D15" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H15" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I15" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J15" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K15" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -16396,7 +16417,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -16407,31 +16428,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H16" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I16" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J16" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K16" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -16539,7 +16560,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -16553,28 +16574,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -16682,7 +16703,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -16693,31 +16714,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G18" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -16825,7 +16846,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -16836,31 +16857,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -16968,7 +16989,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -16979,31 +17000,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -17111,7 +17132,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -17125,28 +17146,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H21" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I21" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J21" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K21" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -17254,7 +17275,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -17265,31 +17286,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D22" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H22" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I22" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J22" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K22" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -17397,7 +17418,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -17408,31 +17429,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D23" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H23" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I23" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J23" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K23" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -17540,7 +17561,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -17554,28 +17575,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G24" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -17683,7 +17704,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -17694,31 +17715,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D25" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G25" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H25" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I25" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J25" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K25" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -17826,7 +17847,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -17837,31 +17858,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D26" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H26" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I26" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J26" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K26" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -17969,7 +17990,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -17980,31 +18001,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -18112,7 +18133,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -18123,31 +18144,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D28" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H28" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I28" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J28" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K28" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -18255,7 +18276,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -18269,28 +18290,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E29" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F29" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H29" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I29" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J29" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K29" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -18398,7 +18419,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -18409,31 +18430,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D30" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E30" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F30" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G30" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H30" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I30" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J30" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K30" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -18541,7 +18562,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -18552,31 +18573,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D31" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E31" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F31" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G31" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H31" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I31" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J31" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K31" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -18684,7 +18705,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -18698,28 +18719,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E32" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F32" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H32" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I32" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J32" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K32" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -18827,7 +18848,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -18838,31 +18859,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D33" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E33" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G33" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H33" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I33" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J33" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K33" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -18970,7 +18991,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -18984,28 +19005,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E34" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F34" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G34" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H34" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I34" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J34" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K34" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -19113,7 +19134,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -19124,31 +19145,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D35" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E35" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F35" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G35" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H35" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I35" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J35" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K35" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -19256,7 +19277,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -19267,31 +19288,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E36" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F36" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G36" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H36" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I36" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J36" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K36" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -19399,7 +19420,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -19410,31 +19431,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E37" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F37" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G37" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H37" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I37" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J37" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K37" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -19542,7 +19563,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -19553,31 +19574,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F38" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G38" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -19685,7 +19706,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -19696,31 +19717,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D39" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E39" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F39" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G39" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H39" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I39" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J39" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K39" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -19828,7 +19849,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -19839,31 +19860,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D40" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E40" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F40" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G40" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H40" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I40" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J40" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K40" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -19971,7 +19992,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -19982,31 +20003,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D41" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E41" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F41" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G41" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H41" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I41" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J41" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K41" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -20114,7 +20135,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -20125,31 +20146,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D42" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E42" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F42" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G42" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H42" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I42" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J42" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K42" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -20257,7 +20278,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -20268,31 +20289,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D43" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E43" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F43" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G43" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H43" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I43" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J43" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K43" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -20400,7 +20421,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -20414,28 +20435,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F44" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G44" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -20543,7 +20564,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -20554,31 +20575,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D45" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E45" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F45" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G45" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H45" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I45" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J45" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K45" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -20686,7 +20707,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -20697,31 +20718,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D46" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E46" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F46" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G46" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H46" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I46" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J46" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K46" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -20829,7 +20850,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -20840,31 +20861,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D47" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E47" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F47" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G47" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H47" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I47" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J47" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K47" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -20972,7 +20993,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -20986,28 +21007,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E48" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F48" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G48" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H48" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I48" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J48" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K48" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -21115,7 +21136,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -21126,31 +21147,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D49" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E49" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F49" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G49" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H49" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I49" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J49" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K49" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -21258,7 +21279,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -21269,31 +21290,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D50" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E50" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F50" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G50" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H50" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I50" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J50" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K50" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -21401,7 +21422,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -21415,28 +21436,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E51" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F51" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G51" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H51" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I51" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J51" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K51" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -21544,7 +21565,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -21555,31 +21576,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D52" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E52" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F52" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G52" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H52" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I52" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J52" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K52" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -21687,7 +21708,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -21698,31 +21719,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D53" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E53" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F53" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G53" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H53" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I53" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J53" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K53" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -21830,7 +21851,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -21841,31 +21862,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D54" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E54" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F54" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G54" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H54" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I54" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J54" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K54" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -21973,7 +21994,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -21984,31 +22005,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D55" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E55" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F55" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G55" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H55" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I55" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J55" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="K55" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -22116,7 +22137,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="193">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -476,7 +476,7 @@
     <t>pset_cg</t>
   </si>
   <si>
-    <t>Flow_BND</t>
+    <t>FLO_BND</t>
   </si>
   <si>
     <t>MINBatMaterials</t>
@@ -8443,8 +8443,7 @@
   <cols>
     <col min="2" max="2" width="21.3727272727273" customWidth="1"/>
     <col min="3" max="3" width="12.7272727272727" customWidth="1"/>
-    <col min="4" max="4" width="11.6363636363636" customWidth="1"/>
-    <col min="5" max="5" width="22.0909090909091" customWidth="1"/>
+    <col min="4" max="5" width="22.0909090909091" customWidth="1"/>
     <col min="6" max="9" width="7.13636363636364" customWidth="1"/>
     <col min="10" max="10" width="10.6363636363636" customWidth="1"/>
     <col min="11" max="11" width="11.2818181818182" customWidth="1"/>
@@ -11990,15 +11989,6 @@
       <c r="AN66" t="s">
         <v>134</v>
       </c>
-      <c r="AO66" s="2"/>
-      <c r="AP66" s="2"/>
-      <c r="AQ66" s="2"/>
-      <c r="AR66" s="2"/>
-      <c r="AS66" s="2"/>
-      <c r="AT66" s="2"/>
-      <c r="AU66" s="2"/>
-      <c r="AV66" s="2"/>
-      <c r="AW66" s="2"/>
       <c r="BE66" s="11"/>
       <c r="BF66" s="11"/>
       <c r="BG66" s="11"/>
@@ -13843,11 +13833,14 @@
       <c r="B91" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C91" s="13">
-        <v>2050</v>
+      <c r="C91" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="D91" s="13" t="s">
         <v>90</v>
+      </c>
+      <c r="E91" t="s">
+        <v>115</v>
       </c>
       <c r="F91" s="9"/>
       <c r="G91" s="9"/>
@@ -13884,6 +13877,9 @@
       <c r="D92" s="15" t="s">
         <v>148</v>
       </c>
+      <c r="E92">
+        <v>2050</v>
+      </c>
       <c r="F92" s="9"/>
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
@@ -13920,7 +13916,9 @@
       <c r="D93" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E93" s="9"/>
+      <c r="E93" s="9">
+        <v>2050</v>
+      </c>
       <c r="F93" s="9"/>
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
@@ -13957,7 +13955,9 @@
       <c r="D94" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="E94" s="9"/>
+      <c r="E94">
+        <v>2050</v>
+      </c>
       <c r="F94" s="9"/>
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
@@ -13994,7 +13994,9 @@
       <c r="D95" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="E95" s="9"/>
+      <c r="E95" s="9">
+        <v>2050</v>
+      </c>
       <c r="F95" s="9"/>
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
@@ -14031,7 +14033,9 @@
       <c r="D96" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="E96" s="9"/>
+      <c r="E96">
+        <v>2050</v>
+      </c>
       <c r="F96" s="9"/>
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
@@ -14068,7 +14072,9 @@
       <c r="D97" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="E97" s="9"/>
+      <c r="E97" s="9">
+        <v>2050</v>
+      </c>
       <c r="F97" s="9"/>
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
@@ -14105,7 +14111,9 @@
       <c r="D98" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="E98" s="9"/>
+      <c r="E98">
+        <v>2050</v>
+      </c>
       <c r="F98" s="9"/>
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
@@ -14142,7 +14150,9 @@
       <c r="D99" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="E99" s="8"/>
+      <c r="E99" s="9">
+        <v>2050</v>
+      </c>
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
@@ -14165,7 +14175,7 @@
       <c r="Y99" s="8"/>
       <c r="Z99" s="8"/>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:5">
       <c r="A100" s="13" t="s">
         <v>83</v>
       </c>
@@ -14179,8 +14189,11 @@
       <c r="D100" s="16" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="101" spans="1:4">
+      <c r="E100">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101" s="13" t="s">
         <v>83</v>
       </c>
@@ -14194,8 +14207,11 @@
       <c r="D101" s="16" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="102" spans="1:4">
+      <c r="E101" s="9">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102" s="13" t="s">
         <v>83</v>
       </c>
@@ -14209,8 +14225,11 @@
       <c r="D102" s="16" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
+      <c r="E102">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
       <c r="A103" s="13" t="s">
         <v>83</v>
       </c>
@@ -14224,8 +14243,11 @@
       <c r="D103" s="16" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="104" spans="1:4">
+      <c r="E103" s="9">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
       <c r="A104" s="13" t="s">
         <v>83</v>
       </c>
@@ -14239,8 +14261,11 @@
       <c r="D104" s="16" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
+      <c r="E104">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
       <c r="A105" s="13" t="s">
         <v>83</v>
       </c>
@@ -14253,6 +14278,9 @@
       </c>
       <c r="D105" s="16" t="s">
         <v>161</v>
+      </c>
+      <c r="E105" s="9">
+        <v>2050</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="174">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -464,16 +464,7 @@
     <t>5. what does that mean list every country??</t>
   </si>
   <si>
-    <t>Limtype</t>
-  </si>
-  <si>
     <t>Saudi Arabia</t>
-  </si>
-  <si>
-    <t>Pset_PN</t>
-  </si>
-  <si>
-    <t>pset_cg</t>
   </si>
   <si>
     <t>FLO_BND</t>
@@ -483,9 +474,6 @@
   </si>
   <si>
     <t>m_lithium</t>
-  </si>
-  <si>
-    <t>MINBatMaterials_MATO</t>
   </si>
   <si>
     <t>m_nickel</t>
@@ -510,51 +498,6 @@
   </si>
   <si>
     <t>*According to BloomBerg that ~2.5times more demand in 2024 vs. 2017 [means that 2.5 times higher demand every seven years] [https://about.bnef.com/blog/lithium-ion-battery-pack-prices-see-largest-drop-since-2017-falling-to-115-per-kilowatt-hour-bloombergnef/]; and a 18% learning rate also from Bloomberg</t>
-  </si>
-  <si>
-    <t>*0.313</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-LFP</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-LMO</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-NCA</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-NMC 111</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-NMC532</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-NMC 622</t>
-  </si>
-  <si>
-    <t>Tra_EV_Batt-NMC 811</t>
-  </si>
-  <si>
-    <t>Util_Rep_Batt-LFP</t>
-  </si>
-  <si>
-    <t>Util_Rep_Batt-LMO</t>
-  </si>
-  <si>
-    <t>Util_Rep_Batt-NCA</t>
-  </si>
-  <si>
-    <t>Util_Rep_Batt-NMC 111</t>
-  </si>
-  <si>
-    <t>Util_Rep_Batt-NMC532</t>
-  </si>
-  <si>
-    <t>Util_Rep_Batt-NMC 622</t>
-  </si>
-  <si>
-    <t>Util_Rep_Batt-NMC 811</t>
   </si>
   <si>
     <t>scenario</t>
@@ -661,7 +604,7 @@
     <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="0.0"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -689,12 +632,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.2"/>
-      <color rgb="FF212529"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -861,12 +798,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -1208,28 +1145,31 @@
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1238,125 +1178,122 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1374,9 +1311,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="51" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
@@ -1864,29 +1800,29 @@
   <dimension ref="A1:AA281"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="20" customWidth="1"/>
-    <col min="2" max="2" width="8.85454545454546" style="20" customWidth="1"/>
-    <col min="3" max="3" width="4.70909090909091" style="20" customWidth="1"/>
-    <col min="4" max="4" width="8.85454545454546" style="20" customWidth="1"/>
-    <col min="5" max="5" width="4.42727272727273" style="20" customWidth="1"/>
-    <col min="6" max="6" width="4.28181818181818" style="20" customWidth="1"/>
-    <col min="7" max="7" width="4.42727272727273" style="20" customWidth="1"/>
-    <col min="8" max="8" width="4.57272727272727" style="20" customWidth="1"/>
-    <col min="9" max="9" width="4" style="20" customWidth="1"/>
-    <col min="10" max="10" width="4.42727272727273" style="20" customWidth="1"/>
-    <col min="11" max="11" width="4.57272727272727" style="20" customWidth="1"/>
-    <col min="12" max="12" width="4.42727272727273" style="20" customWidth="1"/>
-    <col min="13" max="13" width="4" style="20" customWidth="1"/>
-    <col min="14" max="14" width="4.28181818181818" style="20" customWidth="1"/>
-    <col min="15" max="16" width="4.42727272727273" style="20" customWidth="1"/>
-    <col min="17" max="18" width="4.57272727272727" style="20" customWidth="1"/>
-    <col min="19" max="19" width="4.42727272727273" style="20" customWidth="1"/>
-    <col min="20" max="20" width="5" style="20" customWidth="1"/>
-    <col min="21" max="21" width="11.7090909090909" style="20" customWidth="1"/>
-    <col min="22" max="22" width="10.7090909090909" style="20" customWidth="1"/>
-    <col min="23" max="23" width="13.1363636363636" style="20" customWidth="1"/>
-    <col min="24" max="259" width="11.4272727272727" style="20" customWidth="1"/>
-    <col min="260" max="16384" width="9.13636363636364" style="20"/>
+    <col min="1" max="1" width="15" style="19" customWidth="1"/>
+    <col min="2" max="2" width="8.85454545454546" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.70909090909091" style="19" customWidth="1"/>
+    <col min="4" max="4" width="8.85454545454546" style="19" customWidth="1"/>
+    <col min="5" max="5" width="4.42727272727273" style="19" customWidth="1"/>
+    <col min="6" max="6" width="4.28181818181818" style="19" customWidth="1"/>
+    <col min="7" max="7" width="4.42727272727273" style="19" customWidth="1"/>
+    <col min="8" max="8" width="4.57272727272727" style="19" customWidth="1"/>
+    <col min="9" max="9" width="4" style="19" customWidth="1"/>
+    <col min="10" max="10" width="4.42727272727273" style="19" customWidth="1"/>
+    <col min="11" max="11" width="4.57272727272727" style="19" customWidth="1"/>
+    <col min="12" max="12" width="4.42727272727273" style="19" customWidth="1"/>
+    <col min="13" max="13" width="4" style="19" customWidth="1"/>
+    <col min="14" max="14" width="4.28181818181818" style="19" customWidth="1"/>
+    <col min="15" max="16" width="4.42727272727273" style="19" customWidth="1"/>
+    <col min="17" max="18" width="4.57272727272727" style="19" customWidth="1"/>
+    <col min="19" max="19" width="4.42727272727273" style="19" customWidth="1"/>
+    <col min="20" max="20" width="5" style="19" customWidth="1"/>
+    <col min="21" max="21" width="11.7090909090909" style="19" customWidth="1"/>
+    <col min="22" max="22" width="10.7090909090909" style="19" customWidth="1"/>
+    <col min="23" max="23" width="13.1363636363636" style="19" customWidth="1"/>
+    <col min="24" max="259" width="11.4272727272727" style="19" customWidth="1"/>
+    <col min="260" max="16384" width="9.13636363636364" style="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.5" spans="1:21">
@@ -2965,7 +2901,7 @@
       <c r="AA34" s="4"/>
     </row>
     <row r="35" ht="12.5" spans="1:27">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="19" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -2993,7 +2929,7 @@
       <c r="AA35" s="4"/>
     </row>
     <row r="36" ht="12.5" spans="1:27">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="19" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -3021,7 +2957,7 @@
       <c r="AA36" s="4"/>
     </row>
     <row r="37" ht="12.5" spans="1:27">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="19" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -3049,7 +2985,7 @@
       <c r="AA37" s="4"/>
     </row>
     <row r="38" ht="12.5" spans="1:27">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="19" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -3077,7 +3013,7 @@
       <c r="AA38" s="4"/>
     </row>
     <row r="39" ht="12.5" spans="1:27">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="19" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -8739,7 +8675,7 @@
       <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="20" t="s">
         <v>92</v>
       </c>
       <c r="F14">
@@ -8798,7 +8734,7 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
         <v>92</v>
       </c>
       <c r="C18">
@@ -8807,7 +8743,7 @@
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="20" t="s">
         <v>100</v>
       </c>
       <c r="F18" t="s">
@@ -11595,7 +11531,7 @@
       <c r="D45">
         <v>2020</v>
       </c>
-      <c r="E45" s="22" t="s">
+      <c r="E45" s="21" t="s">
         <v>119</v>
       </c>
       <c r="F45" t="s">
@@ -11679,7 +11615,7 @@
       <c r="D55" t="s">
         <v>126</v>
       </c>
-      <c r="E55" s="21" t="s">
+      <c r="E55" s="20" t="s">
         <v>127</v>
       </c>
     </row>
@@ -11871,10 +11807,7 @@
       <c r="AZ65" s="2"/>
       <c r="BA65" s="2"/>
     </row>
-    <row r="66" s="2" customFormat="1" ht="14.5" spans="2:64">
-      <c r="B66" s="2" t="s">
-        <v>131</v>
-      </c>
+    <row r="66" s="2" customFormat="1" ht="14.5" spans="3:64">
       <c r="C66" s="2" t="s">
         <v>56</v>
       </c>
@@ -11957,7 +11890,7 @@
         <v>29</v>
       </c>
       <c r="AD66" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AE66" s="2" t="s">
         <v>31</v>
@@ -11980,14 +11913,14 @@
       <c r="AK66" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AL66" s="11" t="s">
-        <v>133</v>
+      <c r="AL66" t="s">
+        <v>90</v>
       </c>
       <c r="AM66" t="s">
         <v>58</v>
       </c>
-      <c r="AN66" t="s">
-        <v>134</v>
+      <c r="AN66" s="2" t="s">
+        <v>60</v>
       </c>
       <c r="BE66" s="11"/>
       <c r="BF66" s="11"/>
@@ -11998,12 +11931,9 @@
       <c r="BK66" s="11"/>
       <c r="BL66" s="11"/>
     </row>
-    <row r="67" s="2" customFormat="1" ht="16" spans="2:64">
-      <c r="B67" s="2" t="s">
-        <v>68</v>
-      </c>
+    <row r="67" s="2" customFormat="1" ht="16" spans="3:64">
       <c r="C67" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D67" s="2">
         <f t="shared" ref="D67:AK67" si="2">D77/1000</f>
@@ -12141,30 +12071,27 @@
         <v>0</v>
       </c>
       <c r="AL67" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AM67" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AN67" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="BD67" s="18"/>
+        <v>134</v>
+      </c>
+      <c r="AN67" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="BD67" s="17"/>
       <c r="BE67" s="11"/>
       <c r="BF67" s="11"/>
-      <c r="BG67" s="19"/>
+      <c r="BG67" s="18"/>
       <c r="BH67" s="11"/>
       <c r="BI67" s="11"/>
       <c r="BJ67" s="11"/>
       <c r="BK67" s="11"/>
       <c r="BL67" s="11"/>
     </row>
-    <row r="68" s="2" customFormat="1" ht="16" spans="2:40">
-      <c r="B68" s="2" t="s">
-        <v>68</v>
-      </c>
+    <row r="68" s="2" customFormat="1" ht="14.5" spans="3:40">
       <c r="C68" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D68" s="2">
         <f t="shared" ref="D68:AK68" si="3">D78/1000</f>
@@ -12303,21 +12230,18 @@
         <v>0</v>
       </c>
       <c r="AL68" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="AN68" s="17" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" ht="16" spans="2:40">
-      <c r="B69" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN68" s="2" t="s">
         <v>68</v>
       </c>
+    </row>
+    <row r="69" s="2" customFormat="1" ht="14.5" spans="3:40">
       <c r="C69" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D69" s="2">
         <f t="shared" ref="D69:AK69" si="4">D79/1000</f>
@@ -12456,21 +12380,18 @@
         <v>0</v>
       </c>
       <c r="AL69" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AM69" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="AM69" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="AN69" s="17" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" ht="16" spans="2:40">
-      <c r="B70" s="2" t="s">
+      <c r="AN69" s="2" t="s">
         <v>68</v>
       </c>
+    </row>
+    <row r="70" s="2" customFormat="1" ht="14.5" spans="3:40">
       <c r="C70" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D70" s="2">
         <f t="shared" ref="D70:AK70" si="5">D80/1000</f>
@@ -12609,21 +12530,18 @@
         <v>140000</v>
       </c>
       <c r="AL70" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AM70" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="AN70" s="17" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" ht="16" spans="2:40">
-      <c r="B71" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AN70" s="2" t="s">
         <v>68</v>
       </c>
+    </row>
+    <row r="71" s="2" customFormat="1" ht="14.5" spans="3:40">
       <c r="C71" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D71" s="2">
         <f t="shared" ref="D71:AK71" si="6">D81/1000</f>
@@ -12762,21 +12680,18 @@
         <v>0</v>
       </c>
       <c r="AL71" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AN71" s="17" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="72" s="2" customFormat="1" ht="16" spans="2:40">
-      <c r="B72" s="2" t="s">
+      <c r="AN71" s="2" t="s">
         <v>68</v>
       </c>
+    </row>
+    <row r="72" s="2" customFormat="1" ht="14.5" spans="3:40">
       <c r="C72" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D72" s="2">
         <f t="shared" ref="D72:AK72" si="7">D82/1000</f>
@@ -12915,21 +12830,18 @@
         <v>0</v>
       </c>
       <c r="AL72" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="AN72" s="17" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" ht="16" spans="2:49">
-      <c r="B73" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AN72" s="2" t="s">
         <v>68</v>
       </c>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="14.5" spans="3:49">
       <c r="C73" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D73" s="2">
         <f t="shared" ref="D73:AK73" si="8">D83/1000</f>
@@ -13068,13 +12980,13 @@
         <v>0</v>
       </c>
       <c r="AL73" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AM73" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AN73" s="17" t="s">
-        <v>138</v>
+        <v>140</v>
+      </c>
+      <c r="AN73" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="AO73" s="2"/>
       <c r="AP73" s="2"/>
@@ -13089,7 +13001,7 @@
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
@@ -13743,7 +13655,7 @@
     </row>
     <row r="88" spans="2:26">
       <c r="B88" s="8" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="8"/>
@@ -13799,9 +13711,7 @@
     </row>
     <row r="90" spans="1:26">
       <c r="A90" s="13"/>
-      <c r="B90" s="13" t="s">
-        <v>108</v>
-      </c>
+      <c r="B90" s="13"/>
       <c r="C90" s="13"/>
       <c r="D90" s="13"/>
       <c r="F90" s="8"/>
@@ -13826,24 +13736,12 @@
       <c r="Y90" s="8"/>
       <c r="Z90" s="8"/>
     </row>
-    <row r="91" spans="1:26">
-      <c r="A91" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="B91" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C91" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E91" t="s">
-        <v>115</v>
-      </c>
-      <c r="F91" s="9"/>
-      <c r="G91" s="9"/>
+    <row r="91" spans="2:26">
+      <c r="B91" s="13"/>
+      <c r="C91" s="13"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="14"/>
+      <c r="F91"/>
       <c r="H91" s="9"/>
       <c r="I91" s="9"/>
       <c r="J91" s="9"/>
@@ -13864,24 +13762,12 @@
       <c r="Y91" s="8"/>
       <c r="Z91" s="8"/>
     </row>
-    <row r="92" spans="1:26">
-      <c r="A92" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B92" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="E92">
-        <v>2050</v>
-      </c>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
+    <row r="92" spans="2:26">
+      <c r="B92" s="13"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="15"/>
+      <c r="E92" s="13"/>
+      <c r="F92"/>
       <c r="H92" s="9"/>
       <c r="I92" s="9"/>
       <c r="J92" s="9"/>
@@ -13902,25 +13788,12 @@
       <c r="Y92" s="8"/>
       <c r="Z92" s="8"/>
     </row>
-    <row r="93" spans="1:26">
-      <c r="A93" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B93" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C93" s="16" t="str">
-        <f>C92</f>
-        <v>*0.313</v>
-      </c>
-      <c r="D93" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="E93" s="9">
-        <v>2050</v>
-      </c>
+    <row r="93" spans="2:26">
+      <c r="B93" s="13"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="15"/>
+      <c r="E93" s="13"/>
       <c r="F93" s="9"/>
-      <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="9"/>
       <c r="J93" s="9"/>
@@ -13941,25 +13814,12 @@
       <c r="Y93" s="8"/>
       <c r="Z93" s="8"/>
     </row>
-    <row r="94" spans="1:26">
-      <c r="A94" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B94" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C94" s="16" t="str">
-        <f t="shared" ref="C94:C105" si="9">C93</f>
-        <v>*0.313</v>
-      </c>
-      <c r="D94" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="E94">
-        <v>2050</v>
-      </c>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
+    <row r="94" spans="2:26">
+      <c r="B94" s="13"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="15"/>
+      <c r="E94" s="13"/>
+      <c r="F94"/>
       <c r="H94" s="9"/>
       <c r="I94" s="9"/>
       <c r="J94" s="9"/>
@@ -13980,25 +13840,12 @@
       <c r="Y94" s="8"/>
       <c r="Z94" s="8"/>
     </row>
-    <row r="95" spans="1:26">
-      <c r="A95" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B95" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C95" s="16" t="str">
-        <f t="shared" si="9"/>
-        <v>*0.313</v>
-      </c>
-      <c r="D95" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="E95" s="9">
-        <v>2050</v>
-      </c>
+    <row r="95" spans="2:26">
+      <c r="B95" s="13"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="15"/>
+      <c r="E95" s="13"/>
       <c r="F95" s="9"/>
-      <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="9"/>
       <c r="J95" s="9"/>
@@ -14019,25 +13866,12 @@
       <c r="Y95" s="8"/>
       <c r="Z95" s="8"/>
     </row>
-    <row r="96" spans="1:26">
-      <c r="A96" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B96" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C96" s="16" t="str">
-        <f t="shared" si="9"/>
-        <v>*0.313</v>
-      </c>
-      <c r="D96" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="E96">
-        <v>2050</v>
-      </c>
-      <c r="F96" s="9"/>
-      <c r="G96" s="9"/>
+    <row r="96" spans="2:26">
+      <c r="B96" s="13"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="15"/>
+      <c r="E96" s="13"/>
+      <c r="F96"/>
       <c r="H96" s="9"/>
       <c r="I96" s="9"/>
       <c r="J96" s="9"/>
@@ -14058,25 +13892,12 @@
       <c r="Y96" s="8"/>
       <c r="Z96" s="8"/>
     </row>
-    <row r="97" spans="1:26">
-      <c r="A97" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B97" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C97" s="16" t="str">
-        <f t="shared" si="9"/>
-        <v>*0.313</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="E97" s="9">
-        <v>2050</v>
-      </c>
+    <row r="97" spans="2:26">
+      <c r="B97" s="13"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="13"/>
       <c r="F97" s="9"/>
-      <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="9"/>
       <c r="J97" s="9"/>
@@ -14097,25 +13918,12 @@
       <c r="Y97" s="8"/>
       <c r="Z97" s="8"/>
     </row>
-    <row r="98" spans="1:26">
-      <c r="A98" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B98" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C98" s="16" t="str">
-        <f t="shared" si="9"/>
-        <v>*0.313</v>
-      </c>
-      <c r="D98" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="E98">
-        <v>2050</v>
-      </c>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
+    <row r="98" spans="2:26">
+      <c r="B98" s="13"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="15"/>
+      <c r="E98" s="13"/>
+      <c r="F98"/>
       <c r="H98" s="9"/>
       <c r="I98" s="9"/>
       <c r="J98" s="9"/>
@@ -14136,25 +13944,12 @@
       <c r="Y98" s="8"/>
       <c r="Z98" s="8"/>
     </row>
-    <row r="99" spans="1:26">
-      <c r="A99" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B99" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C99" s="16" t="str">
-        <f t="shared" si="9"/>
-        <v>*0.313</v>
-      </c>
-      <c r="D99" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="E99" s="9">
-        <v>2050</v>
-      </c>
-      <c r="F99" s="8"/>
-      <c r="G99" s="8"/>
+    <row r="99" spans="2:26">
+      <c r="B99" s="13"/>
+      <c r="C99" s="16"/>
+      <c r="D99" s="16"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="9"/>
       <c r="H99" s="8"/>
       <c r="I99" s="8"/>
       <c r="J99" s="8"/>
@@ -14175,113 +13970,44 @@
       <c r="Y99" s="8"/>
       <c r="Z99" s="8"/>
     </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B100" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C100" s="16" t="str">
-        <f t="shared" si="9"/>
-        <v>*0.313</v>
-      </c>
-      <c r="D100" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="E100">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
-      <c r="A101" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B101" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C101" s="16" t="str">
-        <f t="shared" si="9"/>
-        <v>*0.313</v>
-      </c>
-      <c r="D101" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="E101" s="9">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
-      <c r="A102" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B102" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C102" s="16" t="str">
-        <f t="shared" si="9"/>
-        <v>*0.313</v>
-      </c>
-      <c r="D102" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="E102">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
-      <c r="A103" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B103" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C103" s="16" t="str">
-        <f t="shared" si="9"/>
-        <v>*0.313</v>
-      </c>
-      <c r="D103" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="E103" s="9">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B104" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C104" s="16" t="str">
-        <f t="shared" si="9"/>
-        <v>*0.313</v>
-      </c>
-      <c r="D104" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="E104">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
-      <c r="A105" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B105" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C105" s="16" t="str">
-        <f t="shared" si="9"/>
-        <v>*0.313</v>
-      </c>
-      <c r="D105" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="E105" s="9">
-        <v>2050</v>
-      </c>
+    <row r="100" spans="2:5">
+      <c r="B100" s="13"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="16"/>
+      <c r="E100" s="13"/>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="13"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="13"/>
+      <c r="F101" s="9"/>
+    </row>
+    <row r="102" spans="2:5">
+      <c r="B102" s="13"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="13"/>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="13"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="16"/>
+      <c r="E103" s="13"/>
+      <c r="F103" s="9"/>
+    </row>
+    <row r="104" spans="2:5">
+      <c r="B104" s="13"/>
+      <c r="C104" s="16"/>
+      <c r="D104" s="16"/>
+      <c r="E104" s="13"/>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="13"/>
+      <c r="C105" s="16"/>
+      <c r="D105" s="16"/>
+      <c r="E105" s="13"/>
+      <c r="F105" s="9"/>
     </row>
   </sheetData>
   <sortState ref="AZ33:BA38">
@@ -14305,7 +14031,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -14317,25 +14043,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="F1" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="I1" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="J1" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="K1" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -14457,28 +14183,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G2" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -14586,7 +14312,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -14597,31 +14323,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="D3" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G3" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H3" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I3" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J3" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K3" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -14729,7 +14455,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -14740,31 +14466,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G4" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H4" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I4" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J4" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K4" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -14872,7 +14598,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -14886,28 +14612,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G5" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H5" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I5" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J5" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K5" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -15015,7 +14741,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -15026,31 +14752,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G6" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H6" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I6" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J6" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K6" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -15158,7 +14884,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -15172,28 +14898,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G7" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H7" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I7" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J7" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K7" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -15301,7 +15027,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -15312,31 +15038,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="D8" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G8" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H8" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I8" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J8" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K8" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -15444,7 +15170,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -15455,31 +15181,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="D9" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G9" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H9" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I9" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J9" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K9" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -15587,7 +15313,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -15598,31 +15324,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G10" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H10" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I10" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J10" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K10" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -15730,7 +15456,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -15741,31 +15467,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="D11" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G11" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H11" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I11" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J11" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K11" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -15873,7 +15599,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -15884,31 +15610,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G12" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H12" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I12" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J12" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K12" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -16016,7 +15742,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -16027,31 +15753,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="D13" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G13" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H13" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I13" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J13" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K13" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -16159,7 +15885,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -16170,31 +15896,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D14" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G14" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H14" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I14" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J14" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K14" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -16302,7 +16028,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -16313,31 +16039,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="D15" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G15" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H15" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I15" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J15" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K15" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -16445,7 +16171,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -16456,31 +16182,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="D16" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G16" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H16" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I16" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J16" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K16" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -16588,7 +16314,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -16602,28 +16328,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G17" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H17" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I17" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J17" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K17" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -16731,7 +16457,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -16742,31 +16468,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="D18" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G18" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H18" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I18" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J18" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K18" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -16874,7 +16600,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -16885,31 +16611,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D19" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G19" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H19" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I19" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J19" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K19" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -17017,7 +16743,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -17028,31 +16754,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="D20" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G20" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H20" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I20" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J20" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K20" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -17160,7 +16886,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -17174,28 +16900,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G21" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H21" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I21" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J21" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K21" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -17303,7 +17029,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -17314,31 +17040,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="D22" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G22" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H22" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I22" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J22" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K22" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -17446,7 +17172,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -17457,31 +17183,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="D23" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G23" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H23" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I23" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J23" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K23" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -17589,7 +17315,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -17603,28 +17329,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G24" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H24" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I24" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J24" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K24" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -17732,7 +17458,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -17743,31 +17469,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="D25" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G25" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H25" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I25" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J25" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K25" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -17875,7 +17601,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -17886,31 +17612,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G26" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H26" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I26" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J26" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K26" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -18018,7 +17744,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -18029,31 +17755,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="D27" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G27" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H27" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I27" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J27" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K27" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -18161,7 +17887,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -18172,31 +17898,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="D28" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G28" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H28" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I28" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J28" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K28" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -18304,7 +18030,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -18318,28 +18044,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E29" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F29" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G29" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H29" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I29" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J29" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K29" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -18447,7 +18173,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -18458,31 +18184,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="D30" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F30" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G30" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H30" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I30" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J30" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K30" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -18590,7 +18316,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -18601,31 +18327,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="D31" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E31" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F31" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G31" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H31" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I31" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J31" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K31" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -18733,7 +18459,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -18747,28 +18473,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E32" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F32" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G32" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H32" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I32" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J32" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K32" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -18876,7 +18602,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -18887,31 +18613,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E33" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F33" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G33" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H33" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I33" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J33" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K33" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -19019,7 +18745,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -19033,28 +18759,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E34" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F34" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G34" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H34" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I34" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J34" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K34" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -19162,7 +18888,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -19173,31 +18899,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="D35" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E35" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F35" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G35" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H35" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I35" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J35" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K35" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -19305,7 +19031,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -19316,31 +19042,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="D36" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E36" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F36" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G36" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H36" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I36" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J36" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K36" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -19448,7 +19174,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -19459,31 +19185,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="D37" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E37" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F37" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G37" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H37" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I37" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J37" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K37" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -19591,7 +19317,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -19602,31 +19328,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="D38" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E38" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F38" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G38" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H38" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I38" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J38" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K38" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -19734,7 +19460,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -19745,31 +19471,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="D39" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E39" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F39" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G39" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H39" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I39" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J39" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K39" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -19877,7 +19603,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -19888,31 +19614,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="D40" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E40" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F40" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G40" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H40" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I40" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J40" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K40" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -20020,7 +19746,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -20031,31 +19757,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="D41" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E41" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F41" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G41" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H41" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I41" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J41" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K41" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -20163,7 +19889,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -20174,31 +19900,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="D42" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E42" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F42" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G42" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H42" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I42" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J42" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K42" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -20306,7 +20032,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -20317,31 +20043,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="D43" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E43" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F43" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G43" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H43" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I43" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J43" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K43" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -20449,7 +20175,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -20463,28 +20189,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E44" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F44" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G44" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H44" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I44" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J44" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K44" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -20592,7 +20318,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -20603,31 +20329,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="D45" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E45" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F45" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G45" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H45" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I45" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J45" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K45" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -20735,7 +20461,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -20746,31 +20472,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="D46" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E46" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F46" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G46" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H46" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I46" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J46" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K46" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -20878,7 +20604,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -20889,31 +20615,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="D47" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E47" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F47" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G47" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H47" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I47" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J47" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K47" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -21021,7 +20747,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -21035,28 +20761,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E48" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F48" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G48" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H48" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I48" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J48" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K48" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -21164,7 +20890,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -21175,31 +20901,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="D49" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E49" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F49" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G49" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H49" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I49" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J49" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K49" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -21307,7 +21033,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -21318,31 +21044,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="D50" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E50" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F50" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G50" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H50" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I50" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J50" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K50" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -21450,7 +21176,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -21464,28 +21190,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E51" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F51" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G51" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H51" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I51" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J51" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K51" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -21593,7 +21319,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -21604,31 +21330,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="D52" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E52" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F52" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G52" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H52" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I52" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J52" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K52" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -21736,7 +21462,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -21747,31 +21473,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="D53" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E53" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F53" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G53" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H53" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I53" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J53" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K53" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -21879,7 +21605,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -21890,31 +21616,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="D54" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E54" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F54" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G54" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H54" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I54" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J54" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K54" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -22022,7 +21748,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -22033,31 +21759,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="D55" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="E55" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="F55" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="G55" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="H55" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="I55" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="J55" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="K55" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -22165,7 +21891,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="195">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -668,7 +668,7 @@
     <numFmt numFmtId="178" formatCode="0.0"/>
     <numFmt numFmtId="179" formatCode="0.000"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -696,18 +696,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.2"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1222,19 +1210,28 @@
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1243,134 +1240,125 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1385,16 +1373,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
@@ -1882,29 +1865,29 @@
   <dimension ref="A1:AA281"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="24" customWidth="1"/>
-    <col min="2" max="2" width="8.85454545454546" style="24" customWidth="1"/>
-    <col min="3" max="3" width="4.70909090909091" style="24" customWidth="1"/>
-    <col min="4" max="4" width="8.85454545454546" style="24" customWidth="1"/>
-    <col min="5" max="5" width="4.42727272727273" style="24" customWidth="1"/>
-    <col min="6" max="6" width="4.28181818181818" style="24" customWidth="1"/>
-    <col min="7" max="7" width="4.42727272727273" style="24" customWidth="1"/>
-    <col min="8" max="8" width="4.57272727272727" style="24" customWidth="1"/>
-    <col min="9" max="9" width="4" style="24" customWidth="1"/>
-    <col min="10" max="10" width="4.42727272727273" style="24" customWidth="1"/>
-    <col min="11" max="11" width="4.57272727272727" style="24" customWidth="1"/>
-    <col min="12" max="12" width="4.42727272727273" style="24" customWidth="1"/>
-    <col min="13" max="13" width="4" style="24" customWidth="1"/>
-    <col min="14" max="14" width="4.28181818181818" style="24" customWidth="1"/>
-    <col min="15" max="16" width="4.42727272727273" style="24" customWidth="1"/>
-    <col min="17" max="18" width="4.57272727272727" style="24" customWidth="1"/>
-    <col min="19" max="19" width="4.42727272727273" style="24" customWidth="1"/>
-    <col min="20" max="20" width="5" style="24" customWidth="1"/>
-    <col min="21" max="21" width="11.7090909090909" style="24" customWidth="1"/>
-    <col min="22" max="22" width="10.7090909090909" style="24" customWidth="1"/>
-    <col min="23" max="23" width="13.1363636363636" style="24" customWidth="1"/>
-    <col min="24" max="259" width="11.4272727272727" style="24" customWidth="1"/>
-    <col min="260" max="16384" width="9.13636363636364" style="24"/>
+    <col min="1" max="1" width="15" style="19" customWidth="1"/>
+    <col min="2" max="2" width="8.85454545454546" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.70909090909091" style="19" customWidth="1"/>
+    <col min="4" max="4" width="8.85454545454546" style="19" customWidth="1"/>
+    <col min="5" max="5" width="4.42727272727273" style="19" customWidth="1"/>
+    <col min="6" max="6" width="4.28181818181818" style="19" customWidth="1"/>
+    <col min="7" max="7" width="4.42727272727273" style="19" customWidth="1"/>
+    <col min="8" max="8" width="4.57272727272727" style="19" customWidth="1"/>
+    <col min="9" max="9" width="4" style="19" customWidth="1"/>
+    <col min="10" max="10" width="4.42727272727273" style="19" customWidth="1"/>
+    <col min="11" max="11" width="4.57272727272727" style="19" customWidth="1"/>
+    <col min="12" max="12" width="4.42727272727273" style="19" customWidth="1"/>
+    <col min="13" max="13" width="4" style="19" customWidth="1"/>
+    <col min="14" max="14" width="4.28181818181818" style="19" customWidth="1"/>
+    <col min="15" max="16" width="4.42727272727273" style="19" customWidth="1"/>
+    <col min="17" max="18" width="4.57272727272727" style="19" customWidth="1"/>
+    <col min="19" max="19" width="4.42727272727273" style="19" customWidth="1"/>
+    <col min="20" max="20" width="5" style="19" customWidth="1"/>
+    <col min="21" max="21" width="11.7090909090909" style="19" customWidth="1"/>
+    <col min="22" max="22" width="10.7090909090909" style="19" customWidth="1"/>
+    <col min="23" max="23" width="13.1363636363636" style="19" customWidth="1"/>
+    <col min="24" max="259" width="11.4272727272727" style="19" customWidth="1"/>
+    <col min="260" max="16384" width="9.13636363636364" style="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.5" spans="1:21">
@@ -2983,7 +2966,7 @@
       <c r="AA34" s="5"/>
     </row>
     <row r="35" ht="12.5" spans="1:27">
-      <c r="A35" s="24" t="s">
+      <c r="A35" s="19" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -3011,7 +2994,7 @@
       <c r="AA35" s="5"/>
     </row>
     <row r="36" ht="12.5" spans="1:27">
-      <c r="A36" s="24" t="s">
+      <c r="A36" s="19" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -3039,7 +3022,7 @@
       <c r="AA36" s="5"/>
     </row>
     <row r="37" ht="12.5" spans="1:27">
-      <c r="A37" s="24" t="s">
+      <c r="A37" s="19" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -3067,7 +3050,7 @@
       <c r="AA37" s="5"/>
     </row>
     <row r="38" ht="12.5" spans="1:27">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="19" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -3095,7 +3078,7 @@
       <c r="AA38" s="5"/>
     </row>
     <row r="39" ht="12.5" spans="1:27">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="19" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -8456,7 +8439,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:BL124"/>
+  <dimension ref="A2:BO124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="2" max="2" width="21.3727272727273" customWidth="1"/>
@@ -8757,7 +8740,7 @@
       <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="20" t="s">
         <v>92</v>
       </c>
       <c r="F14">
@@ -8816,7 +8799,7 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="20" t="s">
         <v>92</v>
       </c>
       <c r="C18">
@@ -8825,7 +8808,7 @@
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E18" s="20" t="s">
         <v>100</v>
       </c>
       <c r="F18" t="s">
@@ -11613,7 +11596,7 @@
       <c r="D45">
         <v>2020</v>
       </c>
-      <c r="E45" s="26" t="s">
+      <c r="E45" s="21" t="s">
         <v>119</v>
       </c>
       <c r="F45" t="s">
@@ -11697,7 +11680,7 @@
       <c r="D55" t="s">
         <v>126</v>
       </c>
-      <c r="E55" s="25" t="s">
+      <c r="E55" s="20" t="s">
         <v>127</v>
       </c>
     </row>
@@ -11834,8 +11817,7 @@
     </row>
     <row r="65" s="1" customFormat="1" spans="1:53">
       <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" t="s">
+      <c r="B65" t="s">
         <v>73</v>
       </c>
       <c r="D65" s="2"/>
@@ -11889,9 +11871,12 @@
       <c r="AZ65" s="2"/>
       <c r="BA65" s="2"/>
     </row>
-    <row r="66" s="2" customFormat="1" ht="14.5" spans="3:64">
+    <row r="66" s="2" customFormat="1" spans="2:67">
+      <c r="B66" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="C66" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>3</v>
@@ -11917,1168 +11902,1164 @@
       <c r="K66" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L66" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M66" s="2" t="s">
+      <c r="L66" t="s">
+        <v>45</v>
+      </c>
+      <c r="M66" t="s">
+        <v>58</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AP66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ66" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N66" s="2" t="s">
+      <c r="AR66" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O66" s="2" t="s">
+      <c r="AS66" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P66" s="2" t="s">
+      <c r="AT66" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q66" s="2" t="s">
+      <c r="AU66" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="R66" s="2" t="s">
+      <c r="AV66" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="S66" s="2" t="s">
+      <c r="AW66" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="T66" s="2" t="s">
+      <c r="AX66" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="U66" s="2" t="s">
+      <c r="AY66" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="V66" s="2" t="s">
+      <c r="AZ66" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="W66" s="2" t="s">
+      <c r="BA66" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="X66" s="2" t="s">
+      <c r="BB66" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Y66" s="2" t="s">
+      <c r="BC66" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Z66" s="2" t="s">
+      <c r="BD66" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AA66" s="2" t="s">
+      <c r="BE66" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AB66" s="2" t="s">
+      <c r="BF66" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AC66" s="2" t="s">
+      <c r="BG66" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AD66" s="2" t="s">
+      <c r="BH66" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="AE66" s="2" t="s">
+      <c r="BI66" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AF66" s="2" t="s">
+      <c r="BJ66" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AG66" s="2" t="s">
+      <c r="BK66" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AH66" s="2" t="s">
+      <c r="BL66" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AI66" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AJ66" s="2" t="s">
+      <c r="BM66" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="BN66" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AK66" s="2" t="s">
+      <c r="BO66" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AL66" t="s">
-        <v>90</v>
-      </c>
-      <c r="AM66" t="s">
-        <v>58</v>
-      </c>
-      <c r="AN66" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="BE66" s="12"/>
-      <c r="BF66" s="12"/>
-      <c r="BG66" s="12"/>
-      <c r="BH66" s="12"/>
-      <c r="BI66" s="12"/>
-      <c r="BJ66" s="12"/>
-      <c r="BK66" s="12"/>
-      <c r="BL66" s="12"/>
-    </row>
-    <row r="67" s="2" customFormat="1" ht="16" spans="3:64">
-      <c r="C67" s="12" t="s">
+    </row>
+    <row r="67" s="2" customFormat="1" ht="14.5" spans="2:67">
+      <c r="B67" s="12" t="s">
         <v>132</v>
       </c>
+      <c r="C67" s="2">
+        <v>0</v>
+      </c>
       <c r="D67" s="2">
-        <f t="shared" ref="D67:AK67" si="2">D77/1000</f>
+        <f>D77/1000</f>
         <v>0</v>
       </c>
       <c r="E67" s="2">
-        <f t="shared" si="2"/>
+        <f>E77/1000</f>
         <v>310</v>
       </c>
       <c r="F67" s="2">
-        <f t="shared" si="2"/>
+        <f>F77/1000</f>
         <v>6200</v>
       </c>
       <c r="G67" s="2">
-        <f t="shared" si="2"/>
+        <f>G77/1000</f>
         <v>0</v>
       </c>
       <c r="H67" s="2">
-        <f t="shared" si="2"/>
+        <f>H77/1000</f>
         <v>0</v>
       </c>
       <c r="I67" s="2">
-        <f t="shared" si="2"/>
+        <f>I77/1000</f>
         <v>0</v>
       </c>
       <c r="J67" s="2">
-        <f t="shared" si="2"/>
+        <f>J77/1000</f>
         <v>250</v>
       </c>
       <c r="K67" s="2">
         <v>2000</v>
       </c>
-      <c r="L67" s="2">
+      <c r="L67" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AP67" s="2">
+        <f t="shared" ref="AP67:BO67" si="2">L77/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AQ67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M67" s="2">
+      <c r="AR67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N67" s="2">
+      <c r="AS67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O67" s="2">
+      <c r="AT67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P67" s="2">
+      <c r="AU67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q67" s="2">
+      <c r="AV67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R67" s="2">
+      <c r="AW67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="S67" s="2">
+      <c r="AX67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T67" s="2">
+      <c r="AY67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U67" s="2">
+      <c r="AZ67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W67" s="2">
+      <c r="BA67" s="2">
         <f t="shared" si="2"/>
         <v>12250</v>
       </c>
-      <c r="X67" s="2">
+      <c r="BB67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Y67" s="2">
+      <c r="BC67" s="2">
         <f t="shared" si="2"/>
         <v>1930</v>
       </c>
-      <c r="Z67" s="2">
+      <c r="BD67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AA67" s="2">
+      <c r="BE67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AB67" s="2">
+      <c r="BF67" s="2">
         <f t="shared" si="2"/>
         <v>3300</v>
       </c>
-      <c r="AC67" s="2">
+      <c r="BG67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD67" s="2">
+      <c r="BH67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AE67" s="2">
+      <c r="BI67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AF67" s="2">
+      <c r="BJ67" s="2">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="AG67" s="2">
+      <c r="BK67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AH67" s="2">
+      <c r="BL67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AI67" s="2">
+      <c r="BM67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AJ67" s="2">
+      <c r="BN67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK67" s="2">
+      <c r="BO67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AL67" s="1" t="s">
+    </row>
+    <row r="68" s="2" customFormat="1" ht="14.5" spans="2:67">
+      <c r="B68" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" s="2">
+        <v>0</v>
+      </c>
+      <c r="D68" s="2">
+        <f>D78/1000</f>
+        <v>0</v>
+      </c>
+      <c r="E68" s="2">
+        <f>E78/1000</f>
+        <v>0</v>
+      </c>
+      <c r="F68" s="2">
+        <f>F78/1000</f>
+        <v>21000</v>
+      </c>
+      <c r="G68" s="2">
+        <f>G78/1000</f>
+        <v>0</v>
+      </c>
+      <c r="H68" s="2">
+        <f>H78/1000</f>
+        <v>0</v>
+      </c>
+      <c r="I68" s="2">
+        <f>I78/1000</f>
+        <v>0</v>
+      </c>
+      <c r="J68" s="2">
+        <f>J78/1000</f>
+        <v>16000</v>
+      </c>
+      <c r="K68" s="2">
+        <f>K78/1000</f>
+        <v>2100</v>
+      </c>
+      <c r="L68" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AM67" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN67" s="2" t="s">
+      <c r="M68" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N68" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="BD67" s="22"/>
-      <c r="BE67" s="12"/>
-      <c r="BF67" s="12"/>
-      <c r="BG67" s="23"/>
-      <c r="BH67" s="12"/>
-      <c r="BI67" s="12"/>
-      <c r="BJ67" s="12"/>
-      <c r="BK67" s="12"/>
-      <c r="BL67" s="12"/>
-    </row>
-    <row r="68" s="2" customFormat="1" ht="14.5" spans="3:40">
-      <c r="C68" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D68" s="2">
-        <f t="shared" ref="D68:AK68" si="3">D78/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E68" s="2">
+      <c r="AP68" s="2">
+        <f t="shared" ref="AP68:BO68" si="3">L78/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F68" s="2">
+      <c r="AR68" s="2">
         <f t="shared" si="3"/>
-        <v>21000</v>
-      </c>
-      <c r="G68" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H68" s="2">
+      <c r="AT68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I68" s="2">
+      <c r="AU68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J68" s="2">
+      <c r="AV68" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW68" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX68" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY68" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AZ68" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA68" s="2">
         <f t="shared" si="3"/>
         <v>16000</v>
       </c>
-      <c r="K68" s="2">
+      <c r="BB68" s="2">
         <f t="shared" si="3"/>
-        <v>2100</v>
-      </c>
-      <c r="L68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="T68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W68" s="2">
-        <f t="shared" si="3"/>
-        <v>16000</v>
-      </c>
-      <c r="X68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BC68" s="2">
         <f t="shared" si="3"/>
         <v>2570</v>
       </c>
-      <c r="Z68" s="2">
+      <c r="BD68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AA68" s="2">
+      <c r="BE68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AB68" s="2">
+      <c r="BF68" s="2">
         <f t="shared" si="3"/>
         <v>52900</v>
       </c>
-      <c r="AC68" s="2">
+      <c r="BG68" s="2">
         <f t="shared" si="3"/>
         <v>7500</v>
       </c>
-      <c r="AD68" s="2">
+      <c r="BH68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE68" s="2">
+      <c r="BI68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF68" s="2">
+      <c r="BJ68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AG68" s="2">
+      <c r="BK68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AH68" s="2">
+      <c r="BL68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AI68" s="2">
+      <c r="BM68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AJ68" s="2">
+      <c r="BN68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AK68" s="2">
+      <c r="BO68" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AL68" s="1" t="s">
+    </row>
+    <row r="69" s="2" customFormat="1" ht="14.5" spans="2:67">
+      <c r="B69" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C69" s="2">
+        <v>0</v>
+      </c>
+      <c r="D69" s="2">
+        <f>D79/1000</f>
+        <v>13</v>
+      </c>
+      <c r="E69" s="2">
+        <f>E79/1000</f>
+        <v>4100</v>
+      </c>
+      <c r="F69" s="2">
+        <f>F79/1000</f>
+        <v>1500</v>
+      </c>
+      <c r="G69" s="2">
+        <f>G79/1000</f>
+        <v>0</v>
+      </c>
+      <c r="H69" s="2">
+        <f>H79/1000</f>
+        <v>0</v>
+      </c>
+      <c r="I69" s="2">
+        <f>I79/1000</f>
+        <v>0</v>
+      </c>
+      <c r="J69" s="2">
+        <f>J79/1000</f>
+        <v>0</v>
+      </c>
+      <c r="K69" s="2">
+        <f>K79/1000</f>
+        <v>140</v>
+      </c>
+      <c r="L69" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AM68" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AN68" s="2" t="s">
+      <c r="M69" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N69" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="69" s="2" customFormat="1" ht="14.5" spans="3:40">
-      <c r="C69" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D69" s="2">
-        <f t="shared" ref="D69:AK69" si="4">D79/1000</f>
-        <v>13</v>
-      </c>
-      <c r="E69" s="2">
+      <c r="AP69" s="2">
+        <f t="shared" ref="AP69:BO69" si="4">L79/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="2">
         <f t="shared" si="4"/>
-        <v>4100</v>
-      </c>
-      <c r="F69" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR69" s="2">
         <f t="shared" si="4"/>
-        <v>1500</v>
-      </c>
-      <c r="G69" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H69" s="2">
+      <c r="AT69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I69" s="2">
+      <c r="AU69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J69" s="2">
+      <c r="AV69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K69" s="2">
+      <c r="AW69" s="2">
         <f t="shared" si="4"/>
-        <v>140</v>
-      </c>
-      <c r="L69" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="M69" s="2">
+      <c r="AY69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N69" s="2">
+      <c r="AZ69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W69" s="2">
+      <c r="BA69" s="2">
         <f t="shared" si="4"/>
         <v>500</v>
       </c>
-      <c r="X69" s="2">
+      <c r="BB69" s="2">
         <f t="shared" si="4"/>
         <v>36</v>
       </c>
-      <c r="Y69" s="2">
+      <c r="BC69" s="2">
         <f t="shared" si="4"/>
         <v>289</v>
       </c>
-      <c r="Z69" s="2">
+      <c r="BD69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AA69" s="2">
+      <c r="BE69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AB69" s="2">
+      <c r="BF69" s="2">
         <f t="shared" si="4"/>
         <v>1517</v>
       </c>
-      <c r="AC69" s="2">
+      <c r="BG69" s="2">
         <f t="shared" si="4"/>
         <v>250</v>
       </c>
-      <c r="AD69" s="2">
+      <c r="BH69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AE69" s="2">
+      <c r="BI69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AF69" s="2">
+      <c r="BJ69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AG69" s="2">
+      <c r="BK69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AH69" s="2">
+      <c r="BL69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AI69" s="2">
+      <c r="BM69" s="2">
         <f t="shared" si="4"/>
         <v>36</v>
       </c>
-      <c r="AJ69" s="2">
+      <c r="BN69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AK69" s="2">
+      <c r="BO69" s="2">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AL69" s="1" t="s">
+    </row>
+    <row r="70" s="2" customFormat="1" ht="14.5" spans="2:67">
+      <c r="B70" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C70" s="2">
+        <v>0</v>
+      </c>
+      <c r="D70" s="2">
+        <f>D80/1000</f>
+        <v>0</v>
+      </c>
+      <c r="E70" s="2">
+        <f>E80/1000</f>
+        <v>74000</v>
+      </c>
+      <c r="F70" s="2">
+        <f>F80/1000</f>
+        <v>270000</v>
+      </c>
+      <c r="G70" s="2">
+        <f>G80/1000</f>
+        <v>0</v>
+      </c>
+      <c r="H70" s="2">
+        <f>H80/1000</f>
+        <v>0</v>
+      </c>
+      <c r="I70" s="2">
+        <f>I80/1000</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="2">
+        <f>J80/1000</f>
+        <v>270000</v>
+      </c>
+      <c r="K70" s="2">
+        <f>K80/1000</f>
+        <v>280000</v>
+      </c>
+      <c r="L70" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AM69" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AN69" s="2" t="s">
+      <c r="M70" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N70" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="70" s="2" customFormat="1" ht="14.5" spans="3:40">
-      <c r="C70" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D70" s="2">
-        <f t="shared" ref="D70:AK70" si="5">D80/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E70" s="2">
+      <c r="AP70" s="2">
+        <f t="shared" ref="AP70:BO70" si="5">L80/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="2">
         <f t="shared" si="5"/>
-        <v>74000</v>
-      </c>
-      <c r="F70" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR70" s="2">
         <f t="shared" si="5"/>
-        <v>270000</v>
-      </c>
-      <c r="G70" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H70" s="2">
+      <c r="AT70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="I70" s="2">
+      <c r="AU70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J70" s="2">
+      <c r="AV70" s="2">
         <f t="shared" si="5"/>
-        <v>270000</v>
-      </c>
-      <c r="K70" s="2">
-        <f t="shared" si="5"/>
-        <v>280000</v>
-      </c>
-      <c r="L70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="P70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S70" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW70" s="2">
         <f t="shared" si="5"/>
         <v>34000</v>
       </c>
-      <c r="T70" s="2">
+      <c r="AX70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U70" s="2">
+      <c r="AY70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V70" s="2">
+      <c r="AZ70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="W70" s="2">
+      <c r="BA70" s="2">
         <f t="shared" si="5"/>
         <v>275000</v>
       </c>
-      <c r="X70" s="2">
+      <c r="BB70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Y70" s="2">
+      <c r="BC70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z70" s="2">
+      <c r="BD70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA70" s="2">
+      <c r="BE70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB70" s="2">
+      <c r="BF70" s="2">
         <f t="shared" si="5"/>
         <v>5000</v>
       </c>
-      <c r="AC70" s="2">
+      <c r="BG70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AD70" s="2">
+      <c r="BH70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AE70" s="2">
+      <c r="BI70" s="2">
         <f t="shared" si="5"/>
         <v>640000</v>
       </c>
-      <c r="AF70" s="2">
+      <c r="BJ70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AG70" s="2">
+      <c r="BK70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AH70" s="2">
+      <c r="BL70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AI70" s="2">
+      <c r="BM70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AJ70" s="2">
+      <c r="BN70" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AK70" s="2">
+      <c r="BO70" s="2">
         <f t="shared" si="5"/>
         <v>140000</v>
       </c>
-      <c r="AL70" s="1" t="s">
+    </row>
+    <row r="71" s="2" customFormat="1" ht="14.5" spans="2:67">
+      <c r="B71" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C71" s="2">
+        <v>0</v>
+      </c>
+      <c r="D71" s="2">
+        <f>D81/1000</f>
+        <v>0</v>
+      </c>
+      <c r="E71" s="2">
+        <f>E81/1000</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="2">
+        <f>F81/1000</f>
+        <v>0</v>
+      </c>
+      <c r="G71" s="2">
+        <f>G81/1000</f>
+        <v>0</v>
+      </c>
+      <c r="H71" s="2">
+        <f>H81/1000</f>
+        <v>0</v>
+      </c>
+      <c r="I71" s="2">
+        <f>I81/1000</f>
+        <v>0</v>
+      </c>
+      <c r="J71" s="2">
+        <f>J81/1000</f>
+        <v>0</v>
+      </c>
+      <c r="K71" s="2">
+        <f>K81/1000</f>
+        <v>0</v>
+      </c>
+      <c r="L71" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AM70" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AN70" s="2" t="s">
+      <c r="M71" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N71" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="71" s="2" customFormat="1" ht="14.5" spans="3:40">
-      <c r="C71" s="12" t="s">
+      <c r="AP71" s="2">
+        <f t="shared" ref="AP71:BO71" si="6">L81/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AR71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AS71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AT71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AU71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AV71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AW71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AX71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AY71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AZ71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BA71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BB71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BC71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BD71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BE71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BF71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BG71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BH71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BI71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BJ71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BK71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BL71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BM71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BN71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BO71" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" ht="14.5" spans="2:67">
+      <c r="B72" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D71" s="2">
-        <f t="shared" ref="D71:AK71" si="6">D81/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="V71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="W71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="X71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Y71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Z71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AB71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AC71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AD71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AE71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AF71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AG71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AH71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AI71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AJ71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AK71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AL71" s="1" t="s">
+      <c r="C72" s="2">
+        <v>0</v>
+      </c>
+      <c r="D72" s="2">
+        <f>D82/1000</f>
+        <v>0</v>
+      </c>
+      <c r="E72" s="2">
+        <f>E82/1000</f>
+        <v>50000</v>
+      </c>
+      <c r="F72" s="2">
+        <f>F82/1000</f>
+        <v>97000</v>
+      </c>
+      <c r="G72" s="2">
+        <f>G82/1000</f>
+        <v>0</v>
+      </c>
+      <c r="H72" s="2">
+        <f>H82/1000</f>
+        <v>0</v>
+      </c>
+      <c r="I72" s="2">
+        <f>I82/1000</f>
+        <v>0</v>
+      </c>
+      <c r="J72" s="2">
+        <f>J82/1000</f>
+        <v>0</v>
+      </c>
+      <c r="K72" s="2">
+        <f>K82/1000</f>
+        <v>27000</v>
+      </c>
+      <c r="L72" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AM71" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="AN71" s="2" t="s">
+      <c r="M72" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="N72" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="72" s="2" customFormat="1" ht="14.5" spans="3:40">
-      <c r="C72" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D72" s="2">
-        <f t="shared" ref="D72:AK72" si="7">D82/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E72" s="2">
+      <c r="AP72" s="2">
+        <f t="shared" ref="AP72:BO72" si="7">L82/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AQ72" s="2">
         <f t="shared" si="7"/>
-        <v>50000</v>
-      </c>
-      <c r="F72" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR72" s="2">
         <f t="shared" si="7"/>
-        <v>97000</v>
-      </c>
-      <c r="G72" s="2">
+        <v>0</v>
+      </c>
+      <c r="AS72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H72" s="2">
+      <c r="AT72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I72" s="2">
+      <c r="AU72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J72" s="2">
+      <c r="AV72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K72" s="2">
+      <c r="AW72" s="2">
         <f t="shared" si="7"/>
-        <v>27000</v>
-      </c>
-      <c r="L72" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="M72" s="2">
+      <c r="AY72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="N72" s="2">
+      <c r="AZ72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="O72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="P72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Q72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="R72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="S72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="T72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="U72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="V72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="W72" s="2">
+      <c r="BA72" s="2">
         <f t="shared" si="7"/>
         <v>324000</v>
       </c>
-      <c r="X72" s="2">
+      <c r="BB72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="Y72" s="2">
+      <c r="BC72" s="2">
         <f t="shared" si="7"/>
         <v>51600</v>
       </c>
-      <c r="Z72" s="2">
+      <c r="BD72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AA72" s="2">
+      <c r="BE72" s="2">
         <f t="shared" si="7"/>
         <v>30000</v>
       </c>
-      <c r="AB72" s="2">
+      <c r="BF72" s="2">
         <f t="shared" si="7"/>
         <v>244000</v>
       </c>
-      <c r="AC72" s="2">
+      <c r="BG72" s="2">
         <f t="shared" si="7"/>
         <v>62000</v>
       </c>
-      <c r="AD72" s="2">
+      <c r="BH72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AE72" s="2">
+      <c r="BI72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AF72" s="2">
+      <c r="BJ72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AG72" s="2">
+      <c r="BK72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH72" s="2">
+      <c r="BL72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AI72" s="2">
+      <c r="BM72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AJ72" s="2">
+      <c r="BN72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK72" s="2">
+      <c r="BO72" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AL72" s="1" t="s">
+    </row>
+    <row r="73" s="1" customFormat="1" ht="14.5" spans="2:67">
+      <c r="B73" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C73" s="2">
+        <v>0</v>
+      </c>
+      <c r="D73" s="2">
+        <f>D83/1000</f>
+        <v>0</v>
+      </c>
+      <c r="E73" s="2">
+        <f>E83/1000</f>
+        <v>69000</v>
+      </c>
+      <c r="F73" s="2">
+        <f>F83/1000</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="2">
+        <f>G83/1000</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="2">
+        <f>H83/1000</f>
+        <v>0</v>
+      </c>
+      <c r="I73" s="2">
+        <f>I83/1000</f>
+        <v>0</v>
+      </c>
+      <c r="J73" s="2">
+        <f>J83/1000</f>
+        <v>74000</v>
+      </c>
+      <c r="K73" s="2">
+        <f>K83/1000</f>
+        <v>52000</v>
+      </c>
+      <c r="L73" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AM72" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="AN72" s="2" t="s">
+      <c r="M73" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="N73" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="73" s="1" customFormat="1" ht="14.5" spans="3:49">
-      <c r="C73" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D73" s="2">
-        <f t="shared" ref="D73:AK73" si="8">D83/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E73" s="2">
+      <c r="AO73" s="2"/>
+      <c r="AP73" s="2">
+        <f t="shared" ref="AP73:BO73" si="8">L83/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="2">
         <f t="shared" si="8"/>
-        <v>69000</v>
-      </c>
-      <c r="F73" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="G73" s="2">
+      <c r="AS73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H73" s="2">
+      <c r="AT73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="I73" s="2">
+      <c r="AU73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J73" s="2">
+      <c r="AV73" s="2">
         <f t="shared" si="8"/>
-        <v>74000</v>
-      </c>
-      <c r="K73" s="2">
-        <f t="shared" si="8"/>
-        <v>52000</v>
-      </c>
-      <c r="L73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="M73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="N73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="P73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Q73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S73" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW73" s="2">
         <f t="shared" si="8"/>
         <v>8000</v>
       </c>
-      <c r="T73" s="2">
+      <c r="AX73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="U73" s="2">
+      <c r="AY73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="V73" s="2">
+      <c r="AZ73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="W73" s="2">
+      <c r="BA73" s="2">
         <f t="shared" si="8"/>
         <v>77100</v>
       </c>
-      <c r="X73" s="2">
+      <c r="BB73" s="2">
         <f t="shared" si="8"/>
         <v>90000</v>
       </c>
-      <c r="Y73" s="2">
+      <c r="BC73" s="2">
         <f t="shared" si="8"/>
         <v>5700</v>
       </c>
-      <c r="Z73" s="2">
+      <c r="BD73" s="2">
         <f t="shared" si="8"/>
         <v>600</v>
       </c>
-      <c r="AA73" s="2">
+      <c r="BE73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AB73" s="2">
+      <c r="BF73" s="2">
         <f t="shared" si="8"/>
         <v>12900</v>
       </c>
-      <c r="AC73" s="2">
+      <c r="BG73" s="2">
         <f t="shared" si="8"/>
         <v>14000</v>
       </c>
-      <c r="AD73" s="2">
+      <c r="BH73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AE73" s="2">
+      <c r="BI73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AF73" s="2">
+      <c r="BJ73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AG73" s="2">
+      <c r="BK73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH73" s="2">
+      <c r="BL73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AI73" s="2">
+      <c r="BM73" s="2">
         <f t="shared" si="8"/>
         <v>90000</v>
       </c>
-      <c r="AJ73" s="2">
+      <c r="BN73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AK73" s="2">
+      <c r="BO73" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AL73" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AM73" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="AN73" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO73" s="2"/>
-      <c r="AP73" s="2"/>
-      <c r="AQ73" s="2"/>
-      <c r="AR73" s="2"/>
-      <c r="AS73" s="2"/>
-      <c r="AT73" s="2"/>
-      <c r="AU73" s="2"/>
-      <c r="AV73" s="2"/>
-      <c r="AW73" s="2"/>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
@@ -13791,504 +13772,472 @@
       <c r="Y89" s="9"/>
       <c r="Z89" s="9"/>
     </row>
-    <row r="90" s="4" customFormat="1" spans="1:4">
-      <c r="A90" s="14"/>
-      <c r="B90" s="14"/>
-      <c r="C90" s="14"/>
-      <c r="D90" s="14"/>
-    </row>
-    <row r="91" s="4" customFormat="1" spans="2:12">
-      <c r="B91" s="14"/>
-      <c r="C91" s="14"/>
-      <c r="D91" s="14"/>
-      <c r="E91" s="15"/>
-      <c r="H91" s="16"/>
-      <c r="I91" s="16"/>
-      <c r="J91" s="16"/>
-      <c r="K91" s="16"/>
-      <c r="L91" s="16"/>
-    </row>
-    <row r="92" s="4" customFormat="1" spans="2:12">
-      <c r="B92" s="14"/>
-      <c r="C92" s="14"/>
-      <c r="D92" s="17"/>
-      <c r="E92" s="14"/>
-      <c r="H92" s="16"/>
-      <c r="I92" s="16"/>
-      <c r="J92" s="16"/>
-      <c r="K92" s="16"/>
-      <c r="L92" s="16"/>
-    </row>
-    <row r="93" s="4" customFormat="1" spans="2:12">
-      <c r="B93" s="14"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="17"/>
-      <c r="E93" s="14"/>
-      <c r="F93" s="16"/>
-      <c r="H93" s="16"/>
-      <c r="I93" s="16"/>
-      <c r="J93" s="16"/>
-      <c r="K93" s="16"/>
-      <c r="L93" s="16"/>
-    </row>
-    <row r="94" s="4" customFormat="1" spans="2:12">
-      <c r="B94" s="14"/>
-      <c r="C94" s="18"/>
-      <c r="D94" s="17"/>
-      <c r="E94" s="14"/>
-      <c r="H94" s="16"/>
-      <c r="I94" s="16"/>
-      <c r="J94" s="16"/>
-      <c r="K94" s="16"/>
-      <c r="L94" s="16"/>
-    </row>
-    <row r="95" s="4" customFormat="1" spans="2:12">
-      <c r="B95" s="14"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="17"/>
-      <c r="E95" s="14"/>
-      <c r="F95" s="16"/>
-      <c r="H95" s="16"/>
-      <c r="I95" s="16"/>
-      <c r="J95" s="16"/>
-      <c r="K95" s="16"/>
-      <c r="L95" s="16"/>
-    </row>
-    <row r="96" s="4" customFormat="1" spans="2:12">
-      <c r="B96" s="14"/>
-      <c r="C96" s="18"/>
-      <c r="D96" s="17"/>
-      <c r="E96" s="14"/>
-      <c r="H96" s="16"/>
-      <c r="I96" s="16"/>
-      <c r="J96" s="16"/>
-      <c r="K96" s="16"/>
-      <c r="L96" s="16"/>
-    </row>
-    <row r="97" s="4" customFormat="1" spans="2:12">
-      <c r="B97" s="14"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="17"/>
-      <c r="E97" s="14"/>
-      <c r="F97" s="16"/>
-      <c r="H97" s="16"/>
-      <c r="I97" s="16"/>
-      <c r="J97" s="16"/>
-      <c r="K97" s="16"/>
-      <c r="L97" s="16"/>
-    </row>
-    <row r="98" s="4" customFormat="1" spans="2:12">
-      <c r="B98" s="14"/>
-      <c r="C98" s="18"/>
-      <c r="D98" s="17"/>
-      <c r="E98" s="14"/>
-      <c r="H98" s="16"/>
-      <c r="I98" s="16"/>
-      <c r="J98" s="16"/>
-      <c r="K98" s="16"/>
-      <c r="L98" s="16"/>
-    </row>
-    <row r="99" s="4" customFormat="1" spans="2:6">
-      <c r="B99" s="14"/>
-      <c r="C99" s="18"/>
-      <c r="E99" s="14"/>
-      <c r="F99" s="16"/>
-    </row>
-    <row r="100" s="4" customFormat="1" spans="2:5">
-      <c r="B100" s="14"/>
-      <c r="C100" s="18"/>
-      <c r="D100" s="18"/>
-      <c r="E100" s="14"/>
-    </row>
-    <row r="101" s="4" customFormat="1" spans="2:7">
-      <c r="B101" s="14"/>
-      <c r="C101" s="18"/>
-      <c r="D101" s="19"/>
-      <c r="E101" s="19"/>
-      <c r="F101" s="19"/>
-      <c r="G101" s="19"/>
-    </row>
-    <row r="102" s="4" customFormat="1" spans="2:4">
-      <c r="B102" s="14"/>
-      <c r="C102" s="18"/>
+    <row r="90" s="4" customFormat="1"/>
+    <row r="91" s="4" customFormat="1" spans="5:12">
+      <c r="E91" s="14"/>
+      <c r="H91" s="15"/>
+      <c r="I91" s="15"/>
+      <c r="J91" s="15"/>
+      <c r="K91" s="15"/>
+      <c r="L91" s="15"/>
+    </row>
+    <row r="92" s="4" customFormat="1" spans="4:12">
+      <c r="D92" s="15"/>
+      <c r="H92" s="15"/>
+      <c r="I92" s="15"/>
+      <c r="J92" s="15"/>
+      <c r="K92" s="15"/>
+      <c r="L92" s="15"/>
+    </row>
+    <row r="93" s="4" customFormat="1" spans="3:12">
+      <c r="C93" s="15"/>
+      <c r="D93" s="15"/>
+      <c r="F93" s="15"/>
+      <c r="H93" s="15"/>
+      <c r="I93" s="15"/>
+      <c r="J93" s="15"/>
+      <c r="K93" s="15"/>
+      <c r="L93" s="15"/>
+    </row>
+    <row r="94" s="4" customFormat="1" spans="3:12">
+      <c r="C94" s="15"/>
+      <c r="D94" s="15"/>
+      <c r="H94" s="15"/>
+      <c r="I94" s="15"/>
+      <c r="J94" s="15"/>
+      <c r="K94" s="15"/>
+      <c r="L94" s="15"/>
+    </row>
+    <row r="95" s="4" customFormat="1" spans="3:12">
+      <c r="C95" s="15"/>
+      <c r="D95" s="15"/>
+      <c r="F95" s="15"/>
+      <c r="H95" s="15"/>
+      <c r="I95" s="15"/>
+      <c r="J95" s="15"/>
+      <c r="K95" s="15"/>
+      <c r="L95" s="15"/>
+    </row>
+    <row r="96" s="4" customFormat="1" spans="3:12">
+      <c r="C96" s="15"/>
+      <c r="D96" s="15"/>
+      <c r="H96" s="15"/>
+      <c r="I96" s="15"/>
+      <c r="J96" s="15"/>
+      <c r="K96" s="15"/>
+      <c r="L96" s="15"/>
+    </row>
+    <row r="97" s="4" customFormat="1" spans="3:12">
+      <c r="C97" s="15"/>
+      <c r="D97" s="15"/>
+      <c r="F97" s="15"/>
+      <c r="H97" s="15"/>
+      <c r="I97" s="15"/>
+      <c r="J97" s="15"/>
+      <c r="K97" s="15"/>
+      <c r="L97" s="15"/>
+    </row>
+    <row r="98" s="4" customFormat="1" spans="3:12">
+      <c r="C98" s="15"/>
+      <c r="D98" s="15"/>
+      <c r="H98" s="15"/>
+      <c r="I98" s="15"/>
+      <c r="J98" s="15"/>
+      <c r="K98" s="15"/>
+      <c r="L98" s="15"/>
+    </row>
+    <row r="99" s="4" customFormat="1" spans="3:6">
+      <c r="C99" s="15"/>
+      <c r="F99" s="15"/>
+    </row>
+    <row r="100" s="4" customFormat="1" spans="3:4">
+      <c r="C100" s="15"/>
+      <c r="D100" s="15"/>
+    </row>
+    <row r="101" s="4" customFormat="1" spans="3:7">
+      <c r="C101" s="15"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="16"/>
+      <c r="F101" s="16"/>
+      <c r="G101" s="16"/>
+    </row>
+    <row r="102" s="4" customFormat="1" spans="3:4">
+      <c r="C102" s="15"/>
       <c r="D102" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="103" s="4" customFormat="1" spans="2:7">
-      <c r="B103" s="14"/>
-      <c r="C103" s="18" t="s">
+    <row r="103" s="4" customFormat="1" spans="3:7">
+      <c r="C103" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D103" s="19" t="s">
+      <c r="D103" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E103" s="19" t="s">
+      <c r="E103" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="F103" s="19" t="s">
+      <c r="F103" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="G103" s="19" t="s">
+      <c r="G103" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="104" s="4" customFormat="1" spans="2:7">
-      <c r="B104" s="14"/>
-      <c r="C104" s="18" t="s">
+    <row r="104" s="4" customFormat="1" spans="3:7">
+      <c r="C104" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D104" s="19" t="s">
+      <c r="D104" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="E104" s="19">
+      <c r="E104" s="16">
         <v>7.11384396954065</v>
       </c>
-      <c r="F104" s="20">
+      <c r="F104" s="17">
         <v>5.40179852616065</v>
       </c>
-      <c r="G104" s="20">
+      <c r="G104" s="17">
         <v>8.85540744288872</v>
       </c>
     </row>
-    <row r="105" s="4" customFormat="1" spans="2:7">
-      <c r="B105" s="14"/>
-      <c r="C105" s="18" t="s">
+    <row r="105" s="4" customFormat="1" spans="3:7">
+      <c r="C105" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D105" s="19" t="s">
+      <c r="D105" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="E105" s="19">
+      <c r="E105" s="16">
         <v>7.11384396954065</v>
       </c>
-      <c r="F105" s="20">
+      <c r="F105" s="17">
         <v>5.40179852616065</v>
       </c>
-      <c r="G105" s="20">
+      <c r="G105" s="17">
         <v>8.85540744288872</v>
       </c>
     </row>
     <row r="106" spans="3:7">
-      <c r="C106" s="18" t="s">
+      <c r="C106" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D106" s="19" t="s">
+      <c r="D106" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="E106" s="19">
+      <c r="E106" s="16">
         <v>7.62975445836404</v>
       </c>
-      <c r="F106" s="20">
+      <c r="F106" s="17">
         <v>5.79354797347089</v>
       </c>
-      <c r="G106" s="20">
+      <c r="G106" s="17">
         <v>9.49761967575534</v>
       </c>
     </row>
     <row r="107" spans="3:7">
-      <c r="C107" s="18" t="s">
+      <c r="C107" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D107" s="19" t="s">
+      <c r="D107" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="E107" s="19">
+      <c r="E107" s="16">
         <v>7.47097081798084</v>
       </c>
-      <c r="F107" s="20">
+      <c r="F107" s="17">
         <v>5.67297781871776</v>
       </c>
-      <c r="G107" s="20">
+      <c r="G107" s="17">
         <v>9.29996366985999</v>
       </c>
     </row>
     <row r="108" spans="3:7">
-      <c r="C108" s="18" t="s">
+      <c r="C108" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D108" s="19" t="s">
+      <c r="D108" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="E108" s="19">
+      <c r="E108" s="16">
         <v>7.51643520019651</v>
       </c>
-      <c r="F108" s="20">
+      <c r="F108" s="17">
         <v>5.70750058953574</v>
       </c>
-      <c r="G108" s="20">
+      <c r="G108" s="17">
         <v>9.35655836403832</v>
       </c>
     </row>
     <row r="109" spans="3:7">
-      <c r="C109" s="18" t="s">
+      <c r="C109" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D109" s="19" t="s">
+      <c r="D109" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="E109" s="19">
+      <c r="E109" s="16">
         <v>7.55036263817244</v>
       </c>
-      <c r="F109" s="20">
+      <c r="F109" s="17">
         <v>5.73326293294031</v>
       </c>
-      <c r="G109" s="20">
+      <c r="G109" s="17">
         <v>9.39879167280766</v>
       </c>
     </row>
     <row r="110" spans="3:7">
-      <c r="C110" s="18" t="s">
+      <c r="C110" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D110" s="19" t="s">
+      <c r="D110" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="E110" s="19">
+      <c r="E110" s="16">
         <v>7.62975445836404</v>
       </c>
-      <c r="F110" s="20">
+      <c r="F110" s="17">
         <v>5.79354797347089</v>
       </c>
-      <c r="G110" s="20">
+      <c r="G110" s="17">
         <v>9.49761967575534</v>
       </c>
     </row>
     <row r="111" spans="3:7">
-      <c r="C111" s="18" t="s">
+      <c r="C111" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D111" s="19" t="s">
+      <c r="D111" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="E111" s="19">
+      <c r="E111" s="16">
         <v>4.18384600835176</v>
       </c>
-      <c r="F111" s="20">
+      <c r="F111" s="17">
         <v>3.17694532056006</v>
       </c>
-      <c r="G111" s="20">
+      <c r="G111" s="17">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="112" spans="3:7">
-      <c r="C112" s="18" t="s">
+      <c r="C112" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D112" s="19" t="s">
+      <c r="D112" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="E112" s="19">
+      <c r="E112" s="16">
         <v>4.18384600835176</v>
       </c>
-      <c r="F112" s="20">
+      <c r="F112" s="17">
         <v>3.17694532056006</v>
       </c>
-      <c r="G112" s="20">
+      <c r="G112" s="17">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="113" spans="3:7">
-      <c r="C113" s="18" t="s">
+      <c r="C113" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D113" s="19" t="s">
+      <c r="D113" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="E113" s="19">
+      <c r="E113" s="16">
         <v>4.18384600835176</v>
       </c>
-      <c r="F113" s="20">
+      <c r="F113" s="17">
         <v>3.17694532056006</v>
       </c>
-      <c r="G113" s="20">
+      <c r="G113" s="17">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="114" spans="3:7">
-      <c r="C114" s="18" t="s">
+      <c r="C114" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D114" s="19" t="s">
+      <c r="D114" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="E114" s="19">
+      <c r="E114" s="16">
         <v>4.18384600835176</v>
       </c>
-      <c r="F114" s="20">
+      <c r="F114" s="17">
         <v>3.17694532056006</v>
       </c>
-      <c r="G114" s="20">
+      <c r="G114" s="17">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="115" spans="3:7">
-      <c r="C115" s="18" t="s">
+      <c r="C115" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D115" s="19" t="s">
+      <c r="D115" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="E115" s="19">
+      <c r="E115" s="16">
         <v>4.18384600835176</v>
       </c>
-      <c r="F115" s="20">
+      <c r="F115" s="17">
         <v>3.17694532056006</v>
       </c>
-      <c r="G115" s="20">
+      <c r="G115" s="17">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="116" spans="3:7">
-      <c r="C116" s="18" t="s">
+      <c r="C116" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D116" s="19" t="s">
+      <c r="D116" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="E116" s="19">
+      <c r="E116" s="16">
         <v>4.18384600835176</v>
       </c>
-      <c r="F116" s="20">
+      <c r="F116" s="17">
         <v>3.17694532056006</v>
       </c>
-      <c r="G116" s="20">
+      <c r="G116" s="17">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="117" spans="3:7">
-      <c r="C117" s="18" t="s">
+      <c r="C117" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D117" s="19" t="s">
+      <c r="D117" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="E117" s="19">
+      <c r="E117" s="16">
         <v>4.18384600835176</v>
       </c>
-      <c r="F117" s="20">
+      <c r="F117" s="17">
         <v>3.17694532056006</v>
       </c>
-      <c r="G117" s="20">
+      <c r="G117" s="17">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="118" spans="3:7">
-      <c r="C118" s="18" t="s">
+      <c r="C118" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D118" s="19" t="s">
+      <c r="D118" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="E118" s="19">
+      <c r="E118" s="16">
         <v>3.56556266273643</v>
       </c>
-      <c r="F118" s="20">
+      <c r="F118" s="17">
         <v>2.70746042741341</v>
       </c>
-      <c r="G118" s="20">
+      <c r="G118" s="17">
         <v>4.4384597641857</v>
       </c>
     </row>
     <row r="119" spans="3:7">
-      <c r="C119" s="18" t="s">
+      <c r="C119" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D119" s="19" t="s">
+      <c r="D119" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="E119" s="19">
+      <c r="E119" s="16">
         <v>3.60087708179809</v>
       </c>
-      <c r="F119" s="20">
+      <c r="F119" s="17">
         <v>2.73427597641857</v>
       </c>
-      <c r="G119" s="20">
+      <c r="G119" s="17">
         <v>4.48241960206338</v>
       </c>
     </row>
     <row r="120" spans="3:7">
-      <c r="C120" s="18" t="s">
+      <c r="C120" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D120" s="19" t="s">
+      <c r="D120" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="E120" s="19">
+      <c r="E120" s="16">
         <v>3.56556266273643</v>
       </c>
-      <c r="F120" s="20">
+      <c r="F120" s="17">
         <v>2.70746042741341</v>
       </c>
-      <c r="G120" s="20">
+      <c r="G120" s="17">
         <v>4.4384597641857</v>
       </c>
     </row>
     <row r="121" spans="3:7">
-      <c r="C121" s="18" t="s">
+      <c r="C121" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D121" s="19" t="s">
+      <c r="D121" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="E121" s="19">
+      <c r="E121" s="16">
         <v>3.56645369688037</v>
       </c>
-      <c r="F121" s="20">
+      <c r="F121" s="17">
         <v>2.70813706705969</v>
       </c>
-      <c r="G121" s="20">
+      <c r="G121" s="17">
         <v>4.43956890198968</v>
       </c>
     </row>
     <row r="122" spans="3:7">
-      <c r="C122" s="18" t="s">
+      <c r="C122" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D122" s="19" t="s">
+      <c r="D122" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="E122" s="19">
+      <c r="E122" s="16">
         <v>3.56585961680177</v>
       </c>
-      <c r="F122" s="20">
+      <c r="F122" s="17">
         <v>2.70768592483419</v>
       </c>
-      <c r="G122" s="20">
+      <c r="G122" s="17">
         <v>4.43882940309506</v>
       </c>
     </row>
     <row r="123" spans="3:7">
-      <c r="C123" s="18" t="s">
+      <c r="C123" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D123" s="19" t="s">
+      <c r="D123" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="E123" s="19">
+      <c r="E123" s="16">
         <v>3.56556266273643</v>
       </c>
-      <c r="F123" s="20">
+      <c r="F123" s="17">
         <v>2.70746042741341</v>
       </c>
-      <c r="G123" s="20">
+      <c r="G123" s="17">
         <v>4.4384597641857</v>
       </c>
     </row>
     <row r="124" spans="3:7">
-      <c r="C124" s="18" t="s">
+      <c r="C124" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D124" s="21" t="s">
+      <c r="D124" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="E124" s="19">
+      <c r="E124" s="16">
         <v>3.56496890198968</v>
       </c>
-      <c r="F124" s="20">
+      <c r="F124" s="17">
         <v>2.70700957995578</v>
       </c>
-      <c r="G124" s="20">
+      <c r="G124" s="17">
         <v>4.43772063375092</v>
       </c>
     </row>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" updateLinks="never"/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" activeTab="1"/>
+    <workbookView windowWidth="18340" windowHeight="8720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TechSelection" sheetId="21" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="197">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -464,7 +464,13 @@
     <t>5. what does that mean list every country??</t>
   </si>
   <si>
+    <t>timeslice</t>
+  </si>
+  <si>
     <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>annual</t>
   </si>
   <si>
     <t>FLO_BND</t>
@@ -861,12 +867,18 @@
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1231,7 +1243,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1255,16 +1267,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1273,92 +1285,92 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1371,13 +1383,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="5" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
@@ -1865,29 +1878,29 @@
   <dimension ref="A1:AA281"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="19" customWidth="1"/>
-    <col min="2" max="2" width="8.85454545454546" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.70909090909091" style="19" customWidth="1"/>
-    <col min="4" max="4" width="8.85454545454546" style="19" customWidth="1"/>
-    <col min="5" max="5" width="4.42727272727273" style="19" customWidth="1"/>
-    <col min="6" max="6" width="4.28181818181818" style="19" customWidth="1"/>
-    <col min="7" max="7" width="4.42727272727273" style="19" customWidth="1"/>
-    <col min="8" max="8" width="4.57272727272727" style="19" customWidth="1"/>
-    <col min="9" max="9" width="4" style="19" customWidth="1"/>
-    <col min="10" max="10" width="4.42727272727273" style="19" customWidth="1"/>
-    <col min="11" max="11" width="4.57272727272727" style="19" customWidth="1"/>
-    <col min="12" max="12" width="4.42727272727273" style="19" customWidth="1"/>
-    <col min="13" max="13" width="4" style="19" customWidth="1"/>
-    <col min="14" max="14" width="4.28181818181818" style="19" customWidth="1"/>
-    <col min="15" max="16" width="4.42727272727273" style="19" customWidth="1"/>
-    <col min="17" max="18" width="4.57272727272727" style="19" customWidth="1"/>
-    <col min="19" max="19" width="4.42727272727273" style="19" customWidth="1"/>
-    <col min="20" max="20" width="5" style="19" customWidth="1"/>
-    <col min="21" max="21" width="11.7090909090909" style="19" customWidth="1"/>
-    <col min="22" max="22" width="10.7090909090909" style="19" customWidth="1"/>
-    <col min="23" max="23" width="13.1363636363636" style="19" customWidth="1"/>
-    <col min="24" max="259" width="11.4272727272727" style="19" customWidth="1"/>
-    <col min="260" max="16384" width="9.13636363636364" style="19"/>
+    <col min="1" max="1" width="15" style="20" customWidth="1"/>
+    <col min="2" max="2" width="8.85454545454546" style="20" customWidth="1"/>
+    <col min="3" max="3" width="4.70909090909091" style="20" customWidth="1"/>
+    <col min="4" max="4" width="8.85454545454546" style="20" customWidth="1"/>
+    <col min="5" max="5" width="4.42727272727273" style="20" customWidth="1"/>
+    <col min="6" max="6" width="4.28181818181818" style="20" customWidth="1"/>
+    <col min="7" max="7" width="4.42727272727273" style="20" customWidth="1"/>
+    <col min="8" max="8" width="4.57272727272727" style="20" customWidth="1"/>
+    <col min="9" max="9" width="4" style="20" customWidth="1"/>
+    <col min="10" max="10" width="4.42727272727273" style="20" customWidth="1"/>
+    <col min="11" max="11" width="4.57272727272727" style="20" customWidth="1"/>
+    <col min="12" max="12" width="4.42727272727273" style="20" customWidth="1"/>
+    <col min="13" max="13" width="4" style="20" customWidth="1"/>
+    <col min="14" max="14" width="4.28181818181818" style="20" customWidth="1"/>
+    <col min="15" max="16" width="4.42727272727273" style="20" customWidth="1"/>
+    <col min="17" max="18" width="4.57272727272727" style="20" customWidth="1"/>
+    <col min="19" max="19" width="4.42727272727273" style="20" customWidth="1"/>
+    <col min="20" max="20" width="5" style="20" customWidth="1"/>
+    <col min="21" max="21" width="11.7090909090909" style="20" customWidth="1"/>
+    <col min="22" max="22" width="10.7090909090909" style="20" customWidth="1"/>
+    <col min="23" max="23" width="13.1363636363636" style="20" customWidth="1"/>
+    <col min="24" max="259" width="11.4272727272727" style="20" customWidth="1"/>
+    <col min="260" max="16384" width="9.13636363636364" style="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.5" spans="1:21">
@@ -2966,7 +2979,7 @@
       <c r="AA34" s="5"/>
     </row>
     <row r="35" ht="12.5" spans="1:27">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="20" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -2994,7 +3007,7 @@
       <c r="AA35" s="5"/>
     </row>
     <row r="36" ht="12.5" spans="1:27">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="20" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -3022,7 +3035,7 @@
       <c r="AA36" s="5"/>
     </row>
     <row r="37" ht="12.5" spans="1:27">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="20" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -3050,7 +3063,7 @@
       <c r="AA37" s="5"/>
     </row>
     <row r="38" ht="12.5" spans="1:27">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="20" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -3078,7 +3091,7 @@
       <c r="AA38" s="5"/>
     </row>
     <row r="39" ht="12.5" spans="1:27">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="20" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -8439,7 +8452,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:BO124"/>
+  <dimension ref="A2:BA124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="2" max="2" width="21.3727272727273" customWidth="1"/>
@@ -8448,7 +8461,7 @@
     <col min="6" max="9" width="7.13636363636364" customWidth="1"/>
     <col min="10" max="10" width="10.6363636363636" customWidth="1"/>
     <col min="11" max="11" width="11.2818181818182" customWidth="1"/>
-    <col min="12" max="12" width="6" customWidth="1"/>
+    <col min="12" max="12" width="15.5454545454545" customWidth="1"/>
     <col min="13" max="24" width="7.13636363636364" customWidth="1"/>
     <col min="25" max="25" width="9.54545454545454" customWidth="1"/>
     <col min="26" max="33" width="7.13636363636364" customWidth="1"/>
@@ -8740,7 +8753,7 @@
       <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="21" t="s">
         <v>92</v>
       </c>
       <c r="F14">
@@ -8799,7 +8812,7 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>92</v>
       </c>
       <c r="C18">
@@ -8808,7 +8821,7 @@
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="21" t="s">
         <v>100</v>
       </c>
       <c r="F18" t="s">
@@ -11596,7 +11609,7 @@
       <c r="D45">
         <v>2020</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="E45" s="22" t="s">
         <v>119</v>
       </c>
       <c r="F45" t="s">
@@ -11680,7 +11693,7 @@
       <c r="D55" t="s">
         <v>126</v>
       </c>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="21" t="s">
         <v>127</v>
       </c>
     </row>
@@ -11719,9 +11732,6 @@
       <c r="O60" s="9"/>
       <c r="P60" s="9"/>
       <c r="Q60" s="9"/>
-      <c r="R60" s="9"/>
-      <c r="S60" s="9"/>
-      <c r="T60" s="9"/>
       <c r="U60" s="9"/>
       <c r="V60" s="9"/>
       <c r="W60" s="9"/>
@@ -11746,9 +11756,6 @@
       <c r="O61" s="9"/>
       <c r="P61" s="9"/>
       <c r="Q61" s="9"/>
-      <c r="R61" s="9"/>
-      <c r="S61" s="9"/>
-      <c r="T61" s="9"/>
       <c r="U61" s="9"/>
       <c r="V61" s="9"/>
       <c r="W61" s="9"/>
@@ -11817,7 +11824,7 @@
     </row>
     <row r="65" s="1" customFormat="1" spans="1:53">
       <c r="A65" s="2"/>
-      <c r="B65" t="s">
+      <c r="B65" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D65" s="2"/>
@@ -11871,1766 +11878,1789 @@
       <c r="AZ65" s="2"/>
       <c r="BA65" s="2"/>
     </row>
-    <row r="66" s="2" customFormat="1" spans="2:67">
+    <row r="66" s="2" customFormat="1" spans="1:40">
+      <c r="A66" s="2" t="s">
+        <v>131</v>
+      </c>
       <c r="B66" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="F66" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="G66" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="H66" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H66" s="2" t="s">
+      <c r="I66" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I66" s="2" t="s">
+      <c r="J66" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J66" s="2" t="s">
+      <c r="K66" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K66" s="2" t="s">
+      <c r="L66" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L66" t="s">
+      <c r="M66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R66" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X66" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA66" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB66" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE66" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AF66" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH66" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI66" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ66" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK66" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM66" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="M66" t="s">
-        <v>58</v>
-      </c>
-      <c r="N66" s="2" t="s">
+      <c r="AN66" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" ht="14.5" spans="1:40">
+      <c r="A67" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0</v>
+      </c>
+      <c r="E67" s="2">
+        <f t="shared" ref="E67:K67" si="2">D77/1000</f>
+        <v>0</v>
+      </c>
+      <c r="F67" s="2">
+        <f t="shared" si="2"/>
+        <v>310</v>
+      </c>
+      <c r="G67" s="2">
+        <f t="shared" si="2"/>
+        <v>6200</v>
+      </c>
+      <c r="H67" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I67" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K67" s="2">
+        <f t="shared" si="2"/>
+        <v>250</v>
+      </c>
+      <c r="L67" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M67" s="2">
+        <f t="shared" ref="M67:AL67" si="3">L77/1000</f>
+        <v>0</v>
+      </c>
+      <c r="N67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="X67" s="2">
+        <f t="shared" si="3"/>
+        <v>12250</v>
+      </c>
+      <c r="Y67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Z67" s="2">
+        <f t="shared" si="3"/>
+        <v>1930</v>
+      </c>
+      <c r="AA67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AB67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AC67" s="2">
+        <f t="shared" si="3"/>
+        <v>3300</v>
+      </c>
+      <c r="AD67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AE67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AF67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AG67" s="2">
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="AP66" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="AQ66" s="2" t="s">
+      <c r="AH67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM67" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN67" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" ht="14.5" spans="1:40">
+      <c r="A68" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D68" s="2">
+        <v>0</v>
+      </c>
+      <c r="E68" s="2">
+        <f t="shared" ref="E68:L68" si="4">D78/1000</f>
+        <v>0</v>
+      </c>
+      <c r="F68" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G68" s="2">
+        <f t="shared" si="4"/>
+        <v>21000</v>
+      </c>
+      <c r="H68" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I68" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J68" s="2">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K68" s="2">
+        <f t="shared" si="4"/>
+        <v>16000</v>
+      </c>
+      <c r="L68" s="2">
+        <f t="shared" si="4"/>
+        <v>2100</v>
+      </c>
+      <c r="M68" s="2">
+        <f t="shared" ref="M68:AL68" si="5">L78/1000</f>
+        <v>0</v>
+      </c>
+      <c r="N68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X68" s="2">
+        <f t="shared" si="5"/>
+        <v>16000</v>
+      </c>
+      <c r="Y68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z68" s="2">
+        <f t="shared" si="5"/>
+        <v>2570</v>
+      </c>
+      <c r="AA68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AC68" s="2">
+        <f t="shared" si="5"/>
+        <v>52900</v>
+      </c>
+      <c r="AD68" s="2">
+        <f t="shared" si="5"/>
+        <v>7500</v>
+      </c>
+      <c r="AE68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AF68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AG68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AH68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM68" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN68" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" ht="14.5" spans="1:40">
+      <c r="A69" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D69" s="2">
+        <v>0</v>
+      </c>
+      <c r="E69" s="2">
+        <f t="shared" ref="E69:L69" si="6">D79/1000</f>
         <v>13</v>
       </c>
-      <c r="AR66" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="AS66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AT66" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AU66" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AV66" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AW66" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AX66" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="AY66" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ66" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="BA66" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="BB66" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="BC66" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="BD66" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="BE66" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="BF66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="BG66" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="BH66" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="BI66" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="BJ66" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="BK66" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="BL66" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="BM66" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="BN66" s="2" t="s">
+      <c r="F69" s="2">
+        <f t="shared" si="6"/>
+        <v>4100</v>
+      </c>
+      <c r="G69" s="2">
+        <f t="shared" si="6"/>
+        <v>1500</v>
+      </c>
+      <c r="H69" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I69" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J69" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K69" s="2">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L69" s="2">
+        <f t="shared" si="6"/>
+        <v>140</v>
+      </c>
+      <c r="M69" s="2">
+        <f t="shared" ref="M69:AL69" si="7">L79/1000</f>
+        <v>0</v>
+      </c>
+      <c r="N69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="R69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="U69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="V69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="W69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X69" s="2">
+        <f t="shared" si="7"/>
+        <v>500</v>
+      </c>
+      <c r="Y69" s="2">
+        <f t="shared" si="7"/>
         <v>36</v>
       </c>
-      <c r="BO66" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="67" s="2" customFormat="1" ht="14.5" spans="2:67">
-      <c r="B67" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C67" s="2">
-        <v>0</v>
-      </c>
-      <c r="D67" s="2">
-        <f>D77/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E67" s="2">
-        <f>E77/1000</f>
-        <v>310</v>
-      </c>
-      <c r="F67" s="2">
-        <f>F77/1000</f>
-        <v>6200</v>
-      </c>
-      <c r="G67" s="2">
-        <f>G77/1000</f>
-        <v>0</v>
-      </c>
-      <c r="H67" s="2">
-        <f>H77/1000</f>
-        <v>0</v>
-      </c>
-      <c r="I67" s="2">
-        <f>I77/1000</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="2">
-        <f>J77/1000</f>
+      <c r="Z69" s="2">
+        <f t="shared" si="7"/>
+        <v>289</v>
+      </c>
+      <c r="AA69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AB69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AC69" s="2">
+        <f t="shared" si="7"/>
+        <v>1517</v>
+      </c>
+      <c r="AD69" s="2">
+        <f t="shared" si="7"/>
         <v>250</v>
       </c>
-      <c r="K67" s="2">
-        <v>2000</v>
-      </c>
-      <c r="L67" s="1" t="s">
+      <c r="AE69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AF69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AG69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AH69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AI69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AJ69" s="2">
+        <f t="shared" si="7"/>
+        <v>36</v>
+      </c>
+      <c r="AK69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AL69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AM69" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN69" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" ht="14.5" spans="1:40">
+      <c r="A70" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M67" s="1" t="s">
+      <c r="B70" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="N67" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="AP67" s="2">
-        <f t="shared" ref="AP67:BO67" si="2">L77/1000</f>
-        <v>0</v>
-      </c>
-      <c r="AQ67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AR67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AS67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AT67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AU67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AV67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AW67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AX67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AY67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AZ67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BA67" s="2">
-        <f t="shared" si="2"/>
-        <v>12250</v>
-      </c>
-      <c r="BB67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BC67" s="2">
-        <f t="shared" si="2"/>
-        <v>1930</v>
-      </c>
-      <c r="BD67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BE67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BF67" s="2">
-        <f t="shared" si="2"/>
-        <v>3300</v>
-      </c>
-      <c r="BG67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BH67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BI67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BJ67" s="2">
-        <f t="shared" si="2"/>
-        <v>60</v>
-      </c>
-      <c r="BK67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BL67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BM67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BN67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BO67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" ht="14.5" spans="2:67">
-      <c r="B68" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C68" s="2">
-        <v>0</v>
-      </c>
-      <c r="D68" s="2">
-        <f>D78/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E68" s="2">
-        <f>E78/1000</f>
-        <v>0</v>
-      </c>
-      <c r="F68" s="2">
-        <f>F78/1000</f>
-        <v>21000</v>
-      </c>
-      <c r="G68" s="2">
-        <f>G78/1000</f>
-        <v>0</v>
-      </c>
-      <c r="H68" s="2">
-        <f>H78/1000</f>
-        <v>0</v>
-      </c>
-      <c r="I68" s="2">
-        <f>I78/1000</f>
-        <v>0</v>
-      </c>
-      <c r="J68" s="2">
-        <f>J78/1000</f>
-        <v>16000</v>
-      </c>
-      <c r="K68" s="2">
-        <f>K78/1000</f>
-        <v>2100</v>
-      </c>
-      <c r="L68" s="1" t="s">
+      <c r="D70" s="2">
+        <v>0</v>
+      </c>
+      <c r="E70" s="2">
+        <f t="shared" ref="E70:L70" si="8">D80/1000</f>
+        <v>0</v>
+      </c>
+      <c r="F70" s="2">
+        <f t="shared" si="8"/>
+        <v>74000</v>
+      </c>
+      <c r="G70" s="2">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="H70" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I70" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J70" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K70" s="2">
+        <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="L70" s="2">
+        <f t="shared" si="8"/>
+        <v>280000</v>
+      </c>
+      <c r="M70" s="2">
+        <f t="shared" ref="M70:AL70" si="9">L80/1000</f>
+        <v>0</v>
+      </c>
+      <c r="N70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Q70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="T70" s="2">
+        <f t="shared" si="9"/>
+        <v>34000</v>
+      </c>
+      <c r="U70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="W70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X70" s="2">
+        <f t="shared" si="9"/>
+        <v>275000</v>
+      </c>
+      <c r="Y70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Z70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AB70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AC70" s="2">
+        <f t="shared" si="9"/>
+        <v>5000</v>
+      </c>
+      <c r="AD70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AE70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AF70" s="2">
+        <f t="shared" si="9"/>
+        <v>640000</v>
+      </c>
+      <c r="AG70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AH70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AI70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AL70" s="2">
+        <f t="shared" si="9"/>
+        <v>140000</v>
+      </c>
+      <c r="AM70" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN70" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" ht="14.5" spans="1:40">
+      <c r="A71" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="B71" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D71" s="2">
+        <v>0</v>
+      </c>
+      <c r="E71" s="2">
+        <f t="shared" ref="E71:L71" si="10">D81/1000</f>
+        <v>0</v>
+      </c>
+      <c r="F71" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="G71" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H71" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I71" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="J71" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="K71" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M71" s="2">
+        <f t="shared" ref="M71:AL71" si="11">L81/1000</f>
+        <v>0</v>
+      </c>
+      <c r="N71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="P71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="R71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="S71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="T71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="U71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="W71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="X71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Y71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Z71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AA71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AC71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AD71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AE71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AF71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AG71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AH71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AI71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AL71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AM71" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="N68" s="2" t="s">
+      <c r="AN71" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" ht="14.5" spans="1:40">
+      <c r="A72" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="AP68" s="2">
-        <f t="shared" ref="AP68:BO68" si="3">L78/1000</f>
-        <v>0</v>
-      </c>
-      <c r="AQ68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AR68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AS68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AT68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AU68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AV68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AW68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AX68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AY68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AZ68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BA68" s="2">
-        <f t="shared" si="3"/>
-        <v>16000</v>
-      </c>
-      <c r="BB68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BC68" s="2">
-        <f t="shared" si="3"/>
-        <v>2570</v>
-      </c>
-      <c r="BD68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BE68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BF68" s="2">
-        <f t="shared" si="3"/>
-        <v>52900</v>
-      </c>
-      <c r="BG68" s="2">
-        <f t="shared" si="3"/>
-        <v>7500</v>
-      </c>
-      <c r="BH68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BI68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BJ68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BK68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BL68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BM68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BN68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BO68" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" ht="14.5" spans="2:67">
-      <c r="B69" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C69" s="2">
-        <v>0</v>
-      </c>
-      <c r="D69" s="2">
-        <f>D79/1000</f>
-        <v>13</v>
-      </c>
-      <c r="E69" s="2">
-        <f>E79/1000</f>
-        <v>4100</v>
-      </c>
-      <c r="F69" s="2">
-        <f>F79/1000</f>
-        <v>1500</v>
-      </c>
-      <c r="G69" s="2">
-        <f>G79/1000</f>
-        <v>0</v>
-      </c>
-      <c r="H69" s="2">
-        <f>H79/1000</f>
-        <v>0</v>
-      </c>
-      <c r="I69" s="2">
-        <f>I79/1000</f>
-        <v>0</v>
-      </c>
-      <c r="J69" s="2">
-        <f>J79/1000</f>
-        <v>0</v>
-      </c>
-      <c r="K69" s="2">
-        <f>K79/1000</f>
-        <v>140</v>
-      </c>
-      <c r="L69" s="1" t="s">
+      <c r="D72" s="2">
+        <v>0</v>
+      </c>
+      <c r="E72" s="2">
+        <f t="shared" ref="E72:L72" si="12">D82/1000</f>
+        <v>0</v>
+      </c>
+      <c r="F72" s="2">
+        <f t="shared" si="12"/>
+        <v>50000</v>
+      </c>
+      <c r="G72" s="2">
+        <f t="shared" si="12"/>
+        <v>97000</v>
+      </c>
+      <c r="H72" s="2">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="I72" s="2">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="J72" s="2">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K72" s="2">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="L72" s="2">
+        <f t="shared" si="12"/>
+        <v>27000</v>
+      </c>
+      <c r="M72" s="2">
+        <f t="shared" ref="M72:AL72" si="13">L82/1000</f>
+        <v>0</v>
+      </c>
+      <c r="N72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="P72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="R72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="S72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="T72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="U72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="V72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="W72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X72" s="2">
+        <f t="shared" si="13"/>
+        <v>324000</v>
+      </c>
+      <c r="Y72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Z72" s="2">
+        <f t="shared" si="13"/>
+        <v>51600</v>
+      </c>
+      <c r="AA72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AB72" s="2">
+        <f t="shared" si="13"/>
+        <v>30000</v>
+      </c>
+      <c r="AC72" s="2">
+        <f t="shared" si="13"/>
+        <v>244000</v>
+      </c>
+      <c r="AD72" s="2">
+        <f t="shared" si="13"/>
+        <v>62000</v>
+      </c>
+      <c r="AE72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AF72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AG72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AH72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AI72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AJ72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AK72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM72" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN72" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="14.5" spans="1:40">
+      <c r="A73" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M69" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="N69" s="2" t="s">
+      <c r="B73" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="AP69" s="2">
-        <f t="shared" ref="AP69:BO69" si="4">L79/1000</f>
-        <v>0</v>
-      </c>
-      <c r="AQ69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AR69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AS69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AT69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AU69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AV69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AW69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AX69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AY69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AZ69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BA69" s="2">
-        <f t="shared" si="4"/>
-        <v>500</v>
-      </c>
-      <c r="BB69" s="2">
-        <f t="shared" si="4"/>
-        <v>36</v>
-      </c>
-      <c r="BC69" s="2">
-        <f t="shared" si="4"/>
-        <v>289</v>
-      </c>
-      <c r="BD69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BE69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BF69" s="2">
-        <f t="shared" si="4"/>
-        <v>1517</v>
-      </c>
-      <c r="BG69" s="2">
-        <f t="shared" si="4"/>
-        <v>250</v>
-      </c>
-      <c r="BH69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BI69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BJ69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BK69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BL69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BM69" s="2">
-        <f t="shared" si="4"/>
-        <v>36</v>
-      </c>
-      <c r="BN69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="BO69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" ht="14.5" spans="2:67">
-      <c r="B70" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C70" s="2">
-        <v>0</v>
-      </c>
-      <c r="D70" s="2">
-        <f>D80/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E70" s="2">
-        <f>E80/1000</f>
+      <c r="D73" s="2">
+        <v>0</v>
+      </c>
+      <c r="E73" s="2">
+        <f t="shared" ref="E73:L73" si="14">D83/1000</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="2">
+        <f t="shared" si="14"/>
+        <v>69000</v>
+      </c>
+      <c r="G73" s="2">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H73" s="2">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="I73" s="2">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="J73" s="2">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="K73" s="2">
+        <f t="shared" si="14"/>
         <v>74000</v>
       </c>
-      <c r="F70" s="2">
-        <f>F80/1000</f>
-        <v>270000</v>
-      </c>
-      <c r="G70" s="2">
-        <f>G80/1000</f>
-        <v>0</v>
-      </c>
-      <c r="H70" s="2">
-        <f>H80/1000</f>
-        <v>0</v>
-      </c>
-      <c r="I70" s="2">
-        <f>I80/1000</f>
-        <v>0</v>
-      </c>
-      <c r="J70" s="2">
-        <f>J80/1000</f>
-        <v>270000</v>
-      </c>
-      <c r="K70" s="2">
-        <f>K80/1000</f>
-        <v>280000</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="M70" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="N70" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP70" s="2">
-        <f t="shared" ref="AP70:BO70" si="5">L80/1000</f>
-        <v>0</v>
-      </c>
-      <c r="AQ70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AR70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AS70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AT70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AU70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AV70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AW70" s="2">
-        <f t="shared" si="5"/>
-        <v>34000</v>
-      </c>
-      <c r="AX70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AY70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AZ70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BA70" s="2">
-        <f t="shared" si="5"/>
-        <v>275000</v>
-      </c>
-      <c r="BB70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BC70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BD70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BE70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BF70" s="2">
-        <f t="shared" si="5"/>
-        <v>5000</v>
-      </c>
-      <c r="BG70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BH70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BI70" s="2">
-        <f t="shared" si="5"/>
-        <v>640000</v>
-      </c>
-      <c r="BJ70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BK70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BL70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BM70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BN70" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BO70" s="2">
-        <f t="shared" si="5"/>
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" ht="14.5" spans="2:67">
-      <c r="B71" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C71" s="2">
-        <v>0</v>
-      </c>
-      <c r="D71" s="2">
-        <f>D81/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E71" s="2">
-        <f>E81/1000</f>
-        <v>0</v>
-      </c>
-      <c r="F71" s="2">
-        <f>F81/1000</f>
-        <v>0</v>
-      </c>
-      <c r="G71" s="2">
-        <f>G81/1000</f>
-        <v>0</v>
-      </c>
-      <c r="H71" s="2">
-        <f>H81/1000</f>
-        <v>0</v>
-      </c>
-      <c r="I71" s="2">
-        <f>I81/1000</f>
-        <v>0</v>
-      </c>
-      <c r="J71" s="2">
-        <f>J81/1000</f>
-        <v>0</v>
-      </c>
-      <c r="K71" s="2">
-        <f>K81/1000</f>
-        <v>0</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N71" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP71" s="2">
-        <f t="shared" ref="AP71:BO71" si="6">L81/1000</f>
-        <v>0</v>
-      </c>
-      <c r="AQ71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AR71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AS71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AT71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AU71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AV71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AW71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AX71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AY71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AZ71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BA71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BB71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BC71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BD71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BE71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BF71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BG71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BH71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BI71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BJ71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BK71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BL71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BM71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BN71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="BO71" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" ht="14.5" spans="2:67">
-      <c r="B72" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C72" s="2">
-        <v>0</v>
-      </c>
-      <c r="D72" s="2">
-        <f>D82/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E72" s="2">
-        <f>E82/1000</f>
-        <v>50000</v>
-      </c>
-      <c r="F72" s="2">
-        <f>F82/1000</f>
-        <v>97000</v>
-      </c>
-      <c r="G72" s="2">
-        <f>G82/1000</f>
-        <v>0</v>
-      </c>
-      <c r="H72" s="2">
-        <f>H82/1000</f>
-        <v>0</v>
-      </c>
-      <c r="I72" s="2">
-        <f>I82/1000</f>
-        <v>0</v>
-      </c>
-      <c r="J72" s="2">
-        <f>J82/1000</f>
-        <v>0</v>
-      </c>
-      <c r="K72" s="2">
-        <f>K82/1000</f>
-        <v>27000</v>
-      </c>
-      <c r="L72" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="M72" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="N72" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AP72" s="2">
-        <f t="shared" ref="AP72:BO72" si="7">L82/1000</f>
-        <v>0</v>
-      </c>
-      <c r="AQ72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AR72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AS72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AT72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AU72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AV72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AW72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AX72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AY72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="AZ72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BA72" s="2">
-        <f t="shared" si="7"/>
-        <v>324000</v>
-      </c>
-      <c r="BB72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BC72" s="2">
-        <f t="shared" si="7"/>
-        <v>51600</v>
-      </c>
-      <c r="BD72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BE72" s="2">
-        <f t="shared" si="7"/>
-        <v>30000</v>
-      </c>
-      <c r="BF72" s="2">
-        <f t="shared" si="7"/>
-        <v>244000</v>
-      </c>
-      <c r="BG72" s="2">
-        <f t="shared" si="7"/>
-        <v>62000</v>
-      </c>
-      <c r="BH72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BI72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BJ72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BK72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BL72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BM72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BN72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="BO72" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" ht="14.5" spans="2:67">
-      <c r="B73" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C73" s="2">
-        <v>0</v>
-      </c>
-      <c r="D73" s="2">
-        <f>D83/1000</f>
-        <v>0</v>
-      </c>
-      <c r="E73" s="2">
-        <f>E83/1000</f>
-        <v>69000</v>
-      </c>
-      <c r="F73" s="2">
-        <f>F83/1000</f>
-        <v>0</v>
-      </c>
-      <c r="G73" s="2">
-        <f>G83/1000</f>
-        <v>0</v>
-      </c>
-      <c r="H73" s="2">
-        <f>H83/1000</f>
-        <v>0</v>
-      </c>
-      <c r="I73" s="2">
-        <f>I83/1000</f>
-        <v>0</v>
-      </c>
-      <c r="J73" s="2">
-        <f>J83/1000</f>
-        <v>74000</v>
-      </c>
-      <c r="K73" s="2">
-        <f>K83/1000</f>
+      <c r="L73" s="2">
+        <f t="shared" si="14"/>
         <v>52000</v>
       </c>
-      <c r="L73" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="M73" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="N73" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AO73" s="2"/>
-      <c r="AP73" s="2">
-        <f t="shared" ref="AP73:BO73" si="8">L83/1000</f>
-        <v>0</v>
-      </c>
-      <c r="AQ73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AR73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AS73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AT73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AU73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AV73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AW73" s="2">
-        <f t="shared" si="8"/>
+      <c r="M73" s="2">
+        <f t="shared" ref="M73:AL73" si="15">L83/1000</f>
+        <v>0</v>
+      </c>
+      <c r="N73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="P73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="Q73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="R73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="S73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="T73" s="2">
+        <f t="shared" si="15"/>
         <v>8000</v>
       </c>
-      <c r="AX73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AY73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AZ73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BA73" s="2">
-        <f t="shared" si="8"/>
+      <c r="U73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="V73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="X73" s="2">
+        <f t="shared" si="15"/>
         <v>77100</v>
       </c>
-      <c r="BB73" s="2">
-        <f t="shared" si="8"/>
+      <c r="Y73" s="2">
+        <f t="shared" si="15"/>
         <v>90000</v>
       </c>
-      <c r="BC73" s="2">
-        <f t="shared" si="8"/>
+      <c r="Z73" s="2">
+        <f t="shared" si="15"/>
         <v>5700</v>
       </c>
-      <c r="BD73" s="2">
-        <f t="shared" si="8"/>
+      <c r="AA73" s="2">
+        <f t="shared" si="15"/>
         <v>600</v>
       </c>
-      <c r="BE73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BF73" s="2">
-        <f t="shared" si="8"/>
+      <c r="AB73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AC73" s="2">
+        <f t="shared" si="15"/>
         <v>12900</v>
       </c>
-      <c r="BG73" s="2">
-        <f t="shared" si="8"/>
+      <c r="AD73" s="2">
+        <f t="shared" si="15"/>
         <v>14000</v>
       </c>
-      <c r="BH73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BI73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BJ73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BK73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BL73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BM73" s="2">
-        <f t="shared" si="8"/>
+      <c r="AE73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AF73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AG73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AH73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AI73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="2">
+        <f t="shared" si="15"/>
         <v>90000</v>
       </c>
-      <c r="BN73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="BO73" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
+      <c r="AK73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AL73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AM73" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN73" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
     <row r="77" s="3" customFormat="1" spans="4:37">
-      <c r="D77" s="13">
-        <v>0</v>
-      </c>
-      <c r="E77" s="13">
+      <c r="D77" s="14">
+        <v>0</v>
+      </c>
+      <c r="E77" s="14">
         <v>310000</v>
       </c>
-      <c r="F77" s="13">
+      <c r="F77" s="14">
         <v>6200000</v>
       </c>
-      <c r="G77" s="13">
-        <v>0</v>
-      </c>
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
-      <c r="J77" s="13">
+      <c r="G77" s="14">
+        <v>0</v>
+      </c>
+      <c r="H77" s="14"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="14">
         <v>250000</v>
       </c>
-      <c r="K77" s="13">
+      <c r="K77" s="14">
         <v>2000000</v>
       </c>
-      <c r="L77" s="13"/>
-      <c r="M77" s="13">
-        <v>0</v>
-      </c>
-      <c r="N77" s="13">
-        <v>0</v>
-      </c>
-      <c r="O77" s="13">
-        <v>0</v>
-      </c>
-      <c r="P77" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="13"/>
-      <c r="R77" s="13"/>
-      <c r="S77" s="13">
-        <v>0</v>
-      </c>
-      <c r="T77" s="13"/>
-      <c r="U77" s="13"/>
-      <c r="V77" s="13">
-        <v>0</v>
-      </c>
-      <c r="W77" s="13">
+      <c r="L77" s="14"/>
+      <c r="M77" s="14">
+        <v>0</v>
+      </c>
+      <c r="N77" s="14">
+        <v>0</v>
+      </c>
+      <c r="O77" s="14">
+        <v>0</v>
+      </c>
+      <c r="P77" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="14"/>
+      <c r="R77" s="14"/>
+      <c r="S77" s="14">
+        <v>0</v>
+      </c>
+      <c r="T77" s="14"/>
+      <c r="U77" s="14"/>
+      <c r="V77" s="14">
+        <v>0</v>
+      </c>
+      <c r="W77" s="14">
         <v>12250000</v>
       </c>
-      <c r="X77" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y77" s="13">
+      <c r="X77" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="14">
         <v>1930000</v>
       </c>
-      <c r="Z77" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB77" s="13">
+      <c r="Z77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="14">
         <v>3300000</v>
       </c>
-      <c r="AC77" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD77" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE77" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF77" s="13">
+      <c r="AC77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="14">
         <v>60000</v>
       </c>
-      <c r="AG77" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH77" s="13"/>
-      <c r="AI77" s="13">
-        <v>0</v>
-      </c>
-      <c r="AJ77" s="13">
-        <v>0</v>
-      </c>
-      <c r="AK77" s="13">
+      <c r="AG77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="14"/>
+      <c r="AI77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="14">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="78" s="3" customFormat="1" spans="4:37">
-      <c r="D78" s="13">
-        <v>0</v>
-      </c>
-      <c r="E78" s="13">
-        <v>0</v>
-      </c>
-      <c r="F78" s="13">
+      <c r="D78" s="14">
+        <v>0</v>
+      </c>
+      <c r="E78" s="14">
+        <v>0</v>
+      </c>
+      <c r="F78" s="14">
         <v>21000000</v>
       </c>
-      <c r="G78" s="13">
-        <v>0</v>
-      </c>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-      <c r="J78" s="13">
+      <c r="G78" s="14">
+        <v>0</v>
+      </c>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="14">
         <v>16000000</v>
       </c>
-      <c r="K78" s="13">
+      <c r="K78" s="14">
         <v>2100000</v>
       </c>
-      <c r="L78" s="13"/>
-      <c r="M78" s="13">
-        <v>0</v>
-      </c>
-      <c r="N78" s="13">
-        <v>0</v>
-      </c>
-      <c r="O78" s="13">
-        <v>0</v>
-      </c>
-      <c r="P78" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="13"/>
-      <c r="R78" s="13"/>
-      <c r="S78" s="13">
-        <v>0</v>
-      </c>
-      <c r="T78" s="13"/>
-      <c r="U78" s="13"/>
-      <c r="V78" s="13">
-        <v>0</v>
-      </c>
-      <c r="W78" s="13">
+      <c r="L78" s="14"/>
+      <c r="M78" s="14">
+        <v>0</v>
+      </c>
+      <c r="N78" s="14">
+        <v>0</v>
+      </c>
+      <c r="O78" s="14">
+        <v>0</v>
+      </c>
+      <c r="P78" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="14"/>
+      <c r="R78" s="14"/>
+      <c r="S78" s="14">
+        <v>0</v>
+      </c>
+      <c r="T78" s="14"/>
+      <c r="U78" s="14"/>
+      <c r="V78" s="14">
+        <v>0</v>
+      </c>
+      <c r="W78" s="14">
         <v>16000000</v>
       </c>
-      <c r="X78" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="13">
+      <c r="X78" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="14">
         <v>2570000</v>
       </c>
-      <c r="Z78" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB78" s="13">
+      <c r="Z78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="14">
         <v>52900000</v>
       </c>
-      <c r="AC78" s="13">
+      <c r="AC78" s="14">
         <v>7500000</v>
       </c>
-      <c r="AD78" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE78" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF78" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG78" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH78" s="13"/>
-      <c r="AI78" s="13">
-        <v>0</v>
-      </c>
-      <c r="AJ78" s="13">
-        <v>0</v>
-      </c>
-      <c r="AK78" s="13">
+      <c r="AD78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="14"/>
+      <c r="AI78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="14">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="79" s="3" customFormat="1" spans="4:37">
-      <c r="D79" s="13">
+      <c r="D79" s="14">
         <v>13000</v>
       </c>
-      <c r="E79" s="13">
+      <c r="E79" s="14">
         <v>4100000</v>
       </c>
-      <c r="F79" s="13">
+      <c r="F79" s="14">
         <v>1500000</v>
       </c>
-      <c r="G79" s="13">
-        <v>0</v>
-      </c>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
-      <c r="J79" s="13">
-        <v>0</v>
-      </c>
-      <c r="K79" s="13">
+      <c r="G79" s="14">
+        <v>0</v>
+      </c>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14">
+        <v>0</v>
+      </c>
+      <c r="K79" s="14">
         <v>140000</v>
       </c>
-      <c r="L79" s="13"/>
-      <c r="M79" s="13">
-        <v>0</v>
-      </c>
-      <c r="N79" s="13">
-        <v>0</v>
-      </c>
-      <c r="O79" s="13">
-        <v>0</v>
-      </c>
-      <c r="P79" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="13"/>
-      <c r="R79" s="13"/>
-      <c r="S79" s="13">
-        <v>0</v>
-      </c>
-      <c r="T79" s="13"/>
-      <c r="U79" s="13"/>
-      <c r="V79" s="13">
-        <v>0</v>
-      </c>
-      <c r="W79" s="13">
+      <c r="L79" s="14"/>
+      <c r="M79" s="14">
+        <v>0</v>
+      </c>
+      <c r="N79" s="14">
+        <v>0</v>
+      </c>
+      <c r="O79" s="14">
+        <v>0</v>
+      </c>
+      <c r="P79" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="14"/>
+      <c r="R79" s="14"/>
+      <c r="S79" s="14">
+        <v>0</v>
+      </c>
+      <c r="T79" s="14"/>
+      <c r="U79" s="14"/>
+      <c r="V79" s="14">
+        <v>0</v>
+      </c>
+      <c r="W79" s="14">
         <v>500000</v>
       </c>
-      <c r="X79" s="13">
+      <c r="X79" s="14">
         <v>36000</v>
       </c>
-      <c r="Y79" s="13">
+      <c r="Y79" s="14">
         <v>289000</v>
       </c>
-      <c r="Z79" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA79" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB79" s="13">
+      <c r="Z79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="14">
         <v>1517000</v>
       </c>
-      <c r="AC79" s="13">
+      <c r="AC79" s="14">
         <v>250000</v>
       </c>
-      <c r="AD79" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE79" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF79" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG79" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH79" s="13"/>
-      <c r="AI79" s="13">
+      <c r="AD79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="14"/>
+      <c r="AI79" s="14">
         <v>36000</v>
       </c>
-      <c r="AJ79" s="13">
-        <v>0</v>
-      </c>
-      <c r="AK79" s="13">
+      <c r="AJ79" s="14">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="80" s="3" customFormat="1" spans="4:37">
-      <c r="D80" s="13">
-        <v>0</v>
-      </c>
-      <c r="E80" s="13">
+      <c r="D80" s="14">
+        <v>0</v>
+      </c>
+      <c r="E80" s="14">
         <v>74000000</v>
       </c>
-      <c r="F80" s="13">
+      <c r="F80" s="14">
         <v>270000000</v>
       </c>
-      <c r="G80" s="13">
-        <v>0</v>
-      </c>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
-      <c r="J80" s="13">
+      <c r="G80" s="14">
+        <v>0</v>
+      </c>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="14">
         <v>270000000</v>
       </c>
-      <c r="K80" s="13">
+      <c r="K80" s="14">
         <v>280000000</v>
       </c>
-      <c r="L80" s="13"/>
-      <c r="M80" s="13">
-        <v>0</v>
-      </c>
-      <c r="N80" s="13">
-        <v>0</v>
-      </c>
-      <c r="O80" s="13">
-        <v>0</v>
-      </c>
-      <c r="P80" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="13"/>
-      <c r="R80" s="13"/>
-      <c r="S80" s="13">
+      <c r="L80" s="14"/>
+      <c r="M80" s="14">
+        <v>0</v>
+      </c>
+      <c r="N80" s="14">
+        <v>0</v>
+      </c>
+      <c r="O80" s="14">
+        <v>0</v>
+      </c>
+      <c r="P80" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="14"/>
+      <c r="R80" s="14"/>
+      <c r="S80" s="14">
         <v>34000000</v>
       </c>
-      <c r="T80" s="13"/>
-      <c r="U80" s="13"/>
-      <c r="V80" s="13">
-        <v>0</v>
-      </c>
-      <c r="W80" s="13">
+      <c r="T80" s="14"/>
+      <c r="U80" s="14"/>
+      <c r="V80" s="14">
+        <v>0</v>
+      </c>
+      <c r="W80" s="14">
         <v>275000000</v>
       </c>
-      <c r="X80" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y80" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z80" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="13">
+      <c r="X80" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="14">
         <v>5000000</v>
       </c>
-      <c r="AC80" s="13">
-        <v>0</v>
-      </c>
-      <c r="AD80" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE80" s="13">
+      <c r="AC80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="14">
         <v>640000000</v>
       </c>
-      <c r="AF80" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG80" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH80" s="13"/>
-      <c r="AI80" s="13">
-        <v>0</v>
-      </c>
-      <c r="AJ80" s="13">
-        <v>0</v>
-      </c>
-      <c r="AK80" s="13">
+      <c r="AF80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="14"/>
+      <c r="AI80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="14">
+        <v>0</v>
+      </c>
+      <c r="AK80" s="14">
         <v>140000000</v>
       </c>
     </row>
     <row r="81" s="3" customFormat="1" spans="4:37">
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
-      <c r="H81" s="13"/>
-      <c r="I81" s="13"/>
-      <c r="J81" s="13"/>
-      <c r="K81" s="13"/>
-      <c r="L81" s="13"/>
-      <c r="M81" s="13"/>
-      <c r="N81" s="13"/>
-      <c r="O81" s="13"/>
-      <c r="P81" s="13"/>
-      <c r="Q81" s="13"/>
-      <c r="R81" s="13"/>
-      <c r="S81" s="13"/>
-      <c r="T81" s="13"/>
-      <c r="U81" s="13"/>
-      <c r="V81" s="13"/>
-      <c r="W81" s="13"/>
-      <c r="X81" s="13"/>
-      <c r="Y81" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z81" s="13"/>
-      <c r="AA81" s="13"/>
-      <c r="AB81" s="13"/>
-      <c r="AC81" s="13"/>
-      <c r="AD81" s="13"/>
-      <c r="AE81" s="13"/>
-      <c r="AF81" s="13"/>
-      <c r="AG81" s="13"/>
-      <c r="AH81" s="13"/>
-      <c r="AI81" s="13"/>
-      <c r="AJ81" s="13"/>
-      <c r="AK81" s="13"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="14"/>
+      <c r="L81" s="14"/>
+      <c r="M81" s="14"/>
+      <c r="N81" s="14"/>
+      <c r="O81" s="14"/>
+      <c r="P81" s="14"/>
+      <c r="Q81" s="14"/>
+      <c r="R81" s="14"/>
+      <c r="S81" s="14"/>
+      <c r="T81" s="14"/>
+      <c r="U81" s="14"/>
+      <c r="V81" s="14"/>
+      <c r="W81" s="14"/>
+      <c r="X81" s="14"/>
+      <c r="Y81" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="14"/>
+      <c r="AA81" s="14"/>
+      <c r="AB81" s="14"/>
+      <c r="AC81" s="14"/>
+      <c r="AD81" s="14"/>
+      <c r="AE81" s="14"/>
+      <c r="AF81" s="14"/>
+      <c r="AG81" s="14"/>
+      <c r="AH81" s="14"/>
+      <c r="AI81" s="14"/>
+      <c r="AJ81" s="14"/>
+      <c r="AK81" s="14"/>
     </row>
     <row r="82" s="3" customFormat="1" spans="4:37">
-      <c r="D82" s="13">
-        <v>0</v>
-      </c>
-      <c r="E82" s="13">
+      <c r="D82" s="14">
+        <v>0</v>
+      </c>
+      <c r="E82" s="14">
         <v>50000000</v>
       </c>
-      <c r="F82" s="13">
+      <c r="F82" s="14">
         <v>97000000</v>
       </c>
-      <c r="G82" s="13">
-        <v>0</v>
-      </c>
-      <c r="H82" s="13"/>
-      <c r="I82" s="13"/>
-      <c r="J82" s="13">
-        <v>0</v>
-      </c>
-      <c r="K82" s="13">
+      <c r="G82" s="14">
+        <v>0</v>
+      </c>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14">
+        <v>0</v>
+      </c>
+      <c r="K82" s="14">
         <v>27000000</v>
       </c>
-      <c r="L82" s="13"/>
-      <c r="M82" s="13">
-        <v>0</v>
-      </c>
-      <c r="N82" s="13">
-        <v>0</v>
-      </c>
-      <c r="O82" s="13">
-        <v>0</v>
-      </c>
-      <c r="P82" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="13"/>
-      <c r="R82" s="13"/>
-      <c r="S82" s="13">
-        <v>0</v>
-      </c>
-      <c r="T82" s="13"/>
-      <c r="U82" s="13"/>
-      <c r="V82" s="13">
-        <v>0</v>
-      </c>
-      <c r="W82" s="13">
+      <c r="L82" s="14"/>
+      <c r="M82" s="14">
+        <v>0</v>
+      </c>
+      <c r="N82" s="14">
+        <v>0</v>
+      </c>
+      <c r="O82" s="14">
+        <v>0</v>
+      </c>
+      <c r="P82" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="14"/>
+      <c r="R82" s="14"/>
+      <c r="S82" s="14">
+        <v>0</v>
+      </c>
+      <c r="T82" s="14"/>
+      <c r="U82" s="14"/>
+      <c r="V82" s="14">
+        <v>0</v>
+      </c>
+      <c r="W82" s="14">
         <v>324000000</v>
       </c>
-      <c r="X82" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y82" s="13">
+      <c r="X82" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="14">
         <v>51600000</v>
       </c>
-      <c r="Z82" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA82" s="13">
+      <c r="Z82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="14">
         <v>30000000</v>
       </c>
-      <c r="AB82" s="13">
+      <c r="AB82" s="14">
         <v>244000000</v>
       </c>
-      <c r="AC82" s="13">
+      <c r="AC82" s="14">
         <v>62000000</v>
       </c>
-      <c r="AD82" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE82" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF82" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG82" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH82" s="13"/>
-      <c r="AI82" s="13">
-        <v>0</v>
-      </c>
-      <c r="AJ82" s="13">
-        <v>0</v>
-      </c>
-      <c r="AK82" s="13">
+      <c r="AD82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="14"/>
+      <c r="AI82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AJ82" s="14">
+        <v>0</v>
+      </c>
+      <c r="AK82" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="83" s="3" customFormat="1" spans="4:37">
-      <c r="D83" s="13">
-        <v>0</v>
-      </c>
-      <c r="E83" s="13">
+      <c r="D83" s="14">
+        <v>0</v>
+      </c>
+      <c r="E83" s="14">
         <v>69000000</v>
       </c>
-      <c r="F83" s="13">
-        <v>0</v>
-      </c>
-      <c r="G83" s="13">
-        <v>0</v>
-      </c>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="13">
+      <c r="F83" s="14">
+        <v>0</v>
+      </c>
+      <c r="G83" s="14">
+        <v>0</v>
+      </c>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="14">
         <v>74000000</v>
       </c>
-      <c r="K83" s="13">
+      <c r="K83" s="14">
         <v>52000000</v>
       </c>
-      <c r="L83" s="13"/>
-      <c r="M83" s="13">
-        <v>0</v>
-      </c>
-      <c r="N83" s="13">
-        <v>0</v>
-      </c>
-      <c r="O83" s="13">
-        <v>0</v>
-      </c>
-      <c r="P83" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="13"/>
-      <c r="R83" s="13"/>
-      <c r="S83" s="13">
+      <c r="L83" s="14"/>
+      <c r="M83" s="14">
+        <v>0</v>
+      </c>
+      <c r="N83" s="14">
+        <v>0</v>
+      </c>
+      <c r="O83" s="14">
+        <v>0</v>
+      </c>
+      <c r="P83" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="14"/>
+      <c r="R83" s="14"/>
+      <c r="S83" s="14">
         <v>8000000</v>
       </c>
-      <c r="T83" s="13"/>
-      <c r="U83" s="13"/>
-      <c r="V83" s="13">
-        <v>0</v>
-      </c>
-      <c r="W83" s="13">
+      <c r="T83" s="14"/>
+      <c r="U83" s="14"/>
+      <c r="V83" s="14">
+        <v>0</v>
+      </c>
+      <c r="W83" s="14">
         <v>77100000</v>
       </c>
-      <c r="X83" s="13">
+      <c r="X83" s="14">
         <v>90000000</v>
       </c>
-      <c r="Y83" s="13">
+      <c r="Y83" s="14">
         <v>5700000</v>
       </c>
-      <c r="Z83" s="13">
+      <c r="Z83" s="14">
         <v>600000</v>
       </c>
-      <c r="AA83" s="13">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="13">
+      <c r="AA83" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="14">
         <v>12900000</v>
       </c>
-      <c r="AC83" s="13">
+      <c r="AC83" s="14">
         <v>14000000</v>
       </c>
-      <c r="AD83" s="13">
-        <v>0</v>
-      </c>
-      <c r="AE83" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="13">
-        <v>0</v>
-      </c>
-      <c r="AG83" s="13">
-        <v>0</v>
-      </c>
-      <c r="AH83" s="13"/>
-      <c r="AI83" s="13">
+      <c r="AD83" s="14">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="14">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="14">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="14">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="14"/>
+      <c r="AI83" s="14">
         <v>90000000</v>
       </c>
-      <c r="AJ83" s="13">
-        <v>0</v>
-      </c>
-      <c r="AK83" s="13">
+      <c r="AJ83" s="14">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="14">
         <v>0</v>
       </c>
     </row>
@@ -13718,7 +13748,7 @@
     </row>
     <row r="88" spans="2:26">
       <c r="B88" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -13774,470 +13804,470 @@
     </row>
     <row r="90" s="4" customFormat="1"/>
     <row r="91" s="4" customFormat="1" spans="5:12">
-      <c r="E91" s="14"/>
-      <c r="H91" s="15"/>
-      <c r="I91" s="15"/>
-      <c r="J91" s="15"/>
-      <c r="K91" s="15"/>
-      <c r="L91" s="15"/>
+      <c r="E91" s="15"/>
+      <c r="H91" s="16"/>
+      <c r="I91" s="16"/>
+      <c r="J91" s="16"/>
+      <c r="K91" s="16"/>
+      <c r="L91" s="16"/>
     </row>
     <row r="92" s="4" customFormat="1" spans="4:12">
-      <c r="D92" s="15"/>
-      <c r="H92" s="15"/>
-      <c r="I92" s="15"/>
-      <c r="J92" s="15"/>
-      <c r="K92" s="15"/>
-      <c r="L92" s="15"/>
+      <c r="D92" s="16"/>
+      <c r="H92" s="16"/>
+      <c r="I92" s="16"/>
+      <c r="J92" s="16"/>
+      <c r="K92" s="16"/>
+      <c r="L92" s="16"/>
     </row>
     <row r="93" s="4" customFormat="1" spans="3:12">
-      <c r="C93" s="15"/>
-      <c r="D93" s="15"/>
-      <c r="F93" s="15"/>
-      <c r="H93" s="15"/>
-      <c r="I93" s="15"/>
-      <c r="J93" s="15"/>
-      <c r="K93" s="15"/>
-      <c r="L93" s="15"/>
+      <c r="C93" s="16"/>
+      <c r="D93" s="16"/>
+      <c r="F93" s="16"/>
+      <c r="H93" s="16"/>
+      <c r="I93" s="16"/>
+      <c r="J93" s="16"/>
+      <c r="K93" s="16"/>
+      <c r="L93" s="16"/>
     </row>
     <row r="94" s="4" customFormat="1" spans="3:12">
-      <c r="C94" s="15"/>
-      <c r="D94" s="15"/>
-      <c r="H94" s="15"/>
-      <c r="I94" s="15"/>
-      <c r="J94" s="15"/>
-      <c r="K94" s="15"/>
-      <c r="L94" s="15"/>
+      <c r="C94" s="16"/>
+      <c r="D94" s="16"/>
+      <c r="H94" s="16"/>
+      <c r="I94" s="16"/>
+      <c r="J94" s="16"/>
+      <c r="K94" s="16"/>
+      <c r="L94" s="16"/>
     </row>
     <row r="95" s="4" customFormat="1" spans="3:12">
-      <c r="C95" s="15"/>
-      <c r="D95" s="15"/>
-      <c r="F95" s="15"/>
-      <c r="H95" s="15"/>
-      <c r="I95" s="15"/>
-      <c r="J95" s="15"/>
-      <c r="K95" s="15"/>
-      <c r="L95" s="15"/>
+      <c r="C95" s="16"/>
+      <c r="D95" s="16"/>
+      <c r="F95" s="16"/>
+      <c r="H95" s="16"/>
+      <c r="I95" s="16"/>
+      <c r="J95" s="16"/>
+      <c r="K95" s="16"/>
+      <c r="L95" s="16"/>
     </row>
     <row r="96" s="4" customFormat="1" spans="3:12">
-      <c r="C96" s="15"/>
-      <c r="D96" s="15"/>
-      <c r="H96" s="15"/>
-      <c r="I96" s="15"/>
-      <c r="J96" s="15"/>
-      <c r="K96" s="15"/>
-      <c r="L96" s="15"/>
+      <c r="C96" s="16"/>
+      <c r="D96" s="16"/>
+      <c r="H96" s="16"/>
+      <c r="I96" s="16"/>
+      <c r="J96" s="16"/>
+      <c r="K96" s="16"/>
+      <c r="L96" s="16"/>
     </row>
     <row r="97" s="4" customFormat="1" spans="3:12">
-      <c r="C97" s="15"/>
-      <c r="D97" s="15"/>
-      <c r="F97" s="15"/>
-      <c r="H97" s="15"/>
-      <c r="I97" s="15"/>
-      <c r="J97" s="15"/>
-      <c r="K97" s="15"/>
-      <c r="L97" s="15"/>
+      <c r="C97" s="16"/>
+      <c r="D97" s="16"/>
+      <c r="F97" s="16"/>
+      <c r="H97" s="16"/>
+      <c r="I97" s="16"/>
+      <c r="J97" s="16"/>
+      <c r="K97" s="16"/>
+      <c r="L97" s="16"/>
     </row>
     <row r="98" s="4" customFormat="1" spans="3:12">
-      <c r="C98" s="15"/>
-      <c r="D98" s="15"/>
-      <c r="H98" s="15"/>
-      <c r="I98" s="15"/>
-      <c r="J98" s="15"/>
-      <c r="K98" s="15"/>
-      <c r="L98" s="15"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="16"/>
+      <c r="H98" s="16"/>
+      <c r="I98" s="16"/>
+      <c r="J98" s="16"/>
+      <c r="K98" s="16"/>
+      <c r="L98" s="16"/>
     </row>
     <row r="99" s="4" customFormat="1" spans="3:6">
-      <c r="C99" s="15"/>
-      <c r="F99" s="15"/>
+      <c r="C99" s="16"/>
+      <c r="F99" s="16"/>
     </row>
     <row r="100" s="4" customFormat="1" spans="3:4">
-      <c r="C100" s="15"/>
-      <c r="D100" s="15"/>
+      <c r="C100" s="16"/>
+      <c r="D100" s="16"/>
     </row>
     <row r="101" s="4" customFormat="1" spans="3:7">
-      <c r="C101" s="15"/>
-      <c r="D101" s="16"/>
-      <c r="E101" s="16"/>
-      <c r="F101" s="16"/>
-      <c r="G101" s="16"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="17"/>
+      <c r="E101" s="17"/>
+      <c r="F101" s="17"/>
+      <c r="G101" s="17"/>
     </row>
     <row r="102" s="4" customFormat="1" spans="3:4">
-      <c r="C102" s="15"/>
+      <c r="C102" s="16"/>
       <c r="D102" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="103" s="4" customFormat="1" spans="3:7">
-      <c r="C103" s="15" t="s">
+      <c r="C103" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D103" s="16" t="s">
+      <c r="D103" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E103" s="16" t="s">
+      <c r="E103" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="F103" s="16" t="s">
+      <c r="F103" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="G103" s="16" t="s">
+      <c r="G103" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="104" s="4" customFormat="1" spans="3:7">
-      <c r="C104" s="15" t="s">
+      <c r="C104" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D104" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="E104" s="16">
+      <c r="D104" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="E104" s="17">
         <v>7.11384396954065</v>
       </c>
-      <c r="F104" s="17">
+      <c r="F104" s="18">
         <v>5.40179852616065</v>
       </c>
-      <c r="G104" s="17">
+      <c r="G104" s="18">
         <v>8.85540744288872</v>
       </c>
     </row>
     <row r="105" s="4" customFormat="1" spans="3:7">
-      <c r="C105" s="15" t="s">
+      <c r="C105" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D105" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="E105" s="16">
+      <c r="D105" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="E105" s="17">
         <v>7.11384396954065</v>
       </c>
-      <c r="F105" s="17">
+      <c r="F105" s="18">
         <v>5.40179852616065</v>
       </c>
-      <c r="G105" s="17">
+      <c r="G105" s="18">
         <v>8.85540744288872</v>
       </c>
     </row>
     <row r="106" spans="3:7">
-      <c r="C106" s="15" t="s">
+      <c r="C106" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D106" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="E106" s="16">
+      <c r="D106" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="E106" s="17">
         <v>7.62975445836404</v>
       </c>
-      <c r="F106" s="17">
+      <c r="F106" s="18">
         <v>5.79354797347089</v>
       </c>
-      <c r="G106" s="17">
+      <c r="G106" s="18">
         <v>9.49761967575534</v>
       </c>
     </row>
     <row r="107" spans="3:7">
-      <c r="C107" s="15" t="s">
+      <c r="C107" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D107" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="E107" s="16">
+      <c r="D107" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="E107" s="17">
         <v>7.47097081798084</v>
       </c>
-      <c r="F107" s="17">
+      <c r="F107" s="18">
         <v>5.67297781871776</v>
       </c>
-      <c r="G107" s="17">
+      <c r="G107" s="18">
         <v>9.29996366985999</v>
       </c>
     </row>
     <row r="108" spans="3:7">
-      <c r="C108" s="15" t="s">
+      <c r="C108" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D108" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="E108" s="16">
+      <c r="D108" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E108" s="17">
         <v>7.51643520019651</v>
       </c>
-      <c r="F108" s="17">
+      <c r="F108" s="18">
         <v>5.70750058953574</v>
       </c>
-      <c r="G108" s="17">
+      <c r="G108" s="18">
         <v>9.35655836403832</v>
       </c>
     </row>
     <row r="109" spans="3:7">
-      <c r="C109" s="15" t="s">
+      <c r="C109" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D109" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="E109" s="16">
+      <c r="D109" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E109" s="17">
         <v>7.55036263817244</v>
       </c>
-      <c r="F109" s="17">
+      <c r="F109" s="18">
         <v>5.73326293294031</v>
       </c>
-      <c r="G109" s="17">
+      <c r="G109" s="18">
         <v>9.39879167280766</v>
       </c>
     </row>
     <row r="110" spans="3:7">
-      <c r="C110" s="15" t="s">
+      <c r="C110" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D110" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E110" s="16">
+      <c r="D110" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="E110" s="17">
         <v>7.62975445836404</v>
       </c>
-      <c r="F110" s="17">
+      <c r="F110" s="18">
         <v>5.79354797347089</v>
       </c>
-      <c r="G110" s="17">
+      <c r="G110" s="18">
         <v>9.49761967575534</v>
       </c>
     </row>
     <row r="111" spans="3:7">
-      <c r="C111" s="15" t="s">
+      <c r="C111" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D111" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="E111" s="16">
+      <c r="D111" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="E111" s="17">
         <v>4.18384600835176</v>
       </c>
-      <c r="F111" s="17">
+      <c r="F111" s="18">
         <v>3.17694532056006</v>
       </c>
-      <c r="G111" s="17">
+      <c r="G111" s="18">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="112" spans="3:7">
-      <c r="C112" s="15" t="s">
+      <c r="C112" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D112" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E112" s="16">
+      <c r="D112" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="E112" s="17">
         <v>4.18384600835176</v>
       </c>
-      <c r="F112" s="17">
+      <c r="F112" s="18">
         <v>3.17694532056006</v>
       </c>
-      <c r="G112" s="17">
+      <c r="G112" s="18">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="113" spans="3:7">
-      <c r="C113" s="15" t="s">
+      <c r="C113" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D113" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="E113" s="16">
+      <c r="D113" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="E113" s="17">
         <v>4.18384600835176</v>
       </c>
-      <c r="F113" s="17">
+      <c r="F113" s="18">
         <v>3.17694532056006</v>
       </c>
-      <c r="G113" s="17">
+      <c r="G113" s="18">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="114" spans="3:7">
-      <c r="C114" s="15" t="s">
+      <c r="C114" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D114" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="E114" s="16">
+      <c r="D114" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E114" s="17">
         <v>4.18384600835176</v>
       </c>
-      <c r="F114" s="17">
+      <c r="F114" s="18">
         <v>3.17694532056006</v>
       </c>
-      <c r="G114" s="17">
+      <c r="G114" s="18">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="115" spans="3:7">
-      <c r="C115" s="15" t="s">
+      <c r="C115" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D115" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="E115" s="16">
+      <c r="D115" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="E115" s="17">
         <v>4.18384600835176</v>
       </c>
-      <c r="F115" s="17">
+      <c r="F115" s="18">
         <v>3.17694532056006</v>
       </c>
-      <c r="G115" s="17">
+      <c r="G115" s="18">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="116" spans="3:7">
-      <c r="C116" s="15" t="s">
+      <c r="C116" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D116" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="E116" s="16">
+      <c r="D116" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="E116" s="17">
         <v>4.18384600835176</v>
       </c>
-      <c r="F116" s="17">
+      <c r="F116" s="18">
         <v>3.17694532056006</v>
       </c>
-      <c r="G116" s="17">
+      <c r="G116" s="18">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="117" spans="3:7">
-      <c r="C117" s="15" t="s">
+      <c r="C117" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D117" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="E117" s="16">
+      <c r="D117" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="E117" s="17">
         <v>4.18384600835176</v>
       </c>
-      <c r="F117" s="17">
+      <c r="F117" s="18">
         <v>3.17694532056006</v>
       </c>
-      <c r="G117" s="17">
+      <c r="G117" s="18">
         <v>5.20810707442889</v>
       </c>
     </row>
     <row r="118" spans="3:7">
-      <c r="C118" s="15" t="s">
+      <c r="C118" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D118" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="E118" s="16">
+      <c r="D118" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="E118" s="17">
         <v>3.56556266273643</v>
       </c>
-      <c r="F118" s="17">
+      <c r="F118" s="18">
         <v>2.70746042741341</v>
       </c>
-      <c r="G118" s="17">
+      <c r="G118" s="18">
         <v>4.4384597641857</v>
       </c>
     </row>
     <row r="119" spans="3:7">
-      <c r="C119" s="15" t="s">
+      <c r="C119" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D119" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="E119" s="16">
+      <c r="D119" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="E119" s="17">
         <v>3.60087708179809</v>
       </c>
-      <c r="F119" s="17">
+      <c r="F119" s="18">
         <v>2.73427597641857</v>
       </c>
-      <c r="G119" s="17">
+      <c r="G119" s="18">
         <v>4.48241960206338</v>
       </c>
     </row>
     <row r="120" spans="3:7">
-      <c r="C120" s="15" t="s">
+      <c r="C120" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D120" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="E120" s="16">
+      <c r="D120" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="E120" s="17">
         <v>3.56556266273643</v>
       </c>
-      <c r="F120" s="17">
+      <c r="F120" s="18">
         <v>2.70746042741341</v>
       </c>
-      <c r="G120" s="17">
+      <c r="G120" s="18">
         <v>4.4384597641857</v>
       </c>
     </row>
     <row r="121" spans="3:7">
-      <c r="C121" s="15" t="s">
+      <c r="C121" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D121" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="E121" s="16">
+      <c r="D121" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="E121" s="17">
         <v>3.56645369688037</v>
       </c>
-      <c r="F121" s="17">
+      <c r="F121" s="18">
         <v>2.70813706705969</v>
       </c>
-      <c r="G121" s="17">
+      <c r="G121" s="18">
         <v>4.43956890198968</v>
       </c>
     </row>
     <row r="122" spans="3:7">
-      <c r="C122" s="15" t="s">
+      <c r="C122" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D122" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="E122" s="16">
+      <c r="D122" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="E122" s="17">
         <v>3.56585961680177</v>
       </c>
-      <c r="F122" s="17">
+      <c r="F122" s="18">
         <v>2.70768592483419</v>
       </c>
-      <c r="G122" s="17">
+      <c r="G122" s="18">
         <v>4.43882940309506</v>
       </c>
     </row>
     <row r="123" spans="3:7">
-      <c r="C123" s="15" t="s">
+      <c r="C123" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D123" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="E123" s="16">
+      <c r="D123" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="E123" s="17">
         <v>3.56556266273643</v>
       </c>
-      <c r="F123" s="17">
+      <c r="F123" s="18">
         <v>2.70746042741341</v>
       </c>
-      <c r="G123" s="17">
+      <c r="G123" s="18">
         <v>4.4384597641857</v>
       </c>
     </row>
     <row r="124" spans="3:7">
-      <c r="C124" s="15" t="s">
+      <c r="C124" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="D124" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="E124" s="16">
+      <c r="D124" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="E124" s="17">
         <v>3.56496890198968</v>
       </c>
-      <c r="F124" s="17">
+      <c r="F124" s="18">
         <v>2.70700957995578</v>
       </c>
-      <c r="G124" s="17">
+      <c r="G124" s="18">
         <v>4.43772063375092</v>
       </c>
     </row>
@@ -14263,7 +14293,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -14275,25 +14305,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -14415,28 +14445,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -14544,7 +14574,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -14555,31 +14585,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -14687,7 +14717,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -14698,31 +14728,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -14830,7 +14860,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -14844,28 +14874,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -14973,7 +15003,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -14984,31 +15014,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -15116,7 +15146,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -15130,28 +15160,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -15259,7 +15289,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -15270,31 +15300,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -15402,7 +15432,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -15413,31 +15443,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -15545,7 +15575,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -15556,31 +15586,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -15688,7 +15718,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -15699,31 +15729,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -15831,7 +15861,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -15842,31 +15872,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -15974,7 +16004,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -15985,31 +16015,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -16117,7 +16147,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -16128,31 +16158,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -16260,7 +16290,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -16271,31 +16301,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G15" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -16403,7 +16433,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -16414,31 +16444,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -16546,7 +16576,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -16560,28 +16590,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G17" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H17" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I17" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J17" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K17" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -16689,7 +16719,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -16700,31 +16730,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -16832,7 +16862,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -16843,31 +16873,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -16975,7 +17005,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -16986,31 +17016,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -17118,7 +17148,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -17132,28 +17162,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G21" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -17261,7 +17291,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -17272,31 +17302,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G22" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -17404,7 +17434,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -17415,31 +17445,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -17547,7 +17577,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -17561,28 +17591,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -17690,7 +17720,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -17701,31 +17731,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G25" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -17833,7 +17863,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -17844,31 +17874,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G26" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -17976,7 +18006,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -17987,31 +18017,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -18119,7 +18149,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -18130,31 +18160,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -18262,7 +18292,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -18276,28 +18306,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -18405,7 +18435,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -18416,31 +18446,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
+        <v>176</v>
+      </c>
+      <c r="D30" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" t="s">
         <v>174</v>
       </c>
-      <c r="D30" t="s">
-        <v>171</v>
-      </c>
-      <c r="E30" t="s">
-        <v>171</v>
-      </c>
-      <c r="F30" t="s">
-        <v>172</v>
-      </c>
       <c r="G30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -18548,7 +18578,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -18559,31 +18589,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" t="s">
+        <v>173</v>
+      </c>
+      <c r="E31" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" t="s">
+        <v>174</v>
+      </c>
+      <c r="G31" t="s">
         <v>175</v>
       </c>
-      <c r="D31" t="s">
-        <v>171</v>
-      </c>
-      <c r="E31" t="s">
-        <v>171</v>
-      </c>
-      <c r="F31" t="s">
-        <v>172</v>
-      </c>
-      <c r="G31" t="s">
-        <v>173</v>
-      </c>
       <c r="H31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -18691,7 +18721,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -18705,28 +18735,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G32" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -18834,7 +18864,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -18845,31 +18875,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -18977,7 +19007,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -18991,28 +19021,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G34" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -19120,7 +19150,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -19131,31 +19161,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G35" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -19263,7 +19293,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -19274,31 +19304,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -19406,7 +19436,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -19417,31 +19447,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G37" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -19549,7 +19579,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -19560,31 +19590,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G38" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -19692,7 +19722,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -19703,31 +19733,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -19835,7 +19865,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -19846,31 +19876,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G40" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -19978,7 +20008,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -19989,31 +20019,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G41" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -20121,7 +20151,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -20132,31 +20162,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D42" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E42" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G42" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H42" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I42" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J42" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K42" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -20264,7 +20294,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -20275,31 +20305,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D43" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E43" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G43" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H43" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I43" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J43" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K43" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -20407,7 +20437,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -20421,28 +20451,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -20550,7 +20580,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -20561,31 +20591,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G45" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -20693,7 +20723,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -20704,31 +20734,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F46" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G46" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -20836,7 +20866,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -20847,31 +20877,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D47" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E47" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G47" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H47" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I47" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J47" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K47" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -20979,7 +21009,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -20993,28 +21023,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F48" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G48" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -21122,7 +21152,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -21133,31 +21163,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G49" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -21265,7 +21295,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -21276,31 +21306,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -21408,7 +21438,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -21422,28 +21452,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G51" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -21551,7 +21581,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -21562,31 +21592,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G52" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -21694,7 +21724,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -21705,31 +21735,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G53" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -21837,7 +21867,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -21848,31 +21878,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G54" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -21980,7 +22010,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -21991,31 +22021,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D55" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E55" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G55" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H55" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I55" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J55" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K55" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -22123,7 +22153,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="196">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -459,9 +459,6 @@
   </si>
   <si>
     <t>AuxStoIN</t>
-  </si>
-  <si>
-    <t>5. what does that mean list every country??</t>
   </si>
   <si>
     <t>timeslice</t>
@@ -856,29 +853,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1243,7 +1234,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1267,16 +1258,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1285,85 +1276,85 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1383,14 +1374,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="5" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
@@ -8458,7 +8449,9 @@
     <col min="2" max="2" width="21.3727272727273" customWidth="1"/>
     <col min="3" max="3" width="12.7272727272727" customWidth="1"/>
     <col min="4" max="5" width="22.0909090909091" customWidth="1"/>
-    <col min="6" max="9" width="7.13636363636364" customWidth="1"/>
+    <col min="6" max="6" width="7.13636363636364" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="9" width="7.13636363636364" customWidth="1"/>
     <col min="10" max="10" width="10.6363636363636" customWidth="1"/>
     <col min="11" max="11" width="11.2818181818182" customWidth="1"/>
     <col min="12" max="12" width="15.5454545454545" customWidth="1"/>
@@ -11818,9 +11811,7 @@
       <c r="Z63" s="9"/>
     </row>
     <row r="64" s="1" customFormat="1" ht="28" spans="1:1">
-      <c r="A64" s="11" t="s">
-        <v>130</v>
-      </c>
+      <c r="A64" s="11"/>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:53">
       <c r="A65" s="2"/>
@@ -11880,7 +11871,7 @@
     </row>
     <row r="66" s="2" customFormat="1" spans="1:40">
       <c r="A66" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>56</v>
@@ -11970,7 +11961,7 @@
         <v>29</v>
       </c>
       <c r="AE66" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AF66" s="2" t="s">
         <v>31</v>
@@ -12002,10 +11993,10 @@
     </row>
     <row r="67" s="2" customFormat="1" ht="14.5" spans="1:40">
       <c r="A67" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>83</v>
@@ -12149,18 +12140,18 @@
         <v>0</v>
       </c>
       <c r="AM67" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN67" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="AN67" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" ht="14.5" spans="1:40">
       <c r="A68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>83</v>
@@ -12305,18 +12296,18 @@
         <v>0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AN68" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" ht="14.5" spans="1:40">
       <c r="A69" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B69" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>83</v>
@@ -12461,18 +12452,18 @@
         <v>0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AN69" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" ht="14.5" spans="1:40">
       <c r="A70" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B70" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>83</v>
@@ -12617,18 +12608,18 @@
         <v>140000</v>
       </c>
       <c r="AM70" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AN70" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" ht="14.5" spans="1:40">
       <c r="A71" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B71" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>83</v>
@@ -12773,18 +12764,18 @@
         <v>0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AN71" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" ht="14.5" spans="1:40">
       <c r="A72" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B72" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>83</v>
@@ -12929,18 +12920,18 @@
         <v>0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AN72" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="14.5" spans="1:40">
       <c r="A73" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>83</v>
@@ -13085,16 +13076,16 @@
         <v>0</v>
       </c>
       <c r="AM73" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AN73" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
@@ -13748,7 +13739,7 @@
     </row>
     <row r="88" spans="2:26">
       <c r="B88" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -13919,7 +13910,7 @@
         <v>118</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E104" s="17">
         <v>7.11384396954065</v>
@@ -13936,7 +13927,7 @@
         <v>118</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E105" s="17">
         <v>7.11384396954065</v>
@@ -13953,7 +13944,7 @@
         <v>118</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E106" s="17">
         <v>7.62975445836404</v>
@@ -13970,7 +13961,7 @@
         <v>118</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E107" s="17">
         <v>7.47097081798084</v>
@@ -13987,7 +13978,7 @@
         <v>118</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E108" s="17">
         <v>7.51643520019651</v>
@@ -14004,7 +13995,7 @@
         <v>118</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E109" s="17">
         <v>7.55036263817244</v>
@@ -14021,7 +14012,7 @@
         <v>118</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E110" s="17">
         <v>7.62975445836404</v>
@@ -14038,7 +14029,7 @@
         <v>118</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E111" s="17">
         <v>4.18384600835176</v>
@@ -14055,7 +14046,7 @@
         <v>118</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E112" s="17">
         <v>4.18384600835176</v>
@@ -14072,7 +14063,7 @@
         <v>118</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E113" s="17">
         <v>4.18384600835176</v>
@@ -14089,7 +14080,7 @@
         <v>118</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E114" s="17">
         <v>4.18384600835176</v>
@@ -14106,7 +14097,7 @@
         <v>118</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E115" s="17">
         <v>4.18384600835176</v>
@@ -14123,7 +14114,7 @@
         <v>118</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E116" s="17">
         <v>4.18384600835176</v>
@@ -14140,7 +14131,7 @@
         <v>118</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E117" s="17">
         <v>4.18384600835176</v>
@@ -14157,7 +14148,7 @@
         <v>118</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E118" s="17">
         <v>3.56556266273643</v>
@@ -14174,7 +14165,7 @@
         <v>118</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E119" s="17">
         <v>3.60087708179809</v>
@@ -14191,7 +14182,7 @@
         <v>118</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E120" s="17">
         <v>3.56556266273643</v>
@@ -14208,7 +14199,7 @@
         <v>118</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E121" s="17">
         <v>3.56645369688037</v>
@@ -14225,7 +14216,7 @@
         <v>118</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E122" s="17">
         <v>3.56585961680177</v>
@@ -14242,7 +14233,7 @@
         <v>118</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E123" s="17">
         <v>3.56556266273643</v>
@@ -14259,7 +14250,7 @@
         <v>118</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E124" s="17">
         <v>3.56496890198968</v>
@@ -14293,7 +14284,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -14305,25 +14296,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>167</v>
-      </c>
-      <c r="F1" t="s">
-        <v>168</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1" t="s">
         <v>169</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>170</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>171</v>
-      </c>
-      <c r="K1" t="s">
-        <v>172</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -14445,28 +14436,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G2" t="s">
         <v>174</v>
       </c>
-      <c r="G2" t="s">
-        <v>175</v>
-      </c>
       <c r="H2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -14574,7 +14565,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -14585,31 +14576,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G3" t="s">
         <v>174</v>
       </c>
-      <c r="G3" t="s">
-        <v>175</v>
-      </c>
       <c r="H3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -14717,7 +14708,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -14728,31 +14719,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G4" t="s">
         <v>174</v>
       </c>
-      <c r="G4" t="s">
-        <v>175</v>
-      </c>
       <c r="H4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -14860,7 +14851,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -14874,28 +14865,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G5" t="s">
         <v>174</v>
       </c>
-      <c r="G5" t="s">
-        <v>175</v>
-      </c>
       <c r="H5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -15003,7 +14994,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -15014,31 +15005,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" t="s">
         <v>174</v>
       </c>
-      <c r="G6" t="s">
-        <v>175</v>
-      </c>
       <c r="H6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -15146,7 +15137,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -15160,28 +15151,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" t="s">
         <v>174</v>
       </c>
-      <c r="G7" t="s">
-        <v>175</v>
-      </c>
       <c r="H7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -15289,7 +15280,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -15300,31 +15291,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" t="s">
         <v>174</v>
       </c>
-      <c r="G8" t="s">
-        <v>175</v>
-      </c>
       <c r="H8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -15432,7 +15423,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -15443,31 +15434,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" t="s">
         <v>174</v>
       </c>
-      <c r="G9" t="s">
-        <v>175</v>
-      </c>
       <c r="H9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -15575,7 +15566,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -15586,31 +15577,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" t="s">
         <v>174</v>
       </c>
-      <c r="G10" t="s">
-        <v>175</v>
-      </c>
       <c r="H10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -15718,7 +15709,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -15729,31 +15720,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G11" t="s">
         <v>174</v>
       </c>
-      <c r="G11" t="s">
-        <v>175</v>
-      </c>
       <c r="H11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -15861,7 +15852,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -15872,31 +15863,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" t="s">
         <v>174</v>
       </c>
-      <c r="G12" t="s">
-        <v>175</v>
-      </c>
       <c r="H12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -16004,7 +15995,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -16015,31 +16006,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" t="s">
         <v>174</v>
       </c>
-      <c r="G13" t="s">
-        <v>175</v>
-      </c>
       <c r="H13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -16147,7 +16138,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -16158,31 +16149,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G14" t="s">
         <v>174</v>
       </c>
-      <c r="G14" t="s">
-        <v>175</v>
-      </c>
       <c r="H14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -16290,7 +16281,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -16301,31 +16292,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
+        <v>173</v>
+      </c>
+      <c r="G15" t="s">
         <v>174</v>
       </c>
-      <c r="G15" t="s">
-        <v>175</v>
-      </c>
       <c r="H15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -16433,7 +16424,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -16444,31 +16435,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
+        <v>173</v>
+      </c>
+      <c r="G16" t="s">
         <v>174</v>
       </c>
-      <c r="G16" t="s">
-        <v>175</v>
-      </c>
       <c r="H16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -16576,7 +16567,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -16590,28 +16581,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
+        <v>173</v>
+      </c>
+      <c r="G17" t="s">
         <v>174</v>
       </c>
-      <c r="G17" t="s">
-        <v>175</v>
-      </c>
       <c r="H17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -16719,7 +16710,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -16730,31 +16721,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
+        <v>173</v>
+      </c>
+      <c r="G18" t="s">
         <v>174</v>
       </c>
-      <c r="G18" t="s">
-        <v>175</v>
-      </c>
       <c r="H18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -16862,7 +16853,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -16873,31 +16864,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
+        <v>173</v>
+      </c>
+      <c r="G19" t="s">
         <v>174</v>
       </c>
-      <c r="G19" t="s">
-        <v>175</v>
-      </c>
       <c r="H19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -17005,7 +16996,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -17016,31 +17007,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
+        <v>173</v>
+      </c>
+      <c r="G20" t="s">
         <v>174</v>
       </c>
-      <c r="G20" t="s">
-        <v>175</v>
-      </c>
       <c r="H20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -17148,7 +17139,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -17162,28 +17153,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G21" t="s">
         <v>174</v>
       </c>
-      <c r="G21" t="s">
-        <v>175</v>
-      </c>
       <c r="H21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -17291,7 +17282,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -17302,31 +17293,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" t="s">
         <v>174</v>
       </c>
-      <c r="G22" t="s">
-        <v>175</v>
-      </c>
       <c r="H22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -17434,7 +17425,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -17445,31 +17436,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" t="s">
         <v>174</v>
       </c>
-      <c r="G23" t="s">
-        <v>175</v>
-      </c>
       <c r="H23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -17577,7 +17568,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -17591,28 +17582,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
+        <v>173</v>
+      </c>
+      <c r="G24" t="s">
         <v>174</v>
       </c>
-      <c r="G24" t="s">
-        <v>175</v>
-      </c>
       <c r="H24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -17720,7 +17711,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -17731,31 +17722,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
+        <v>173</v>
+      </c>
+      <c r="G25" t="s">
         <v>174</v>
       </c>
-      <c r="G25" t="s">
-        <v>175</v>
-      </c>
       <c r="H25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -17863,7 +17854,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -17874,31 +17865,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
+        <v>173</v>
+      </c>
+      <c r="G26" t="s">
         <v>174</v>
       </c>
-      <c r="G26" t="s">
-        <v>175</v>
-      </c>
       <c r="H26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -18006,7 +17997,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -18017,31 +18008,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
+        <v>173</v>
+      </c>
+      <c r="G27" t="s">
         <v>174</v>
       </c>
-      <c r="G27" t="s">
-        <v>175</v>
-      </c>
       <c r="H27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -18149,7 +18140,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -18160,31 +18151,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
+        <v>173</v>
+      </c>
+      <c r="G28" t="s">
         <v>174</v>
       </c>
-      <c r="G28" t="s">
-        <v>175</v>
-      </c>
       <c r="H28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -18292,7 +18283,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -18306,28 +18297,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
+        <v>172</v>
+      </c>
+      <c r="E29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29" t="s">
         <v>173</v>
       </c>
-      <c r="E29" t="s">
-        <v>173</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>174</v>
       </c>
-      <c r="G29" t="s">
-        <v>175</v>
-      </c>
       <c r="H29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -18435,7 +18426,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -18446,31 +18437,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D30" t="s">
+        <v>172</v>
+      </c>
+      <c r="E30" t="s">
+        <v>172</v>
+      </c>
+      <c r="F30" t="s">
         <v>173</v>
       </c>
-      <c r="E30" t="s">
-        <v>173</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>174</v>
       </c>
-      <c r="G30" t="s">
-        <v>175</v>
-      </c>
       <c r="H30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -18578,7 +18569,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -18589,31 +18580,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D31" t="s">
+        <v>172</v>
+      </c>
+      <c r="E31" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31" t="s">
         <v>173</v>
       </c>
-      <c r="E31" t="s">
-        <v>173</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>174</v>
       </c>
-      <c r="G31" t="s">
-        <v>175</v>
-      </c>
       <c r="H31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -18721,7 +18712,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -18735,28 +18726,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
+        <v>172</v>
+      </c>
+      <c r="E32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F32" t="s">
         <v>173</v>
       </c>
-      <c r="E32" t="s">
-        <v>173</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>174</v>
       </c>
-      <c r="G32" t="s">
-        <v>175</v>
-      </c>
       <c r="H32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -18864,7 +18855,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -18875,31 +18866,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" t="s">
         <v>173</v>
       </c>
-      <c r="E33" t="s">
-        <v>173</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>174</v>
       </c>
-      <c r="G33" t="s">
-        <v>175</v>
-      </c>
       <c r="H33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -19007,7 +18998,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -19021,28 +19012,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F34" t="s">
         <v>173</v>
       </c>
-      <c r="E34" t="s">
-        <v>173</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>174</v>
       </c>
-      <c r="G34" t="s">
-        <v>175</v>
-      </c>
       <c r="H34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -19150,7 +19141,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -19161,31 +19152,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D35" t="s">
+        <v>172</v>
+      </c>
+      <c r="E35" t="s">
+        <v>172</v>
+      </c>
+      <c r="F35" t="s">
         <v>173</v>
       </c>
-      <c r="E35" t="s">
-        <v>173</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>174</v>
       </c>
-      <c r="G35" t="s">
-        <v>175</v>
-      </c>
       <c r="H35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -19293,7 +19284,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -19304,31 +19295,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D36" t="s">
+        <v>172</v>
+      </c>
+      <c r="E36" t="s">
+        <v>172</v>
+      </c>
+      <c r="F36" t="s">
         <v>173</v>
       </c>
-      <c r="E36" t="s">
-        <v>173</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>174</v>
       </c>
-      <c r="G36" t="s">
-        <v>175</v>
-      </c>
       <c r="H36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -19436,7 +19427,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -19447,31 +19438,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D37" t="s">
+        <v>172</v>
+      </c>
+      <c r="E37" t="s">
+        <v>172</v>
+      </c>
+      <c r="F37" t="s">
         <v>173</v>
       </c>
-      <c r="E37" t="s">
-        <v>173</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>174</v>
       </c>
-      <c r="G37" t="s">
-        <v>175</v>
-      </c>
       <c r="H37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -19579,7 +19570,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -19590,31 +19581,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s">
+        <v>172</v>
+      </c>
+      <c r="E38" t="s">
+        <v>172</v>
+      </c>
+      <c r="F38" t="s">
         <v>173</v>
       </c>
-      <c r="E38" t="s">
-        <v>173</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>174</v>
       </c>
-      <c r="G38" t="s">
-        <v>175</v>
-      </c>
       <c r="H38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -19722,7 +19713,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -19733,31 +19724,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D39" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" t="s">
         <v>173</v>
       </c>
-      <c r="E39" t="s">
-        <v>173</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>174</v>
       </c>
-      <c r="G39" t="s">
-        <v>175</v>
-      </c>
       <c r="H39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -19865,7 +19856,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -19876,31 +19867,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D40" t="s">
+        <v>172</v>
+      </c>
+      <c r="E40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" t="s">
         <v>173</v>
       </c>
-      <c r="E40" t="s">
-        <v>173</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>174</v>
       </c>
-      <c r="G40" t="s">
-        <v>175</v>
-      </c>
       <c r="H40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -20008,7 +19999,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -20019,31 +20010,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D41" t="s">
+        <v>172</v>
+      </c>
+      <c r="E41" t="s">
+        <v>172</v>
+      </c>
+      <c r="F41" t="s">
         <v>173</v>
       </c>
-      <c r="E41" t="s">
-        <v>173</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>174</v>
       </c>
-      <c r="G41" t="s">
-        <v>175</v>
-      </c>
       <c r="H41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -20151,7 +20142,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -20162,31 +20153,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D42" t="s">
+        <v>172</v>
+      </c>
+      <c r="E42" t="s">
+        <v>172</v>
+      </c>
+      <c r="F42" t="s">
         <v>173</v>
       </c>
-      <c r="E42" t="s">
-        <v>173</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>174</v>
       </c>
-      <c r="G42" t="s">
-        <v>175</v>
-      </c>
       <c r="H42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -20294,7 +20285,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -20305,31 +20296,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D43" t="s">
+        <v>172</v>
+      </c>
+      <c r="E43" t="s">
+        <v>172</v>
+      </c>
+      <c r="F43" t="s">
         <v>173</v>
       </c>
-      <c r="E43" t="s">
-        <v>173</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>174</v>
       </c>
-      <c r="G43" t="s">
-        <v>175</v>
-      </c>
       <c r="H43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -20437,7 +20428,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -20451,28 +20442,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
+        <v>172</v>
+      </c>
+      <c r="E44" t="s">
+        <v>172</v>
+      </c>
+      <c r="F44" t="s">
         <v>173</v>
       </c>
-      <c r="E44" t="s">
-        <v>173</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>174</v>
       </c>
-      <c r="G44" t="s">
-        <v>175</v>
-      </c>
       <c r="H44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -20580,7 +20571,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -20591,31 +20582,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D45" t="s">
+        <v>172</v>
+      </c>
+      <c r="E45" t="s">
+        <v>172</v>
+      </c>
+      <c r="F45" t="s">
         <v>173</v>
       </c>
-      <c r="E45" t="s">
-        <v>173</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>174</v>
       </c>
-      <c r="G45" t="s">
-        <v>175</v>
-      </c>
       <c r="H45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -20723,7 +20714,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -20734,31 +20725,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D46" t="s">
+        <v>172</v>
+      </c>
+      <c r="E46" t="s">
+        <v>172</v>
+      </c>
+      <c r="F46" t="s">
         <v>173</v>
       </c>
-      <c r="E46" t="s">
-        <v>173</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>174</v>
       </c>
-      <c r="G46" t="s">
-        <v>175</v>
-      </c>
       <c r="H46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -20866,7 +20857,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -20877,31 +20868,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D47" t="s">
+        <v>172</v>
+      </c>
+      <c r="E47" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" t="s">
         <v>173</v>
       </c>
-      <c r="E47" t="s">
-        <v>173</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>174</v>
       </c>
-      <c r="G47" t="s">
-        <v>175</v>
-      </c>
       <c r="H47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -21009,7 +21000,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -21023,28 +21014,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
+        <v>172</v>
+      </c>
+      <c r="E48" t="s">
+        <v>172</v>
+      </c>
+      <c r="F48" t="s">
         <v>173</v>
       </c>
-      <c r="E48" t="s">
-        <v>173</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>174</v>
       </c>
-      <c r="G48" t="s">
-        <v>175</v>
-      </c>
       <c r="H48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -21152,7 +21143,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -21163,31 +21154,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D49" t="s">
+        <v>172</v>
+      </c>
+      <c r="E49" t="s">
+        <v>172</v>
+      </c>
+      <c r="F49" t="s">
         <v>173</v>
       </c>
-      <c r="E49" t="s">
-        <v>173</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>174</v>
       </c>
-      <c r="G49" t="s">
-        <v>175</v>
-      </c>
       <c r="H49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -21295,7 +21286,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -21306,31 +21297,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E50" t="s">
+        <v>172</v>
+      </c>
+      <c r="F50" t="s">
         <v>173</v>
       </c>
-      <c r="E50" t="s">
-        <v>173</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>174</v>
       </c>
-      <c r="G50" t="s">
-        <v>175</v>
-      </c>
       <c r="H50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -21438,7 +21429,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -21452,28 +21443,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
+        <v>172</v>
+      </c>
+      <c r="E51" t="s">
+        <v>172</v>
+      </c>
+      <c r="F51" t="s">
         <v>173</v>
       </c>
-      <c r="E51" t="s">
-        <v>173</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>174</v>
       </c>
-      <c r="G51" t="s">
-        <v>175</v>
-      </c>
       <c r="H51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -21581,7 +21572,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -21592,31 +21583,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D52" t="s">
+        <v>172</v>
+      </c>
+      <c r="E52" t="s">
+        <v>172</v>
+      </c>
+      <c r="F52" t="s">
         <v>173</v>
       </c>
-      <c r="E52" t="s">
-        <v>173</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>174</v>
       </c>
-      <c r="G52" t="s">
-        <v>175</v>
-      </c>
       <c r="H52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -21724,7 +21715,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -21735,31 +21726,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D53" t="s">
+        <v>172</v>
+      </c>
+      <c r="E53" t="s">
+        <v>172</v>
+      </c>
+      <c r="F53" t="s">
         <v>173</v>
       </c>
-      <c r="E53" t="s">
-        <v>173</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>174</v>
       </c>
-      <c r="G53" t="s">
-        <v>175</v>
-      </c>
       <c r="H53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -21867,7 +21858,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -21878,31 +21869,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D54" t="s">
+        <v>172</v>
+      </c>
+      <c r="E54" t="s">
+        <v>172</v>
+      </c>
+      <c r="F54" t="s">
         <v>173</v>
       </c>
-      <c r="E54" t="s">
-        <v>173</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>174</v>
       </c>
-      <c r="G54" t="s">
-        <v>175</v>
-      </c>
       <c r="H54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -22010,7 +22001,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -22021,31 +22012,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D55" t="s">
+        <v>172</v>
+      </c>
+      <c r="E55" t="s">
+        <v>172</v>
+      </c>
+      <c r="F55" t="s">
         <v>173</v>
       </c>
-      <c r="E55" t="s">
-        <v>173</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>174</v>
       </c>
-      <c r="G55" t="s">
-        <v>175</v>
-      </c>
       <c r="H55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -22153,7 +22144,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" updateLinks="never"/>
   <bookViews>
-    <workbookView windowWidth="18340" windowHeight="8720" activeTab="1"/>
+    <workbookView windowWidth="18350" windowHeight="8710" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TechSelection" sheetId="21" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="196">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -853,12 +853,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -13882,13 +13882,21 @@
       <c r="F101" s="17"/>
       <c r="G101" s="17"/>
     </row>
-    <row r="102" s="4" customFormat="1" spans="3:4">
+    <row r="102" s="4" customFormat="1" spans="3:20">
       <c r="C102" s="16"/>
       <c r="D102" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="103" s="4" customFormat="1" spans="3:7">
+      <c r="K102" s="16"/>
+      <c r="L102" t="s">
+        <v>73</v>
+      </c>
+      <c r="S102" s="16"/>
+      <c r="T102" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="103" s="4" customFormat="1" spans="3:23">
       <c r="C103" s="16" t="s">
         <v>56</v>
       </c>
@@ -13904,8 +13912,44 @@
       <c r="G103" s="17" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="104" s="4" customFormat="1" spans="3:7">
+      <c r="J103" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K103" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L103" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="M103" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="N103" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="O103" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="R103" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S103" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="T103" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="U103" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="V103" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="W103" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" s="4" customFormat="1" spans="3:23">
       <c r="C104" s="16" t="s">
         <v>118</v>
       </c>
@@ -13921,8 +13965,47 @@
       <c r="G104" s="18">
         <v>8.85540744288872</v>
       </c>
-    </row>
-    <row r="105" s="4" customFormat="1" spans="3:7">
+      <c r="J104" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K104" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L104" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="M104" s="17">
+        <f>E104*0.313</f>
+        <v>2.22663316246622</v>
+      </c>
+      <c r="N104" s="17">
+        <f>F104*0.313</f>
+        <v>1.69076293868828</v>
+      </c>
+      <c r="O104" s="17">
+        <f>G104*0.313</f>
+        <v>2.77174252962417</v>
+      </c>
+      <c r="R104" s="4">
+        <v>0</v>
+      </c>
+      <c r="S104" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T104" s="17">
+        <v>5</v>
+      </c>
+      <c r="U104" s="17">
+        <v>5</v>
+      </c>
+      <c r="V104" s="17">
+        <v>5</v>
+      </c>
+      <c r="W104" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" s="4" customFormat="1" spans="3:23">
       <c r="C105" s="16" t="s">
         <v>118</v>
       </c>
@@ -13938,8 +14021,47 @@
       <c r="G105" s="18">
         <v>8.85540744288872</v>
       </c>
-    </row>
-    <row r="106" spans="3:7">
+      <c r="J105" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K105" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L105" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="M105" s="17">
+        <f t="shared" ref="M105:M124" si="16">E105*0.313</f>
+        <v>2.22663316246622</v>
+      </c>
+      <c r="N105" s="17">
+        <f t="shared" ref="N105:N124" si="17">F105*0.313</f>
+        <v>1.69076293868828</v>
+      </c>
+      <c r="O105" s="17">
+        <f t="shared" ref="O105:O124" si="18">G105*0.313</f>
+        <v>2.77174252962417</v>
+      </c>
+      <c r="R105" s="4">
+        <v>0</v>
+      </c>
+      <c r="S105" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T105" s="17">
+        <v>5</v>
+      </c>
+      <c r="U105" s="17">
+        <v>5</v>
+      </c>
+      <c r="V105" s="17">
+        <v>5</v>
+      </c>
+      <c r="W105" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="3:23">
       <c r="C106" s="16" t="s">
         <v>118</v>
       </c>
@@ -13955,8 +14077,47 @@
       <c r="G106" s="18">
         <v>9.49761967575534</v>
       </c>
-    </row>
-    <row r="107" spans="3:7">
+      <c r="J106" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K106" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L106" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M106" s="17">
+        <f t="shared" si="16"/>
+        <v>2.38811314546794</v>
+      </c>
+      <c r="N106" s="17">
+        <f t="shared" si="17"/>
+        <v>1.81338051569639</v>
+      </c>
+      <c r="O106" s="17">
+        <f t="shared" si="18"/>
+        <v>2.97275495851142</v>
+      </c>
+      <c r="R106" s="4">
+        <v>0</v>
+      </c>
+      <c r="S106" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T106" s="17">
+        <v>5</v>
+      </c>
+      <c r="U106" s="17">
+        <v>5</v>
+      </c>
+      <c r="V106" s="17">
+        <v>5</v>
+      </c>
+      <c r="W106" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="3:23">
       <c r="C107" s="16" t="s">
         <v>118</v>
       </c>
@@ -13972,8 +14133,47 @@
       <c r="G107" s="18">
         <v>9.29996366985999</v>
       </c>
-    </row>
-    <row r="108" spans="3:7">
+      <c r="J107" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K107" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L107" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="M107" s="17">
+        <f t="shared" si="16"/>
+        <v>2.338413866028</v>
+      </c>
+      <c r="N107" s="17">
+        <f t="shared" si="17"/>
+        <v>1.77564205725866</v>
+      </c>
+      <c r="O107" s="17">
+        <f t="shared" si="18"/>
+        <v>2.91088862866618</v>
+      </c>
+      <c r="R107" s="4">
+        <v>0</v>
+      </c>
+      <c r="S107" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T107" s="17">
+        <v>5</v>
+      </c>
+      <c r="U107" s="17">
+        <v>5</v>
+      </c>
+      <c r="V107" s="17">
+        <v>5</v>
+      </c>
+      <c r="W107" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="3:23">
       <c r="C108" s="16" t="s">
         <v>118</v>
       </c>
@@ -13989,8 +14189,47 @@
       <c r="G108" s="18">
         <v>9.35655836403832</v>
       </c>
-    </row>
-    <row r="109" spans="3:7">
+      <c r="J108" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K108" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L108" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="M108" s="17">
+        <f t="shared" si="16"/>
+        <v>2.35264421766151</v>
+      </c>
+      <c r="N108" s="17">
+        <f t="shared" si="17"/>
+        <v>1.78644768452469</v>
+      </c>
+      <c r="O108" s="17">
+        <f t="shared" si="18"/>
+        <v>2.92860276794399</v>
+      </c>
+      <c r="R108" s="4">
+        <v>0</v>
+      </c>
+      <c r="S108" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T108" s="17">
+        <v>5</v>
+      </c>
+      <c r="U108" s="17">
+        <v>5</v>
+      </c>
+      <c r="V108" s="17">
+        <v>5</v>
+      </c>
+      <c r="W108" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="3:23">
       <c r="C109" s="16" t="s">
         <v>118</v>
       </c>
@@ -14006,8 +14245,47 @@
       <c r="G109" s="18">
         <v>9.39879167280766</v>
       </c>
-    </row>
-    <row r="110" spans="3:7">
+      <c r="J109" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K109" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L109" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="M109" s="17">
+        <f t="shared" si="16"/>
+        <v>2.36326350574797</v>
+      </c>
+      <c r="N109" s="17">
+        <f t="shared" si="17"/>
+        <v>1.79451129801032</v>
+      </c>
+      <c r="O109" s="17">
+        <f t="shared" si="18"/>
+        <v>2.9418217935888</v>
+      </c>
+      <c r="R109" s="4">
+        <v>0</v>
+      </c>
+      <c r="S109" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T109" s="17">
+        <v>5</v>
+      </c>
+      <c r="U109" s="17">
+        <v>5</v>
+      </c>
+      <c r="V109" s="17">
+        <v>5</v>
+      </c>
+      <c r="W109" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="3:23">
       <c r="C110" s="16" t="s">
         <v>118</v>
       </c>
@@ -14023,8 +14301,47 @@
       <c r="G110" s="18">
         <v>9.49761967575534</v>
       </c>
-    </row>
-    <row r="111" spans="3:7">
+      <c r="J110" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K110" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L110" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="M110" s="17">
+        <f t="shared" si="16"/>
+        <v>2.38811314546794</v>
+      </c>
+      <c r="N110" s="17">
+        <f t="shared" si="17"/>
+        <v>1.81338051569639</v>
+      </c>
+      <c r="O110" s="17">
+        <f t="shared" si="18"/>
+        <v>2.97275495851142</v>
+      </c>
+      <c r="R110" s="4">
+        <v>0</v>
+      </c>
+      <c r="S110" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T110" s="17">
+        <v>5</v>
+      </c>
+      <c r="U110" s="17">
+        <v>5</v>
+      </c>
+      <c r="V110" s="17">
+        <v>5</v>
+      </c>
+      <c r="W110" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="3:23">
       <c r="C111" s="16" t="s">
         <v>118</v>
       </c>
@@ -14040,8 +14357,47 @@
       <c r="G111" s="18">
         <v>5.20810707442889</v>
       </c>
-    </row>
-    <row r="112" spans="3:7">
+      <c r="J111" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K111" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L111" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="M111" s="17">
+        <f t="shared" si="16"/>
+        <v>1.3095438006141</v>
+      </c>
+      <c r="N111" s="17">
+        <f t="shared" si="17"/>
+        <v>0.994383885335299</v>
+      </c>
+      <c r="O111" s="17">
+        <f t="shared" si="18"/>
+        <v>1.63013751429624</v>
+      </c>
+      <c r="R111" s="4">
+        <v>0</v>
+      </c>
+      <c r="S111" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T111" s="17">
+        <v>5</v>
+      </c>
+      <c r="U111" s="17">
+        <v>5</v>
+      </c>
+      <c r="V111" s="17">
+        <v>5</v>
+      </c>
+      <c r="W111" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="3:23">
       <c r="C112" s="16" t="s">
         <v>118</v>
       </c>
@@ -14057,8 +14413,47 @@
       <c r="G112" s="18">
         <v>5.20810707442889</v>
       </c>
-    </row>
-    <row r="113" spans="3:7">
+      <c r="J112" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K112" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L112" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="M112" s="17">
+        <f t="shared" si="16"/>
+        <v>1.3095438006141</v>
+      </c>
+      <c r="N112" s="17">
+        <f t="shared" si="17"/>
+        <v>0.994383885335299</v>
+      </c>
+      <c r="O112" s="17">
+        <f t="shared" si="18"/>
+        <v>1.63013751429624</v>
+      </c>
+      <c r="R112" s="4">
+        <v>0</v>
+      </c>
+      <c r="S112" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T112" s="17">
+        <v>5</v>
+      </c>
+      <c r="U112" s="17">
+        <v>5</v>
+      </c>
+      <c r="V112" s="17">
+        <v>5</v>
+      </c>
+      <c r="W112" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="3:23">
       <c r="C113" s="16" t="s">
         <v>118</v>
       </c>
@@ -14074,8 +14469,47 @@
       <c r="G113" s="18">
         <v>5.20810707442889</v>
       </c>
-    </row>
-    <row r="114" spans="3:7">
+      <c r="J113" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K113" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L113" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="M113" s="17">
+        <f t="shared" si="16"/>
+        <v>1.3095438006141</v>
+      </c>
+      <c r="N113" s="17">
+        <f t="shared" si="17"/>
+        <v>0.994383885335299</v>
+      </c>
+      <c r="O113" s="17">
+        <f t="shared" si="18"/>
+        <v>1.63013751429624</v>
+      </c>
+      <c r="R113" s="4">
+        <v>0</v>
+      </c>
+      <c r="S113" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T113" s="17">
+        <v>5</v>
+      </c>
+      <c r="U113" s="17">
+        <v>5</v>
+      </c>
+      <c r="V113" s="17">
+        <v>5</v>
+      </c>
+      <c r="W113" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="3:23">
       <c r="C114" s="16" t="s">
         <v>118</v>
       </c>
@@ -14091,8 +14525,47 @@
       <c r="G114" s="18">
         <v>5.20810707442889</v>
       </c>
-    </row>
-    <row r="115" spans="3:7">
+      <c r="J114" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K114" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L114" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="M114" s="17">
+        <f t="shared" si="16"/>
+        <v>1.3095438006141</v>
+      </c>
+      <c r="N114" s="17">
+        <f t="shared" si="17"/>
+        <v>0.994383885335299</v>
+      </c>
+      <c r="O114" s="17">
+        <f t="shared" si="18"/>
+        <v>1.63013751429624</v>
+      </c>
+      <c r="R114" s="4">
+        <v>0</v>
+      </c>
+      <c r="S114" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T114" s="17">
+        <v>5</v>
+      </c>
+      <c r="U114" s="17">
+        <v>5</v>
+      </c>
+      <c r="V114" s="17">
+        <v>5</v>
+      </c>
+      <c r="W114" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="3:23">
       <c r="C115" s="16" t="s">
         <v>118</v>
       </c>
@@ -14108,8 +14581,47 @@
       <c r="G115" s="18">
         <v>5.20810707442889</v>
       </c>
-    </row>
-    <row r="116" spans="3:7">
+      <c r="J115" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K115" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L115" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="M115" s="17">
+        <f t="shared" si="16"/>
+        <v>1.3095438006141</v>
+      </c>
+      <c r="N115" s="17">
+        <f t="shared" si="17"/>
+        <v>0.994383885335299</v>
+      </c>
+      <c r="O115" s="17">
+        <f t="shared" si="18"/>
+        <v>1.63013751429624</v>
+      </c>
+      <c r="R115" s="4">
+        <v>0</v>
+      </c>
+      <c r="S115" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T115" s="17">
+        <v>5</v>
+      </c>
+      <c r="U115" s="17">
+        <v>5</v>
+      </c>
+      <c r="V115" s="17">
+        <v>5</v>
+      </c>
+      <c r="W115" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="3:23">
       <c r="C116" s="16" t="s">
         <v>118</v>
       </c>
@@ -14125,8 +14637,47 @@
       <c r="G116" s="18">
         <v>5.20810707442889</v>
       </c>
-    </row>
-    <row r="117" spans="3:7">
+      <c r="J116" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K116" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L116" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="M116" s="17">
+        <f t="shared" si="16"/>
+        <v>1.3095438006141</v>
+      </c>
+      <c r="N116" s="17">
+        <f t="shared" si="17"/>
+        <v>0.994383885335299</v>
+      </c>
+      <c r="O116" s="17">
+        <f t="shared" si="18"/>
+        <v>1.63013751429624</v>
+      </c>
+      <c r="R116" s="4">
+        <v>0</v>
+      </c>
+      <c r="S116" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T116" s="17">
+        <v>5</v>
+      </c>
+      <c r="U116" s="17">
+        <v>5</v>
+      </c>
+      <c r="V116" s="17">
+        <v>5</v>
+      </c>
+      <c r="W116" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="3:23">
       <c r="C117" s="16" t="s">
         <v>118</v>
       </c>
@@ -14142,8 +14693,47 @@
       <c r="G117" s="18">
         <v>5.20810707442889</v>
       </c>
-    </row>
-    <row r="118" spans="3:7">
+      <c r="J117" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K117" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L117" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="M117" s="17">
+        <f t="shared" si="16"/>
+        <v>1.3095438006141</v>
+      </c>
+      <c r="N117" s="17">
+        <f t="shared" si="17"/>
+        <v>0.994383885335299</v>
+      </c>
+      <c r="O117" s="17">
+        <f t="shared" si="18"/>
+        <v>1.63013751429624</v>
+      </c>
+      <c r="R117" s="4">
+        <v>0</v>
+      </c>
+      <c r="S117" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T117" s="17">
+        <v>5</v>
+      </c>
+      <c r="U117" s="17">
+        <v>5</v>
+      </c>
+      <c r="V117" s="17">
+        <v>5</v>
+      </c>
+      <c r="W117" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="3:23">
       <c r="C118" s="16" t="s">
         <v>118</v>
       </c>
@@ -14159,8 +14749,47 @@
       <c r="G118" s="18">
         <v>4.4384597641857</v>
       </c>
-    </row>
-    <row r="119" spans="3:7">
+      <c r="J118" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K118" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L118" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="M118" s="17">
+        <f t="shared" si="16"/>
+        <v>1.1160211134365</v>
+      </c>
+      <c r="N118" s="17">
+        <f t="shared" si="17"/>
+        <v>0.847435113780397</v>
+      </c>
+      <c r="O118" s="17">
+        <f t="shared" si="18"/>
+        <v>1.38923790619012</v>
+      </c>
+      <c r="R118" s="4">
+        <v>0</v>
+      </c>
+      <c r="S118" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T118" s="17">
+        <v>5</v>
+      </c>
+      <c r="U118" s="17">
+        <v>5</v>
+      </c>
+      <c r="V118" s="17">
+        <v>5</v>
+      </c>
+      <c r="W118" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="3:23">
       <c r="C119" s="16" t="s">
         <v>118</v>
       </c>
@@ -14176,8 +14805,47 @@
       <c r="G119" s="18">
         <v>4.48241960206338</v>
       </c>
-    </row>
-    <row r="120" spans="3:7">
+      <c r="J119" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K119" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L119" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="M119" s="17">
+        <f t="shared" si="16"/>
+        <v>1.1270745266028</v>
+      </c>
+      <c r="N119" s="17">
+        <f t="shared" si="17"/>
+        <v>0.855828380619012</v>
+      </c>
+      <c r="O119" s="17">
+        <f t="shared" si="18"/>
+        <v>1.40299733544584</v>
+      </c>
+      <c r="R119" s="4">
+        <v>0</v>
+      </c>
+      <c r="S119" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T119" s="17">
+        <v>5</v>
+      </c>
+      <c r="U119" s="17">
+        <v>5</v>
+      </c>
+      <c r="V119" s="17">
+        <v>5</v>
+      </c>
+      <c r="W119" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="3:23">
       <c r="C120" s="16" t="s">
         <v>118</v>
       </c>
@@ -14193,8 +14861,47 @@
       <c r="G120" s="18">
         <v>4.4384597641857</v>
       </c>
-    </row>
-    <row r="121" spans="3:7">
+      <c r="J120" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K120" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L120" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="M120" s="17">
+        <f t="shared" si="16"/>
+        <v>1.1160211134365</v>
+      </c>
+      <c r="N120" s="17">
+        <f t="shared" si="17"/>
+        <v>0.847435113780397</v>
+      </c>
+      <c r="O120" s="17">
+        <f t="shared" si="18"/>
+        <v>1.38923790619012</v>
+      </c>
+      <c r="R120" s="4">
+        <v>0</v>
+      </c>
+      <c r="S120" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T120" s="17">
+        <v>5</v>
+      </c>
+      <c r="U120" s="17">
+        <v>5</v>
+      </c>
+      <c r="V120" s="17">
+        <v>5</v>
+      </c>
+      <c r="W120" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="3:23">
       <c r="C121" s="16" t="s">
         <v>118</v>
       </c>
@@ -14210,8 +14917,47 @@
       <c r="G121" s="18">
         <v>4.43956890198968</v>
       </c>
-    </row>
-    <row r="122" spans="3:7">
+      <c r="J121" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K121" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L121" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="M121" s="17">
+        <f t="shared" si="16"/>
+        <v>1.11630000712356</v>
+      </c>
+      <c r="N121" s="17">
+        <f t="shared" si="17"/>
+        <v>0.847646901989683</v>
+      </c>
+      <c r="O121" s="17">
+        <f t="shared" si="18"/>
+        <v>1.38958506632277</v>
+      </c>
+      <c r="R121" s="4">
+        <v>0</v>
+      </c>
+      <c r="S121" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T121" s="17">
+        <v>5</v>
+      </c>
+      <c r="U121" s="17">
+        <v>5</v>
+      </c>
+      <c r="V121" s="17">
+        <v>5</v>
+      </c>
+      <c r="W121" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="3:23">
       <c r="C122" s="16" t="s">
         <v>118</v>
       </c>
@@ -14227,8 +14973,47 @@
       <c r="G122" s="18">
         <v>4.43882940309506</v>
       </c>
-    </row>
-    <row r="123" spans="3:7">
+      <c r="J122" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K122" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L122" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="M122" s="17">
+        <f t="shared" si="16"/>
+        <v>1.11611406005895</v>
+      </c>
+      <c r="N122" s="17">
+        <f t="shared" si="17"/>
+        <v>0.847505694473101</v>
+      </c>
+      <c r="O122" s="17">
+        <f t="shared" si="18"/>
+        <v>1.38935360316875</v>
+      </c>
+      <c r="R122" s="4">
+        <v>0</v>
+      </c>
+      <c r="S122" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T122" s="17">
+        <v>5</v>
+      </c>
+      <c r="U122" s="17">
+        <v>5</v>
+      </c>
+      <c r="V122" s="17">
+        <v>5</v>
+      </c>
+      <c r="W122" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="3:23">
       <c r="C123" s="16" t="s">
         <v>118</v>
       </c>
@@ -14244,8 +15029,47 @@
       <c r="G123" s="18">
         <v>4.4384597641857</v>
       </c>
-    </row>
-    <row r="124" spans="3:7">
+      <c r="J123" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K123" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L123" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="M123" s="17">
+        <f t="shared" si="16"/>
+        <v>1.1160211134365</v>
+      </c>
+      <c r="N123" s="17">
+        <f t="shared" si="17"/>
+        <v>0.847435113780397</v>
+      </c>
+      <c r="O123" s="17">
+        <f t="shared" si="18"/>
+        <v>1.38923790619012</v>
+      </c>
+      <c r="R123" s="4">
+        <v>0</v>
+      </c>
+      <c r="S123" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T123" s="17">
+        <v>5</v>
+      </c>
+      <c r="U123" s="17">
+        <v>5</v>
+      </c>
+      <c r="V123" s="17">
+        <v>5</v>
+      </c>
+      <c r="W123" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="3:23">
       <c r="C124" s="16" t="s">
         <v>118</v>
       </c>
@@ -14260,6 +15084,45 @@
       </c>
       <c r="G124" s="18">
         <v>4.43772063375092</v>
+      </c>
+      <c r="J124" s="4">
+        <v>2050</v>
+      </c>
+      <c r="K124" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="L124" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="M124" s="17">
+        <f t="shared" si="16"/>
+        <v>1.11583526632277</v>
+      </c>
+      <c r="N124" s="17">
+        <f t="shared" si="17"/>
+        <v>0.847293998526159</v>
+      </c>
+      <c r="O124" s="17">
+        <f t="shared" si="18"/>
+        <v>1.38900655836404</v>
+      </c>
+      <c r="R124" s="4">
+        <v>0</v>
+      </c>
+      <c r="S124" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="T124" s="17">
+        <v>5</v>
+      </c>
+      <c r="U124" s="17">
+        <v>5</v>
+      </c>
+      <c r="V124" s="17">
+        <v>5</v>
+      </c>
+      <c r="W124" s="17">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" updateLinks="never"/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8710" activeTab="1"/>
+    <workbookView windowHeight="7510" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TechSelection" sheetId="21" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="196">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -1361,7 +1361,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1382,6 +1382,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
@@ -1869,29 +1871,29 @@
   <dimension ref="A1:AA281"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="20" customWidth="1"/>
-    <col min="2" max="2" width="8.85454545454546" style="20" customWidth="1"/>
-    <col min="3" max="3" width="4.70909090909091" style="20" customWidth="1"/>
-    <col min="4" max="4" width="8.85454545454546" style="20" customWidth="1"/>
-    <col min="5" max="5" width="4.42727272727273" style="20" customWidth="1"/>
-    <col min="6" max="6" width="4.28181818181818" style="20" customWidth="1"/>
-    <col min="7" max="7" width="4.42727272727273" style="20" customWidth="1"/>
-    <col min="8" max="8" width="4.57272727272727" style="20" customWidth="1"/>
-    <col min="9" max="9" width="4" style="20" customWidth="1"/>
-    <col min="10" max="10" width="4.42727272727273" style="20" customWidth="1"/>
-    <col min="11" max="11" width="4.57272727272727" style="20" customWidth="1"/>
-    <col min="12" max="12" width="4.42727272727273" style="20" customWidth="1"/>
-    <col min="13" max="13" width="4" style="20" customWidth="1"/>
-    <col min="14" max="14" width="4.28181818181818" style="20" customWidth="1"/>
-    <col min="15" max="16" width="4.42727272727273" style="20" customWidth="1"/>
-    <col min="17" max="18" width="4.57272727272727" style="20" customWidth="1"/>
-    <col min="19" max="19" width="4.42727272727273" style="20" customWidth="1"/>
-    <col min="20" max="20" width="5" style="20" customWidth="1"/>
-    <col min="21" max="21" width="11.7090909090909" style="20" customWidth="1"/>
-    <col min="22" max="22" width="10.7090909090909" style="20" customWidth="1"/>
-    <col min="23" max="23" width="13.1363636363636" style="20" customWidth="1"/>
-    <col min="24" max="259" width="11.4272727272727" style="20" customWidth="1"/>
-    <col min="260" max="16384" width="9.13636363636364" style="20"/>
+    <col min="1" max="1" width="15" style="22" customWidth="1"/>
+    <col min="2" max="2" width="8.85454545454546" style="22" customWidth="1"/>
+    <col min="3" max="3" width="4.70909090909091" style="22" customWidth="1"/>
+    <col min="4" max="4" width="8.85454545454546" style="22" customWidth="1"/>
+    <col min="5" max="5" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="6" max="6" width="4.28181818181818" style="22" customWidth="1"/>
+    <col min="7" max="7" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="8" max="8" width="4.57272727272727" style="22" customWidth="1"/>
+    <col min="9" max="9" width="4" style="22" customWidth="1"/>
+    <col min="10" max="10" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="11" max="11" width="4.57272727272727" style="22" customWidth="1"/>
+    <col min="12" max="12" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="13" max="13" width="4" style="22" customWidth="1"/>
+    <col min="14" max="14" width="4.28181818181818" style="22" customWidth="1"/>
+    <col min="15" max="16" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="17" max="18" width="4.57272727272727" style="22" customWidth="1"/>
+    <col min="19" max="19" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="20" max="20" width="5" style="22" customWidth="1"/>
+    <col min="21" max="21" width="11.7090909090909" style="22" customWidth="1"/>
+    <col min="22" max="22" width="10.7090909090909" style="22" customWidth="1"/>
+    <col min="23" max="23" width="13.1363636363636" style="22" customWidth="1"/>
+    <col min="24" max="259" width="11.4272727272727" style="22" customWidth="1"/>
+    <col min="260" max="16384" width="9.13636363636364" style="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.5" spans="1:21">
@@ -2970,7 +2972,7 @@
       <c r="AA34" s="5"/>
     </row>
     <row r="35" ht="12.5" spans="1:27">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="22" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -2998,7 +3000,7 @@
       <c r="AA35" s="5"/>
     </row>
     <row r="36" ht="12.5" spans="1:27">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="22" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -3026,7 +3028,7 @@
       <c r="AA36" s="5"/>
     </row>
     <row r="37" ht="12.5" spans="1:27">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -3054,7 +3056,7 @@
       <c r="AA37" s="5"/>
     </row>
     <row r="38" ht="12.5" spans="1:27">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="22" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -3082,7 +3084,7 @@
       <c r="AA38" s="5"/>
     </row>
     <row r="39" ht="12.5" spans="1:27">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="22" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -8443,7 +8445,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:BA124"/>
+  <dimension ref="A2:CM124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="2" max="2" width="21.3727272727273" customWidth="1"/>
@@ -8455,7 +8457,9 @@
     <col min="10" max="10" width="10.6363636363636" customWidth="1"/>
     <col min="11" max="11" width="11.2818181818182" customWidth="1"/>
     <col min="12" max="12" width="15.5454545454545" customWidth="1"/>
-    <col min="13" max="24" width="7.13636363636364" customWidth="1"/>
+    <col min="13" max="18" width="7.13636363636364" customWidth="1"/>
+    <col min="19" max="19" width="12.7272727272727" customWidth="1"/>
+    <col min="20" max="24" width="7.13636363636364" customWidth="1"/>
     <col min="25" max="25" width="9.54545454545454" customWidth="1"/>
     <col min="26" max="33" width="7.13636363636364" customWidth="1"/>
     <col min="34" max="37" width="6" customWidth="1"/>
@@ -8746,7 +8750,7 @@
       <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="23" t="s">
         <v>92</v>
       </c>
       <c r="F14">
@@ -8805,7 +8809,7 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="23" t="s">
         <v>92</v>
       </c>
       <c r="C18">
@@ -8814,7 +8818,7 @@
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="23" t="s">
         <v>100</v>
       </c>
       <c r="F18" t="s">
@@ -11602,7 +11606,7 @@
       <c r="D45">
         <v>2020</v>
       </c>
-      <c r="E45" s="22" t="s">
+      <c r="E45" s="24" t="s">
         <v>119</v>
       </c>
       <c r="F45" t="s">
@@ -11686,7 +11690,7 @@
       <c r="D55" t="s">
         <v>126</v>
       </c>
-      <c r="E55" s="21" t="s">
+      <c r="E55" s="23" t="s">
         <v>127</v>
       </c>
     </row>
@@ -11813,7 +11817,7 @@
     <row r="64" s="1" customFormat="1" ht="28" spans="1:1">
       <c r="A64" s="11"/>
     </row>
-    <row r="65" s="1" customFormat="1" spans="1:53">
+    <row r="65" s="1" customFormat="1" spans="1:91">
       <c r="A65" s="2"/>
       <c r="B65" s="12" t="s">
         <v>73</v>
@@ -11859,7 +11863,9 @@
       <c r="AP65" s="2"/>
       <c r="AQ65" s="2"/>
       <c r="AR65" s="2"/>
-      <c r="AS65" s="2"/>
+      <c r="AS65" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="AT65" s="2"/>
       <c r="AU65" s="2"/>
       <c r="AV65" s="2"/>
@@ -11868,8 +11874,17 @@
       <c r="AY65" s="2"/>
       <c r="AZ65" s="2"/>
       <c r="BA65" s="2"/>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="1:40">
+      <c r="CG65" s="20"/>
+      <c r="CH65" s="20"/>
+      <c r="CI65" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="CJ65" s="20"/>
+      <c r="CK65" s="20"/>
+      <c r="CL65" s="20"/>
+      <c r="CM65" s="20"/>
+    </row>
+    <row r="66" s="2" customFormat="1" spans="1:91">
       <c r="A66" s="2" t="s">
         <v>130</v>
       </c>
@@ -11990,8 +12005,152 @@
       <c r="AN66" s="12" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="67" s="2" customFormat="1" ht="14.5" spans="1:40">
+      <c r="AQ66" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AR66" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="AS66" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AT66" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AU66" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AV66" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AW66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AX66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AY66" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AZ66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BA66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BC66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="BD66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="BE66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="BF66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="BG66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="BH66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="BI66" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BJ66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="BK66" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="BL66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="BM66" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="BN66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="BO66" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="BP66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="BQ66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="BR66" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="BS66" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="BV66" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW66" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="BX66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="BY66" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="BZ66" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="CA66" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="CB66" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="CC66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="CD66" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="CE66" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="CG66" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="CH66" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="CI66" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="CJ66" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="CK66" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="CL66" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="CM66" s="21" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" ht="14.5" spans="1:91">
       <c r="A67" s="2" t="s">
         <v>132</v>
       </c>
@@ -12145,8 +12304,152 @@
       <c r="AN67" s="1" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="68" s="2" customFormat="1" ht="14.5" spans="1:40">
+      <c r="AQ67" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AR67" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS67" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT67" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU67" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV67" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW67" s="2">
+        <v>310</v>
+      </c>
+      <c r="AX67" s="2">
+        <v>6200</v>
+      </c>
+      <c r="AY67" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB67" s="2">
+        <v>250</v>
+      </c>
+      <c r="BC67" s="2">
+        <v>2000</v>
+      </c>
+      <c r="BD67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BK67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BO67" s="2">
+        <v>12250</v>
+      </c>
+      <c r="BP67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ67" s="2">
+        <v>1930</v>
+      </c>
+      <c r="BR67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT67" s="2">
+        <v>3300</v>
+      </c>
+      <c r="BU67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX67" s="2">
+        <v>60</v>
+      </c>
+      <c r="BY67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD67" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="CE67" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="CG67" s="21">
+        <v>0</v>
+      </c>
+      <c r="CH67" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CI67" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CJ67" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="CK67" s="21">
+        <v>5</v>
+      </c>
+      <c r="CL67" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM67" s="21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" ht="14.5" spans="1:91">
       <c r="A68" s="2" t="s">
         <v>132</v>
       </c>
@@ -12301,8 +12604,152 @@
       <c r="AN68" s="1" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="69" s="2" customFormat="1" ht="14.5" spans="1:40">
+      <c r="AQ68" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AR68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS68" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT68" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU68" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV68" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW68" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX68" s="2">
+        <v>21000</v>
+      </c>
+      <c r="AY68" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB68" s="2">
+        <v>16000</v>
+      </c>
+      <c r="BC68" s="2">
+        <v>2100</v>
+      </c>
+      <c r="BD68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BK68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BO68" s="2">
+        <v>16000</v>
+      </c>
+      <c r="BP68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ68" s="2">
+        <v>2570</v>
+      </c>
+      <c r="BR68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT68" s="2">
+        <v>52900</v>
+      </c>
+      <c r="BU68" s="2">
+        <v>7500</v>
+      </c>
+      <c r="BV68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD68" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="CE68" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CG68" s="21">
+        <v>0</v>
+      </c>
+      <c r="CH68" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CI68" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CJ68" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="CK68" s="21">
+        <v>5</v>
+      </c>
+      <c r="CL68" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM68" s="21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" ht="14.5" spans="1:91">
       <c r="A69" s="2" t="s">
         <v>132</v>
       </c>
@@ -12457,8 +12904,152 @@
       <c r="AN69" s="1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="70" s="2" customFormat="1" ht="14.5" spans="1:40">
+      <c r="AQ69" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AR69" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS69" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT69" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU69" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV69" s="2">
+        <v>13</v>
+      </c>
+      <c r="AW69" s="2">
+        <v>4100</v>
+      </c>
+      <c r="AX69" s="2">
+        <v>1500</v>
+      </c>
+      <c r="AY69" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BC69" s="2">
+        <v>140</v>
+      </c>
+      <c r="BD69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BK69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BO69" s="2">
+        <v>500</v>
+      </c>
+      <c r="BP69" s="2">
+        <v>36</v>
+      </c>
+      <c r="BQ69" s="2">
+        <v>289</v>
+      </c>
+      <c r="BR69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT69" s="2">
+        <v>1517</v>
+      </c>
+      <c r="BU69" s="2">
+        <v>250</v>
+      </c>
+      <c r="BV69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA69" s="2">
+        <v>36</v>
+      </c>
+      <c r="CB69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD69" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="CE69" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="CG69" s="21">
+        <v>0</v>
+      </c>
+      <c r="CH69" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CI69" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CJ69" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="CK69" s="21">
+        <v>5</v>
+      </c>
+      <c r="CL69" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM69" s="21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" ht="14.5" spans="1:91">
       <c r="A70" s="2" t="s">
         <v>132</v>
       </c>
@@ -12613,8 +13204,152 @@
       <c r="AN70" s="1" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="71" s="2" customFormat="1" ht="14.5" spans="1:40">
+      <c r="AQ70" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AR70" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS70" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT70" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU70" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV70" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW70" s="2">
+        <v>74000</v>
+      </c>
+      <c r="AX70" s="2">
+        <v>270000</v>
+      </c>
+      <c r="AY70" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB70" s="2">
+        <v>270000</v>
+      </c>
+      <c r="BC70" s="2">
+        <v>280000</v>
+      </c>
+      <c r="BD70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BK70" s="2">
+        <v>34000</v>
+      </c>
+      <c r="BL70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BO70" s="2">
+        <v>275000</v>
+      </c>
+      <c r="BP70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT70" s="2">
+        <v>5000</v>
+      </c>
+      <c r="BU70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW70" s="2">
+        <v>640000</v>
+      </c>
+      <c r="BX70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC70" s="2">
+        <v>140000</v>
+      </c>
+      <c r="CD70" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="CE70" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="CG70" s="21">
+        <v>0</v>
+      </c>
+      <c r="CH70" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CI70" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CJ70" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="CK70" s="21">
+        <v>5</v>
+      </c>
+      <c r="CL70" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM70" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" ht="14.5" spans="1:91">
       <c r="A71" s="2" t="s">
         <v>132</v>
       </c>
@@ -12769,8 +13504,152 @@
       <c r="AN71" s="1" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="72" s="2" customFormat="1" ht="14.5" spans="1:40">
+      <c r="AQ71" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AR71" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS71" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT71" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU71" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV71" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW71" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX71" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY71" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BC71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BK71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BO71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY71" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD71" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="CE71" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="CG71" s="21">
+        <v>0</v>
+      </c>
+      <c r="CH71" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CI71" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CJ71" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="CK71" s="21">
+        <v>5</v>
+      </c>
+      <c r="CL71" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM71" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" ht="14.5" spans="1:91">
       <c r="A72" s="2" t="s">
         <v>132</v>
       </c>
@@ -12925,8 +13804,152 @@
       <c r="AN72" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="73" s="1" customFormat="1" ht="14.5" spans="1:40">
+      <c r="AQ72" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AR72" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS72" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT72" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU72" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV72" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW72" s="2">
+        <v>50000</v>
+      </c>
+      <c r="AX72" s="2">
+        <v>97000</v>
+      </c>
+      <c r="AY72" s="2">
+        <v>0</v>
+      </c>
+      <c r="AZ72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BC72" s="2">
+        <v>27000</v>
+      </c>
+      <c r="BD72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BG72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BK72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BO72" s="2">
+        <v>324000</v>
+      </c>
+      <c r="BP72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ72" s="2">
+        <v>51600</v>
+      </c>
+      <c r="BR72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS72" s="2">
+        <v>30000</v>
+      </c>
+      <c r="BT72" s="2">
+        <v>244000</v>
+      </c>
+      <c r="BU72" s="2">
+        <v>62000</v>
+      </c>
+      <c r="BV72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BX72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CC72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD72" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="CE72" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="CG72" s="21">
+        <v>0</v>
+      </c>
+      <c r="CH72" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CI72" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CJ72" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="CK72" s="21">
+        <v>5</v>
+      </c>
+      <c r="CL72" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM72" s="21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="14.5" spans="1:91">
       <c r="A73" s="2" t="s">
         <v>132</v>
       </c>
@@ -13079,6 +14102,150 @@
         <v>134</v>
       </c>
       <c r="AN73" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AQ73" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AR73" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS73" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AT73" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW73" s="1">
+        <v>69000</v>
+      </c>
+      <c r="AX73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB73" s="1">
+        <v>74000</v>
+      </c>
+      <c r="BC73" s="1">
+        <v>52000</v>
+      </c>
+      <c r="BD73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK73" s="1">
+        <v>8000</v>
+      </c>
+      <c r="BL73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BM73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO73" s="1">
+        <v>77100</v>
+      </c>
+      <c r="BP73" s="1">
+        <v>90000</v>
+      </c>
+      <c r="BQ73" s="1">
+        <v>5700</v>
+      </c>
+      <c r="BR73" s="1">
+        <v>600</v>
+      </c>
+      <c r="BS73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BT73" s="1">
+        <v>12900</v>
+      </c>
+      <c r="BU73" s="1">
+        <v>14000</v>
+      </c>
+      <c r="BV73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BX73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BY73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BZ73" s="1">
+        <v>0</v>
+      </c>
+      <c r="CA73" s="1">
+        <v>90000</v>
+      </c>
+      <c r="CB73" s="1">
+        <v>0</v>
+      </c>
+      <c r="CC73" s="1">
+        <v>0</v>
+      </c>
+      <c r="CD73" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="CE73" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="CG73" s="21">
+        <v>0</v>
+      </c>
+      <c r="CH73" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="CI73" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="CJ73" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="CK73" s="21">
+        <v>5</v>
+      </c>
+      <c r="CL73" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="CM73" s="20" t="s">
         <v>141</v>
       </c>
     </row>
@@ -13992,8 +15159,8 @@
       <c r="S104" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T104" s="17">
-        <v>5</v>
+      <c r="T104" s="17" t="s">
+        <v>144</v>
       </c>
       <c r="U104" s="17">
         <v>5</v>
@@ -14048,8 +15215,8 @@
       <c r="S105" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T105" s="17">
-        <v>5</v>
+      <c r="T105" s="17" t="s">
+        <v>145</v>
       </c>
       <c r="U105" s="17">
         <v>5</v>
@@ -14104,8 +15271,8 @@
       <c r="S106" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T106" s="17">
-        <v>5</v>
+      <c r="T106" s="17" t="s">
+        <v>146</v>
       </c>
       <c r="U106" s="17">
         <v>5</v>
@@ -14160,8 +15327,8 @@
       <c r="S107" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T107" s="17">
-        <v>5</v>
+      <c r="T107" s="17" t="s">
+        <v>147</v>
       </c>
       <c r="U107" s="17">
         <v>5</v>
@@ -14216,8 +15383,8 @@
       <c r="S108" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T108" s="17">
-        <v>5</v>
+      <c r="T108" s="17" t="s">
+        <v>148</v>
       </c>
       <c r="U108" s="17">
         <v>5</v>
@@ -14272,8 +15439,8 @@
       <c r="S109" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T109" s="17">
-        <v>5</v>
+      <c r="T109" s="17" t="s">
+        <v>149</v>
       </c>
       <c r="U109" s="17">
         <v>5</v>
@@ -14328,8 +15495,8 @@
       <c r="S110" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T110" s="17">
-        <v>5</v>
+      <c r="T110" s="17" t="s">
+        <v>150</v>
       </c>
       <c r="U110" s="17">
         <v>5</v>
@@ -14384,8 +15551,8 @@
       <c r="S111" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T111" s="17">
-        <v>5</v>
+      <c r="T111" s="17" t="s">
+        <v>151</v>
       </c>
       <c r="U111" s="17">
         <v>5</v>
@@ -14440,8 +15607,8 @@
       <c r="S112" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T112" s="17">
-        <v>5</v>
+      <c r="T112" s="17" t="s">
+        <v>152</v>
       </c>
       <c r="U112" s="17">
         <v>5</v>
@@ -14496,8 +15663,8 @@
       <c r="S113" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T113" s="17">
-        <v>5</v>
+      <c r="T113" s="17" t="s">
+        <v>153</v>
       </c>
       <c r="U113" s="17">
         <v>5</v>
@@ -14552,8 +15719,8 @@
       <c r="S114" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T114" s="17">
-        <v>5</v>
+      <c r="T114" s="17" t="s">
+        <v>154</v>
       </c>
       <c r="U114" s="17">
         <v>5</v>
@@ -14608,8 +15775,8 @@
       <c r="S115" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T115" s="17">
-        <v>5</v>
+      <c r="T115" s="17" t="s">
+        <v>155</v>
       </c>
       <c r="U115" s="17">
         <v>5</v>
@@ -14664,8 +15831,8 @@
       <c r="S116" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T116" s="17">
-        <v>5</v>
+      <c r="T116" s="17" t="s">
+        <v>156</v>
       </c>
       <c r="U116" s="17">
         <v>5</v>
@@ -14720,8 +15887,8 @@
       <c r="S117" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T117" s="17">
-        <v>5</v>
+      <c r="T117" s="17" t="s">
+        <v>157</v>
       </c>
       <c r="U117" s="17">
         <v>5</v>
@@ -14776,8 +15943,8 @@
       <c r="S118" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T118" s="17">
-        <v>5</v>
+      <c r="T118" s="17" t="s">
+        <v>158</v>
       </c>
       <c r="U118" s="17">
         <v>5</v>
@@ -14832,8 +15999,8 @@
       <c r="S119" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T119" s="17">
-        <v>5</v>
+      <c r="T119" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="U119" s="17">
         <v>5</v>
@@ -14888,8 +16055,8 @@
       <c r="S120" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T120" s="17">
-        <v>5</v>
+      <c r="T120" s="17" t="s">
+        <v>160</v>
       </c>
       <c r="U120" s="17">
         <v>5</v>
@@ -14944,8 +16111,8 @@
       <c r="S121" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T121" s="17">
-        <v>5</v>
+      <c r="T121" s="17" t="s">
+        <v>161</v>
       </c>
       <c r="U121" s="17">
         <v>5</v>
@@ -15000,8 +16167,8 @@
       <c r="S122" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T122" s="17">
-        <v>5</v>
+      <c r="T122" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="U122" s="17">
         <v>5</v>
@@ -15056,8 +16223,8 @@
       <c r="S123" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T123" s="17">
-        <v>5</v>
+      <c r="T123" s="17" t="s">
+        <v>163</v>
       </c>
       <c r="U123" s="17">
         <v>5</v>
@@ -15112,8 +16279,8 @@
       <c r="S124" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T124" s="17">
-        <v>5</v>
+      <c r="T124" s="17" t="s">
+        <v>164</v>
       </c>
       <c r="U124" s="17">
         <v>5</v>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -12158,7 +12158,7 @@
         <v>133</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D67" s="2">
         <v>0</v>
@@ -12314,7 +12314,7 @@
         <v>133</v>
       </c>
       <c r="AT67" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="AU67" s="2">
         <v>0</v>
@@ -12437,7 +12437,7 @@
         <v>133</v>
       </c>
       <c r="CJ67" s="21" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="CK67" s="21">
         <v>5</v>
@@ -12457,7 +12457,7 @@
         <v>133</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D68" s="2">
         <v>0</v>
@@ -12614,7 +12614,7 @@
         <v>133</v>
       </c>
       <c r="AT68" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="AU68" s="2">
         <v>0</v>
@@ -12737,7 +12737,7 @@
         <v>133</v>
       </c>
       <c r="CJ68" s="21" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="CK68" s="21">
         <v>5</v>
@@ -12757,7 +12757,7 @@
         <v>133</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D69" s="2">
         <v>0</v>
@@ -12914,7 +12914,7 @@
         <v>133</v>
       </c>
       <c r="AT69" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="AU69" s="2">
         <v>0</v>
@@ -13037,7 +13037,7 @@
         <v>133</v>
       </c>
       <c r="CJ69" s="21" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="CK69" s="21">
         <v>5</v>
@@ -13057,7 +13057,7 @@
         <v>133</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D70" s="2">
         <v>0</v>
@@ -13214,7 +13214,7 @@
         <v>133</v>
       </c>
       <c r="AT70" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="AU70" s="2">
         <v>0</v>
@@ -13337,7 +13337,7 @@
         <v>133</v>
       </c>
       <c r="CJ70" s="21" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="CK70" s="21">
         <v>5</v>
@@ -13357,7 +13357,7 @@
         <v>133</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D71" s="2">
         <v>0</v>
@@ -13514,7 +13514,7 @@
         <v>133</v>
       </c>
       <c r="AT71" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="AU71" s="2">
         <v>0</v>
@@ -13637,7 +13637,7 @@
         <v>133</v>
       </c>
       <c r="CJ71" s="21" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="CK71" s="21">
         <v>5</v>
@@ -13657,7 +13657,7 @@
         <v>133</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D72" s="2">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>133</v>
       </c>
       <c r="AT72" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="AU72" s="2">
         <v>0</v>
@@ -13937,7 +13937,7 @@
         <v>133</v>
       </c>
       <c r="CJ72" s="21" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="CK72" s="21">
         <v>5</v>
@@ -13957,7 +13957,7 @@
         <v>133</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D73" s="2">
         <v>0</v>
@@ -14113,8 +14113,8 @@
       <c r="AS73" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="AT73" s="1" t="s">
-        <v>83</v>
+      <c r="AT73" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="AU73" s="1">
         <v>0</v>
@@ -14236,8 +14236,8 @@
       <c r="CI73" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="CJ73" s="20" t="s">
-        <v>83</v>
+      <c r="CJ73" s="21" t="s">
+        <v>68</v>
       </c>
       <c r="CK73" s="21">
         <v>5</v>
@@ -15049,21 +15049,21 @@
       <c r="F101" s="17"/>
       <c r="G101" s="17"/>
     </row>
-    <row r="102" s="4" customFormat="1" spans="3:20">
+    <row r="102" s="4" customFormat="1" spans="3:26">
       <c r="C102" s="16"/>
       <c r="D102" t="s">
         <v>73</v>
       </c>
-      <c r="K102" s="16"/>
-      <c r="L102" t="s">
+      <c r="M102" s="16"/>
+      <c r="N102" t="s">
         <v>73</v>
       </c>
-      <c r="S102" s="16"/>
-      <c r="T102" t="s">
+      <c r="Y102" s="16"/>
+      <c r="Z102" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="103" s="4" customFormat="1" spans="3:23">
+    <row r="103" s="4" customFormat="1" spans="3:29">
       <c r="C103" s="16" t="s">
         <v>56</v>
       </c>
@@ -15079,44 +15079,44 @@
       <c r="G103" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J103" s="4" t="s">
+      <c r="L103" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="K103" s="16" t="s">
+      <c r="M103" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="L103" s="17" t="s">
+      <c r="N103" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="M103" s="17" t="s">
+      <c r="O103" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="N103" s="17" t="s">
+      <c r="P103" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="O103" s="17" t="s">
+      <c r="Q103" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="R103" s="4" t="s">
+      <c r="X103" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="S103" s="16" t="s">
+      <c r="Y103" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="T103" s="17" t="s">
+      <c r="Z103" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="U103" s="17" t="s">
+      <c r="AA103" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="V103" s="17" t="s">
+      <c r="AB103" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="W103" s="17" t="s">
+      <c r="AC103" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="104" s="4" customFormat="1" spans="3:23">
+    <row r="104" s="4" customFormat="1" spans="3:29">
       <c r="C104" s="16" t="s">
         <v>118</v>
       </c>
@@ -15132,47 +15132,47 @@
       <c r="G104" s="18">
         <v>8.85540744288872</v>
       </c>
-      <c r="J104" s="4">
+      <c r="L104" s="4">
         <v>2050</v>
       </c>
-      <c r="K104" s="16" t="s">
+      <c r="M104" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L104" s="17" t="s">
+      <c r="N104" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="M104" s="17">
+      <c r="O104" s="17">
         <f>E104*0.313</f>
         <v>2.22663316246622</v>
       </c>
-      <c r="N104" s="17">
+      <c r="P104" s="17">
         <f>F104*0.313</f>
         <v>1.69076293868828</v>
       </c>
-      <c r="O104" s="17">
+      <c r="Q104" s="17">
         <f>G104*0.313</f>
         <v>2.77174252962417</v>
       </c>
-      <c r="R104" s="4">
-        <v>0</v>
-      </c>
-      <c r="S104" s="16" t="s">
+      <c r="X104" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T104" s="17" t="s">
+      <c r="Z104" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="U104" s="17">
+      <c r="AA104" s="17">
         <v>5</v>
       </c>
-      <c r="V104" s="17">
+      <c r="AB104" s="17">
         <v>5</v>
       </c>
-      <c r="W104" s="17">
+      <c r="AC104" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="105" s="4" customFormat="1" spans="3:23">
+    <row r="105" s="4" customFormat="1" spans="3:29">
       <c r="C105" s="16" t="s">
         <v>118</v>
       </c>
@@ -15188,47 +15188,47 @@
       <c r="G105" s="18">
         <v>8.85540744288872</v>
       </c>
-      <c r="J105" s="4">
+      <c r="L105" s="4">
         <v>2050</v>
       </c>
-      <c r="K105" s="16" t="s">
+      <c r="M105" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L105" s="17" t="s">
+      <c r="N105" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="M105" s="17">
-        <f t="shared" ref="M105:M124" si="16">E105*0.313</f>
+      <c r="O105" s="17">
+        <f t="shared" ref="O105:O124" si="16">E105*0.313</f>
         <v>2.22663316246622</v>
       </c>
-      <c r="N105" s="17">
-        <f t="shared" ref="N105:N124" si="17">F105*0.313</f>
+      <c r="P105" s="17">
+        <f t="shared" ref="P105:P124" si="17">F105*0.313</f>
         <v>1.69076293868828</v>
       </c>
-      <c r="O105" s="17">
-        <f t="shared" ref="O105:O124" si="18">G105*0.313</f>
+      <c r="Q105" s="17">
+        <f t="shared" ref="Q105:Q124" si="18">G105*0.313</f>
         <v>2.77174252962417</v>
       </c>
-      <c r="R105" s="4">
-        <v>0</v>
-      </c>
-      <c r="S105" s="16" t="s">
+      <c r="X105" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T105" s="17" t="s">
+      <c r="Z105" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="U105" s="17">
+      <c r="AA105" s="17">
         <v>5</v>
       </c>
-      <c r="V105" s="17">
+      <c r="AB105" s="17">
         <v>5</v>
       </c>
-      <c r="W105" s="17">
+      <c r="AC105" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="3:23">
+    <row r="106" spans="3:29">
       <c r="C106" s="16" t="s">
         <v>118</v>
       </c>
@@ -15244,47 +15244,47 @@
       <c r="G106" s="18">
         <v>9.49761967575534</v>
       </c>
-      <c r="J106" s="4">
+      <c r="L106" s="4">
         <v>2050</v>
       </c>
-      <c r="K106" s="16" t="s">
+      <c r="M106" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L106" s="17" t="s">
+      <c r="N106" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="M106" s="17">
+      <c r="O106" s="17">
         <f t="shared" si="16"/>
         <v>2.38811314546794</v>
       </c>
-      <c r="N106" s="17">
+      <c r="P106" s="17">
         <f t="shared" si="17"/>
         <v>1.81338051569639</v>
       </c>
-      <c r="O106" s="17">
+      <c r="Q106" s="17">
         <f t="shared" si="18"/>
         <v>2.97275495851142</v>
       </c>
-      <c r="R106" s="4">
-        <v>0</v>
-      </c>
-      <c r="S106" s="16" t="s">
+      <c r="X106" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T106" s="17" t="s">
+      <c r="Z106" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="U106" s="17">
+      <c r="AA106" s="17">
         <v>5</v>
       </c>
-      <c r="V106" s="17">
+      <c r="AB106" s="17">
         <v>5</v>
       </c>
-      <c r="W106" s="17">
+      <c r="AC106" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="3:23">
+    <row r="107" spans="3:29">
       <c r="C107" s="16" t="s">
         <v>118</v>
       </c>
@@ -15300,47 +15300,47 @@
       <c r="G107" s="18">
         <v>9.29996366985999</v>
       </c>
-      <c r="J107" s="4">
+      <c r="L107" s="4">
         <v>2050</v>
       </c>
-      <c r="K107" s="16" t="s">
+      <c r="M107" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L107" s="17" t="s">
+      <c r="N107" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="M107" s="17">
+      <c r="O107" s="17">
         <f t="shared" si="16"/>
         <v>2.338413866028</v>
       </c>
-      <c r="N107" s="17">
+      <c r="P107" s="17">
         <f t="shared" si="17"/>
         <v>1.77564205725866</v>
       </c>
-      <c r="O107" s="17">
+      <c r="Q107" s="17">
         <f t="shared" si="18"/>
         <v>2.91088862866618</v>
       </c>
-      <c r="R107" s="4">
-        <v>0</v>
-      </c>
-      <c r="S107" s="16" t="s">
+      <c r="X107" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T107" s="17" t="s">
+      <c r="Z107" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="U107" s="17">
+      <c r="AA107" s="17">
         <v>5</v>
       </c>
-      <c r="V107" s="17">
+      <c r="AB107" s="17">
         <v>5</v>
       </c>
-      <c r="W107" s="17">
+      <c r="AC107" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="3:23">
+    <row r="108" spans="3:29">
       <c r="C108" s="16" t="s">
         <v>118</v>
       </c>
@@ -15356,47 +15356,47 @@
       <c r="G108" s="18">
         <v>9.35655836403832</v>
       </c>
-      <c r="J108" s="4">
+      <c r="L108" s="4">
         <v>2050</v>
       </c>
-      <c r="K108" s="16" t="s">
+      <c r="M108" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L108" s="17" t="s">
+      <c r="N108" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="M108" s="17">
+      <c r="O108" s="17">
         <f t="shared" si="16"/>
         <v>2.35264421766151</v>
       </c>
-      <c r="N108" s="17">
+      <c r="P108" s="17">
         <f t="shared" si="17"/>
         <v>1.78644768452469</v>
       </c>
-      <c r="O108" s="17">
+      <c r="Q108" s="17">
         <f t="shared" si="18"/>
         <v>2.92860276794399</v>
       </c>
-      <c r="R108" s="4">
-        <v>0</v>
-      </c>
-      <c r="S108" s="16" t="s">
+      <c r="X108" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T108" s="17" t="s">
+      <c r="Z108" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="U108" s="17">
+      <c r="AA108" s="17">
         <v>5</v>
       </c>
-      <c r="V108" s="17">
+      <c r="AB108" s="17">
         <v>5</v>
       </c>
-      <c r="W108" s="17">
+      <c r="AC108" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="3:23">
+    <row r="109" spans="3:29">
       <c r="C109" s="16" t="s">
         <v>118</v>
       </c>
@@ -15412,47 +15412,47 @@
       <c r="G109" s="18">
         <v>9.39879167280766</v>
       </c>
-      <c r="J109" s="4">
+      <c r="L109" s="4">
         <v>2050</v>
       </c>
-      <c r="K109" s="16" t="s">
+      <c r="M109" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L109" s="17" t="s">
+      <c r="N109" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="M109" s="17">
+      <c r="O109" s="17">
         <f t="shared" si="16"/>
         <v>2.36326350574797</v>
       </c>
-      <c r="N109" s="17">
+      <c r="P109" s="17">
         <f t="shared" si="17"/>
         <v>1.79451129801032</v>
       </c>
-      <c r="O109" s="17">
+      <c r="Q109" s="17">
         <f t="shared" si="18"/>
         <v>2.9418217935888</v>
       </c>
-      <c r="R109" s="4">
-        <v>0</v>
-      </c>
-      <c r="S109" s="16" t="s">
+      <c r="X109" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T109" s="17" t="s">
+      <c r="Z109" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="U109" s="17">
+      <c r="AA109" s="17">
         <v>5</v>
       </c>
-      <c r="V109" s="17">
+      <c r="AB109" s="17">
         <v>5</v>
       </c>
-      <c r="W109" s="17">
+      <c r="AC109" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="3:23">
+    <row r="110" spans="3:29">
       <c r="C110" s="16" t="s">
         <v>118</v>
       </c>
@@ -15468,47 +15468,47 @@
       <c r="G110" s="18">
         <v>9.49761967575534</v>
       </c>
-      <c r="J110" s="4">
+      <c r="L110" s="4">
         <v>2050</v>
       </c>
-      <c r="K110" s="16" t="s">
+      <c r="M110" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L110" s="17" t="s">
+      <c r="N110" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="M110" s="17">
+      <c r="O110" s="17">
         <f t="shared" si="16"/>
         <v>2.38811314546794</v>
       </c>
-      <c r="N110" s="17">
+      <c r="P110" s="17">
         <f t="shared" si="17"/>
         <v>1.81338051569639</v>
       </c>
-      <c r="O110" s="17">
+      <c r="Q110" s="17">
         <f t="shared" si="18"/>
         <v>2.97275495851142</v>
       </c>
-      <c r="R110" s="4">
-        <v>0</v>
-      </c>
-      <c r="S110" s="16" t="s">
+      <c r="X110" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y110" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T110" s="17" t="s">
+      <c r="Z110" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="U110" s="17">
+      <c r="AA110" s="17">
         <v>5</v>
       </c>
-      <c r="V110" s="17">
+      <c r="AB110" s="17">
         <v>5</v>
       </c>
-      <c r="W110" s="17">
+      <c r="AC110" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="3:23">
+    <row r="111" spans="3:29">
       <c r="C111" s="16" t="s">
         <v>118</v>
       </c>
@@ -15524,47 +15524,47 @@
       <c r="G111" s="18">
         <v>5.20810707442889</v>
       </c>
-      <c r="J111" s="4">
+      <c r="L111" s="4">
         <v>2050</v>
       </c>
-      <c r="K111" s="16" t="s">
+      <c r="M111" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L111" s="17" t="s">
+      <c r="N111" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="M111" s="17">
+      <c r="O111" s="17">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="N111" s="17">
+      <c r="P111" s="17">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="O111" s="17">
+      <c r="Q111" s="17">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
-      <c r="R111" s="4">
-        <v>0</v>
-      </c>
-      <c r="S111" s="16" t="s">
+      <c r="X111" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T111" s="17" t="s">
+      <c r="Z111" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="U111" s="17">
+      <c r="AA111" s="17">
         <v>5</v>
       </c>
-      <c r="V111" s="17">
+      <c r="AB111" s="17">
         <v>5</v>
       </c>
-      <c r="W111" s="17">
+      <c r="AC111" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="3:23">
+    <row r="112" spans="3:29">
       <c r="C112" s="16" t="s">
         <v>118</v>
       </c>
@@ -15580,47 +15580,47 @@
       <c r="G112" s="18">
         <v>5.20810707442889</v>
       </c>
-      <c r="J112" s="4">
+      <c r="L112" s="4">
         <v>2050</v>
       </c>
-      <c r="K112" s="16" t="s">
+      <c r="M112" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L112" s="17" t="s">
+      <c r="N112" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="M112" s="17">
+      <c r="O112" s="17">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="N112" s="17">
+      <c r="P112" s="17">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="O112" s="17">
+      <c r="Q112" s="17">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
-      <c r="R112" s="4">
-        <v>0</v>
-      </c>
-      <c r="S112" s="16" t="s">
+      <c r="X112" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y112" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T112" s="17" t="s">
+      <c r="Z112" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="U112" s="17">
+      <c r="AA112" s="17">
         <v>5</v>
       </c>
-      <c r="V112" s="17">
+      <c r="AB112" s="17">
         <v>5</v>
       </c>
-      <c r="W112" s="17">
+      <c r="AC112" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="3:23">
+    <row r="113" spans="3:29">
       <c r="C113" s="16" t="s">
         <v>118</v>
       </c>
@@ -15636,47 +15636,47 @@
       <c r="G113" s="18">
         <v>5.20810707442889</v>
       </c>
-      <c r="J113" s="4">
+      <c r="L113" s="4">
         <v>2050</v>
       </c>
-      <c r="K113" s="16" t="s">
+      <c r="M113" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L113" s="17" t="s">
+      <c r="N113" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="M113" s="17">
+      <c r="O113" s="17">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="N113" s="17">
+      <c r="P113" s="17">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="O113" s="17">
+      <c r="Q113" s="17">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
-      <c r="R113" s="4">
-        <v>0</v>
-      </c>
-      <c r="S113" s="16" t="s">
+      <c r="X113" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y113" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T113" s="17" t="s">
+      <c r="Z113" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="U113" s="17">
+      <c r="AA113" s="17">
         <v>5</v>
       </c>
-      <c r="V113" s="17">
+      <c r="AB113" s="17">
         <v>5</v>
       </c>
-      <c r="W113" s="17">
+      <c r="AC113" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="3:23">
+    <row r="114" spans="3:29">
       <c r="C114" s="16" t="s">
         <v>118</v>
       </c>
@@ -15692,47 +15692,47 @@
       <c r="G114" s="18">
         <v>5.20810707442889</v>
       </c>
-      <c r="J114" s="4">
+      <c r="L114" s="4">
         <v>2050</v>
       </c>
-      <c r="K114" s="16" t="s">
+      <c r="M114" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L114" s="17" t="s">
+      <c r="N114" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="M114" s="17">
+      <c r="O114" s="17">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="N114" s="17">
+      <c r="P114" s="17">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="O114" s="17">
+      <c r="Q114" s="17">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
-      <c r="R114" s="4">
-        <v>0</v>
-      </c>
-      <c r="S114" s="16" t="s">
+      <c r="X114" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y114" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T114" s="17" t="s">
+      <c r="Z114" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="U114" s="17">
+      <c r="AA114" s="17">
         <v>5</v>
       </c>
-      <c r="V114" s="17">
+      <c r="AB114" s="17">
         <v>5</v>
       </c>
-      <c r="W114" s="17">
+      <c r="AC114" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="3:23">
+    <row r="115" spans="3:29">
       <c r="C115" s="16" t="s">
         <v>118</v>
       </c>
@@ -15748,47 +15748,47 @@
       <c r="G115" s="18">
         <v>5.20810707442889</v>
       </c>
-      <c r="J115" s="4">
+      <c r="L115" s="4">
         <v>2050</v>
       </c>
-      <c r="K115" s="16" t="s">
+      <c r="M115" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L115" s="17" t="s">
+      <c r="N115" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="M115" s="17">
+      <c r="O115" s="17">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="N115" s="17">
+      <c r="P115" s="17">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="O115" s="17">
+      <c r="Q115" s="17">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
-      <c r="R115" s="4">
-        <v>0</v>
-      </c>
-      <c r="S115" s="16" t="s">
+      <c r="X115" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y115" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T115" s="17" t="s">
+      <c r="Z115" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="U115" s="17">
+      <c r="AA115" s="17">
         <v>5</v>
       </c>
-      <c r="V115" s="17">
+      <c r="AB115" s="17">
         <v>5</v>
       </c>
-      <c r="W115" s="17">
+      <c r="AC115" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="3:23">
+    <row r="116" spans="3:29">
       <c r="C116" s="16" t="s">
         <v>118</v>
       </c>
@@ -15804,47 +15804,47 @@
       <c r="G116" s="18">
         <v>5.20810707442889</v>
       </c>
-      <c r="J116" s="4">
+      <c r="L116" s="4">
         <v>2050</v>
       </c>
-      <c r="K116" s="16" t="s">
+      <c r="M116" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L116" s="17" t="s">
+      <c r="N116" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="M116" s="17">
+      <c r="O116" s="17">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="N116" s="17">
+      <c r="P116" s="17">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="O116" s="17">
+      <c r="Q116" s="17">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
-      <c r="R116" s="4">
-        <v>0</v>
-      </c>
-      <c r="S116" s="16" t="s">
+      <c r="X116" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T116" s="17" t="s">
+      <c r="Z116" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="U116" s="17">
+      <c r="AA116" s="17">
         <v>5</v>
       </c>
-      <c r="V116" s="17">
+      <c r="AB116" s="17">
         <v>5</v>
       </c>
-      <c r="W116" s="17">
+      <c r="AC116" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="3:23">
+    <row r="117" spans="3:29">
       <c r="C117" s="16" t="s">
         <v>118</v>
       </c>
@@ -15860,47 +15860,47 @@
       <c r="G117" s="18">
         <v>5.20810707442889</v>
       </c>
-      <c r="J117" s="4">
+      <c r="L117" s="4">
         <v>2050</v>
       </c>
-      <c r="K117" s="16" t="s">
+      <c r="M117" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L117" s="17" t="s">
+      <c r="N117" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="M117" s="17">
+      <c r="O117" s="17">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="N117" s="17">
+      <c r="P117" s="17">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="O117" s="17">
+      <c r="Q117" s="17">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
-      <c r="R117" s="4">
-        <v>0</v>
-      </c>
-      <c r="S117" s="16" t="s">
+      <c r="X117" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y117" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T117" s="17" t="s">
+      <c r="Z117" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="U117" s="17">
+      <c r="AA117" s="17">
         <v>5</v>
       </c>
-      <c r="V117" s="17">
+      <c r="AB117" s="17">
         <v>5</v>
       </c>
-      <c r="W117" s="17">
+      <c r="AC117" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="3:23">
+    <row r="118" spans="3:29">
       <c r="C118" s="16" t="s">
         <v>118</v>
       </c>
@@ -15916,47 +15916,47 @@
       <c r="G118" s="18">
         <v>4.4384597641857</v>
       </c>
-      <c r="J118" s="4">
+      <c r="L118" s="4">
         <v>2050</v>
       </c>
-      <c r="K118" s="16" t="s">
+      <c r="M118" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L118" s="17" t="s">
+      <c r="N118" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="M118" s="17">
+      <c r="O118" s="17">
         <f t="shared" si="16"/>
         <v>1.1160211134365</v>
       </c>
-      <c r="N118" s="17">
+      <c r="P118" s="17">
         <f t="shared" si="17"/>
         <v>0.847435113780397</v>
       </c>
-      <c r="O118" s="17">
+      <c r="Q118" s="17">
         <f t="shared" si="18"/>
         <v>1.38923790619012</v>
       </c>
-      <c r="R118" s="4">
-        <v>0</v>
-      </c>
-      <c r="S118" s="16" t="s">
+      <c r="X118" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y118" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T118" s="17" t="s">
+      <c r="Z118" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="U118" s="17">
+      <c r="AA118" s="17">
         <v>5</v>
       </c>
-      <c r="V118" s="17">
+      <c r="AB118" s="17">
         <v>5</v>
       </c>
-      <c r="W118" s="17">
+      <c r="AC118" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="3:23">
+    <row r="119" spans="3:29">
       <c r="C119" s="16" t="s">
         <v>118</v>
       </c>
@@ -15972,47 +15972,47 @@
       <c r="G119" s="18">
         <v>4.48241960206338</v>
       </c>
-      <c r="J119" s="4">
+      <c r="L119" s="4">
         <v>2050</v>
       </c>
-      <c r="K119" s="16" t="s">
+      <c r="M119" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L119" s="17" t="s">
+      <c r="N119" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="M119" s="17">
+      <c r="O119" s="17">
         <f t="shared" si="16"/>
         <v>1.1270745266028</v>
       </c>
-      <c r="N119" s="17">
+      <c r="P119" s="17">
         <f t="shared" si="17"/>
         <v>0.855828380619012</v>
       </c>
-      <c r="O119" s="17">
+      <c r="Q119" s="17">
         <f t="shared" si="18"/>
         <v>1.40299733544584</v>
       </c>
-      <c r="R119" s="4">
-        <v>0</v>
-      </c>
-      <c r="S119" s="16" t="s">
+      <c r="X119" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y119" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T119" s="17" t="s">
+      <c r="Z119" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="U119" s="17">
+      <c r="AA119" s="17">
         <v>5</v>
       </c>
-      <c r="V119" s="17">
+      <c r="AB119" s="17">
         <v>5</v>
       </c>
-      <c r="W119" s="17">
+      <c r="AC119" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="3:23">
+    <row r="120" spans="3:29">
       <c r="C120" s="16" t="s">
         <v>118</v>
       </c>
@@ -16028,47 +16028,47 @@
       <c r="G120" s="18">
         <v>4.4384597641857</v>
       </c>
-      <c r="J120" s="4">
+      <c r="L120" s="4">
         <v>2050</v>
       </c>
-      <c r="K120" s="16" t="s">
+      <c r="M120" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L120" s="17" t="s">
+      <c r="N120" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="M120" s="17">
+      <c r="O120" s="17">
         <f t="shared" si="16"/>
         <v>1.1160211134365</v>
       </c>
-      <c r="N120" s="17">
+      <c r="P120" s="17">
         <f t="shared" si="17"/>
         <v>0.847435113780397</v>
       </c>
-      <c r="O120" s="17">
+      <c r="Q120" s="17">
         <f t="shared" si="18"/>
         <v>1.38923790619012</v>
       </c>
-      <c r="R120" s="4">
-        <v>0</v>
-      </c>
-      <c r="S120" s="16" t="s">
+      <c r="X120" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y120" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T120" s="17" t="s">
+      <c r="Z120" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="U120" s="17">
+      <c r="AA120" s="17">
         <v>5</v>
       </c>
-      <c r="V120" s="17">
+      <c r="AB120" s="17">
         <v>5</v>
       </c>
-      <c r="W120" s="17">
+      <c r="AC120" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="3:23">
+    <row r="121" spans="3:29">
       <c r="C121" s="16" t="s">
         <v>118</v>
       </c>
@@ -16084,47 +16084,47 @@
       <c r="G121" s="18">
         <v>4.43956890198968</v>
       </c>
-      <c r="J121" s="4">
+      <c r="L121" s="4">
         <v>2050</v>
       </c>
-      <c r="K121" s="16" t="s">
+      <c r="M121" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L121" s="17" t="s">
+      <c r="N121" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="M121" s="17">
+      <c r="O121" s="17">
         <f t="shared" si="16"/>
         <v>1.11630000712356</v>
       </c>
-      <c r="N121" s="17">
+      <c r="P121" s="17">
         <f t="shared" si="17"/>
         <v>0.847646901989683</v>
       </c>
-      <c r="O121" s="17">
+      <c r="Q121" s="17">
         <f t="shared" si="18"/>
         <v>1.38958506632277</v>
       </c>
-      <c r="R121" s="4">
-        <v>0</v>
-      </c>
-      <c r="S121" s="16" t="s">
+      <c r="X121" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y121" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T121" s="17" t="s">
+      <c r="Z121" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="U121" s="17">
+      <c r="AA121" s="17">
         <v>5</v>
       </c>
-      <c r="V121" s="17">
+      <c r="AB121" s="17">
         <v>5</v>
       </c>
-      <c r="W121" s="17">
+      <c r="AC121" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="122" spans="3:23">
+    <row r="122" spans="3:29">
       <c r="C122" s="16" t="s">
         <v>118</v>
       </c>
@@ -16140,47 +16140,47 @@
       <c r="G122" s="18">
         <v>4.43882940309506</v>
       </c>
-      <c r="J122" s="4">
+      <c r="L122" s="4">
         <v>2050</v>
       </c>
-      <c r="K122" s="16" t="s">
+      <c r="M122" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L122" s="17" t="s">
+      <c r="N122" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="M122" s="17">
+      <c r="O122" s="17">
         <f t="shared" si="16"/>
         <v>1.11611406005895</v>
       </c>
-      <c r="N122" s="17">
+      <c r="P122" s="17">
         <f t="shared" si="17"/>
         <v>0.847505694473101</v>
       </c>
-      <c r="O122" s="17">
+      <c r="Q122" s="17">
         <f t="shared" si="18"/>
         <v>1.38935360316875</v>
       </c>
-      <c r="R122" s="4">
-        <v>0</v>
-      </c>
-      <c r="S122" s="16" t="s">
+      <c r="X122" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y122" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T122" s="17" t="s">
+      <c r="Z122" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="U122" s="17">
+      <c r="AA122" s="17">
         <v>5</v>
       </c>
-      <c r="V122" s="17">
+      <c r="AB122" s="17">
         <v>5</v>
       </c>
-      <c r="W122" s="17">
+      <c r="AC122" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="123" spans="3:23">
+    <row r="123" spans="3:29">
       <c r="C123" s="16" t="s">
         <v>118</v>
       </c>
@@ -16196,47 +16196,47 @@
       <c r="G123" s="18">
         <v>4.4384597641857</v>
       </c>
-      <c r="J123" s="4">
+      <c r="L123" s="4">
         <v>2050</v>
       </c>
-      <c r="K123" s="16" t="s">
+      <c r="M123" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L123" s="17" t="s">
+      <c r="N123" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="M123" s="17">
+      <c r="O123" s="17">
         <f t="shared" si="16"/>
         <v>1.1160211134365</v>
       </c>
-      <c r="N123" s="17">
+      <c r="P123" s="17">
         <f t="shared" si="17"/>
         <v>0.847435113780397</v>
       </c>
-      <c r="O123" s="17">
+      <c r="Q123" s="17">
         <f t="shared" si="18"/>
         <v>1.38923790619012</v>
       </c>
-      <c r="R123" s="4">
-        <v>0</v>
-      </c>
-      <c r="S123" s="16" t="s">
+      <c r="X123" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y123" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T123" s="17" t="s">
+      <c r="Z123" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="U123" s="17">
+      <c r="AA123" s="17">
         <v>5</v>
       </c>
-      <c r="V123" s="17">
+      <c r="AB123" s="17">
         <v>5</v>
       </c>
-      <c r="W123" s="17">
+      <c r="AC123" s="17">
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="3:23">
+    <row r="124" spans="3:29">
       <c r="C124" s="16" t="s">
         <v>118</v>
       </c>
@@ -16252,43 +16252,43 @@
       <c r="G124" s="18">
         <v>4.43772063375092</v>
       </c>
-      <c r="J124" s="4">
+      <c r="L124" s="4">
         <v>2050</v>
       </c>
-      <c r="K124" s="16" t="s">
+      <c r="M124" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="L124" s="19" t="s">
+      <c r="N124" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="M124" s="17">
+      <c r="O124" s="17">
         <f t="shared" si="16"/>
         <v>1.11583526632277</v>
       </c>
-      <c r="N124" s="17">
+      <c r="P124" s="17">
         <f t="shared" si="17"/>
         <v>0.847293998526159</v>
       </c>
-      <c r="O124" s="17">
+      <c r="Q124" s="17">
         <f t="shared" si="18"/>
         <v>1.38900655836404</v>
       </c>
-      <c r="R124" s="4">
-        <v>0</v>
-      </c>
-      <c r="S124" s="16" t="s">
+      <c r="X124" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y124" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="T124" s="17" t="s">
+      <c r="Z124" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="U124" s="17">
+      <c r="AA124" s="17">
         <v>5</v>
       </c>
-      <c r="V124" s="17">
+      <c r="AB124" s="17">
         <v>5</v>
       </c>
-      <c r="W124" s="17">
+      <c r="AC124" s="17">
         <v>5</v>
       </c>
     </row>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -671,7 +671,7 @@
     <numFmt numFmtId="178" formatCode="0.0"/>
     <numFmt numFmtId="179" formatCode="0.000"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -685,13 +685,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -1213,28 +1206,31 @@
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1243,125 +1239,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1373,16 +1366,15 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="51" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -1871,29 +1863,29 @@
   <dimension ref="A1:AA281"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="22" customWidth="1"/>
-    <col min="2" max="2" width="8.85454545454546" style="22" customWidth="1"/>
-    <col min="3" max="3" width="4.70909090909091" style="22" customWidth="1"/>
-    <col min="4" max="4" width="8.85454545454546" style="22" customWidth="1"/>
-    <col min="5" max="5" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="6" max="6" width="4.28181818181818" style="22" customWidth="1"/>
-    <col min="7" max="7" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="8" max="8" width="4.57272727272727" style="22" customWidth="1"/>
-    <col min="9" max="9" width="4" style="22" customWidth="1"/>
-    <col min="10" max="10" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="11" max="11" width="4.57272727272727" style="22" customWidth="1"/>
-    <col min="12" max="12" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="13" max="13" width="4" style="22" customWidth="1"/>
-    <col min="14" max="14" width="4.28181818181818" style="22" customWidth="1"/>
-    <col min="15" max="16" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="17" max="18" width="4.57272727272727" style="22" customWidth="1"/>
-    <col min="19" max="19" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="20" max="20" width="5" style="22" customWidth="1"/>
-    <col min="21" max="21" width="11.7090909090909" style="22" customWidth="1"/>
-    <col min="22" max="22" width="10.7090909090909" style="22" customWidth="1"/>
-    <col min="23" max="23" width="13.1363636363636" style="22" customWidth="1"/>
-    <col min="24" max="259" width="11.4272727272727" style="22" customWidth="1"/>
-    <col min="260" max="16384" width="9.13636363636364" style="22"/>
+    <col min="1" max="1" width="15" style="21" customWidth="1"/>
+    <col min="2" max="2" width="8.85454545454546" style="21" customWidth="1"/>
+    <col min="3" max="3" width="4.70909090909091" style="21" customWidth="1"/>
+    <col min="4" max="4" width="8.85454545454546" style="21" customWidth="1"/>
+    <col min="5" max="5" width="4.42727272727273" style="21" customWidth="1"/>
+    <col min="6" max="6" width="4.28181818181818" style="21" customWidth="1"/>
+    <col min="7" max="7" width="4.42727272727273" style="21" customWidth="1"/>
+    <col min="8" max="8" width="4.57272727272727" style="21" customWidth="1"/>
+    <col min="9" max="9" width="4" style="21" customWidth="1"/>
+    <col min="10" max="10" width="4.42727272727273" style="21" customWidth="1"/>
+    <col min="11" max="11" width="4.57272727272727" style="21" customWidth="1"/>
+    <col min="12" max="12" width="4.42727272727273" style="21" customWidth="1"/>
+    <col min="13" max="13" width="4" style="21" customWidth="1"/>
+    <col min="14" max="14" width="4.28181818181818" style="21" customWidth="1"/>
+    <col min="15" max="16" width="4.42727272727273" style="21" customWidth="1"/>
+    <col min="17" max="18" width="4.57272727272727" style="21" customWidth="1"/>
+    <col min="19" max="19" width="4.42727272727273" style="21" customWidth="1"/>
+    <col min="20" max="20" width="5" style="21" customWidth="1"/>
+    <col min="21" max="21" width="11.7090909090909" style="21" customWidth="1"/>
+    <col min="22" max="22" width="10.7090909090909" style="21" customWidth="1"/>
+    <col min="23" max="23" width="13.1363636363636" style="21" customWidth="1"/>
+    <col min="24" max="259" width="11.4272727272727" style="21" customWidth="1"/>
+    <col min="260" max="16384" width="9.13636363636364" style="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.5" spans="1:21">
@@ -2972,7 +2964,7 @@
       <c r="AA34" s="5"/>
     </row>
     <row r="35" ht="12.5" spans="1:27">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="21" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -3000,7 +2992,7 @@
       <c r="AA35" s="5"/>
     </row>
     <row r="36" ht="12.5" spans="1:27">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="21" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -3028,7 +3020,7 @@
       <c r="AA36" s="5"/>
     </row>
     <row r="37" ht="12.5" spans="1:27">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="21" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -3056,7 +3048,7 @@
       <c r="AA37" s="5"/>
     </row>
     <row r="38" ht="12.5" spans="1:27">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="21" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -3084,7 +3076,7 @@
       <c r="AA38" s="5"/>
     </row>
     <row r="39" ht="12.5" spans="1:27">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="21" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -8465,7 +8457,10 @@
     <col min="34" max="37" width="6" customWidth="1"/>
     <col min="38" max="38" width="15.5454545454545" customWidth="1"/>
     <col min="39" max="39" width="13.6363636363636" customWidth="1"/>
-    <col min="40" max="49" width="6" customWidth="1"/>
+    <col min="40" max="43" width="6" customWidth="1"/>
+    <col min="44" max="44" width="8.45454545454546" customWidth="1"/>
+    <col min="45" max="45" width="10.3636363636364" customWidth="1"/>
+    <col min="46" max="49" width="6" customWidth="1"/>
     <col min="50" max="50" width="12.2818181818182" customWidth="1"/>
     <col min="51" max="51" width="13.6363636363636" customWidth="1"/>
   </cols>
@@ -8750,7 +8745,7 @@
       <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="22" t="s">
         <v>92</v>
       </c>
       <c r="F14">
@@ -8809,7 +8804,7 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="22" t="s">
         <v>92</v>
       </c>
       <c r="C18">
@@ -8818,7 +8813,7 @@
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="22" t="s">
         <v>100</v>
       </c>
       <c r="F18" t="s">
@@ -11606,7 +11601,7 @@
       <c r="D45">
         <v>2020</v>
       </c>
-      <c r="E45" s="24" t="s">
+      <c r="E45" s="23" t="s">
         <v>119</v>
       </c>
       <c r="F45" t="s">
@@ -11690,7 +11685,7 @@
       <c r="D55" t="s">
         <v>126</v>
       </c>
-      <c r="E55" s="23" t="s">
+      <c r="E55" s="22" t="s">
         <v>127</v>
       </c>
     </row>
@@ -11814,75 +11809,72 @@
       <c r="Y63" s="9"/>
       <c r="Z63" s="9"/>
     </row>
-    <row r="64" s="1" customFormat="1" ht="28" spans="1:1">
-      <c r="A64" s="11"/>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="1:91">
-      <c r="A65" s="2"/>
-      <c r="B65" s="12" t="s">
+    <row r="64" s="1" customFormat="1" spans="1:91">
+      <c r="A64" s="2"/>
+      <c r="B64" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" s="2"/>
-      <c r="Q65" s="2"/>
-      <c r="R65" s="2"/>
-      <c r="S65" s="2"/>
-      <c r="T65" s="2"/>
-      <c r="U65" s="2"/>
-      <c r="V65" s="2"/>
-      <c r="W65" s="2"/>
-      <c r="X65" s="2"/>
-      <c r="Y65" s="2"/>
-      <c r="Z65" s="2"/>
-      <c r="AA65" s="2"/>
-      <c r="AB65" s="2"/>
-      <c r="AC65" s="2"/>
-      <c r="AD65" s="2"/>
-      <c r="AE65" s="2"/>
-      <c r="AF65" s="2"/>
-      <c r="AG65" s="2"/>
-      <c r="AH65" s="2"/>
-      <c r="AI65" s="2"/>
-      <c r="AJ65" s="2"/>
-      <c r="AK65" s="2"/>
-      <c r="AL65" s="2"/>
-      <c r="AM65" s="2"/>
-      <c r="AN65" s="2"/>
-      <c r="AO65" s="2"/>
-      <c r="AP65" s="2"/>
-      <c r="AQ65" s="2"/>
-      <c r="AR65" s="2"/>
-      <c r="AS65" s="2" t="s">
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="2"/>
+      <c r="T64" s="2"/>
+      <c r="U64" s="2"/>
+      <c r="V64" s="2"/>
+      <c r="W64" s="2"/>
+      <c r="X64" s="2"/>
+      <c r="Y64" s="2"/>
+      <c r="Z64" s="2"/>
+      <c r="AA64" s="2"/>
+      <c r="AB64" s="2"/>
+      <c r="AC64" s="2"/>
+      <c r="AD64" s="2"/>
+      <c r="AE64" s="2"/>
+      <c r="AF64" s="2"/>
+      <c r="AG64" s="2"/>
+      <c r="AH64" s="2"/>
+      <c r="AI64" s="2"/>
+      <c r="AJ64" s="2"/>
+      <c r="AK64" s="2"/>
+      <c r="AL64" s="2"/>
+      <c r="AM64" s="2"/>
+      <c r="AN64" s="2"/>
+      <c r="AO64" s="2"/>
+      <c r="AP64" s="2"/>
+      <c r="AQ64" s="2"/>
+      <c r="AR64" s="2"/>
+      <c r="AS64" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AT65" s="2"/>
-      <c r="AU65" s="2"/>
-      <c r="AV65" s="2"/>
-      <c r="AW65" s="2"/>
-      <c r="AX65" s="2"/>
-      <c r="AY65" s="2"/>
-      <c r="AZ65" s="2"/>
-      <c r="BA65" s="2"/>
-      <c r="CG65" s="20"/>
-      <c r="CH65" s="20"/>
-      <c r="CI65" s="20" t="s">
+      <c r="AT64" s="2"/>
+      <c r="AU64" s="2"/>
+      <c r="AV64" s="2"/>
+      <c r="AW64" s="2"/>
+      <c r="AX64" s="2"/>
+      <c r="AY64" s="2"/>
+      <c r="AZ64" s="2"/>
+      <c r="BA64" s="2"/>
+      <c r="CG64" s="12"/>
+      <c r="CH64" s="12"/>
+      <c r="CI64" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="CJ65" s="20"/>
-      <c r="CK65" s="20"/>
-      <c r="CL65" s="20"/>
-      <c r="CM65" s="20"/>
+      <c r="CJ64" s="12"/>
+      <c r="CK64" s="12"/>
+      <c r="CL64" s="12"/>
+      <c r="CM64" s="12"/>
     </row>
     <row r="66" s="2" customFormat="1" spans="1:91">
       <c r="A66" s="2" t="s">
@@ -11999,10 +11991,10 @@
       <c r="AL66" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM66" s="12" t="s">
+      <c r="AM66" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="AN66" s="12" t="s">
+      <c r="AN66" s="11" t="s">
         <v>59</v>
       </c>
       <c r="AQ66" s="2" t="s">
@@ -12128,25 +12120,25 @@
       <c r="CE66" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="CG66" s="21" t="s">
+      <c r="CG66" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="CH66" s="21" t="s">
+      <c r="CH66" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="CI66" s="21" t="s">
+      <c r="CI66" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="CJ66" s="21" t="s">
+      <c r="CJ66" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="CK66" s="21" t="s">
+      <c r="CK66" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="CL66" s="21" t="s">
+      <c r="CL66" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="CM66" s="21" t="s">
+      <c r="CM66" s="20" t="s">
         <v>59</v>
       </c>
     </row>
@@ -12427,25 +12419,25 @@
       <c r="CE67" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="CG67" s="21">
-        <v>0</v>
-      </c>
-      <c r="CH67" s="21" t="s">
+      <c r="CG67" s="20">
+        <v>0</v>
+      </c>
+      <c r="CH67" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="CI67" s="21" t="s">
+      <c r="CI67" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="CJ67" s="21" t="s">
+      <c r="CJ67" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK67" s="21">
+      <c r="CK67" s="20">
         <v>5</v>
       </c>
-      <c r="CL67" s="21" t="s">
+      <c r="CL67" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="CM67" s="21" t="s">
+      <c r="CM67" s="20" t="s">
         <v>135</v>
       </c>
     </row>
@@ -12727,25 +12719,25 @@
       <c r="CE68" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="CG68" s="21">
-        <v>0</v>
-      </c>
-      <c r="CH68" s="21" t="s">
+      <c r="CG68" s="20">
+        <v>0</v>
+      </c>
+      <c r="CH68" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="CI68" s="21" t="s">
+      <c r="CI68" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="CJ68" s="21" t="s">
+      <c r="CJ68" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK68" s="21">
+      <c r="CK68" s="20">
         <v>5</v>
       </c>
-      <c r="CL68" s="21" t="s">
+      <c r="CL68" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="CM68" s="21" t="s">
+      <c r="CM68" s="20" t="s">
         <v>136</v>
       </c>
     </row>
@@ -13027,25 +13019,25 @@
       <c r="CE69" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="CG69" s="21">
-        <v>0</v>
-      </c>
-      <c r="CH69" s="21" t="s">
+      <c r="CG69" s="20">
+        <v>0</v>
+      </c>
+      <c r="CH69" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="CI69" s="21" t="s">
+      <c r="CI69" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="CJ69" s="21" t="s">
+      <c r="CJ69" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK69" s="21">
+      <c r="CK69" s="20">
         <v>5</v>
       </c>
-      <c r="CL69" s="21" t="s">
+      <c r="CL69" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="CM69" s="21" t="s">
+      <c r="CM69" s="20" t="s">
         <v>137</v>
       </c>
     </row>
@@ -13327,25 +13319,25 @@
       <c r="CE70" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="CG70" s="21">
-        <v>0</v>
-      </c>
-      <c r="CH70" s="21" t="s">
+      <c r="CG70" s="20">
+        <v>0</v>
+      </c>
+      <c r="CH70" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="CI70" s="21" t="s">
+      <c r="CI70" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="CJ70" s="21" t="s">
+      <c r="CJ70" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK70" s="21">
+      <c r="CK70" s="20">
         <v>5</v>
       </c>
-      <c r="CL70" s="21" t="s">
+      <c r="CL70" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="CM70" s="21" t="s">
+      <c r="CM70" s="20" t="s">
         <v>138</v>
       </c>
     </row>
@@ -13627,25 +13619,25 @@
       <c r="CE71" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="CG71" s="21">
-        <v>0</v>
-      </c>
-      <c r="CH71" s="21" t="s">
+      <c r="CG71" s="20">
+        <v>0</v>
+      </c>
+      <c r="CH71" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="CI71" s="21" t="s">
+      <c r="CI71" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="CJ71" s="21" t="s">
+      <c r="CJ71" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK71" s="21">
+      <c r="CK71" s="20">
         <v>5</v>
       </c>
-      <c r="CL71" s="21" t="s">
+      <c r="CL71" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="CM71" s="21" t="s">
+      <c r="CM71" s="20" t="s">
         <v>139</v>
       </c>
     </row>
@@ -13927,25 +13919,25 @@
       <c r="CE72" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="CG72" s="21">
-        <v>0</v>
-      </c>
-      <c r="CH72" s="21" t="s">
+      <c r="CG72" s="20">
+        <v>0</v>
+      </c>
+      <c r="CH72" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="CI72" s="21" t="s">
+      <c r="CI72" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="CJ72" s="21" t="s">
+      <c r="CJ72" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK72" s="21">
+      <c r="CK72" s="20">
         <v>5</v>
       </c>
-      <c r="CL72" s="21" t="s">
+      <c r="CL72" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="CM72" s="21" t="s">
+      <c r="CM72" s="20" t="s">
         <v>140</v>
       </c>
     </row>
@@ -14227,25 +14219,25 @@
       <c r="CE73" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="CG73" s="21">
-        <v>0</v>
-      </c>
-      <c r="CH73" s="20" t="s">
+      <c r="CG73" s="20">
+        <v>0</v>
+      </c>
+      <c r="CH73" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="CI73" s="20" t="s">
+      <c r="CI73" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="CJ73" s="21" t="s">
+      <c r="CJ73" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK73" s="21">
+      <c r="CK73" s="20">
         <v>5</v>
       </c>
-      <c r="CL73" s="20" t="s">
+      <c r="CL73" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="CM73" s="20" t="s">
+      <c r="CM73" s="12" t="s">
         <v>141</v>
       </c>
     </row>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" updateLinks="never"/>
   <bookViews>
-    <workbookView windowHeight="7510" activeTab="1"/>
+    <workbookView windowHeight="7520" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TechSelection" sheetId="21" r:id="rId1"/>
@@ -1366,8 +1366,8 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -8455,8 +8455,7 @@
     <col min="25" max="25" width="9.54545454545454" customWidth="1"/>
     <col min="26" max="33" width="7.13636363636364" customWidth="1"/>
     <col min="34" max="37" width="6" customWidth="1"/>
-    <col min="38" max="38" width="15.5454545454545" customWidth="1"/>
-    <col min="39" max="39" width="13.6363636363636" customWidth="1"/>
+    <col min="38" max="39" width="15.5454545454545" customWidth="1"/>
     <col min="40" max="43" width="6" customWidth="1"/>
     <col min="44" max="44" width="8.45454545454546" customWidth="1"/>
     <col min="45" max="45" width="10.3636363636364" customWidth="1"/>
@@ -11782,7 +11781,7 @@
       <c r="Y62" s="9"/>
       <c r="Z62" s="9"/>
     </row>
-    <row r="63" spans="2:26">
+    <row r="63" spans="2:87">
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
@@ -11808,73 +11807,73 @@
       <c r="X63" s="9"/>
       <c r="Y63" s="9"/>
       <c r="Z63" s="9"/>
-    </row>
-    <row r="64" s="1" customFormat="1" spans="1:91">
-      <c r="A64" s="2"/>
-      <c r="B64" s="11" t="s">
+      <c r="AS63" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-      <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
-      <c r="P64" s="2"/>
-      <c r="Q64" s="2"/>
-      <c r="R64" s="2"/>
-      <c r="S64" s="2"/>
-      <c r="T64" s="2"/>
-      <c r="U64" s="2"/>
-      <c r="V64" s="2"/>
-      <c r="W64" s="2"/>
-      <c r="X64" s="2"/>
-      <c r="Y64" s="2"/>
-      <c r="Z64" s="2"/>
-      <c r="AA64" s="2"/>
-      <c r="AB64" s="2"/>
-      <c r="AC64" s="2"/>
-      <c r="AD64" s="2"/>
-      <c r="AE64" s="2"/>
-      <c r="AF64" s="2"/>
-      <c r="AG64" s="2"/>
-      <c r="AH64" s="2"/>
-      <c r="AI64" s="2"/>
-      <c r="AJ64" s="2"/>
-      <c r="AK64" s="2"/>
-      <c r="AL64" s="2"/>
-      <c r="AM64" s="2"/>
-      <c r="AN64" s="2"/>
-      <c r="AO64" s="2"/>
-      <c r="AP64" s="2"/>
-      <c r="AQ64" s="2"/>
-      <c r="AR64" s="2"/>
-      <c r="AS64" s="2" t="s">
+      <c r="CI63" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="AT64" s="2"/>
-      <c r="AU64" s="2"/>
-      <c r="AV64" s="2"/>
-      <c r="AW64" s="2"/>
-      <c r="AX64" s="2"/>
-      <c r="AY64" s="2"/>
-      <c r="AZ64" s="2"/>
-      <c r="BA64" s="2"/>
-      <c r="CG64" s="12"/>
-      <c r="CH64" s="12"/>
-      <c r="CI64" s="12" t="s">
+    </row>
+    <row r="65" s="1" customFormat="1" spans="1:91">
+      <c r="A65" s="2"/>
+      <c r="B65" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="CJ64" s="12"/>
-      <c r="CK64" s="12"/>
-      <c r="CL64" s="12"/>
-      <c r="CM64" s="12"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
+      <c r="T65" s="2"/>
+      <c r="U65" s="2"/>
+      <c r="V65" s="2"/>
+      <c r="W65" s="2"/>
+      <c r="X65" s="2"/>
+      <c r="Y65" s="2"/>
+      <c r="Z65" s="2"/>
+      <c r="AA65" s="2"/>
+      <c r="AB65" s="2"/>
+      <c r="AC65" s="2"/>
+      <c r="AD65" s="2"/>
+      <c r="AE65" s="2"/>
+      <c r="AF65" s="2"/>
+      <c r="AG65" s="2"/>
+      <c r="AH65" s="2"/>
+      <c r="AI65" s="2"/>
+      <c r="AJ65" s="2"/>
+      <c r="AK65" s="2"/>
+      <c r="AL65" s="2"/>
+      <c r="AM65" s="2"/>
+      <c r="AN65" s="2"/>
+      <c r="AO65" s="2"/>
+      <c r="AP65" s="2"/>
+      <c r="AQ65" s="2"/>
+      <c r="AR65" s="2"/>
+      <c r="AT65" s="2"/>
+      <c r="AU65" s="2"/>
+      <c r="AV65" s="2"/>
+      <c r="AW65" s="2"/>
+      <c r="AX65" s="2"/>
+      <c r="AY65" s="2"/>
+      <c r="AZ65" s="2"/>
+      <c r="BA65" s="2"/>
+      <c r="CG65" s="11"/>
+      <c r="CH65" s="11"/>
+      <c r="CJ65" s="11"/>
+      <c r="CK65" s="11"/>
+      <c r="CL65" s="11"/>
+      <c r="CM65" s="11"/>
     </row>
     <row r="66" s="2" customFormat="1" spans="1:91">
       <c r="A66" s="2" t="s">
@@ -11991,10 +11990,10 @@
       <c r="AL66" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM66" s="11" t="s">
+      <c r="AM66" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AN66" s="11" t="s">
+      <c r="AN66" s="12" t="s">
         <v>59</v>
       </c>
       <c r="AQ66" s="2" t="s">
@@ -14222,10 +14221,10 @@
       <c r="CG73" s="20">
         <v>0</v>
       </c>
-      <c r="CH73" s="12" t="s">
+      <c r="CH73" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="CI73" s="12" t="s">
+      <c r="CI73" s="11" t="s">
         <v>133</v>
       </c>
       <c r="CJ73" s="20" t="s">
@@ -14234,10 +14233,10 @@
       <c r="CK73" s="20">
         <v>5</v>
       </c>
-      <c r="CL73" s="12" t="s">
+      <c r="CL73" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="CM73" s="12" t="s">
+      <c r="CM73" s="11" t="s">
         <v>141</v>
       </c>
     </row>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="199">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -467,6 +467,12 @@
     <t>Saudi Arabia</t>
   </si>
   <si>
+    <t>cset</t>
+  </si>
+  <si>
+    <t>cn</t>
+  </si>
+  <si>
     <t>annual</t>
   </si>
   <si>
@@ -474,6 +480,9 @@
   </si>
   <si>
     <t>MINBatMaterials</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_MATO</t>
   </si>
   <si>
     <t>m_lithium</t>
@@ -8437,7 +8446,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:CM124"/>
+  <dimension ref="A2:CU124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="2" max="2" width="21.3727272727273" customWidth="1"/>
@@ -8456,7 +8465,9 @@
     <col min="26" max="33" width="7.13636363636364" customWidth="1"/>
     <col min="34" max="37" width="6" customWidth="1"/>
     <col min="38" max="39" width="15.5454545454545" customWidth="1"/>
-    <col min="40" max="43" width="6" customWidth="1"/>
+    <col min="40" max="40" width="22.6363636363636" customWidth="1"/>
+    <col min="41" max="41" width="13.6363636363636" customWidth="1"/>
+    <col min="42" max="43" width="6" customWidth="1"/>
     <col min="44" max="44" width="8.45454545454546" customWidth="1"/>
     <col min="45" max="45" width="10.3636363636364" customWidth="1"/>
     <col min="46" max="49" width="6" customWidth="1"/>
@@ -11781,7 +11792,7 @@
       <c r="Y62" s="9"/>
       <c r="Z62" s="9"/>
     </row>
-    <row r="63" spans="2:87">
+    <row r="63" spans="2:95">
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
@@ -11807,14 +11818,14 @@
       <c r="X63" s="9"/>
       <c r="Y63" s="9"/>
       <c r="Z63" s="9"/>
-      <c r="AS63" s="2" t="s">
+      <c r="BA63" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="CI63" s="11" t="s">
+      <c r="CQ63" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="65" s="1" customFormat="1" spans="1:91">
+    <row r="65" s="1" customFormat="1" spans="1:99">
       <c r="A65" s="2"/>
       <c r="B65" s="12" t="s">
         <v>73</v>
@@ -11858,24 +11869,24 @@
       <c r="AN65" s="2"/>
       <c r="AO65" s="2"/>
       <c r="AP65" s="2"/>
-      <c r="AQ65" s="2"/>
-      <c r="AR65" s="2"/>
-      <c r="AT65" s="2"/>
-      <c r="AU65" s="2"/>
-      <c r="AV65" s="2"/>
-      <c r="AW65" s="2"/>
-      <c r="AX65" s="2"/>
       <c r="AY65" s="2"/>
       <c r="AZ65" s="2"/>
-      <c r="BA65" s="2"/>
-      <c r="CG65" s="11"/>
-      <c r="CH65" s="11"/>
-      <c r="CJ65" s="11"/>
-      <c r="CK65" s="11"/>
-      <c r="CL65" s="11"/>
-      <c r="CM65" s="11"/>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="1:91">
+      <c r="BB65" s="2"/>
+      <c r="BC65" s="2"/>
+      <c r="BD65" s="2"/>
+      <c r="BE65" s="2"/>
+      <c r="BF65" s="2"/>
+      <c r="BG65" s="2"/>
+      <c r="BH65" s="2"/>
+      <c r="BI65" s="2"/>
+      <c r="CO65" s="11"/>
+      <c r="CP65" s="11"/>
+      <c r="CR65" s="11"/>
+      <c r="CS65" s="11"/>
+      <c r="CT65" s="11"/>
+      <c r="CU65" s="11"/>
+    </row>
+    <row r="66" s="2" customFormat="1" spans="1:99">
       <c r="A66" s="2" t="s">
         <v>130</v>
       </c>
@@ -11994,159 +12005,162 @@
         <v>45</v>
       </c>
       <c r="AN66" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="AO66" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AY66" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AZ66" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BA66" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="BB66" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="BC66" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="BD66" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="BE66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="BG66" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="BH66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="BJ66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="BK66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="BL66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="BM66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="BN66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="BO66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="BP66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="BQ66" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BR66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="BS66" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="BT66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="BU66" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="BV66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="BW66" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="BX66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="BY66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="BZ66" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA66" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="CC66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="CD66" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="CE66" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="CF66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="CG66" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="CH66" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="CI66" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="CJ66" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="CK66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="CL66" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="CM66" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AQ66" s="2" t="s">
+      <c r="CO66" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="AR66" s="2" t="s">
+      <c r="CP66" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="AS66" s="2" t="s">
+      <c r="CQ66" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="AT66" s="2" t="s">
+      <c r="CR66" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="AU66" s="2" t="s">
+      <c r="CS66" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="AV66" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AW66" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AY66" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="AZ66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="BA66" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="BB66" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="BC66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="BD66" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="BE66" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="BF66" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="BG66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="BH66" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="BI66" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BJ66" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="BK66" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="BL66" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="BM66" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="BN66" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="BO66" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="BP66" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="BQ66" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="BR66" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="BS66" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="BT66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="BU66" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="BV66" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="BW66" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="BX66" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="BY66" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="BZ66" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="CA66" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="CB66" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="CC66" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="CD66" s="2" t="s">
+      <c r="CT66" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="CE66" s="2" t="s">
+      <c r="CU66" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="CG66" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="CH66" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="CI66" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="CJ66" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="CK66" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="CL66" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="CM66" s="20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="67" s="2" customFormat="1" ht="14.5" spans="1:91">
+    </row>
+    <row r="67" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A67" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>68</v>
@@ -12290,74 +12304,53 @@
         <v>0</v>
       </c>
       <c r="AM67" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN67" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO67" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AY67" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AZ67" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AN67" s="1" t="s">
+      <c r="BA67" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AQ67" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AR67" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AS67" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AT67" s="2" t="s">
+      <c r="BB67" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU67" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV67" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW67" s="2">
+      <c r="BC67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE67" s="2">
         <v>310</v>
       </c>
-      <c r="AX67" s="2">
+      <c r="BF67" s="2">
         <v>6200</v>
       </c>
-      <c r="AY67" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB67" s="2">
+      <c r="BG67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ67" s="2">
         <v>250</v>
       </c>
-      <c r="BC67" s="2">
+      <c r="BK67" s="2">
         <v>2000</v>
       </c>
-      <c r="BD67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK67" s="2">
-        <v>0</v>
-      </c>
       <c r="BL67" s="2">
         <v>0</v>
       </c>
@@ -12368,84 +12361,108 @@
         <v>0</v>
       </c>
       <c r="BO67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW67" s="2">
         <v>12250</v>
       </c>
-      <c r="BP67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ67" s="2">
+      <c r="BX67" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY67" s="2">
         <v>1930</v>
       </c>
-      <c r="BR67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT67" s="2">
+      <c r="BZ67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB67" s="2">
         <v>3300</v>
       </c>
-      <c r="BU67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX67" s="2">
+      <c r="CC67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CE67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF67" s="2">
         <v>60</v>
       </c>
-      <c r="BY67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD67" s="2" t="s">
+      <c r="CG67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CI67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK67" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL67" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CM67" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="CO67" s="20">
+        <v>0</v>
+      </c>
+      <c r="CP67" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="CE67" s="2" t="s">
+      <c r="CQ67" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="CG67" s="20">
-        <v>0</v>
-      </c>
-      <c r="CH67" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="CI67" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="CJ67" s="20" t="s">
+      <c r="CR67" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK67" s="20">
+      <c r="CS67" s="20">
         <v>5</v>
       </c>
-      <c r="CL67" s="20" t="s">
+      <c r="CT67" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="CU67" s="20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" ht="14.5" spans="1:99">
+      <c r="A68" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="CM67" s="20" t="s">
+      <c r="B68" s="13" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" ht="14.5" spans="1:91">
-      <c r="A68" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>68</v>
@@ -12590,162 +12607,165 @@
         <v>0</v>
       </c>
       <c r="AM68" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN68" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO68" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="AY68" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AZ68" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AN68" s="1" t="s">
+      <c r="BA68" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BB68" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="BC68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF68" s="2">
+        <v>21000</v>
+      </c>
+      <c r="BG68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ68" s="2">
+        <v>16000</v>
+      </c>
+      <c r="BK68" s="2">
+        <v>2100</v>
+      </c>
+      <c r="BL68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BO68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW68" s="2">
+        <v>16000</v>
+      </c>
+      <c r="BX68" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY68" s="2">
+        <v>2570</v>
+      </c>
+      <c r="BZ68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB68" s="2">
+        <v>52900</v>
+      </c>
+      <c r="CC68" s="2">
+        <v>7500</v>
+      </c>
+      <c r="CD68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CE68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CI68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK68" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL68" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AQ68" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AR68" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AS68" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AT68" s="2" t="s">
+      <c r="CM68" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="CO68" s="20">
+        <v>0</v>
+      </c>
+      <c r="CP68" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="CQ68" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="CR68" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="AU68" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV68" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW68" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX68" s="2">
-        <v>21000</v>
-      </c>
-      <c r="AY68" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB68" s="2">
-        <v>16000</v>
-      </c>
-      <c r="BC68" s="2">
-        <v>2100</v>
-      </c>
-      <c r="BD68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO68" s="2">
-        <v>16000</v>
-      </c>
-      <c r="BP68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ68" s="2">
-        <v>2570</v>
-      </c>
-      <c r="BR68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT68" s="2">
-        <v>52900</v>
-      </c>
-      <c r="BU68" s="2">
-        <v>7500</v>
-      </c>
-      <c r="BV68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD68" s="2" t="s">
+      <c r="CS68" s="20">
+        <v>5</v>
+      </c>
+      <c r="CT68" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="CU68" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" ht="14.5" spans="1:99">
+      <c r="A69" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="CE68" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="CG68" s="20">
-        <v>0</v>
-      </c>
-      <c r="CH68" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="CI68" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="CJ68" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="CK68" s="20">
-        <v>5</v>
-      </c>
-      <c r="CL68" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="CM68" s="20" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" ht="14.5" spans="1:91">
-      <c r="A69" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="B69" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>68</v>
@@ -12890,74 +12910,53 @@
         <v>0</v>
       </c>
       <c r="AM69" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN69" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO69" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AY69" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AZ69" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AN69" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AQ69" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AR69" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AS69" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AT69" s="2" t="s">
+      <c r="BA69" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BB69" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU69" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV69" s="2">
+      <c r="BC69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD69" s="2">
         <v>13</v>
       </c>
-      <c r="AW69" s="2">
+      <c r="BE69" s="2">
         <v>4100</v>
       </c>
-      <c r="AX69" s="2">
+      <c r="BF69" s="2">
         <v>1500</v>
       </c>
-      <c r="AY69" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BC69" s="2">
+      <c r="BG69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BK69" s="2">
         <v>140</v>
       </c>
-      <c r="BD69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK69" s="2">
-        <v>0</v>
-      </c>
       <c r="BL69" s="2">
         <v>0</v>
       </c>
@@ -12968,84 +12967,108 @@
         <v>0</v>
       </c>
       <c r="BO69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV69" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW69" s="2">
         <v>500</v>
       </c>
-      <c r="BP69" s="2">
+      <c r="BX69" s="2">
         <v>36</v>
       </c>
-      <c r="BQ69" s="2">
+      <c r="BY69" s="2">
         <v>289</v>
       </c>
-      <c r="BR69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT69" s="2">
+      <c r="BZ69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB69" s="2">
         <v>1517</v>
       </c>
-      <c r="BU69" s="2">
+      <c r="CC69" s="2">
         <v>250</v>
       </c>
-      <c r="BV69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA69" s="2">
+      <c r="CD69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CE69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CI69" s="2">
         <v>36</v>
       </c>
-      <c r="CB69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD69" s="2" t="s">
+      <c r="CJ69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK69" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL69" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CM69" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="CO69" s="20">
+        <v>0</v>
+      </c>
+      <c r="CP69" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="CE69" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="CG69" s="20">
-        <v>0</v>
-      </c>
-      <c r="CH69" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="CI69" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="CJ69" s="20" t="s">
+      <c r="CQ69" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="CR69" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK69" s="20">
+      <c r="CS69" s="20">
         <v>5</v>
       </c>
-      <c r="CL69" s="20" t="s">
+      <c r="CT69" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="CU69" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" ht="14.5" spans="1:99">
+      <c r="A70" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="CM69" s="20" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" ht="14.5" spans="1:91">
-      <c r="A70" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="B70" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>68</v>
@@ -13190,162 +13213,165 @@
         <v>140000</v>
       </c>
       <c r="AM70" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN70" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO70" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AY70" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AZ70" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AN70" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="AQ70" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AR70" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AS70" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AT70" s="2" t="s">
+      <c r="BA70" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BB70" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU70" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV70" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW70" s="2">
+      <c r="BC70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE70" s="2">
         <v>74000</v>
       </c>
-      <c r="AX70" s="2">
+      <c r="BF70" s="2">
         <v>270000</v>
       </c>
-      <c r="AY70" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB70" s="2">
+      <c r="BG70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ70" s="2">
         <v>270000</v>
       </c>
-      <c r="BC70" s="2">
+      <c r="BK70" s="2">
         <v>280000</v>
       </c>
-      <c r="BD70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK70" s="2">
+      <c r="BL70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BN70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BO70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS70" s="2">
         <v>34000</v>
       </c>
-      <c r="BL70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO70" s="2">
+      <c r="BT70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW70" s="2">
         <v>275000</v>
       </c>
-      <c r="BP70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT70" s="2">
+      <c r="BX70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY70" s="2">
+        <v>0</v>
+      </c>
+      <c r="BZ70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CB70" s="2">
         <v>5000</v>
       </c>
-      <c r="BU70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW70" s="2">
+      <c r="CC70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CE70" s="2">
         <v>640000</v>
       </c>
-      <c r="BX70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC70" s="2">
+      <c r="CF70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CI70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ70" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK70" s="2">
         <v>140000</v>
       </c>
-      <c r="CD70" s="2" t="s">
+      <c r="CL70" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CM70" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="CO70" s="20">
+        <v>0</v>
+      </c>
+      <c r="CP70" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="CE70" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="CG70" s="20">
-        <v>0</v>
-      </c>
-      <c r="CH70" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="CI70" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="CJ70" s="20" t="s">
+      <c r="CQ70" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="CR70" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK70" s="20">
+      <c r="CS70" s="20">
         <v>5</v>
       </c>
-      <c r="CL70" s="20" t="s">
+      <c r="CT70" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="CU70" s="20" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" ht="14.5" spans="1:99">
+      <c r="A71" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="CM70" s="20" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" ht="14.5" spans="1:91">
-      <c r="A71" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="B71" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>68</v>
@@ -13490,47 +13516,26 @@
         <v>0</v>
       </c>
       <c r="AM71" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN71" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO71" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="AY71" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AZ71" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AN71" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="AQ71" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AR71" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AS71" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AT71" s="2" t="s">
+      <c r="BA71" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BB71" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU71" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV71" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW71" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX71" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY71" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB71" s="2">
-        <v>0</v>
-      </c>
       <c r="BC71" s="2">
         <v>0</v>
       </c>
@@ -13612,40 +13617,64 @@
       <c r="CC71" s="2">
         <v>0</v>
       </c>
-      <c r="CD71" s="2" t="s">
+      <c r="CD71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CE71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CI71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK71" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL71" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CM71" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CO71" s="20">
+        <v>0</v>
+      </c>
+      <c r="CP71" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="CE71" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="CG71" s="20">
-        <v>0</v>
-      </c>
-      <c r="CH71" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="CI71" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="CJ71" s="20" t="s">
+      <c r="CQ71" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="CR71" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK71" s="20">
+      <c r="CS71" s="20">
         <v>5</v>
       </c>
-      <c r="CL71" s="20" t="s">
+      <c r="CT71" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="CU71" s="20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" ht="14.5" spans="1:99">
+      <c r="A72" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="CM71" s="20" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" ht="14.5" spans="1:91">
-      <c r="A72" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="B72" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>68</v>
@@ -13790,74 +13819,53 @@
         <v>0</v>
       </c>
       <c r="AM72" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN72" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO72" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AY72" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AZ72" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AN72" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="AQ72" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AR72" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="AS72" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="AT72" s="2" t="s">
+      <c r="BA72" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BB72" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU72" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV72" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW72" s="2">
+      <c r="BC72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE72" s="2">
         <v>50000</v>
       </c>
-      <c r="AX72" s="2">
+      <c r="BF72" s="2">
         <v>97000</v>
       </c>
-      <c r="AY72" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BC72" s="2">
+      <c r="BG72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BK72" s="2">
         <v>27000</v>
       </c>
-      <c r="BD72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK72" s="2">
-        <v>0</v>
-      </c>
       <c r="BL72" s="2">
         <v>0</v>
       </c>
@@ -13868,84 +13876,108 @@
         <v>0</v>
       </c>
       <c r="BO72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BU72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BV72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BW72" s="2">
         <v>324000</v>
       </c>
-      <c r="BP72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ72" s="2">
+      <c r="BX72" s="2">
+        <v>0</v>
+      </c>
+      <c r="BY72" s="2">
         <v>51600</v>
       </c>
-      <c r="BR72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS72" s="2">
+      <c r="BZ72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CA72" s="2">
         <v>30000</v>
       </c>
-      <c r="BT72" s="2">
+      <c r="CB72" s="2">
         <v>244000</v>
       </c>
-      <c r="BU72" s="2">
+      <c r="CC72" s="2">
         <v>62000</v>
       </c>
-      <c r="BV72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD72" s="2" t="s">
+      <c r="CD72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CE72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CF72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CI72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CK72" s="2">
+        <v>0</v>
+      </c>
+      <c r="CL72" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CM72" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="CO72" s="20">
+        <v>0</v>
+      </c>
+      <c r="CP72" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="CE72" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="CG72" s="20">
-        <v>0</v>
-      </c>
-      <c r="CH72" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="CI72" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="CJ72" s="20" t="s">
+      <c r="CQ72" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="CR72" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK72" s="20">
+      <c r="CS72" s="20">
         <v>5</v>
       </c>
-      <c r="CL72" s="20" t="s">
+      <c r="CT72" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="CU72" s="20" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="14.5" spans="1:99">
+      <c r="A73" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="CM72" s="20" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" ht="14.5" spans="1:91">
-      <c r="A73" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="B73" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>68</v>
@@ -14090,160 +14122,163 @@
         <v>0</v>
       </c>
       <c r="AM73" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AN73" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AO73" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AY73" s="2">
+        <v>2050</v>
+      </c>
+      <c r="AZ73" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AN73" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="AQ73" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AR73" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="AS73" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="AT73" s="2" t="s">
+      <c r="BA73" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="BB73" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AU73" s="1">
-        <v>0</v>
-      </c>
-      <c r="AV73" s="1">
-        <v>0</v>
-      </c>
-      <c r="AW73" s="1">
+      <c r="BC73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE73" s="1">
         <v>69000</v>
       </c>
-      <c r="AX73" s="1">
-        <v>0</v>
-      </c>
-      <c r="AY73" s="1">
-        <v>0</v>
-      </c>
-      <c r="AZ73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BA73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB73" s="1">
+      <c r="BF73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BG73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BJ73" s="1">
         <v>74000</v>
       </c>
-      <c r="BC73" s="1">
+      <c r="BK73" s="1">
         <v>52000</v>
       </c>
-      <c r="BD73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BH73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK73" s="1">
+      <c r="BL73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BM73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BQ73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BS73" s="1">
         <v>8000</v>
       </c>
-      <c r="BL73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO73" s="1">
+      <c r="BT73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BU73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BV73" s="1">
+        <v>0</v>
+      </c>
+      <c r="BW73" s="1">
         <v>77100</v>
       </c>
-      <c r="BP73" s="1">
+      <c r="BX73" s="1">
         <v>90000</v>
       </c>
-      <c r="BQ73" s="1">
+      <c r="BY73" s="1">
         <v>5700</v>
       </c>
-      <c r="BR73" s="1">
+      <c r="BZ73" s="1">
         <v>600</v>
       </c>
-      <c r="BS73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BT73" s="1">
+      <c r="CA73" s="1">
+        <v>0</v>
+      </c>
+      <c r="CB73" s="1">
         <v>12900</v>
       </c>
-      <c r="BU73" s="1">
+      <c r="CC73" s="1">
         <v>14000</v>
       </c>
-      <c r="BV73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BX73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BY73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BZ73" s="1">
-        <v>0</v>
-      </c>
-      <c r="CA73" s="1">
+      <c r="CD73" s="1">
+        <v>0</v>
+      </c>
+      <c r="CE73" s="1">
+        <v>0</v>
+      </c>
+      <c r="CF73" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG73" s="1">
+        <v>0</v>
+      </c>
+      <c r="CH73" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI73" s="1">
         <v>90000</v>
       </c>
-      <c r="CB73" s="1">
-        <v>0</v>
-      </c>
-      <c r="CC73" s="1">
-        <v>0</v>
-      </c>
-      <c r="CD73" s="1" t="s">
+      <c r="CJ73" s="1">
+        <v>0</v>
+      </c>
+      <c r="CK73" s="1">
+        <v>0</v>
+      </c>
+      <c r="CL73" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="CM73" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="CO73" s="20">
+        <v>0</v>
+      </c>
+      <c r="CP73" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="CE73" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="CG73" s="20">
-        <v>0</v>
-      </c>
-      <c r="CH73" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CI73" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="CJ73" s="20" t="s">
+      <c r="CQ73" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="CR73" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="CK73" s="20">
+      <c r="CS73" s="20">
         <v>5</v>
       </c>
-      <c r="CL73" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="CM73" s="11" t="s">
-        <v>141</v>
+      <c r="CT73" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="CU73" s="11" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
@@ -14897,7 +14932,7 @@
     </row>
     <row r="88" spans="2:26">
       <c r="B88" s="9" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -15112,7 +15147,7 @@
         <v>118</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E104" s="17">
         <v>7.11384396954065</v>
@@ -15130,7 +15165,7 @@
         <v>118</v>
       </c>
       <c r="N104" s="17" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="O104" s="17">
         <f>E104*0.313</f>
@@ -15151,7 +15186,7 @@
         <v>118</v>
       </c>
       <c r="Z104" s="17" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AA104" s="17">
         <v>5</v>
@@ -15168,7 +15203,7 @@
         <v>118</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E105" s="17">
         <v>7.11384396954065</v>
@@ -15186,7 +15221,7 @@
         <v>118</v>
       </c>
       <c r="N105" s="17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O105" s="17">
         <f t="shared" ref="O105:O124" si="16">E105*0.313</f>
@@ -15207,7 +15242,7 @@
         <v>118</v>
       </c>
       <c r="Z105" s="17" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AA105" s="17">
         <v>5</v>
@@ -15224,7 +15259,7 @@
         <v>118</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E106" s="17">
         <v>7.62975445836404</v>
@@ -15242,7 +15277,7 @@
         <v>118</v>
       </c>
       <c r="N106" s="17" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="O106" s="17">
         <f t="shared" si="16"/>
@@ -15263,7 +15298,7 @@
         <v>118</v>
       </c>
       <c r="Z106" s="17" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AA106" s="17">
         <v>5</v>
@@ -15280,7 +15315,7 @@
         <v>118</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E107" s="17">
         <v>7.47097081798084</v>
@@ -15298,7 +15333,7 @@
         <v>118</v>
       </c>
       <c r="N107" s="17" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O107" s="17">
         <f t="shared" si="16"/>
@@ -15319,7 +15354,7 @@
         <v>118</v>
       </c>
       <c r="Z107" s="17" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AA107" s="17">
         <v>5</v>
@@ -15336,7 +15371,7 @@
         <v>118</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E108" s="17">
         <v>7.51643520019651</v>
@@ -15354,7 +15389,7 @@
         <v>118</v>
       </c>
       <c r="N108" s="17" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O108" s="17">
         <f t="shared" si="16"/>
@@ -15375,7 +15410,7 @@
         <v>118</v>
       </c>
       <c r="Z108" s="17" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AA108" s="17">
         <v>5</v>
@@ -15392,7 +15427,7 @@
         <v>118</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E109" s="17">
         <v>7.55036263817244</v>
@@ -15410,7 +15445,7 @@
         <v>118</v>
       </c>
       <c r="N109" s="17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="O109" s="17">
         <f t="shared" si="16"/>
@@ -15431,7 +15466,7 @@
         <v>118</v>
       </c>
       <c r="Z109" s="17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AA109" s="17">
         <v>5</v>
@@ -15448,7 +15483,7 @@
         <v>118</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E110" s="17">
         <v>7.62975445836404</v>
@@ -15466,7 +15501,7 @@
         <v>118</v>
       </c>
       <c r="N110" s="17" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O110" s="17">
         <f t="shared" si="16"/>
@@ -15487,7 +15522,7 @@
         <v>118</v>
       </c>
       <c r="Z110" s="17" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AA110" s="17">
         <v>5</v>
@@ -15504,7 +15539,7 @@
         <v>118</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E111" s="17">
         <v>4.18384600835176</v>
@@ -15522,7 +15557,7 @@
         <v>118</v>
       </c>
       <c r="N111" s="17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="O111" s="17">
         <f t="shared" si="16"/>
@@ -15543,7 +15578,7 @@
         <v>118</v>
       </c>
       <c r="Z111" s="17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AA111" s="17">
         <v>5</v>
@@ -15560,7 +15595,7 @@
         <v>118</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E112" s="17">
         <v>4.18384600835176</v>
@@ -15578,7 +15613,7 @@
         <v>118</v>
       </c>
       <c r="N112" s="17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O112" s="17">
         <f t="shared" si="16"/>
@@ -15599,7 +15634,7 @@
         <v>118</v>
       </c>
       <c r="Z112" s="17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AA112" s="17">
         <v>5</v>
@@ -15616,7 +15651,7 @@
         <v>118</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E113" s="17">
         <v>4.18384600835176</v>
@@ -15634,7 +15669,7 @@
         <v>118</v>
       </c>
       <c r="N113" s="17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="O113" s="17">
         <f t="shared" si="16"/>
@@ -15655,7 +15690,7 @@
         <v>118</v>
       </c>
       <c r="Z113" s="17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AA113" s="17">
         <v>5</v>
@@ -15672,7 +15707,7 @@
         <v>118</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E114" s="17">
         <v>4.18384600835176</v>
@@ -15690,7 +15725,7 @@
         <v>118</v>
       </c>
       <c r="N114" s="17" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O114" s="17">
         <f t="shared" si="16"/>
@@ -15711,7 +15746,7 @@
         <v>118</v>
       </c>
       <c r="Z114" s="17" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AA114" s="17">
         <v>5</v>
@@ -15728,7 +15763,7 @@
         <v>118</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E115" s="17">
         <v>4.18384600835176</v>
@@ -15746,7 +15781,7 @@
         <v>118</v>
       </c>
       <c r="N115" s="17" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="O115" s="17">
         <f t="shared" si="16"/>
@@ -15767,7 +15802,7 @@
         <v>118</v>
       </c>
       <c r="Z115" s="17" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AA115" s="17">
         <v>5</v>
@@ -15784,7 +15819,7 @@
         <v>118</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E116" s="17">
         <v>4.18384600835176</v>
@@ -15802,7 +15837,7 @@
         <v>118</v>
       </c>
       <c r="N116" s="17" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="O116" s="17">
         <f t="shared" si="16"/>
@@ -15823,7 +15858,7 @@
         <v>118</v>
       </c>
       <c r="Z116" s="17" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AA116" s="17">
         <v>5</v>
@@ -15840,7 +15875,7 @@
         <v>118</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E117" s="17">
         <v>4.18384600835176</v>
@@ -15858,7 +15893,7 @@
         <v>118</v>
       </c>
       <c r="N117" s="17" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="O117" s="17">
         <f t="shared" si="16"/>
@@ -15879,7 +15914,7 @@
         <v>118</v>
       </c>
       <c r="Z117" s="17" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AA117" s="17">
         <v>5</v>
@@ -15896,7 +15931,7 @@
         <v>118</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E118" s="17">
         <v>3.56556266273643</v>
@@ -15914,7 +15949,7 @@
         <v>118</v>
       </c>
       <c r="N118" s="17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="O118" s="17">
         <f t="shared" si="16"/>
@@ -15935,7 +15970,7 @@
         <v>118</v>
       </c>
       <c r="Z118" s="17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AA118" s="17">
         <v>5</v>
@@ -15952,7 +15987,7 @@
         <v>118</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E119" s="17">
         <v>3.60087708179809</v>
@@ -15970,7 +16005,7 @@
         <v>118</v>
       </c>
       <c r="N119" s="17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="O119" s="17">
         <f t="shared" si="16"/>
@@ -15991,7 +16026,7 @@
         <v>118</v>
       </c>
       <c r="Z119" s="17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AA119" s="17">
         <v>5</v>
@@ -16008,7 +16043,7 @@
         <v>118</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E120" s="17">
         <v>3.56556266273643</v>
@@ -16026,7 +16061,7 @@
         <v>118</v>
       </c>
       <c r="N120" s="17" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O120" s="17">
         <f t="shared" si="16"/>
@@ -16047,7 +16082,7 @@
         <v>118</v>
       </c>
       <c r="Z120" s="17" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AA120" s="17">
         <v>5</v>
@@ -16064,7 +16099,7 @@
         <v>118</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E121" s="17">
         <v>3.56645369688037</v>
@@ -16082,7 +16117,7 @@
         <v>118</v>
       </c>
       <c r="N121" s="17" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="O121" s="17">
         <f t="shared" si="16"/>
@@ -16103,7 +16138,7 @@
         <v>118</v>
       </c>
       <c r="Z121" s="17" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AA121" s="17">
         <v>5</v>
@@ -16120,7 +16155,7 @@
         <v>118</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E122" s="17">
         <v>3.56585961680177</v>
@@ -16138,7 +16173,7 @@
         <v>118</v>
       </c>
       <c r="N122" s="17" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O122" s="17">
         <f t="shared" si="16"/>
@@ -16159,7 +16194,7 @@
         <v>118</v>
       </c>
       <c r="Z122" s="17" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AA122" s="17">
         <v>5</v>
@@ -16176,7 +16211,7 @@
         <v>118</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E123" s="17">
         <v>3.56556266273643</v>
@@ -16194,7 +16229,7 @@
         <v>118</v>
       </c>
       <c r="N123" s="17" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="O123" s="17">
         <f t="shared" si="16"/>
@@ -16215,7 +16250,7 @@
         <v>118</v>
       </c>
       <c r="Z123" s="17" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AA123" s="17">
         <v>5</v>
@@ -16232,7 +16267,7 @@
         <v>118</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E124" s="17">
         <v>3.56496890198968</v>
@@ -16250,7 +16285,7 @@
         <v>118</v>
       </c>
       <c r="N124" s="19" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="O124" s="17">
         <f t="shared" si="16"/>
@@ -16271,7 +16306,7 @@
         <v>118</v>
       </c>
       <c r="Z124" s="17" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AA124" s="17">
         <v>5</v>
@@ -16305,7 +16340,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -16317,25 +16352,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -16457,28 +16492,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -16586,7 +16621,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -16597,31 +16632,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -16729,7 +16764,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -16740,31 +16775,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -16872,7 +16907,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -16886,28 +16921,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -17015,7 +17050,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -17026,31 +17061,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -17158,7 +17193,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -17172,28 +17207,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -17301,7 +17336,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -17312,31 +17347,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -17444,7 +17479,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -17455,31 +17490,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -17587,7 +17622,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -17598,31 +17633,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -17730,7 +17765,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -17741,31 +17776,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -17873,7 +17908,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -17884,31 +17919,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G12" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -18016,7 +18051,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -18027,31 +18062,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -18159,7 +18194,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -18170,31 +18205,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H14" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I14" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J14" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K14" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -18302,7 +18337,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -18313,31 +18348,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -18445,7 +18480,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -18456,31 +18491,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H16" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I16" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J16" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K16" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -18588,7 +18623,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -18602,28 +18637,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -18731,7 +18766,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -18742,31 +18777,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D18" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G18" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H18" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I18" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J18" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K18" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -18874,7 +18909,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -18885,31 +18920,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D19" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H19" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I19" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J19" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K19" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -19017,7 +19052,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -19028,31 +19063,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -19160,7 +19195,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -19174,28 +19209,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H21" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I21" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J21" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K21" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -19303,7 +19338,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -19314,31 +19349,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D22" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H22" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I22" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J22" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K22" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -19446,7 +19481,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -19457,31 +19492,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -19589,7 +19624,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -19603,28 +19638,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -19732,7 +19767,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -19743,31 +19778,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D25" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G25" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H25" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I25" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J25" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K25" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -19875,7 +19910,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -19886,31 +19921,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D26" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H26" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I26" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J26" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K26" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -20018,7 +20053,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -20029,31 +20064,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D27" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H27" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I27" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J27" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K27" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -20161,7 +20196,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -20172,31 +20207,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -20304,7 +20339,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -20318,28 +20353,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E29" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F29" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H29" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I29" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J29" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K29" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -20447,7 +20482,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -20458,31 +20493,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F30" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G30" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -20590,7 +20625,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -20601,31 +20636,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" t="s">
+        <v>175</v>
+      </c>
+      <c r="E31" t="s">
+        <v>175</v>
+      </c>
+      <c r="F31" t="s">
         <v>176</v>
       </c>
-      <c r="D31" t="s">
-        <v>172</v>
-      </c>
-      <c r="E31" t="s">
-        <v>172</v>
-      </c>
-      <c r="F31" t="s">
-        <v>173</v>
-      </c>
       <c r="G31" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -20733,7 +20768,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -20747,28 +20782,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E32" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F32" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H32" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I32" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J32" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K32" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -20876,7 +20911,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -20887,31 +20922,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" t="s">
+        <v>175</v>
+      </c>
+      <c r="E33" t="s">
+        <v>175</v>
+      </c>
+      <c r="F33" t="s">
+        <v>176</v>
+      </c>
+      <c r="G33" t="s">
         <v>177</v>
       </c>
-      <c r="D33" t="s">
-        <v>172</v>
-      </c>
-      <c r="E33" t="s">
-        <v>172</v>
-      </c>
-      <c r="F33" t="s">
-        <v>173</v>
-      </c>
-      <c r="G33" t="s">
-        <v>174</v>
-      </c>
       <c r="H33" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I33" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J33" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K33" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -21019,7 +21054,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -21033,28 +21068,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E34" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F34" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G34" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H34" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I34" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J34" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K34" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -21162,7 +21197,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -21173,31 +21208,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D35" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E35" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F35" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G35" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H35" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I35" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J35" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K35" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -21305,7 +21340,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -21316,31 +21351,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E36" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F36" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G36" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H36" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I36" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J36" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K36" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -21448,7 +21483,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -21459,31 +21494,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F37" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G37" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -21591,7 +21626,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -21602,31 +21637,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D38" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E38" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F38" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G38" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H38" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I38" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J38" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K38" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -21734,7 +21769,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -21745,31 +21780,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D39" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E39" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F39" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G39" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H39" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I39" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J39" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K39" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -21877,7 +21912,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -21888,31 +21923,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D40" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E40" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F40" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G40" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H40" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I40" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J40" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K40" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -22020,7 +22055,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -22031,31 +22066,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D41" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E41" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F41" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G41" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H41" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I41" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J41" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K41" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -22163,7 +22198,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -22174,31 +22209,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D42" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E42" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F42" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G42" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H42" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I42" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J42" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K42" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -22306,7 +22341,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -22317,31 +22352,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D43" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E43" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F43" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G43" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H43" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I43" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J43" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K43" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -22449,7 +22484,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -22463,28 +22498,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E44" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F44" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G44" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H44" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I44" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J44" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K44" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -22592,7 +22627,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -22603,31 +22638,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D45" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E45" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F45" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G45" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H45" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I45" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J45" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K45" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -22735,7 +22770,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -22746,31 +22781,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D46" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E46" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F46" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G46" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H46" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I46" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J46" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K46" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -22878,7 +22913,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -22889,31 +22924,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D47" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E47" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F47" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G47" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H47" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I47" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J47" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K47" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -23021,7 +23056,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -23035,28 +23070,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E48" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F48" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G48" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H48" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I48" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J48" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K48" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -23164,7 +23199,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -23175,31 +23210,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D49" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E49" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F49" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G49" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H49" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I49" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J49" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K49" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -23307,7 +23342,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -23318,31 +23353,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F50" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G50" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -23450,7 +23485,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -23464,28 +23499,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F51" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G51" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -23593,7 +23628,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -23604,31 +23639,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F52" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G52" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -23736,7 +23771,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -23747,31 +23782,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D53" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E53" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F53" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G53" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H53" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I53" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J53" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K53" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -23879,7 +23914,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -23890,31 +23925,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D54" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E54" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F54" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G54" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H54" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I54" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J54" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K54" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -24022,7 +24057,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -24033,31 +24068,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D55" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E55" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F55" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G55" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H55" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I55" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J55" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K55" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -24165,7 +24200,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="198">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -467,10 +467,7 @@
     <t>Saudi Arabia</t>
   </si>
   <si>
-    <t>cset</t>
-  </si>
-  <si>
-    <t>cn</t>
+    <t>cset_set</t>
   </si>
   <si>
     <t>annual</t>
@@ -855,12 +852,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -8452,7 +8449,7 @@
     <col min="2" max="2" width="21.3727272727273" customWidth="1"/>
     <col min="3" max="3" width="12.7272727272727" customWidth="1"/>
     <col min="4" max="5" width="22.0909090909091" customWidth="1"/>
-    <col min="6" max="6" width="7.13636363636364" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="7.13636363636364" customWidth="1"/>
     <col min="10" max="10" width="10.6363636363636" customWidth="1"/>
@@ -8460,7 +8457,9 @@
     <col min="12" max="12" width="15.5454545454545" customWidth="1"/>
     <col min="13" max="18" width="7.13636363636364" customWidth="1"/>
     <col min="19" max="19" width="12.7272727272727" customWidth="1"/>
-    <col min="20" max="24" width="7.13636363636364" customWidth="1"/>
+    <col min="20" max="20" width="8.63636363636364" customWidth="1"/>
+    <col min="21" max="21" width="7.81818181818182" customWidth="1"/>
+    <col min="22" max="24" width="7.13636363636364" customWidth="1"/>
     <col min="25" max="25" width="9.54545454545454" customWidth="1"/>
     <col min="26" max="33" width="7.13636363636364" customWidth="1"/>
     <col min="34" max="37" width="6" customWidth="1"/>
@@ -12007,8 +12006,8 @@
       <c r="AN66" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="AO66" s="2" t="s">
-        <v>133</v>
+      <c r="AO66" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="AY66" s="2" t="s">
         <v>79</v>
@@ -12157,10 +12156,10 @@
     </row>
     <row r="67" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A67" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>68</v>
@@ -12304,22 +12303,22 @@
         <v>0</v>
       </c>
       <c r="AM67" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN67" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AN67" s="2" t="s">
+      <c r="AO67" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="AO67" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="AY67" s="2">
         <v>2050</v>
       </c>
       <c r="AZ67" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA67" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="BA67" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="BB67" s="2" t="s">
         <v>68</v>
@@ -12430,19 +12429,19 @@
         <v>0</v>
       </c>
       <c r="CL67" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CM67" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="CO67" s="20">
         <v>0</v>
       </c>
       <c r="CP67" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ67" s="20" t="s">
         <v>134</v>
-      </c>
-      <c r="CQ67" s="20" t="s">
-        <v>135</v>
       </c>
       <c r="CR67" s="20" t="s">
         <v>68</v>
@@ -12451,18 +12450,18 @@
         <v>5</v>
       </c>
       <c r="CT67" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CU67" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A68" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>68</v>
@@ -12607,22 +12606,22 @@
         <v>0</v>
       </c>
       <c r="AM68" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN68" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AN68" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="AO68" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AY68" s="2">
         <v>2050</v>
       </c>
       <c r="AZ68" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA68" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="BA68" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="BB68" s="2" t="s">
         <v>68</v>
@@ -12733,19 +12732,19 @@
         <v>0</v>
       </c>
       <c r="CL68" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CM68" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="CO68" s="20">
         <v>0</v>
       </c>
       <c r="CP68" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ68" s="20" t="s">
         <v>134</v>
-      </c>
-      <c r="CQ68" s="20" t="s">
-        <v>135</v>
       </c>
       <c r="CR68" s="20" t="s">
         <v>68</v>
@@ -12754,18 +12753,18 @@
         <v>5</v>
       </c>
       <c r="CT68" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CU68" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A69" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B69" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>68</v>
@@ -12910,22 +12909,22 @@
         <v>0</v>
       </c>
       <c r="AM69" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN69" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AN69" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="AO69" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AY69" s="2">
         <v>2050</v>
       </c>
       <c r="AZ69" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA69" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="BA69" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="BB69" s="2" t="s">
         <v>68</v>
@@ -13036,19 +13035,19 @@
         <v>0</v>
       </c>
       <c r="CL69" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CM69" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="CO69" s="20">
         <v>0</v>
       </c>
       <c r="CP69" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ69" s="20" t="s">
         <v>134</v>
-      </c>
-      <c r="CQ69" s="20" t="s">
-        <v>135</v>
       </c>
       <c r="CR69" s="20" t="s">
         <v>68</v>
@@ -13057,18 +13056,18 @@
         <v>5</v>
       </c>
       <c r="CT69" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CU69" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A70" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B70" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>68</v>
@@ -13213,22 +13212,22 @@
         <v>140000</v>
       </c>
       <c r="AM70" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN70" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AN70" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="AO70" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AY70" s="2">
         <v>2050</v>
       </c>
       <c r="AZ70" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA70" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="BA70" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="BB70" s="2" t="s">
         <v>68</v>
@@ -13339,19 +13338,19 @@
         <v>140000</v>
       </c>
       <c r="CL70" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CM70" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CO70" s="20">
         <v>0</v>
       </c>
       <c r="CP70" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ70" s="20" t="s">
         <v>134</v>
-      </c>
-      <c r="CQ70" s="20" t="s">
-        <v>135</v>
       </c>
       <c r="CR70" s="20" t="s">
         <v>68</v>
@@ -13360,18 +13359,18 @@
         <v>5</v>
       </c>
       <c r="CT70" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CU70" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A71" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B71" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>68</v>
@@ -13516,22 +13515,22 @@
         <v>0</v>
       </c>
       <c r="AM71" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN71" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AN71" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="AO71" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AY71" s="2">
         <v>2050</v>
       </c>
       <c r="AZ71" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA71" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="BA71" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="BB71" s="2" t="s">
         <v>68</v>
@@ -13642,19 +13641,19 @@
         <v>0</v>
       </c>
       <c r="CL71" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CM71" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="CO71" s="20">
         <v>0</v>
       </c>
       <c r="CP71" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ71" s="20" t="s">
         <v>134</v>
-      </c>
-      <c r="CQ71" s="20" t="s">
-        <v>135</v>
       </c>
       <c r="CR71" s="20" t="s">
         <v>68</v>
@@ -13663,18 +13662,18 @@
         <v>5</v>
       </c>
       <c r="CT71" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CU71" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A72" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B72" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>68</v>
@@ -13819,22 +13818,22 @@
         <v>0</v>
       </c>
       <c r="AM72" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN72" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AN72" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="AO72" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AY72" s="2">
         <v>2050</v>
       </c>
       <c r="AZ72" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA72" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="BA72" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="BB72" s="2" t="s">
         <v>68</v>
@@ -13945,19 +13944,19 @@
         <v>0</v>
       </c>
       <c r="CL72" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CM72" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="CO72" s="20">
         <v>0</v>
       </c>
       <c r="CP72" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ72" s="20" t="s">
         <v>134</v>
-      </c>
-      <c r="CQ72" s="20" t="s">
-        <v>135</v>
       </c>
       <c r="CR72" s="20" t="s">
         <v>68</v>
@@ -13966,18 +13965,18 @@
         <v>5</v>
       </c>
       <c r="CT72" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CU72" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="14.5" spans="1:99">
       <c r="A73" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B73" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>135</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>68</v>
@@ -14122,22 +14121,22 @@
         <v>0</v>
       </c>
       <c r="AM73" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN73" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AN73" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="AO73" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AY73" s="2">
         <v>2050</v>
       </c>
       <c r="AZ73" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA73" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="BA73" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="BB73" s="2" t="s">
         <v>68</v>
@@ -14248,19 +14247,19 @@
         <v>0</v>
       </c>
       <c r="CL73" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CM73" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="CO73" s="20">
         <v>0</v>
       </c>
       <c r="CP73" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ73" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="CQ73" s="11" t="s">
-        <v>135</v>
       </c>
       <c r="CR73" s="20" t="s">
         <v>68</v>
@@ -14269,16 +14268,16 @@
         <v>5</v>
       </c>
       <c r="CT73" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CU73" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
@@ -14932,7 +14931,7 @@
     </row>
     <row r="88" spans="2:26">
       <c r="B88" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -15147,7 +15146,7 @@
         <v>118</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E104" s="17">
         <v>7.11384396954065</v>
@@ -15165,7 +15164,7 @@
         <v>118</v>
       </c>
       <c r="N104" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O104" s="17">
         <f>E104*0.313</f>
@@ -15186,7 +15185,7 @@
         <v>118</v>
       </c>
       <c r="Z104" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AA104" s="17">
         <v>5</v>
@@ -15203,7 +15202,7 @@
         <v>118</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E105" s="17">
         <v>7.11384396954065</v>
@@ -15221,7 +15220,7 @@
         <v>118</v>
       </c>
       <c r="N105" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O105" s="17">
         <f t="shared" ref="O105:O124" si="16">E105*0.313</f>
@@ -15242,7 +15241,7 @@
         <v>118</v>
       </c>
       <c r="Z105" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA105" s="17">
         <v>5</v>
@@ -15259,7 +15258,7 @@
         <v>118</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E106" s="17">
         <v>7.62975445836404</v>
@@ -15277,7 +15276,7 @@
         <v>118</v>
       </c>
       <c r="N106" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O106" s="17">
         <f t="shared" si="16"/>
@@ -15298,7 +15297,7 @@
         <v>118</v>
       </c>
       <c r="Z106" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA106" s="17">
         <v>5</v>
@@ -15315,7 +15314,7 @@
         <v>118</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E107" s="17">
         <v>7.47097081798084</v>
@@ -15333,7 +15332,7 @@
         <v>118</v>
       </c>
       <c r="N107" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O107" s="17">
         <f t="shared" si="16"/>
@@ -15354,7 +15353,7 @@
         <v>118</v>
       </c>
       <c r="Z107" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AA107" s="17">
         <v>5</v>
@@ -15371,7 +15370,7 @@
         <v>118</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E108" s="17">
         <v>7.51643520019651</v>
@@ -15389,7 +15388,7 @@
         <v>118</v>
       </c>
       <c r="N108" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O108" s="17">
         <f t="shared" si="16"/>
@@ -15410,7 +15409,7 @@
         <v>118</v>
       </c>
       <c r="Z108" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA108" s="17">
         <v>5</v>
@@ -15427,7 +15426,7 @@
         <v>118</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E109" s="17">
         <v>7.55036263817244</v>
@@ -15445,7 +15444,7 @@
         <v>118</v>
       </c>
       <c r="N109" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O109" s="17">
         <f t="shared" si="16"/>
@@ -15466,7 +15465,7 @@
         <v>118</v>
       </c>
       <c r="Z109" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AA109" s="17">
         <v>5</v>
@@ -15483,7 +15482,7 @@
         <v>118</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E110" s="17">
         <v>7.62975445836404</v>
@@ -15501,7 +15500,7 @@
         <v>118</v>
       </c>
       <c r="N110" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O110" s="17">
         <f t="shared" si="16"/>
@@ -15522,7 +15521,7 @@
         <v>118</v>
       </c>
       <c r="Z110" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AA110" s="17">
         <v>5</v>
@@ -15539,7 +15538,7 @@
         <v>118</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E111" s="17">
         <v>4.18384600835176</v>
@@ -15557,7 +15556,7 @@
         <v>118</v>
       </c>
       <c r="N111" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O111" s="17">
         <f t="shared" si="16"/>
@@ -15578,7 +15577,7 @@
         <v>118</v>
       </c>
       <c r="Z111" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AA111" s="17">
         <v>5</v>
@@ -15595,7 +15594,7 @@
         <v>118</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E112" s="17">
         <v>4.18384600835176</v>
@@ -15613,7 +15612,7 @@
         <v>118</v>
       </c>
       <c r="N112" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O112" s="17">
         <f t="shared" si="16"/>
@@ -15634,7 +15633,7 @@
         <v>118</v>
       </c>
       <c r="Z112" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AA112" s="17">
         <v>5</v>
@@ -15651,7 +15650,7 @@
         <v>118</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E113" s="17">
         <v>4.18384600835176</v>
@@ -15669,7 +15668,7 @@
         <v>118</v>
       </c>
       <c r="N113" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O113" s="17">
         <f t="shared" si="16"/>
@@ -15690,7 +15689,7 @@
         <v>118</v>
       </c>
       <c r="Z113" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AA113" s="17">
         <v>5</v>
@@ -15707,7 +15706,7 @@
         <v>118</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E114" s="17">
         <v>4.18384600835176</v>
@@ -15725,7 +15724,7 @@
         <v>118</v>
       </c>
       <c r="N114" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O114" s="17">
         <f t="shared" si="16"/>
@@ -15746,7 +15745,7 @@
         <v>118</v>
       </c>
       <c r="Z114" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA114" s="17">
         <v>5</v>
@@ -15763,7 +15762,7 @@
         <v>118</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E115" s="17">
         <v>4.18384600835176</v>
@@ -15781,7 +15780,7 @@
         <v>118</v>
       </c>
       <c r="N115" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O115" s="17">
         <f t="shared" si="16"/>
@@ -15802,7 +15801,7 @@
         <v>118</v>
       </c>
       <c r="Z115" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA115" s="17">
         <v>5</v>
@@ -15819,7 +15818,7 @@
         <v>118</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E116" s="17">
         <v>4.18384600835176</v>
@@ -15837,7 +15836,7 @@
         <v>118</v>
       </c>
       <c r="N116" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O116" s="17">
         <f t="shared" si="16"/>
@@ -15858,7 +15857,7 @@
         <v>118</v>
       </c>
       <c r="Z116" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA116" s="17">
         <v>5</v>
@@ -15875,7 +15874,7 @@
         <v>118</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E117" s="17">
         <v>4.18384600835176</v>
@@ -15893,7 +15892,7 @@
         <v>118</v>
       </c>
       <c r="N117" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O117" s="17">
         <f t="shared" si="16"/>
@@ -15914,7 +15913,7 @@
         <v>118</v>
       </c>
       <c r="Z117" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA117" s="17">
         <v>5</v>
@@ -15931,7 +15930,7 @@
         <v>118</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E118" s="17">
         <v>3.56556266273643</v>
@@ -15949,7 +15948,7 @@
         <v>118</v>
       </c>
       <c r="N118" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O118" s="17">
         <f t="shared" si="16"/>
@@ -15970,7 +15969,7 @@
         <v>118</v>
       </c>
       <c r="Z118" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA118" s="17">
         <v>5</v>
@@ -15987,7 +15986,7 @@
         <v>118</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E119" s="17">
         <v>3.60087708179809</v>
@@ -16005,7 +16004,7 @@
         <v>118</v>
       </c>
       <c r="N119" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O119" s="17">
         <f t="shared" si="16"/>
@@ -16026,7 +16025,7 @@
         <v>118</v>
       </c>
       <c r="Z119" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AA119" s="17">
         <v>5</v>
@@ -16043,7 +16042,7 @@
         <v>118</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E120" s="17">
         <v>3.56556266273643</v>
@@ -16061,7 +16060,7 @@
         <v>118</v>
       </c>
       <c r="N120" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O120" s="17">
         <f t="shared" si="16"/>
@@ -16082,7 +16081,7 @@
         <v>118</v>
       </c>
       <c r="Z120" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA120" s="17">
         <v>5</v>
@@ -16099,7 +16098,7 @@
         <v>118</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E121" s="17">
         <v>3.56645369688037</v>
@@ -16117,7 +16116,7 @@
         <v>118</v>
       </c>
       <c r="N121" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O121" s="17">
         <f t="shared" si="16"/>
@@ -16138,7 +16137,7 @@
         <v>118</v>
       </c>
       <c r="Z121" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA121" s="17">
         <v>5</v>
@@ -16155,7 +16154,7 @@
         <v>118</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E122" s="17">
         <v>3.56585961680177</v>
@@ -16173,7 +16172,7 @@
         <v>118</v>
       </c>
       <c r="N122" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O122" s="17">
         <f t="shared" si="16"/>
@@ -16194,7 +16193,7 @@
         <v>118</v>
       </c>
       <c r="Z122" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA122" s="17">
         <v>5</v>
@@ -16211,7 +16210,7 @@
         <v>118</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E123" s="17">
         <v>3.56556266273643</v>
@@ -16229,7 +16228,7 @@
         <v>118</v>
       </c>
       <c r="N123" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O123" s="17">
         <f t="shared" si="16"/>
@@ -16250,7 +16249,7 @@
         <v>118</v>
       </c>
       <c r="Z123" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA123" s="17">
         <v>5</v>
@@ -16267,7 +16266,7 @@
         <v>118</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E124" s="17">
         <v>3.56496890198968</v>
@@ -16285,7 +16284,7 @@
         <v>118</v>
       </c>
       <c r="N124" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O124" s="17">
         <f t="shared" si="16"/>
@@ -16306,7 +16305,7 @@
         <v>118</v>
       </c>
       <c r="Z124" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AA124" s="17">
         <v>5</v>
@@ -16340,7 +16339,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -16352,25 +16351,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1" t="s">
         <v>169</v>
-      </c>
-      <c r="F1" t="s">
-        <v>170</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I1" t="s">
         <v>171</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>172</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>173</v>
-      </c>
-      <c r="K1" t="s">
-        <v>174</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -16492,28 +16491,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2" t="s">
         <v>176</v>
       </c>
-      <c r="G2" t="s">
-        <v>177</v>
-      </c>
       <c r="H2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -16621,7 +16620,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -16632,31 +16631,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G3" t="s">
         <v>176</v>
       </c>
-      <c r="G3" t="s">
-        <v>177</v>
-      </c>
       <c r="H3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -16764,7 +16763,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -16775,31 +16774,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G4" t="s">
         <v>176</v>
       </c>
-      <c r="G4" t="s">
-        <v>177</v>
-      </c>
       <c r="H4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -16907,7 +16906,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -16921,28 +16920,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G5" t="s">
         <v>176</v>
       </c>
-      <c r="G5" t="s">
-        <v>177</v>
-      </c>
       <c r="H5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -17050,7 +17049,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -17061,31 +17060,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G6" t="s">
         <v>176</v>
       </c>
-      <c r="G6" t="s">
-        <v>177</v>
-      </c>
       <c r="H6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -17193,7 +17192,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -17207,28 +17206,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G7" t="s">
         <v>176</v>
       </c>
-      <c r="G7" t="s">
-        <v>177</v>
-      </c>
       <c r="H7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -17336,7 +17335,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -17347,31 +17346,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G8" t="s">
         <v>176</v>
       </c>
-      <c r="G8" t="s">
-        <v>177</v>
-      </c>
       <c r="H8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -17479,7 +17478,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -17490,31 +17489,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G9" t="s">
         <v>176</v>
       </c>
-      <c r="G9" t="s">
-        <v>177</v>
-      </c>
       <c r="H9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -17622,7 +17621,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -17633,31 +17632,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" t="s">
         <v>176</v>
       </c>
-      <c r="G10" t="s">
-        <v>177</v>
-      </c>
       <c r="H10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -17765,7 +17764,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -17776,31 +17775,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
+        <v>175</v>
+      </c>
+      <c r="G11" t="s">
         <v>176</v>
       </c>
-      <c r="G11" t="s">
-        <v>177</v>
-      </c>
       <c r="H11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -17908,7 +17907,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -17919,31 +17918,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
+        <v>175</v>
+      </c>
+      <c r="G12" t="s">
         <v>176</v>
       </c>
-      <c r="G12" t="s">
-        <v>177</v>
-      </c>
       <c r="H12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -18051,7 +18050,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -18062,31 +18061,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
+        <v>175</v>
+      </c>
+      <c r="G13" t="s">
         <v>176</v>
       </c>
-      <c r="G13" t="s">
-        <v>177</v>
-      </c>
       <c r="H13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -18194,7 +18193,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -18205,31 +18204,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
+        <v>175</v>
+      </c>
+      <c r="G14" t="s">
         <v>176</v>
       </c>
-      <c r="G14" t="s">
-        <v>177</v>
-      </c>
       <c r="H14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -18337,7 +18336,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -18348,31 +18347,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
+        <v>175</v>
+      </c>
+      <c r="G15" t="s">
         <v>176</v>
       </c>
-      <c r="G15" t="s">
-        <v>177</v>
-      </c>
       <c r="H15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -18480,7 +18479,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -18491,31 +18490,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" t="s">
         <v>176</v>
       </c>
-      <c r="G16" t="s">
-        <v>177</v>
-      </c>
       <c r="H16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -18623,7 +18622,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -18637,28 +18636,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
+        <v>175</v>
+      </c>
+      <c r="G17" t="s">
         <v>176</v>
       </c>
-      <c r="G17" t="s">
-        <v>177</v>
-      </c>
       <c r="H17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -18766,7 +18765,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -18777,31 +18776,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
+        <v>175</v>
+      </c>
+      <c r="G18" t="s">
         <v>176</v>
       </c>
-      <c r="G18" t="s">
-        <v>177</v>
-      </c>
       <c r="H18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -18909,7 +18908,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -18920,31 +18919,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
+        <v>175</v>
+      </c>
+      <c r="G19" t="s">
         <v>176</v>
       </c>
-      <c r="G19" t="s">
-        <v>177</v>
-      </c>
       <c r="H19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -19052,7 +19051,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -19063,31 +19062,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G20" t="s">
         <v>176</v>
       </c>
-      <c r="G20" t="s">
-        <v>177</v>
-      </c>
       <c r="H20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -19195,7 +19194,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -19209,28 +19208,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
+        <v>175</v>
+      </c>
+      <c r="G21" t="s">
         <v>176</v>
       </c>
-      <c r="G21" t="s">
-        <v>177</v>
-      </c>
       <c r="H21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -19338,7 +19337,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -19349,31 +19348,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
+        <v>175</v>
+      </c>
+      <c r="G22" t="s">
         <v>176</v>
       </c>
-      <c r="G22" t="s">
-        <v>177</v>
-      </c>
       <c r="H22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -19481,7 +19480,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -19492,31 +19491,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
+        <v>175</v>
+      </c>
+      <c r="G23" t="s">
         <v>176</v>
       </c>
-      <c r="G23" t="s">
-        <v>177</v>
-      </c>
       <c r="H23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -19624,7 +19623,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -19638,28 +19637,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
+        <v>175</v>
+      </c>
+      <c r="G24" t="s">
         <v>176</v>
       </c>
-      <c r="G24" t="s">
-        <v>177</v>
-      </c>
       <c r="H24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -19767,7 +19766,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -19778,31 +19777,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
+        <v>175</v>
+      </c>
+      <c r="G25" t="s">
         <v>176</v>
       </c>
-      <c r="G25" t="s">
-        <v>177</v>
-      </c>
       <c r="H25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -19910,7 +19909,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -19921,31 +19920,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26" t="s">
         <v>176</v>
       </c>
-      <c r="G26" t="s">
-        <v>177</v>
-      </c>
       <c r="H26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -20053,7 +20052,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -20064,31 +20063,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
+        <v>175</v>
+      </c>
+      <c r="G27" t="s">
         <v>176</v>
       </c>
-      <c r="G27" t="s">
-        <v>177</v>
-      </c>
       <c r="H27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -20196,7 +20195,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -20207,31 +20206,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
+        <v>175</v>
+      </c>
+      <c r="G28" t="s">
         <v>176</v>
       </c>
-      <c r="G28" t="s">
-        <v>177</v>
-      </c>
       <c r="H28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -20339,7 +20338,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -20353,28 +20352,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" t="s">
+        <v>174</v>
+      </c>
+      <c r="F29" t="s">
         <v>175</v>
       </c>
-      <c r="E29" t="s">
-        <v>175</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>176</v>
       </c>
-      <c r="G29" t="s">
-        <v>177</v>
-      </c>
       <c r="H29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -20482,7 +20481,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -20493,31 +20492,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D30" t="s">
+        <v>174</v>
+      </c>
+      <c r="E30" t="s">
+        <v>174</v>
+      </c>
+      <c r="F30" t="s">
         <v>175</v>
       </c>
-      <c r="E30" t="s">
-        <v>175</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>176</v>
       </c>
-      <c r="G30" t="s">
-        <v>177</v>
-      </c>
       <c r="H30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -20625,7 +20624,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -20636,31 +20635,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D31" t="s">
+        <v>174</v>
+      </c>
+      <c r="E31" t="s">
+        <v>174</v>
+      </c>
+      <c r="F31" t="s">
         <v>175</v>
       </c>
-      <c r="E31" t="s">
-        <v>175</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>176</v>
       </c>
-      <c r="G31" t="s">
-        <v>177</v>
-      </c>
       <c r="H31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -20768,7 +20767,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -20782,28 +20781,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
+        <v>174</v>
+      </c>
+      <c r="E32" t="s">
+        <v>174</v>
+      </c>
+      <c r="F32" t="s">
         <v>175</v>
       </c>
-      <c r="E32" t="s">
-        <v>175</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>176</v>
       </c>
-      <c r="G32" t="s">
-        <v>177</v>
-      </c>
       <c r="H32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -20911,7 +20910,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -20922,31 +20921,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D33" t="s">
+        <v>174</v>
+      </c>
+      <c r="E33" t="s">
+        <v>174</v>
+      </c>
+      <c r="F33" t="s">
         <v>175</v>
       </c>
-      <c r="E33" t="s">
-        <v>175</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>176</v>
       </c>
-      <c r="G33" t="s">
-        <v>177</v>
-      </c>
       <c r="H33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -21054,7 +21053,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -21068,28 +21067,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
+        <v>174</v>
+      </c>
+      <c r="E34" t="s">
+        <v>174</v>
+      </c>
+      <c r="F34" t="s">
         <v>175</v>
       </c>
-      <c r="E34" t="s">
-        <v>175</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>176</v>
       </c>
-      <c r="G34" t="s">
-        <v>177</v>
-      </c>
       <c r="H34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -21197,7 +21196,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -21208,31 +21207,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D35" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" t="s">
         <v>175</v>
       </c>
-      <c r="E35" t="s">
-        <v>175</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>176</v>
       </c>
-      <c r="G35" t="s">
-        <v>177</v>
-      </c>
       <c r="H35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -21340,7 +21339,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -21351,31 +21350,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D36" t="s">
+        <v>174</v>
+      </c>
+      <c r="E36" t="s">
+        <v>174</v>
+      </c>
+      <c r="F36" t="s">
         <v>175</v>
       </c>
-      <c r="E36" t="s">
-        <v>175</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>176</v>
       </c>
-      <c r="G36" t="s">
-        <v>177</v>
-      </c>
       <c r="H36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -21483,7 +21482,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -21494,31 +21493,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D37" t="s">
+        <v>174</v>
+      </c>
+      <c r="E37" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37" t="s">
         <v>175</v>
       </c>
-      <c r="E37" t="s">
-        <v>175</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>176</v>
       </c>
-      <c r="G37" t="s">
-        <v>177</v>
-      </c>
       <c r="H37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -21626,7 +21625,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -21637,31 +21636,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D38" t="s">
+        <v>174</v>
+      </c>
+      <c r="E38" t="s">
+        <v>174</v>
+      </c>
+      <c r="F38" t="s">
         <v>175</v>
       </c>
-      <c r="E38" t="s">
-        <v>175</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>176</v>
       </c>
-      <c r="G38" t="s">
-        <v>177</v>
-      </c>
       <c r="H38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -21769,7 +21768,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -21780,31 +21779,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D39" t="s">
+        <v>174</v>
+      </c>
+      <c r="E39" t="s">
+        <v>174</v>
+      </c>
+      <c r="F39" t="s">
         <v>175</v>
       </c>
-      <c r="E39" t="s">
-        <v>175</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>176</v>
       </c>
-      <c r="G39" t="s">
-        <v>177</v>
-      </c>
       <c r="H39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -21912,7 +21911,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -21923,31 +21922,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D40" t="s">
+        <v>174</v>
+      </c>
+      <c r="E40" t="s">
+        <v>174</v>
+      </c>
+      <c r="F40" t="s">
         <v>175</v>
       </c>
-      <c r="E40" t="s">
-        <v>175</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>176</v>
       </c>
-      <c r="G40" t="s">
-        <v>177</v>
-      </c>
       <c r="H40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -22055,7 +22054,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -22066,31 +22065,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D41" t="s">
+        <v>174</v>
+      </c>
+      <c r="E41" t="s">
+        <v>174</v>
+      </c>
+      <c r="F41" t="s">
         <v>175</v>
       </c>
-      <c r="E41" t="s">
-        <v>175</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>176</v>
       </c>
-      <c r="G41" t="s">
-        <v>177</v>
-      </c>
       <c r="H41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -22198,7 +22197,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -22209,31 +22208,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D42" t="s">
+        <v>174</v>
+      </c>
+      <c r="E42" t="s">
+        <v>174</v>
+      </c>
+      <c r="F42" t="s">
         <v>175</v>
       </c>
-      <c r="E42" t="s">
-        <v>175</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>176</v>
       </c>
-      <c r="G42" t="s">
-        <v>177</v>
-      </c>
       <c r="H42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -22341,7 +22340,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -22352,31 +22351,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D43" t="s">
+        <v>174</v>
+      </c>
+      <c r="E43" t="s">
+        <v>174</v>
+      </c>
+      <c r="F43" t="s">
         <v>175</v>
       </c>
-      <c r="E43" t="s">
-        <v>175</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>176</v>
       </c>
-      <c r="G43" t="s">
-        <v>177</v>
-      </c>
       <c r="H43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -22484,7 +22483,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -22498,28 +22497,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
+        <v>174</v>
+      </c>
+      <c r="E44" t="s">
+        <v>174</v>
+      </c>
+      <c r="F44" t="s">
         <v>175</v>
       </c>
-      <c r="E44" t="s">
-        <v>175</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>176</v>
       </c>
-      <c r="G44" t="s">
-        <v>177</v>
-      </c>
       <c r="H44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -22627,7 +22626,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -22638,31 +22637,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D45" t="s">
+        <v>174</v>
+      </c>
+      <c r="E45" t="s">
+        <v>174</v>
+      </c>
+      <c r="F45" t="s">
         <v>175</v>
       </c>
-      <c r="E45" t="s">
-        <v>175</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>176</v>
       </c>
-      <c r="G45" t="s">
-        <v>177</v>
-      </c>
       <c r="H45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -22770,7 +22769,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -22781,31 +22780,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D46" t="s">
+        <v>174</v>
+      </c>
+      <c r="E46" t="s">
+        <v>174</v>
+      </c>
+      <c r="F46" t="s">
         <v>175</v>
       </c>
-      <c r="E46" t="s">
-        <v>175</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>176</v>
       </c>
-      <c r="G46" t="s">
-        <v>177</v>
-      </c>
       <c r="H46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -22913,7 +22912,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -22924,31 +22923,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D47" t="s">
+        <v>174</v>
+      </c>
+      <c r="E47" t="s">
+        <v>174</v>
+      </c>
+      <c r="F47" t="s">
         <v>175</v>
       </c>
-      <c r="E47" t="s">
-        <v>175</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>176</v>
       </c>
-      <c r="G47" t="s">
-        <v>177</v>
-      </c>
       <c r="H47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -23056,7 +23055,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -23070,28 +23069,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
+        <v>174</v>
+      </c>
+      <c r="E48" t="s">
+        <v>174</v>
+      </c>
+      <c r="F48" t="s">
         <v>175</v>
       </c>
-      <c r="E48" t="s">
-        <v>175</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>176</v>
       </c>
-      <c r="G48" t="s">
-        <v>177</v>
-      </c>
       <c r="H48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -23199,7 +23198,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -23210,31 +23209,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D49" t="s">
+        <v>174</v>
+      </c>
+      <c r="E49" t="s">
+        <v>174</v>
+      </c>
+      <c r="F49" t="s">
         <v>175</v>
       </c>
-      <c r="E49" t="s">
-        <v>175</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>176</v>
       </c>
-      <c r="G49" t="s">
-        <v>177</v>
-      </c>
       <c r="H49" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I49" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J49" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K49" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -23342,7 +23341,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -23353,31 +23352,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D50" t="s">
+        <v>174</v>
+      </c>
+      <c r="E50" t="s">
+        <v>174</v>
+      </c>
+      <c r="F50" t="s">
         <v>175</v>
       </c>
-      <c r="E50" t="s">
-        <v>175</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>176</v>
       </c>
-      <c r="G50" t="s">
-        <v>177</v>
-      </c>
       <c r="H50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -23485,7 +23484,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -23499,28 +23498,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
+        <v>174</v>
+      </c>
+      <c r="E51" t="s">
+        <v>174</v>
+      </c>
+      <c r="F51" t="s">
         <v>175</v>
       </c>
-      <c r="E51" t="s">
-        <v>175</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>176</v>
       </c>
-      <c r="G51" t="s">
-        <v>177</v>
-      </c>
       <c r="H51" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I51" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J51" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K51" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -23628,7 +23627,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -23639,31 +23638,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D52" t="s">
+        <v>174</v>
+      </c>
+      <c r="E52" t="s">
+        <v>174</v>
+      </c>
+      <c r="F52" t="s">
         <v>175</v>
       </c>
-      <c r="E52" t="s">
-        <v>175</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>176</v>
       </c>
-      <c r="G52" t="s">
-        <v>177</v>
-      </c>
       <c r="H52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -23771,7 +23770,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -23782,31 +23781,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D53" t="s">
+        <v>174</v>
+      </c>
+      <c r="E53" t="s">
+        <v>174</v>
+      </c>
+      <c r="F53" t="s">
         <v>175</v>
       </c>
-      <c r="E53" t="s">
-        <v>175</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>176</v>
       </c>
-      <c r="G53" t="s">
-        <v>177</v>
-      </c>
       <c r="H53" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I53" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J53" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K53" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -23914,7 +23913,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -23925,31 +23924,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D54" t="s">
+        <v>174</v>
+      </c>
+      <c r="E54" t="s">
+        <v>174</v>
+      </c>
+      <c r="F54" t="s">
         <v>175</v>
       </c>
-      <c r="E54" t="s">
-        <v>175</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>176</v>
       </c>
-      <c r="G54" t="s">
-        <v>177</v>
-      </c>
       <c r="H54" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I54" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J54" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K54" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -24057,7 +24056,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -24068,31 +24067,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D55" t="s">
+        <v>174</v>
+      </c>
+      <c r="E55" t="s">
+        <v>174</v>
+      </c>
+      <c r="F55" t="s">
         <v>175</v>
       </c>
-      <c r="E55" t="s">
-        <v>175</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>176</v>
       </c>
-      <c r="G55" t="s">
-        <v>177</v>
-      </c>
       <c r="H55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -24200,7 +24199,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="197">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -467,9 +467,6 @@
     <t>Saudi Arabia</t>
   </si>
   <si>
-    <t>cset_set</t>
-  </si>
-  <si>
     <t>annual</t>
   </si>
   <si>
@@ -677,7 +674,7 @@
     <numFmt numFmtId="178" formatCode="0.0"/>
     <numFmt numFmtId="179" formatCode="0.000"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -698,6 +695,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -852,12 +855,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <charset val="0"/>
@@ -1212,31 +1215,28 @@
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1245,122 +1245,125 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1381,6 +1384,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -1869,29 +1873,29 @@
   <dimension ref="A1:AA281"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="21" customWidth="1"/>
-    <col min="2" max="2" width="8.85454545454546" style="21" customWidth="1"/>
-    <col min="3" max="3" width="4.70909090909091" style="21" customWidth="1"/>
-    <col min="4" max="4" width="8.85454545454546" style="21" customWidth="1"/>
-    <col min="5" max="5" width="4.42727272727273" style="21" customWidth="1"/>
-    <col min="6" max="6" width="4.28181818181818" style="21" customWidth="1"/>
-    <col min="7" max="7" width="4.42727272727273" style="21" customWidth="1"/>
-    <col min="8" max="8" width="4.57272727272727" style="21" customWidth="1"/>
-    <col min="9" max="9" width="4" style="21" customWidth="1"/>
-    <col min="10" max="10" width="4.42727272727273" style="21" customWidth="1"/>
-    <col min="11" max="11" width="4.57272727272727" style="21" customWidth="1"/>
-    <col min="12" max="12" width="4.42727272727273" style="21" customWidth="1"/>
-    <col min="13" max="13" width="4" style="21" customWidth="1"/>
-    <col min="14" max="14" width="4.28181818181818" style="21" customWidth="1"/>
-    <col min="15" max="16" width="4.42727272727273" style="21" customWidth="1"/>
-    <col min="17" max="18" width="4.57272727272727" style="21" customWidth="1"/>
-    <col min="19" max="19" width="4.42727272727273" style="21" customWidth="1"/>
-    <col min="20" max="20" width="5" style="21" customWidth="1"/>
-    <col min="21" max="21" width="11.7090909090909" style="21" customWidth="1"/>
-    <col min="22" max="22" width="10.7090909090909" style="21" customWidth="1"/>
-    <col min="23" max="23" width="13.1363636363636" style="21" customWidth="1"/>
-    <col min="24" max="259" width="11.4272727272727" style="21" customWidth="1"/>
-    <col min="260" max="16384" width="9.13636363636364" style="21"/>
+    <col min="1" max="1" width="15" style="22" customWidth="1"/>
+    <col min="2" max="2" width="8.85454545454546" style="22" customWidth="1"/>
+    <col min="3" max="3" width="4.70909090909091" style="22" customWidth="1"/>
+    <col min="4" max="4" width="8.85454545454546" style="22" customWidth="1"/>
+    <col min="5" max="5" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="6" max="6" width="4.28181818181818" style="22" customWidth="1"/>
+    <col min="7" max="7" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="8" max="8" width="4.57272727272727" style="22" customWidth="1"/>
+    <col min="9" max="9" width="4" style="22" customWidth="1"/>
+    <col min="10" max="10" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="11" max="11" width="4.57272727272727" style="22" customWidth="1"/>
+    <col min="12" max="12" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="13" max="13" width="4" style="22" customWidth="1"/>
+    <col min="14" max="14" width="4.28181818181818" style="22" customWidth="1"/>
+    <col min="15" max="16" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="17" max="18" width="4.57272727272727" style="22" customWidth="1"/>
+    <col min="19" max="19" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="20" max="20" width="5" style="22" customWidth="1"/>
+    <col min="21" max="21" width="11.7090909090909" style="22" customWidth="1"/>
+    <col min="22" max="22" width="10.7090909090909" style="22" customWidth="1"/>
+    <col min="23" max="23" width="13.1363636363636" style="22" customWidth="1"/>
+    <col min="24" max="259" width="11.4272727272727" style="22" customWidth="1"/>
+    <col min="260" max="16384" width="9.13636363636364" style="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.5" spans="1:21">
@@ -2970,7 +2974,7 @@
       <c r="AA34" s="5"/>
     </row>
     <row r="35" ht="12.5" spans="1:27">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="22" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -2998,7 +3002,7 @@
       <c r="AA35" s="5"/>
     </row>
     <row r="36" ht="12.5" spans="1:27">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="22" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -3026,7 +3030,7 @@
       <c r="AA36" s="5"/>
     </row>
     <row r="37" ht="12.5" spans="1:27">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -3054,7 +3058,7 @@
       <c r="AA37" s="5"/>
     </row>
     <row r="38" ht="12.5" spans="1:27">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="22" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -3082,7 +3086,7 @@
       <c r="AA38" s="5"/>
     </row>
     <row r="39" ht="12.5" spans="1:27">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="22" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -8754,7 +8758,7 @@
       <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="23" t="s">
         <v>92</v>
       </c>
       <c r="F14">
@@ -8813,7 +8817,7 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="23" t="s">
         <v>92</v>
       </c>
       <c r="C18">
@@ -8822,7 +8826,7 @@
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="23" t="s">
         <v>100</v>
       </c>
       <c r="F18" t="s">
@@ -11610,7 +11614,7 @@
       <c r="D45">
         <v>2020</v>
       </c>
-      <c r="E45" s="23" t="s">
+      <c r="E45" s="24" t="s">
         <v>119</v>
       </c>
       <c r="F45" t="s">
@@ -11694,7 +11698,7 @@
       <c r="D55" t="s">
         <v>126</v>
       </c>
-      <c r="E55" s="22" t="s">
+      <c r="E55" s="23" t="s">
         <v>127</v>
       </c>
     </row>
@@ -12004,10 +12008,10 @@
         <v>45</v>
       </c>
       <c r="AN66" s="12" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="AO66" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AY66" s="2" t="s">
         <v>79</v>
@@ -12132,34 +12136,34 @@
       <c r="CM66" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="CO66" s="20" t="s">
+      <c r="CO66" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="CP66" s="20" t="s">
+      <c r="CP66" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="CQ66" s="20" t="s">
+      <c r="CQ66" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="CR66" s="20" t="s">
+      <c r="CR66" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="CS66" s="20" t="s">
+      <c r="CS66" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="CT66" s="20" t="s">
+      <c r="CT66" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="CU66" s="20" t="s">
+      <c r="CU66" s="21" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A67" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>68</v>
@@ -12303,22 +12307,22 @@
         <v>0</v>
       </c>
       <c r="AM67" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN67" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AN67" s="2" t="s">
+      <c r="AO67" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="AO67" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="AY67" s="2">
         <v>2050</v>
       </c>
       <c r="AZ67" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA67" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BA67" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BB67" s="2" t="s">
         <v>68</v>
@@ -12429,39 +12433,39 @@
         <v>0</v>
       </c>
       <c r="CL67" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM67" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="CO67" s="20">
-        <v>0</v>
-      </c>
-      <c r="CP67" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="CO67" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP67" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ67" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="CQ67" s="20" t="s">
+      <c r="CR67" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS67" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT67" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="CR67" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS67" s="20">
-        <v>5</v>
-      </c>
-      <c r="CT67" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="CU67" s="20" t="s">
-        <v>137</v>
+      <c r="CU67" s="21" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>68</v>
@@ -12606,22 +12610,22 @@
         <v>0</v>
       </c>
       <c r="AM68" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN68" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AN68" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="AO68" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AY68" s="2">
         <v>2050</v>
       </c>
       <c r="AZ68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA68" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BA68" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BB68" s="2" t="s">
         <v>68</v>
@@ -12732,39 +12736,39 @@
         <v>0</v>
       </c>
       <c r="CL68" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM68" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="CO68" s="20">
-        <v>0</v>
-      </c>
-      <c r="CP68" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="CO68" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP68" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ68" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="CQ68" s="20" t="s">
+      <c r="CR68" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS68" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT68" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="CR68" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS68" s="20">
-        <v>5</v>
-      </c>
-      <c r="CT68" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="CU68" s="20" t="s">
-        <v>138</v>
+      <c r="CU68" s="21" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A69" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B69" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>68</v>
@@ -12909,22 +12913,22 @@
         <v>0</v>
       </c>
       <c r="AM69" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN69" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AN69" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="AO69" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AY69" s="2">
         <v>2050</v>
       </c>
       <c r="AZ69" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA69" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BA69" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BB69" s="2" t="s">
         <v>68</v>
@@ -13035,39 +13039,39 @@
         <v>0</v>
       </c>
       <c r="CL69" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM69" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="CO69" s="20">
-        <v>0</v>
-      </c>
-      <c r="CP69" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="CO69" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP69" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ69" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="CQ69" s="20" t="s">
+      <c r="CR69" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS69" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT69" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="CR69" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS69" s="20">
-        <v>5</v>
-      </c>
-      <c r="CT69" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="CU69" s="20" t="s">
-        <v>139</v>
+      <c r="CU69" s="21" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A70" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B70" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>68</v>
@@ -13159,9 +13163,8 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Z70" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
+      <c r="Z70" s="20">
+        <v>100</v>
       </c>
       <c r="AA70" s="2">
         <f t="shared" si="9"/>
@@ -13212,22 +13215,22 @@
         <v>140000</v>
       </c>
       <c r="AM70" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN70" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AN70" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="AO70" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AY70" s="2">
         <v>2050</v>
       </c>
       <c r="AZ70" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA70" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BA70" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BB70" s="2" t="s">
         <v>68</v>
@@ -13338,39 +13341,39 @@
         <v>140000</v>
       </c>
       <c r="CL70" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM70" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="CO70" s="20">
-        <v>0</v>
-      </c>
-      <c r="CP70" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="CO70" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP70" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ70" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="CQ70" s="20" t="s">
+      <c r="CR70" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS70" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT70" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="CR70" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS70" s="20">
-        <v>5</v>
-      </c>
-      <c r="CT70" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="CU70" s="20" t="s">
-        <v>140</v>
+      <c r="CU70" s="21" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A71" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B71" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>68</v>
@@ -13406,9 +13409,8 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L71" s="2">
-        <f t="shared" si="10"/>
-        <v>0</v>
+      <c r="L71" s="20">
+        <v>100</v>
       </c>
       <c r="M71" s="2">
         <f t="shared" ref="M71:AL71" si="11">L81/1000</f>
@@ -13462,9 +13464,8 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Z71" s="2">
-        <f t="shared" si="11"/>
-        <v>0</v>
+      <c r="Z71" s="20">
+        <v>100</v>
       </c>
       <c r="AA71" s="2">
         <f t="shared" si="11"/>
@@ -13515,22 +13516,22 @@
         <v>0</v>
       </c>
       <c r="AM71" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN71" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AN71" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="AO71" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AY71" s="2">
         <v>2050</v>
       </c>
       <c r="AZ71" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA71" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BA71" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BB71" s="2" t="s">
         <v>68</v>
@@ -13641,39 +13642,39 @@
         <v>0</v>
       </c>
       <c r="CL71" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM71" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="CO71" s="20">
-        <v>0</v>
-      </c>
-      <c r="CP71" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="CO71" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP71" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ71" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="CQ71" s="20" t="s">
+      <c r="CR71" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS71" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT71" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="CR71" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS71" s="20">
-        <v>5</v>
-      </c>
-      <c r="CT71" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="CU71" s="20" t="s">
-        <v>141</v>
+      <c r="CU71" s="21" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A72" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B72" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>68</v>
@@ -13818,22 +13819,22 @@
         <v>0</v>
       </c>
       <c r="AM72" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN72" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AN72" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="AO72" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AY72" s="2">
         <v>2050</v>
       </c>
       <c r="AZ72" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA72" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BA72" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BB72" s="2" t="s">
         <v>68</v>
@@ -13944,39 +13945,39 @@
         <v>0</v>
       </c>
       <c r="CL72" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM72" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="CO72" s="20">
-        <v>0</v>
-      </c>
-      <c r="CP72" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="CO72" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP72" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ72" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="CQ72" s="20" t="s">
+      <c r="CR72" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS72" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT72" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="CR72" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS72" s="20">
-        <v>5</v>
-      </c>
-      <c r="CT72" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="CU72" s="20" t="s">
-        <v>142</v>
+      <c r="CU72" s="21" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="14.5" spans="1:99">
       <c r="A73" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>68</v>
@@ -14121,22 +14122,22 @@
         <v>0</v>
       </c>
       <c r="AM73" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN73" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AN73" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="AO73" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AY73" s="2">
         <v>2050</v>
       </c>
       <c r="AZ73" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA73" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="BA73" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="BB73" s="2" t="s">
         <v>68</v>
@@ -14247,37 +14248,37 @@
         <v>0</v>
       </c>
       <c r="CL73" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM73" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="CO73" s="20">
+        <v>142</v>
+      </c>
+      <c r="CO73" s="21">
         <v>0</v>
       </c>
       <c r="CP73" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ73" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="CQ73" s="11" t="s">
+      <c r="CR73" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS73" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT73" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="CR73" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS73" s="20">
-        <v>5</v>
-      </c>
-      <c r="CT73" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="CU73" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
@@ -14931,7 +14932,7 @@
     </row>
     <row r="88" spans="2:26">
       <c r="B88" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -15146,7 +15147,7 @@
         <v>118</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E104" s="17">
         <v>7.11384396954065</v>
@@ -15164,7 +15165,7 @@
         <v>118</v>
       </c>
       <c r="N104" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O104" s="17">
         <f>E104*0.313</f>
@@ -15185,7 +15186,7 @@
         <v>118</v>
       </c>
       <c r="Z104" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AA104" s="17">
         <v>5</v>
@@ -15202,7 +15203,7 @@
         <v>118</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E105" s="17">
         <v>7.11384396954065</v>
@@ -15220,7 +15221,7 @@
         <v>118</v>
       </c>
       <c r="N105" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O105" s="17">
         <f t="shared" ref="O105:O124" si="16">E105*0.313</f>
@@ -15241,7 +15242,7 @@
         <v>118</v>
       </c>
       <c r="Z105" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AA105" s="17">
         <v>5</v>
@@ -15258,7 +15259,7 @@
         <v>118</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E106" s="17">
         <v>7.62975445836404</v>
@@ -15276,7 +15277,7 @@
         <v>118</v>
       </c>
       <c r="N106" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O106" s="17">
         <f t="shared" si="16"/>
@@ -15297,7 +15298,7 @@
         <v>118</v>
       </c>
       <c r="Z106" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA106" s="17">
         <v>5</v>
@@ -15314,7 +15315,7 @@
         <v>118</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E107" s="17">
         <v>7.47097081798084</v>
@@ -15332,7 +15333,7 @@
         <v>118</v>
       </c>
       <c r="N107" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O107" s="17">
         <f t="shared" si="16"/>
@@ -15353,7 +15354,7 @@
         <v>118</v>
       </c>
       <c r="Z107" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA107" s="17">
         <v>5</v>
@@ -15370,7 +15371,7 @@
         <v>118</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E108" s="17">
         <v>7.51643520019651</v>
@@ -15388,7 +15389,7 @@
         <v>118</v>
       </c>
       <c r="N108" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O108" s="17">
         <f t="shared" si="16"/>
@@ -15409,7 +15410,7 @@
         <v>118</v>
       </c>
       <c r="Z108" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AA108" s="17">
         <v>5</v>
@@ -15426,7 +15427,7 @@
         <v>118</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E109" s="17">
         <v>7.55036263817244</v>
@@ -15444,7 +15445,7 @@
         <v>118</v>
       </c>
       <c r="N109" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O109" s="17">
         <f t="shared" si="16"/>
@@ -15465,7 +15466,7 @@
         <v>118</v>
       </c>
       <c r="Z109" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA109" s="17">
         <v>5</v>
@@ -15482,7 +15483,7 @@
         <v>118</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E110" s="17">
         <v>7.62975445836404</v>
@@ -15500,7 +15501,7 @@
         <v>118</v>
       </c>
       <c r="N110" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O110" s="17">
         <f t="shared" si="16"/>
@@ -15521,7 +15522,7 @@
         <v>118</v>
       </c>
       <c r="Z110" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AA110" s="17">
         <v>5</v>
@@ -15538,7 +15539,7 @@
         <v>118</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E111" s="17">
         <v>4.18384600835176</v>
@@ -15556,7 +15557,7 @@
         <v>118</v>
       </c>
       <c r="N111" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O111" s="17">
         <f t="shared" si="16"/>
@@ -15577,7 +15578,7 @@
         <v>118</v>
       </c>
       <c r="Z111" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AA111" s="17">
         <v>5</v>
@@ -15594,7 +15595,7 @@
         <v>118</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E112" s="17">
         <v>4.18384600835176</v>
@@ -15612,7 +15613,7 @@
         <v>118</v>
       </c>
       <c r="N112" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O112" s="17">
         <f t="shared" si="16"/>
@@ -15633,7 +15634,7 @@
         <v>118</v>
       </c>
       <c r="Z112" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AA112" s="17">
         <v>5</v>
@@ -15650,7 +15651,7 @@
         <v>118</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E113" s="17">
         <v>4.18384600835176</v>
@@ -15668,7 +15669,7 @@
         <v>118</v>
       </c>
       <c r="N113" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O113" s="17">
         <f t="shared" si="16"/>
@@ -15689,7 +15690,7 @@
         <v>118</v>
       </c>
       <c r="Z113" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AA113" s="17">
         <v>5</v>
@@ -15706,7 +15707,7 @@
         <v>118</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E114" s="17">
         <v>4.18384600835176</v>
@@ -15724,7 +15725,7 @@
         <v>118</v>
       </c>
       <c r="N114" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O114" s="17">
         <f t="shared" si="16"/>
@@ -15745,7 +15746,7 @@
         <v>118</v>
       </c>
       <c r="Z114" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AA114" s="17">
         <v>5</v>
@@ -15762,7 +15763,7 @@
         <v>118</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E115" s="17">
         <v>4.18384600835176</v>
@@ -15780,7 +15781,7 @@
         <v>118</v>
       </c>
       <c r="N115" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O115" s="17">
         <f t="shared" si="16"/>
@@ -15801,7 +15802,7 @@
         <v>118</v>
       </c>
       <c r="Z115" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA115" s="17">
         <v>5</v>
@@ -15818,7 +15819,7 @@
         <v>118</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E116" s="17">
         <v>4.18384600835176</v>
@@ -15836,7 +15837,7 @@
         <v>118</v>
       </c>
       <c r="N116" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O116" s="17">
         <f t="shared" si="16"/>
@@ -15857,7 +15858,7 @@
         <v>118</v>
       </c>
       <c r="Z116" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA116" s="17">
         <v>5</v>
@@ -15874,7 +15875,7 @@
         <v>118</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E117" s="17">
         <v>4.18384600835176</v>
@@ -15892,7 +15893,7 @@
         <v>118</v>
       </c>
       <c r="N117" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O117" s="17">
         <f t="shared" si="16"/>
@@ -15913,7 +15914,7 @@
         <v>118</v>
       </c>
       <c r="Z117" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA117" s="17">
         <v>5</v>
@@ -15930,7 +15931,7 @@
         <v>118</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E118" s="17">
         <v>3.56556266273643</v>
@@ -15948,7 +15949,7 @@
         <v>118</v>
       </c>
       <c r="N118" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O118" s="17">
         <f t="shared" si="16"/>
@@ -15969,7 +15970,7 @@
         <v>118</v>
       </c>
       <c r="Z118" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA118" s="17">
         <v>5</v>
@@ -15986,7 +15987,7 @@
         <v>118</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E119" s="17">
         <v>3.60087708179809</v>
@@ -16004,7 +16005,7 @@
         <v>118</v>
       </c>
       <c r="N119" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O119" s="17">
         <f t="shared" si="16"/>
@@ -16025,7 +16026,7 @@
         <v>118</v>
       </c>
       <c r="Z119" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA119" s="17">
         <v>5</v>
@@ -16042,7 +16043,7 @@
         <v>118</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E120" s="17">
         <v>3.56556266273643</v>
@@ -16060,7 +16061,7 @@
         <v>118</v>
       </c>
       <c r="N120" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O120" s="17">
         <f t="shared" si="16"/>
@@ -16081,7 +16082,7 @@
         <v>118</v>
       </c>
       <c r="Z120" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AA120" s="17">
         <v>5</v>
@@ -16098,7 +16099,7 @@
         <v>118</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E121" s="17">
         <v>3.56645369688037</v>
@@ -16116,7 +16117,7 @@
         <v>118</v>
       </c>
       <c r="N121" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O121" s="17">
         <f t="shared" si="16"/>
@@ -16137,7 +16138,7 @@
         <v>118</v>
       </c>
       <c r="Z121" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA121" s="17">
         <v>5</v>
@@ -16154,7 +16155,7 @@
         <v>118</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E122" s="17">
         <v>3.56585961680177</v>
@@ -16172,7 +16173,7 @@
         <v>118</v>
       </c>
       <c r="N122" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O122" s="17">
         <f t="shared" si="16"/>
@@ -16193,7 +16194,7 @@
         <v>118</v>
       </c>
       <c r="Z122" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA122" s="17">
         <v>5</v>
@@ -16210,7 +16211,7 @@
         <v>118</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E123" s="17">
         <v>3.56556266273643</v>
@@ -16228,7 +16229,7 @@
         <v>118</v>
       </c>
       <c r="N123" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O123" s="17">
         <f t="shared" si="16"/>
@@ -16249,7 +16250,7 @@
         <v>118</v>
       </c>
       <c r="Z123" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA123" s="17">
         <v>5</v>
@@ -16266,7 +16267,7 @@
         <v>118</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E124" s="17">
         <v>3.56496890198968</v>
@@ -16284,7 +16285,7 @@
         <v>118</v>
       </c>
       <c r="N124" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O124" s="17">
         <f t="shared" si="16"/>
@@ -16305,7 +16306,7 @@
         <v>118</v>
       </c>
       <c r="Z124" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA124" s="17">
         <v>5</v>
@@ -16339,7 +16340,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -16351,25 +16352,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>169</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1" t="s">
         <v>170</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>171</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>172</v>
-      </c>
-      <c r="K1" t="s">
-        <v>173</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -16491,28 +16492,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G2" t="s">
         <v>175</v>
       </c>
-      <c r="G2" t="s">
-        <v>176</v>
-      </c>
       <c r="H2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -16620,7 +16621,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -16631,31 +16632,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G3" t="s">
         <v>175</v>
       </c>
-      <c r="G3" t="s">
-        <v>176</v>
-      </c>
       <c r="H3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -16763,7 +16764,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -16774,31 +16775,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G4" t="s">
         <v>175</v>
       </c>
-      <c r="G4" t="s">
-        <v>176</v>
-      </c>
       <c r="H4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -16906,7 +16907,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -16920,28 +16921,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G5" t="s">
         <v>175</v>
       </c>
-      <c r="G5" t="s">
-        <v>176</v>
-      </c>
       <c r="H5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -17049,7 +17050,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -17060,31 +17061,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G6" t="s">
         <v>175</v>
       </c>
-      <c r="G6" t="s">
-        <v>176</v>
-      </c>
       <c r="H6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -17192,7 +17193,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -17206,28 +17207,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" t="s">
         <v>175</v>
       </c>
-      <c r="G7" t="s">
-        <v>176</v>
-      </c>
       <c r="H7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -17335,7 +17336,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -17346,31 +17347,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
+        <v>174</v>
+      </c>
+      <c r="G8" t="s">
         <v>175</v>
       </c>
-      <c r="G8" t="s">
-        <v>176</v>
-      </c>
       <c r="H8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -17478,7 +17479,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -17489,31 +17490,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G9" t="s">
         <v>175</v>
       </c>
-      <c r="G9" t="s">
-        <v>176</v>
-      </c>
       <c r="H9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -17621,7 +17622,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -17632,31 +17633,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
+        <v>174</v>
+      </c>
+      <c r="G10" t="s">
         <v>175</v>
       </c>
-      <c r="G10" t="s">
-        <v>176</v>
-      </c>
       <c r="H10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -17764,7 +17765,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -17775,31 +17776,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
+        <v>174</v>
+      </c>
+      <c r="G11" t="s">
         <v>175</v>
       </c>
-      <c r="G11" t="s">
-        <v>176</v>
-      </c>
       <c r="H11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -17907,7 +17908,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -17918,31 +17919,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
+        <v>174</v>
+      </c>
+      <c r="G12" t="s">
         <v>175</v>
       </c>
-      <c r="G12" t="s">
-        <v>176</v>
-      </c>
       <c r="H12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -18050,7 +18051,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -18061,31 +18062,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
+        <v>174</v>
+      </c>
+      <c r="G13" t="s">
         <v>175</v>
       </c>
-      <c r="G13" t="s">
-        <v>176</v>
-      </c>
       <c r="H13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -18193,7 +18194,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -18204,31 +18205,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14" t="s">
         <v>175</v>
       </c>
-      <c r="G14" t="s">
-        <v>176</v>
-      </c>
       <c r="H14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -18336,7 +18337,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -18347,31 +18348,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
+        <v>174</v>
+      </c>
+      <c r="G15" t="s">
         <v>175</v>
       </c>
-      <c r="G15" t="s">
-        <v>176</v>
-      </c>
       <c r="H15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -18479,7 +18480,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -18490,31 +18491,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
+        <v>174</v>
+      </c>
+      <c r="G16" t="s">
         <v>175</v>
       </c>
-      <c r="G16" t="s">
-        <v>176</v>
-      </c>
       <c r="H16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -18622,7 +18623,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -18636,28 +18637,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
+        <v>174</v>
+      </c>
+      <c r="G17" t="s">
         <v>175</v>
       </c>
-      <c r="G17" t="s">
-        <v>176</v>
-      </c>
       <c r="H17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -18765,7 +18766,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -18776,31 +18777,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" t="s">
         <v>175</v>
       </c>
-      <c r="G18" t="s">
-        <v>176</v>
-      </c>
       <c r="H18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -18908,7 +18909,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -18919,31 +18920,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
+        <v>174</v>
+      </c>
+      <c r="G19" t="s">
         <v>175</v>
       </c>
-      <c r="G19" t="s">
-        <v>176</v>
-      </c>
       <c r="H19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -19051,7 +19052,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -19062,31 +19063,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
+        <v>174</v>
+      </c>
+      <c r="G20" t="s">
         <v>175</v>
       </c>
-      <c r="G20" t="s">
-        <v>176</v>
-      </c>
       <c r="H20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -19194,7 +19195,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -19208,28 +19209,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
+        <v>174</v>
+      </c>
+      <c r="G21" t="s">
         <v>175</v>
       </c>
-      <c r="G21" t="s">
-        <v>176</v>
-      </c>
       <c r="H21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -19337,7 +19338,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -19348,31 +19349,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
+        <v>174</v>
+      </c>
+      <c r="G22" t="s">
         <v>175</v>
       </c>
-      <c r="G22" t="s">
-        <v>176</v>
-      </c>
       <c r="H22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -19480,7 +19481,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -19491,31 +19492,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
+        <v>174</v>
+      </c>
+      <c r="G23" t="s">
         <v>175</v>
       </c>
-      <c r="G23" t="s">
-        <v>176</v>
-      </c>
       <c r="H23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -19623,7 +19624,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -19637,28 +19638,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
+        <v>174</v>
+      </c>
+      <c r="G24" t="s">
         <v>175</v>
       </c>
-      <c r="G24" t="s">
-        <v>176</v>
-      </c>
       <c r="H24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -19766,7 +19767,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -19777,31 +19778,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
+        <v>174</v>
+      </c>
+      <c r="G25" t="s">
         <v>175</v>
       </c>
-      <c r="G25" t="s">
-        <v>176</v>
-      </c>
       <c r="H25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -19909,7 +19910,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -19920,31 +19921,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
+        <v>174</v>
+      </c>
+      <c r="G26" t="s">
         <v>175</v>
       </c>
-      <c r="G26" t="s">
-        <v>176</v>
-      </c>
       <c r="H26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -20052,7 +20053,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -20063,31 +20064,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
+        <v>174</v>
+      </c>
+      <c r="G27" t="s">
         <v>175</v>
       </c>
-      <c r="G27" t="s">
-        <v>176</v>
-      </c>
       <c r="H27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -20195,7 +20196,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -20206,31 +20207,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
+        <v>174</v>
+      </c>
+      <c r="G28" t="s">
         <v>175</v>
       </c>
-      <c r="G28" t="s">
-        <v>176</v>
-      </c>
       <c r="H28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -20338,7 +20339,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -20352,28 +20353,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
+        <v>173</v>
+      </c>
+      <c r="E29" t="s">
+        <v>173</v>
+      </c>
+      <c r="F29" t="s">
         <v>174</v>
       </c>
-      <c r="E29" t="s">
-        <v>174</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>175</v>
       </c>
-      <c r="G29" t="s">
-        <v>176</v>
-      </c>
       <c r="H29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -20481,7 +20482,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -20492,31 +20493,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D30" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" t="s">
         <v>174</v>
       </c>
-      <c r="E30" t="s">
-        <v>174</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>175</v>
       </c>
-      <c r="G30" t="s">
-        <v>176</v>
-      </c>
       <c r="H30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -20624,7 +20625,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -20635,31 +20636,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D31" t="s">
+        <v>173</v>
+      </c>
+      <c r="E31" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" t="s">
         <v>174</v>
       </c>
-      <c r="E31" t="s">
-        <v>174</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>175</v>
       </c>
-      <c r="G31" t="s">
-        <v>176</v>
-      </c>
       <c r="H31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -20767,7 +20768,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -20781,28 +20782,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32" t="s">
         <v>174</v>
       </c>
-      <c r="E32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>175</v>
       </c>
-      <c r="G32" t="s">
-        <v>176</v>
-      </c>
       <c r="H32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -20910,7 +20911,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -20921,31 +20922,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D33" t="s">
+        <v>173</v>
+      </c>
+      <c r="E33" t="s">
+        <v>173</v>
+      </c>
+      <c r="F33" t="s">
         <v>174</v>
       </c>
-      <c r="E33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>175</v>
       </c>
-      <c r="G33" t="s">
-        <v>176</v>
-      </c>
       <c r="H33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -21053,7 +21054,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -21067,28 +21068,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" t="s">
         <v>174</v>
       </c>
-      <c r="E34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>175</v>
       </c>
-      <c r="G34" t="s">
-        <v>176</v>
-      </c>
       <c r="H34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -21196,7 +21197,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -21207,31 +21208,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D35" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35" t="s">
         <v>174</v>
       </c>
-      <c r="E35" t="s">
-        <v>174</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>175</v>
       </c>
-      <c r="G35" t="s">
-        <v>176</v>
-      </c>
       <c r="H35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -21339,7 +21340,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -21350,31 +21351,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" t="s">
+        <v>173</v>
+      </c>
+      <c r="F36" t="s">
         <v>174</v>
       </c>
-      <c r="E36" t="s">
-        <v>174</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>175</v>
       </c>
-      <c r="G36" t="s">
-        <v>176</v>
-      </c>
       <c r="H36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -21482,7 +21483,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -21493,31 +21494,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D37" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" t="s">
         <v>174</v>
       </c>
-      <c r="E37" t="s">
-        <v>174</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>175</v>
       </c>
-      <c r="G37" t="s">
-        <v>176</v>
-      </c>
       <c r="H37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -21625,7 +21626,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -21636,31 +21637,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D38" t="s">
+        <v>173</v>
+      </c>
+      <c r="E38" t="s">
+        <v>173</v>
+      </c>
+      <c r="F38" t="s">
         <v>174</v>
       </c>
-      <c r="E38" t="s">
-        <v>174</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>175</v>
       </c>
-      <c r="G38" t="s">
-        <v>176</v>
-      </c>
       <c r="H38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -21768,7 +21769,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -21779,31 +21780,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D39" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" t="s">
+        <v>173</v>
+      </c>
+      <c r="F39" t="s">
         <v>174</v>
       </c>
-      <c r="E39" t="s">
-        <v>174</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>175</v>
       </c>
-      <c r="G39" t="s">
-        <v>176</v>
-      </c>
       <c r="H39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -21911,7 +21912,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -21922,31 +21923,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D40" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" t="s">
+        <v>173</v>
+      </c>
+      <c r="F40" t="s">
         <v>174</v>
       </c>
-      <c r="E40" t="s">
-        <v>174</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>175</v>
       </c>
-      <c r="G40" t="s">
-        <v>176</v>
-      </c>
       <c r="H40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -22054,7 +22055,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -22065,31 +22066,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D41" t="s">
+        <v>173</v>
+      </c>
+      <c r="E41" t="s">
+        <v>173</v>
+      </c>
+      <c r="F41" t="s">
         <v>174</v>
       </c>
-      <c r="E41" t="s">
-        <v>174</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>175</v>
       </c>
-      <c r="G41" t="s">
-        <v>176</v>
-      </c>
       <c r="H41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -22197,7 +22198,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -22208,31 +22209,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D42" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" t="s">
+        <v>173</v>
+      </c>
+      <c r="F42" t="s">
         <v>174</v>
       </c>
-      <c r="E42" t="s">
-        <v>174</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>175</v>
       </c>
-      <c r="G42" t="s">
-        <v>176</v>
-      </c>
       <c r="H42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -22340,7 +22341,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -22351,31 +22352,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D43" t="s">
+        <v>173</v>
+      </c>
+      <c r="E43" t="s">
+        <v>173</v>
+      </c>
+      <c r="F43" t="s">
         <v>174</v>
       </c>
-      <c r="E43" t="s">
-        <v>174</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>175</v>
       </c>
-      <c r="G43" t="s">
-        <v>176</v>
-      </c>
       <c r="H43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -22483,7 +22484,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -22497,28 +22498,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44" t="s">
+        <v>173</v>
+      </c>
+      <c r="F44" t="s">
         <v>174</v>
       </c>
-      <c r="E44" t="s">
-        <v>174</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>175</v>
       </c>
-      <c r="G44" t="s">
-        <v>176</v>
-      </c>
       <c r="H44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -22626,7 +22627,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -22637,31 +22638,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F45" t="s">
         <v>174</v>
       </c>
-      <c r="E45" t="s">
-        <v>174</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>175</v>
       </c>
-      <c r="G45" t="s">
-        <v>176</v>
-      </c>
       <c r="H45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -22769,7 +22770,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -22780,31 +22781,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F46" t="s">
         <v>174</v>
       </c>
-      <c r="E46" t="s">
-        <v>174</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>175</v>
       </c>
-      <c r="G46" t="s">
-        <v>176</v>
-      </c>
       <c r="H46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -22912,7 +22913,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -22923,31 +22924,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D47" t="s">
+        <v>173</v>
+      </c>
+      <c r="E47" t="s">
+        <v>173</v>
+      </c>
+      <c r="F47" t="s">
         <v>174</v>
       </c>
-      <c r="E47" t="s">
-        <v>174</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>175</v>
       </c>
-      <c r="G47" t="s">
-        <v>176</v>
-      </c>
       <c r="H47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -23055,7 +23056,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -23069,28 +23070,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
+        <v>173</v>
+      </c>
+      <c r="E48" t="s">
+        <v>173</v>
+      </c>
+      <c r="F48" t="s">
         <v>174</v>
       </c>
-      <c r="E48" t="s">
-        <v>174</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>175</v>
       </c>
-      <c r="G48" t="s">
-        <v>176</v>
-      </c>
       <c r="H48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -23198,7 +23199,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -23209,31 +23210,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D49" t="s">
+        <v>173</v>
+      </c>
+      <c r="E49" t="s">
+        <v>173</v>
+      </c>
+      <c r="F49" t="s">
         <v>174</v>
       </c>
-      <c r="E49" t="s">
-        <v>174</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>175</v>
       </c>
-      <c r="G49" t="s">
-        <v>176</v>
-      </c>
       <c r="H49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -23341,7 +23342,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -23352,31 +23353,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D50" t="s">
+        <v>173</v>
+      </c>
+      <c r="E50" t="s">
+        <v>173</v>
+      </c>
+      <c r="F50" t="s">
         <v>174</v>
       </c>
-      <c r="E50" t="s">
-        <v>174</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>175</v>
       </c>
-      <c r="G50" t="s">
-        <v>176</v>
-      </c>
       <c r="H50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -23484,7 +23485,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -23498,28 +23499,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E51" t="s">
+        <v>173</v>
+      </c>
+      <c r="F51" t="s">
         <v>174</v>
       </c>
-      <c r="E51" t="s">
-        <v>174</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>175</v>
       </c>
-      <c r="G51" t="s">
-        <v>176</v>
-      </c>
       <c r="H51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -23627,7 +23628,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -23638,31 +23639,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D52" t="s">
+        <v>173</v>
+      </c>
+      <c r="E52" t="s">
+        <v>173</v>
+      </c>
+      <c r="F52" t="s">
         <v>174</v>
       </c>
-      <c r="E52" t="s">
-        <v>174</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>175</v>
       </c>
-      <c r="G52" t="s">
-        <v>176</v>
-      </c>
       <c r="H52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -23770,7 +23771,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -23781,31 +23782,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D53" t="s">
+        <v>173</v>
+      </c>
+      <c r="E53" t="s">
+        <v>173</v>
+      </c>
+      <c r="F53" t="s">
         <v>174</v>
       </c>
-      <c r="E53" t="s">
-        <v>174</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>175</v>
       </c>
-      <c r="G53" t="s">
-        <v>176</v>
-      </c>
       <c r="H53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -23913,7 +23914,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -23924,31 +23925,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D54" t="s">
+        <v>173</v>
+      </c>
+      <c r="E54" t="s">
+        <v>173</v>
+      </c>
+      <c r="F54" t="s">
         <v>174</v>
       </c>
-      <c r="E54" t="s">
-        <v>174</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>175</v>
       </c>
-      <c r="G54" t="s">
-        <v>176</v>
-      </c>
       <c r="H54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -24056,7 +24057,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -24067,31 +24068,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D55" t="s">
+        <v>173</v>
+      </c>
+      <c r="E55" t="s">
+        <v>173</v>
+      </c>
+      <c r="F55" t="s">
         <v>174</v>
       </c>
-      <c r="E55" t="s">
-        <v>174</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>175</v>
       </c>
-      <c r="G55" t="s">
-        <v>176</v>
-      </c>
       <c r="H55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -24199,7 +24200,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="196">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -474,9 +474,6 @@
   </si>
   <si>
     <t>MINBatMaterials</t>
-  </si>
-  <si>
-    <t>MINBatMaterials_MATO</t>
   </si>
   <si>
     <t>m_lithium</t>
@@ -12309,11 +12306,11 @@
       <c r="AM67" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AN67" s="2" t="s">
+      <c r="AN67" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AO67" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AY67" s="2">
         <v>2050</v>
@@ -12436,7 +12433,7 @@
         <v>134</v>
       </c>
       <c r="CM67" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="CO67" s="21">
         <v>0</v>
@@ -12457,7 +12454,7 @@
         <v>134</v>
       </c>
       <c r="CU67" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" ht="14.5" spans="1:99">
@@ -12612,11 +12609,11 @@
       <c r="AM68" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AN68" s="2" t="s">
-        <v>135</v>
+      <c r="AN68" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="AO68" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AY68" s="2">
         <v>2050</v>
@@ -12739,7 +12736,7 @@
         <v>134</v>
       </c>
       <c r="CM68" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="CO68" s="21">
         <v>0</v>
@@ -12760,7 +12757,7 @@
         <v>134</v>
       </c>
       <c r="CU68" s="21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" ht="14.5" spans="1:99">
@@ -12915,11 +12912,11 @@
       <c r="AM69" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AN69" s="2" t="s">
-        <v>135</v>
+      <c r="AN69" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="AO69" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AY69" s="2">
         <v>2050</v>
@@ -13042,7 +13039,7 @@
         <v>134</v>
       </c>
       <c r="CM69" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="CO69" s="21">
         <v>0</v>
@@ -13063,7 +13060,7 @@
         <v>134</v>
       </c>
       <c r="CU69" s="21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" ht="14.5" spans="1:99">
@@ -13217,11 +13214,11 @@
       <c r="AM70" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AN70" s="2" t="s">
-        <v>135</v>
+      <c r="AN70" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="AO70" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AY70" s="2">
         <v>2050</v>
@@ -13344,7 +13341,7 @@
         <v>134</v>
       </c>
       <c r="CM70" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="CO70" s="21">
         <v>0</v>
@@ -13365,7 +13362,7 @@
         <v>134</v>
       </c>
       <c r="CU70" s="21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" ht="14.5" spans="1:99">
@@ -13518,11 +13515,11 @@
       <c r="AM71" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AN71" s="2" t="s">
-        <v>135</v>
+      <c r="AN71" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="AO71" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AY71" s="2">
         <v>2050</v>
@@ -13645,7 +13642,7 @@
         <v>134</v>
       </c>
       <c r="CM71" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="CO71" s="21">
         <v>0</v>
@@ -13666,7 +13663,7 @@
         <v>134</v>
       </c>
       <c r="CU71" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" ht="14.5" spans="1:99">
@@ -13821,11 +13818,11 @@
       <c r="AM72" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AN72" s="2" t="s">
-        <v>135</v>
+      <c r="AN72" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="AO72" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AY72" s="2">
         <v>2050</v>
@@ -13948,7 +13945,7 @@
         <v>134</v>
       </c>
       <c r="CM72" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CO72" s="21">
         <v>0</v>
@@ -13969,7 +13966,7 @@
         <v>134</v>
       </c>
       <c r="CU72" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="14.5" spans="1:99">
@@ -14124,11 +14121,11 @@
       <c r="AM73" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="AN73" s="2" t="s">
-        <v>135</v>
+      <c r="AN73" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="AO73" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AY73" s="2">
         <v>2050</v>
@@ -14251,7 +14248,7 @@
         <v>134</v>
       </c>
       <c r="CM73" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="CO73" s="21">
         <v>0</v>
@@ -14272,13 +14269,13 @@
         <v>134</v>
       </c>
       <c r="CU73" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
@@ -14932,7 +14929,7 @@
     </row>
     <row r="88" spans="2:26">
       <c r="B88" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -15147,7 +15144,7 @@
         <v>118</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E104" s="17">
         <v>7.11384396954065</v>
@@ -15165,7 +15162,7 @@
         <v>118</v>
       </c>
       <c r="N104" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O104" s="17">
         <f>E104*0.313</f>
@@ -15186,7 +15183,7 @@
         <v>118</v>
       </c>
       <c r="Z104" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AA104" s="17">
         <v>5</v>
@@ -15203,7 +15200,7 @@
         <v>118</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E105" s="17">
         <v>7.11384396954065</v>
@@ -15221,7 +15218,7 @@
         <v>118</v>
       </c>
       <c r="N105" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O105" s="17">
         <f t="shared" ref="O105:O124" si="16">E105*0.313</f>
@@ -15242,7 +15239,7 @@
         <v>118</v>
       </c>
       <c r="Z105" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AA105" s="17">
         <v>5</v>
@@ -15259,7 +15256,7 @@
         <v>118</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E106" s="17">
         <v>7.62975445836404</v>
@@ -15277,7 +15274,7 @@
         <v>118</v>
       </c>
       <c r="N106" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O106" s="17">
         <f t="shared" si="16"/>
@@ -15298,7 +15295,7 @@
         <v>118</v>
       </c>
       <c r="Z106" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AA106" s="17">
         <v>5</v>
@@ -15315,7 +15312,7 @@
         <v>118</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E107" s="17">
         <v>7.47097081798084</v>
@@ -15333,7 +15330,7 @@
         <v>118</v>
       </c>
       <c r="N107" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O107" s="17">
         <f t="shared" si="16"/>
@@ -15354,7 +15351,7 @@
         <v>118</v>
       </c>
       <c r="Z107" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA107" s="17">
         <v>5</v>
@@ -15371,7 +15368,7 @@
         <v>118</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E108" s="17">
         <v>7.51643520019651</v>
@@ -15389,7 +15386,7 @@
         <v>118</v>
       </c>
       <c r="N108" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O108" s="17">
         <f t="shared" si="16"/>
@@ -15410,7 +15407,7 @@
         <v>118</v>
       </c>
       <c r="Z108" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA108" s="17">
         <v>5</v>
@@ -15427,7 +15424,7 @@
         <v>118</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E109" s="17">
         <v>7.55036263817244</v>
@@ -15445,7 +15442,7 @@
         <v>118</v>
       </c>
       <c r="N109" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O109" s="17">
         <f t="shared" si="16"/>
@@ -15466,7 +15463,7 @@
         <v>118</v>
       </c>
       <c r="Z109" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AA109" s="17">
         <v>5</v>
@@ -15483,7 +15480,7 @@
         <v>118</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E110" s="17">
         <v>7.62975445836404</v>
@@ -15501,7 +15498,7 @@
         <v>118</v>
       </c>
       <c r="N110" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O110" s="17">
         <f t="shared" si="16"/>
@@ -15522,7 +15519,7 @@
         <v>118</v>
       </c>
       <c r="Z110" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA110" s="17">
         <v>5</v>
@@ -15539,7 +15536,7 @@
         <v>118</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E111" s="17">
         <v>4.18384600835176</v>
@@ -15557,7 +15554,7 @@
         <v>118</v>
       </c>
       <c r="N111" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O111" s="17">
         <f t="shared" si="16"/>
@@ -15578,7 +15575,7 @@
         <v>118</v>
       </c>
       <c r="Z111" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AA111" s="17">
         <v>5</v>
@@ -15595,7 +15592,7 @@
         <v>118</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E112" s="17">
         <v>4.18384600835176</v>
@@ -15613,7 +15610,7 @@
         <v>118</v>
       </c>
       <c r="N112" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O112" s="17">
         <f t="shared" si="16"/>
@@ -15634,7 +15631,7 @@
         <v>118</v>
       </c>
       <c r="Z112" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AA112" s="17">
         <v>5</v>
@@ -15651,7 +15648,7 @@
         <v>118</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E113" s="17">
         <v>4.18384600835176</v>
@@ -15669,7 +15666,7 @@
         <v>118</v>
       </c>
       <c r="N113" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O113" s="17">
         <f t="shared" si="16"/>
@@ -15690,7 +15687,7 @@
         <v>118</v>
       </c>
       <c r="Z113" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AA113" s="17">
         <v>5</v>
@@ -15707,7 +15704,7 @@
         <v>118</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E114" s="17">
         <v>4.18384600835176</v>
@@ -15725,7 +15722,7 @@
         <v>118</v>
       </c>
       <c r="N114" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O114" s="17">
         <f t="shared" si="16"/>
@@ -15746,7 +15743,7 @@
         <v>118</v>
       </c>
       <c r="Z114" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AA114" s="17">
         <v>5</v>
@@ -15763,7 +15760,7 @@
         <v>118</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E115" s="17">
         <v>4.18384600835176</v>
@@ -15781,7 +15778,7 @@
         <v>118</v>
       </c>
       <c r="N115" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O115" s="17">
         <f t="shared" si="16"/>
@@ -15802,7 +15799,7 @@
         <v>118</v>
       </c>
       <c r="Z115" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AA115" s="17">
         <v>5</v>
@@ -15819,7 +15816,7 @@
         <v>118</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E116" s="17">
         <v>4.18384600835176</v>
@@ -15837,7 +15834,7 @@
         <v>118</v>
       </c>
       <c r="N116" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O116" s="17">
         <f t="shared" si="16"/>
@@ -15858,7 +15855,7 @@
         <v>118</v>
       </c>
       <c r="Z116" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA116" s="17">
         <v>5</v>
@@ -15875,7 +15872,7 @@
         <v>118</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E117" s="17">
         <v>4.18384600835176</v>
@@ -15893,7 +15890,7 @@
         <v>118</v>
       </c>
       <c r="N117" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O117" s="17">
         <f t="shared" si="16"/>
@@ -15914,7 +15911,7 @@
         <v>118</v>
       </c>
       <c r="Z117" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA117" s="17">
         <v>5</v>
@@ -15931,7 +15928,7 @@
         <v>118</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E118" s="17">
         <v>3.56556266273643</v>
@@ -15949,7 +15946,7 @@
         <v>118</v>
       </c>
       <c r="N118" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O118" s="17">
         <f t="shared" si="16"/>
@@ -15970,7 +15967,7 @@
         <v>118</v>
       </c>
       <c r="Z118" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA118" s="17">
         <v>5</v>
@@ -15987,7 +15984,7 @@
         <v>118</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E119" s="17">
         <v>3.60087708179809</v>
@@ -16005,7 +16002,7 @@
         <v>118</v>
       </c>
       <c r="N119" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O119" s="17">
         <f t="shared" si="16"/>
@@ -16026,7 +16023,7 @@
         <v>118</v>
       </c>
       <c r="Z119" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA119" s="17">
         <v>5</v>
@@ -16043,7 +16040,7 @@
         <v>118</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E120" s="17">
         <v>3.56556266273643</v>
@@ -16061,7 +16058,7 @@
         <v>118</v>
       </c>
       <c r="N120" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O120" s="17">
         <f t="shared" si="16"/>
@@ -16082,7 +16079,7 @@
         <v>118</v>
       </c>
       <c r="Z120" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA120" s="17">
         <v>5</v>
@@ -16099,7 +16096,7 @@
         <v>118</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E121" s="17">
         <v>3.56645369688037</v>
@@ -16117,7 +16114,7 @@
         <v>118</v>
       </c>
       <c r="N121" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O121" s="17">
         <f t="shared" si="16"/>
@@ -16138,7 +16135,7 @@
         <v>118</v>
       </c>
       <c r="Z121" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AA121" s="17">
         <v>5</v>
@@ -16155,7 +16152,7 @@
         <v>118</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E122" s="17">
         <v>3.56585961680177</v>
@@ -16173,7 +16170,7 @@
         <v>118</v>
       </c>
       <c r="N122" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O122" s="17">
         <f t="shared" si="16"/>
@@ -16194,7 +16191,7 @@
         <v>118</v>
       </c>
       <c r="Z122" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA122" s="17">
         <v>5</v>
@@ -16211,7 +16208,7 @@
         <v>118</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E123" s="17">
         <v>3.56556266273643</v>
@@ -16229,7 +16226,7 @@
         <v>118</v>
       </c>
       <c r="N123" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O123" s="17">
         <f t="shared" si="16"/>
@@ -16250,7 +16247,7 @@
         <v>118</v>
       </c>
       <c r="Z123" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA123" s="17">
         <v>5</v>
@@ -16267,7 +16264,7 @@
         <v>118</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E124" s="17">
         <v>3.56496890198968</v>
@@ -16285,7 +16282,7 @@
         <v>118</v>
       </c>
       <c r="N124" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O124" s="17">
         <f t="shared" si="16"/>
@@ -16306,7 +16303,7 @@
         <v>118</v>
       </c>
       <c r="Z124" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA124" s="17">
         <v>5</v>
@@ -16340,7 +16337,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -16352,25 +16349,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>167</v>
-      </c>
-      <c r="F1" t="s">
-        <v>168</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1" t="s">
         <v>169</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>170</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>171</v>
-      </c>
-      <c r="K1" t="s">
-        <v>172</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -16492,28 +16489,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G2" t="s">
         <v>174</v>
       </c>
-      <c r="G2" t="s">
-        <v>175</v>
-      </c>
       <c r="H2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -16621,7 +16618,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -16632,31 +16629,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G3" t="s">
         <v>174</v>
       </c>
-      <c r="G3" t="s">
-        <v>175</v>
-      </c>
       <c r="H3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -16764,7 +16761,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -16775,31 +16772,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G4" t="s">
         <v>174</v>
       </c>
-      <c r="G4" t="s">
-        <v>175</v>
-      </c>
       <c r="H4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -16907,7 +16904,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -16921,28 +16918,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G5" t="s">
         <v>174</v>
       </c>
-      <c r="G5" t="s">
-        <v>175</v>
-      </c>
       <c r="H5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -17050,7 +17047,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -17061,31 +17058,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" t="s">
         <v>174</v>
       </c>
-      <c r="G6" t="s">
-        <v>175</v>
-      </c>
       <c r="H6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -17193,7 +17190,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -17207,28 +17204,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" t="s">
         <v>174</v>
       </c>
-      <c r="G7" t="s">
-        <v>175</v>
-      </c>
       <c r="H7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -17336,7 +17333,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -17347,31 +17344,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" t="s">
         <v>174</v>
       </c>
-      <c r="G8" t="s">
-        <v>175</v>
-      </c>
       <c r="H8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -17479,7 +17476,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -17490,31 +17487,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" t="s">
         <v>174</v>
       </c>
-      <c r="G9" t="s">
-        <v>175</v>
-      </c>
       <c r="H9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -17622,7 +17619,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -17633,31 +17630,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" t="s">
         <v>174</v>
       </c>
-      <c r="G10" t="s">
-        <v>175</v>
-      </c>
       <c r="H10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -17765,7 +17762,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -17776,31 +17773,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G11" t="s">
         <v>174</v>
       </c>
-      <c r="G11" t="s">
-        <v>175</v>
-      </c>
       <c r="H11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -17908,7 +17905,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -17919,31 +17916,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" t="s">
         <v>174</v>
       </c>
-      <c r="G12" t="s">
-        <v>175</v>
-      </c>
       <c r="H12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -18051,7 +18048,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -18062,31 +18059,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" t="s">
         <v>174</v>
       </c>
-      <c r="G13" t="s">
-        <v>175</v>
-      </c>
       <c r="H13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -18194,7 +18191,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -18205,31 +18202,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G14" t="s">
         <v>174</v>
       </c>
-      <c r="G14" t="s">
-        <v>175</v>
-      </c>
       <c r="H14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -18337,7 +18334,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -18348,31 +18345,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
+        <v>173</v>
+      </c>
+      <c r="G15" t="s">
         <v>174</v>
       </c>
-      <c r="G15" t="s">
-        <v>175</v>
-      </c>
       <c r="H15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -18480,7 +18477,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -18491,31 +18488,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
+        <v>173</v>
+      </c>
+      <c r="G16" t="s">
         <v>174</v>
       </c>
-      <c r="G16" t="s">
-        <v>175</v>
-      </c>
       <c r="H16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -18623,7 +18620,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -18637,28 +18634,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
+        <v>173</v>
+      </c>
+      <c r="G17" t="s">
         <v>174</v>
       </c>
-      <c r="G17" t="s">
-        <v>175</v>
-      </c>
       <c r="H17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -18766,7 +18763,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -18777,31 +18774,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
+        <v>173</v>
+      </c>
+      <c r="G18" t="s">
         <v>174</v>
       </c>
-      <c r="G18" t="s">
-        <v>175</v>
-      </c>
       <c r="H18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -18909,7 +18906,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -18920,31 +18917,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
+        <v>173</v>
+      </c>
+      <c r="G19" t="s">
         <v>174</v>
       </c>
-      <c r="G19" t="s">
-        <v>175</v>
-      </c>
       <c r="H19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -19052,7 +19049,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -19063,31 +19060,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
+        <v>173</v>
+      </c>
+      <c r="G20" t="s">
         <v>174</v>
       </c>
-      <c r="G20" t="s">
-        <v>175</v>
-      </c>
       <c r="H20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -19195,7 +19192,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -19209,28 +19206,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G21" t="s">
         <v>174</v>
       </c>
-      <c r="G21" t="s">
-        <v>175</v>
-      </c>
       <c r="H21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -19338,7 +19335,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -19349,31 +19346,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" t="s">
         <v>174</v>
       </c>
-      <c r="G22" t="s">
-        <v>175</v>
-      </c>
       <c r="H22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -19481,7 +19478,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -19492,31 +19489,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" t="s">
         <v>174</v>
       </c>
-      <c r="G23" t="s">
-        <v>175</v>
-      </c>
       <c r="H23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -19624,7 +19621,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -19638,28 +19635,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
+        <v>173</v>
+      </c>
+      <c r="G24" t="s">
         <v>174</v>
       </c>
-      <c r="G24" t="s">
-        <v>175</v>
-      </c>
       <c r="H24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -19767,7 +19764,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -19778,31 +19775,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
+        <v>173</v>
+      </c>
+      <c r="G25" t="s">
         <v>174</v>
       </c>
-      <c r="G25" t="s">
-        <v>175</v>
-      </c>
       <c r="H25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -19910,7 +19907,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -19921,31 +19918,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
+        <v>173</v>
+      </c>
+      <c r="G26" t="s">
         <v>174</v>
       </c>
-      <c r="G26" t="s">
-        <v>175</v>
-      </c>
       <c r="H26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -20053,7 +20050,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -20064,31 +20061,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
+        <v>173</v>
+      </c>
+      <c r="G27" t="s">
         <v>174</v>
       </c>
-      <c r="G27" t="s">
-        <v>175</v>
-      </c>
       <c r="H27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -20196,7 +20193,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -20207,31 +20204,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
+        <v>173</v>
+      </c>
+      <c r="G28" t="s">
         <v>174</v>
       </c>
-      <c r="G28" t="s">
-        <v>175</v>
-      </c>
       <c r="H28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -20339,7 +20336,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -20353,28 +20350,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
+        <v>172</v>
+      </c>
+      <c r="E29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29" t="s">
         <v>173</v>
       </c>
-      <c r="E29" t="s">
-        <v>173</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>174</v>
       </c>
-      <c r="G29" t="s">
-        <v>175</v>
-      </c>
       <c r="H29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -20482,7 +20479,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -20493,31 +20490,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D30" t="s">
+        <v>172</v>
+      </c>
+      <c r="E30" t="s">
+        <v>172</v>
+      </c>
+      <c r="F30" t="s">
         <v>173</v>
       </c>
-      <c r="E30" t="s">
-        <v>173</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>174</v>
       </c>
-      <c r="G30" t="s">
-        <v>175</v>
-      </c>
       <c r="H30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -20625,7 +20622,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -20636,31 +20633,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D31" t="s">
+        <v>172</v>
+      </c>
+      <c r="E31" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31" t="s">
         <v>173</v>
       </c>
-      <c r="E31" t="s">
-        <v>173</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>174</v>
       </c>
-      <c r="G31" t="s">
-        <v>175</v>
-      </c>
       <c r="H31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -20768,7 +20765,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -20782,28 +20779,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
+        <v>172</v>
+      </c>
+      <c r="E32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F32" t="s">
         <v>173</v>
       </c>
-      <c r="E32" t="s">
-        <v>173</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>174</v>
       </c>
-      <c r="G32" t="s">
-        <v>175</v>
-      </c>
       <c r="H32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -20911,7 +20908,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -20922,31 +20919,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" t="s">
         <v>173</v>
       </c>
-      <c r="E33" t="s">
-        <v>173</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>174</v>
       </c>
-      <c r="G33" t="s">
-        <v>175</v>
-      </c>
       <c r="H33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -21054,7 +21051,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -21068,28 +21065,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F34" t="s">
         <v>173</v>
       </c>
-      <c r="E34" t="s">
-        <v>173</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>174</v>
       </c>
-      <c r="G34" t="s">
-        <v>175</v>
-      </c>
       <c r="H34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -21197,7 +21194,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -21208,31 +21205,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D35" t="s">
+        <v>172</v>
+      </c>
+      <c r="E35" t="s">
+        <v>172</v>
+      </c>
+      <c r="F35" t="s">
         <v>173</v>
       </c>
-      <c r="E35" t="s">
-        <v>173</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>174</v>
       </c>
-      <c r="G35" t="s">
-        <v>175</v>
-      </c>
       <c r="H35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -21340,7 +21337,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -21351,31 +21348,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D36" t="s">
+        <v>172</v>
+      </c>
+      <c r="E36" t="s">
+        <v>172</v>
+      </c>
+      <c r="F36" t="s">
         <v>173</v>
       </c>
-      <c r="E36" t="s">
-        <v>173</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>174</v>
       </c>
-      <c r="G36" t="s">
-        <v>175</v>
-      </c>
       <c r="H36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -21483,7 +21480,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -21494,31 +21491,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D37" t="s">
+        <v>172</v>
+      </c>
+      <c r="E37" t="s">
+        <v>172</v>
+      </c>
+      <c r="F37" t="s">
         <v>173</v>
       </c>
-      <c r="E37" t="s">
-        <v>173</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>174</v>
       </c>
-      <c r="G37" t="s">
-        <v>175</v>
-      </c>
       <c r="H37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -21626,7 +21623,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -21637,31 +21634,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s">
+        <v>172</v>
+      </c>
+      <c r="E38" t="s">
+        <v>172</v>
+      </c>
+      <c r="F38" t="s">
         <v>173</v>
       </c>
-      <c r="E38" t="s">
-        <v>173</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>174</v>
       </c>
-      <c r="G38" t="s">
-        <v>175</v>
-      </c>
       <c r="H38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -21769,7 +21766,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -21780,31 +21777,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D39" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" t="s">
         <v>173</v>
       </c>
-      <c r="E39" t="s">
-        <v>173</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>174</v>
       </c>
-      <c r="G39" t="s">
-        <v>175</v>
-      </c>
       <c r="H39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -21912,7 +21909,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -21923,31 +21920,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D40" t="s">
+        <v>172</v>
+      </c>
+      <c r="E40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" t="s">
         <v>173</v>
       </c>
-      <c r="E40" t="s">
-        <v>173</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>174</v>
       </c>
-      <c r="G40" t="s">
-        <v>175</v>
-      </c>
       <c r="H40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -22055,7 +22052,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -22066,31 +22063,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D41" t="s">
+        <v>172</v>
+      </c>
+      <c r="E41" t="s">
+        <v>172</v>
+      </c>
+      <c r="F41" t="s">
         <v>173</v>
       </c>
-      <c r="E41" t="s">
-        <v>173</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>174</v>
       </c>
-      <c r="G41" t="s">
-        <v>175</v>
-      </c>
       <c r="H41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -22198,7 +22195,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -22209,31 +22206,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D42" t="s">
+        <v>172</v>
+      </c>
+      <c r="E42" t="s">
+        <v>172</v>
+      </c>
+      <c r="F42" t="s">
         <v>173</v>
       </c>
-      <c r="E42" t="s">
-        <v>173</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>174</v>
       </c>
-      <c r="G42" t="s">
-        <v>175</v>
-      </c>
       <c r="H42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -22341,7 +22338,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -22352,31 +22349,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D43" t="s">
+        <v>172</v>
+      </c>
+      <c r="E43" t="s">
+        <v>172</v>
+      </c>
+      <c r="F43" t="s">
         <v>173</v>
       </c>
-      <c r="E43" t="s">
-        <v>173</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>174</v>
       </c>
-      <c r="G43" t="s">
-        <v>175</v>
-      </c>
       <c r="H43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -22484,7 +22481,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -22498,28 +22495,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
+        <v>172</v>
+      </c>
+      <c r="E44" t="s">
+        <v>172</v>
+      </c>
+      <c r="F44" t="s">
         <v>173</v>
       </c>
-      <c r="E44" t="s">
-        <v>173</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>174</v>
       </c>
-      <c r="G44" t="s">
-        <v>175</v>
-      </c>
       <c r="H44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -22627,7 +22624,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -22638,31 +22635,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D45" t="s">
+        <v>172</v>
+      </c>
+      <c r="E45" t="s">
+        <v>172</v>
+      </c>
+      <c r="F45" t="s">
         <v>173</v>
       </c>
-      <c r="E45" t="s">
-        <v>173</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>174</v>
       </c>
-      <c r="G45" t="s">
-        <v>175</v>
-      </c>
       <c r="H45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -22770,7 +22767,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -22781,31 +22778,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D46" t="s">
+        <v>172</v>
+      </c>
+      <c r="E46" t="s">
+        <v>172</v>
+      </c>
+      <c r="F46" t="s">
         <v>173</v>
       </c>
-      <c r="E46" t="s">
-        <v>173</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>174</v>
       </c>
-      <c r="G46" t="s">
-        <v>175</v>
-      </c>
       <c r="H46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -22913,7 +22910,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -22924,31 +22921,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D47" t="s">
+        <v>172</v>
+      </c>
+      <c r="E47" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" t="s">
         <v>173</v>
       </c>
-      <c r="E47" t="s">
-        <v>173</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>174</v>
       </c>
-      <c r="G47" t="s">
-        <v>175</v>
-      </c>
       <c r="H47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -23056,7 +23053,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -23070,28 +23067,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
+        <v>172</v>
+      </c>
+      <c r="E48" t="s">
+        <v>172</v>
+      </c>
+      <c r="F48" t="s">
         <v>173</v>
       </c>
-      <c r="E48" t="s">
-        <v>173</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>174</v>
       </c>
-      <c r="G48" t="s">
-        <v>175</v>
-      </c>
       <c r="H48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -23199,7 +23196,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -23210,31 +23207,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D49" t="s">
+        <v>172</v>
+      </c>
+      <c r="E49" t="s">
+        <v>172</v>
+      </c>
+      <c r="F49" t="s">
         <v>173</v>
       </c>
-      <c r="E49" t="s">
-        <v>173</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>174</v>
       </c>
-      <c r="G49" t="s">
-        <v>175</v>
-      </c>
       <c r="H49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -23342,7 +23339,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -23353,31 +23350,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E50" t="s">
+        <v>172</v>
+      </c>
+      <c r="F50" t="s">
         <v>173</v>
       </c>
-      <c r="E50" t="s">
-        <v>173</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>174</v>
       </c>
-      <c r="G50" t="s">
-        <v>175</v>
-      </c>
       <c r="H50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -23485,7 +23482,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -23499,28 +23496,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
+        <v>172</v>
+      </c>
+      <c r="E51" t="s">
+        <v>172</v>
+      </c>
+      <c r="F51" t="s">
         <v>173</v>
       </c>
-      <c r="E51" t="s">
-        <v>173</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>174</v>
       </c>
-      <c r="G51" t="s">
-        <v>175</v>
-      </c>
       <c r="H51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -23628,7 +23625,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -23639,31 +23636,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D52" t="s">
+        <v>172</v>
+      </c>
+      <c r="E52" t="s">
+        <v>172</v>
+      </c>
+      <c r="F52" t="s">
         <v>173</v>
       </c>
-      <c r="E52" t="s">
-        <v>173</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>174</v>
       </c>
-      <c r="G52" t="s">
-        <v>175</v>
-      </c>
       <c r="H52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -23771,7 +23768,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -23782,31 +23779,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D53" t="s">
+        <v>172</v>
+      </c>
+      <c r="E53" t="s">
+        <v>172</v>
+      </c>
+      <c r="F53" t="s">
         <v>173</v>
       </c>
-      <c r="E53" t="s">
-        <v>173</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>174</v>
       </c>
-      <c r="G53" t="s">
-        <v>175</v>
-      </c>
       <c r="H53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -23914,7 +23911,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -23925,31 +23922,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D54" t="s">
+        <v>172</v>
+      </c>
+      <c r="E54" t="s">
+        <v>172</v>
+      </c>
+      <c r="F54" t="s">
         <v>173</v>
       </c>
-      <c r="E54" t="s">
-        <v>173</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>174</v>
       </c>
-      <c r="G54" t="s">
-        <v>175</v>
-      </c>
       <c r="H54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -24057,7 +24054,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -24068,31 +24065,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D55" t="s">
+        <v>172</v>
+      </c>
+      <c r="E55" t="s">
+        <v>172</v>
+      </c>
+      <c r="F55" t="s">
         <v>173</v>
       </c>
-      <c r="E55" t="s">
-        <v>173</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>174</v>
       </c>
-      <c r="G55" t="s">
-        <v>175</v>
-      </c>
       <c r="H55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -24200,7 +24197,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook" updateLinks="never"/>
   <bookViews>
-    <workbookView windowHeight="7520" activeTab="1"/>
+    <workbookView windowWidth="18340" windowHeight="8720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TechSelection" sheetId="21" r:id="rId1"/>
@@ -1372,8 +1372,8 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -11821,15 +11821,17 @@
       <c r="BA63" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="CQ63" s="11" t="s">
+      <c r="CQ63" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:99">
       <c r="A65" s="2"/>
-      <c r="B65" s="12" t="s">
-        <v>73</v>
-      </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
@@ -11879,12 +11881,12 @@
       <c r="BG65" s="2"/>
       <c r="BH65" s="2"/>
       <c r="BI65" s="2"/>
-      <c r="CO65" s="11"/>
-      <c r="CP65" s="11"/>
-      <c r="CR65" s="11"/>
-      <c r="CS65" s="11"/>
-      <c r="CT65" s="11"/>
-      <c r="CU65" s="11"/>
+      <c r="CO65" s="12"/>
+      <c r="CP65" s="12"/>
+      <c r="CR65" s="12"/>
+      <c r="CS65" s="12"/>
+      <c r="CT65" s="12"/>
+      <c r="CU65" s="12"/>
     </row>
     <row r="66" s="2" customFormat="1" spans="1:99">
       <c r="A66" s="2" t="s">
@@ -12001,13 +12003,13 @@
       <c r="AL66" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM66" s="12" t="s">
+      <c r="AM66" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="AN66" s="12" t="s">
+      <c r="AN66" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="AO66" s="12" t="s">
+      <c r="AO66" s="11" t="s">
         <v>58</v>
       </c>
       <c r="AY66" s="2" t="s">
@@ -14253,10 +14255,10 @@
       <c r="CO73" s="21">
         <v>0</v>
       </c>
-      <c r="CP73" s="11" t="s">
+      <c r="CP73" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="CQ73" s="11" t="s">
+      <c r="CQ73" s="12" t="s">
         <v>133</v>
       </c>
       <c r="CR73" s="21" t="s">
@@ -14265,10 +14267,10 @@
       <c r="CS73" s="21">
         <v>5</v>
       </c>
-      <c r="CT73" s="11" t="s">
+      <c r="CT73" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="CU73" s="11" t="s">
+      <c r="CU73" s="12" t="s">
         <v>141</v>
       </c>
     </row>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="198">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -467,6 +467,9 @@
     <t>Saudi Arabia</t>
   </si>
   <si>
+    <t>cset_set</t>
+  </si>
+  <si>
     <t>annual</t>
   </si>
   <si>
@@ -474,6 +477,9 @@
   </si>
   <si>
     <t>MINBatMaterials</t>
+  </si>
+  <si>
+    <t>MINBatMaterials_MATO</t>
   </si>
   <si>
     <t>m_lithium</t>
@@ -671,7 +677,7 @@
     <numFmt numFmtId="178" formatCode="0.0"/>
     <numFmt numFmtId="179" formatCode="0.000"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -698,6 +704,12 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.2"/>
+      <color rgb="FF212529"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -863,7 +875,7 @@
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -885,6 +897,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1212,31 +1230,28 @@
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1245,37 +1260,37 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1290,77 +1305,80 @@
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1372,8 +1390,8 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1382,6 +1400,7 @@
     <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -1870,29 +1889,29 @@
   <dimension ref="A1:AA281"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="22" customWidth="1"/>
-    <col min="2" max="2" width="8.85454545454546" style="22" customWidth="1"/>
-    <col min="3" max="3" width="4.70909090909091" style="22" customWidth="1"/>
-    <col min="4" max="4" width="8.85454545454546" style="22" customWidth="1"/>
-    <col min="5" max="5" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="6" max="6" width="4.28181818181818" style="22" customWidth="1"/>
-    <col min="7" max="7" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="8" max="8" width="4.57272727272727" style="22" customWidth="1"/>
-    <col min="9" max="9" width="4" style="22" customWidth="1"/>
-    <col min="10" max="10" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="11" max="11" width="4.57272727272727" style="22" customWidth="1"/>
-    <col min="12" max="12" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="13" max="13" width="4" style="22" customWidth="1"/>
-    <col min="14" max="14" width="4.28181818181818" style="22" customWidth="1"/>
-    <col min="15" max="16" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="17" max="18" width="4.57272727272727" style="22" customWidth="1"/>
-    <col min="19" max="19" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="20" max="20" width="5" style="22" customWidth="1"/>
-    <col min="21" max="21" width="11.7090909090909" style="22" customWidth="1"/>
-    <col min="22" max="22" width="10.7090909090909" style="22" customWidth="1"/>
-    <col min="23" max="23" width="13.1363636363636" style="22" customWidth="1"/>
-    <col min="24" max="259" width="11.4272727272727" style="22" customWidth="1"/>
-    <col min="260" max="16384" width="9.13636363636364" style="22"/>
+    <col min="1" max="1" width="15" style="23" customWidth="1"/>
+    <col min="2" max="2" width="8.85454545454546" style="23" customWidth="1"/>
+    <col min="3" max="3" width="4.70909090909091" style="23" customWidth="1"/>
+    <col min="4" max="4" width="8.85454545454546" style="23" customWidth="1"/>
+    <col min="5" max="5" width="4.42727272727273" style="23" customWidth="1"/>
+    <col min="6" max="6" width="4.28181818181818" style="23" customWidth="1"/>
+    <col min="7" max="7" width="4.42727272727273" style="23" customWidth="1"/>
+    <col min="8" max="8" width="4.57272727272727" style="23" customWidth="1"/>
+    <col min="9" max="9" width="4" style="23" customWidth="1"/>
+    <col min="10" max="10" width="4.42727272727273" style="23" customWidth="1"/>
+    <col min="11" max="11" width="4.57272727272727" style="23" customWidth="1"/>
+    <col min="12" max="12" width="4.42727272727273" style="23" customWidth="1"/>
+    <col min="13" max="13" width="4" style="23" customWidth="1"/>
+    <col min="14" max="14" width="4.28181818181818" style="23" customWidth="1"/>
+    <col min="15" max="16" width="4.42727272727273" style="23" customWidth="1"/>
+    <col min="17" max="18" width="4.57272727272727" style="23" customWidth="1"/>
+    <col min="19" max="19" width="4.42727272727273" style="23" customWidth="1"/>
+    <col min="20" max="20" width="5" style="23" customWidth="1"/>
+    <col min="21" max="21" width="11.7090909090909" style="23" customWidth="1"/>
+    <col min="22" max="22" width="10.7090909090909" style="23" customWidth="1"/>
+    <col min="23" max="23" width="13.1363636363636" style="23" customWidth="1"/>
+    <col min="24" max="259" width="11.4272727272727" style="23" customWidth="1"/>
+    <col min="260" max="16384" width="9.13636363636364" style="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.5" spans="1:21">
@@ -2971,7 +2990,7 @@
       <c r="AA34" s="5"/>
     </row>
     <row r="35" ht="12.5" spans="1:27">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="23" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -2999,7 +3018,7 @@
       <c r="AA35" s="5"/>
     </row>
     <row r="36" ht="12.5" spans="1:27">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="23" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -3027,7 +3046,7 @@
       <c r="AA36" s="5"/>
     </row>
     <row r="37" ht="12.5" spans="1:27">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="23" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -3055,7 +3074,7 @@
       <c r="AA37" s="5"/>
     </row>
     <row r="38" ht="12.5" spans="1:27">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="23" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -3083,7 +3102,7 @@
       <c r="AA38" s="5"/>
     </row>
     <row r="39" ht="12.5" spans="1:27">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="23" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -8755,7 +8774,7 @@
       <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="24" t="s">
         <v>92</v>
       </c>
       <c r="F14">
@@ -8814,7 +8833,7 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="24" t="s">
         <v>92</v>
       </c>
       <c r="C18">
@@ -8823,7 +8842,7 @@
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="24" t="s">
         <v>100</v>
       </c>
       <c r="F18" t="s">
@@ -11611,7 +11630,7 @@
       <c r="D45">
         <v>2020</v>
       </c>
-      <c r="E45" s="24" t="s">
+      <c r="E45" s="25" t="s">
         <v>119</v>
       </c>
       <c r="F45" t="s">
@@ -11695,7 +11714,7 @@
       <c r="D55" t="s">
         <v>126</v>
       </c>
-      <c r="E55" s="23" t="s">
+      <c r="E55" s="24" t="s">
         <v>127</v>
       </c>
     </row>
@@ -11821,17 +11840,15 @@
       <c r="BA63" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="CQ63" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2">
-      <c r="B64" s="11" t="s">
+      <c r="CQ63" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:99">
       <c r="A65" s="2"/>
+      <c r="B65" s="12" t="s">
+        <v>73</v>
+      </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
@@ -11881,12 +11898,12 @@
       <c r="BG65" s="2"/>
       <c r="BH65" s="2"/>
       <c r="BI65" s="2"/>
-      <c r="CO65" s="12"/>
-      <c r="CP65" s="12"/>
-      <c r="CR65" s="12"/>
-      <c r="CS65" s="12"/>
-      <c r="CT65" s="12"/>
-      <c r="CU65" s="12"/>
+      <c r="CO65" s="11"/>
+      <c r="CP65" s="11"/>
+      <c r="CR65" s="11"/>
+      <c r="CS65" s="11"/>
+      <c r="CT65" s="11"/>
+      <c r="CU65" s="11"/>
     </row>
     <row r="66" s="2" customFormat="1" spans="1:99">
       <c r="A66" s="2" t="s">
@@ -12003,13 +12020,16 @@
       <c r="AL66" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM66" s="11" t="s">
+      <c r="AM66" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AN66" s="11" t="s">
+      <c r="AN66" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="AO66" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AO66" s="11" t="s">
+      <c r="AP66" s="12" t="s">
         <v>58</v>
       </c>
       <c r="AY66" s="2" t="s">
@@ -12135,34 +12155,34 @@
       <c r="CM66" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="CO66" s="21" t="s">
+      <c r="CO66" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="CP66" s="21" t="s">
+      <c r="CP66" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="CQ66" s="21" t="s">
+      <c r="CQ66" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="CR66" s="21" t="s">
+      <c r="CR66" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="CS66" s="21" t="s">
+      <c r="CS66" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="CT66" s="21" t="s">
+      <c r="CT66" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="CU66" s="21" t="s">
+      <c r="CU66" s="22" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" ht="14.5" spans="1:99">
+    <row r="67" s="2" customFormat="1" ht="16" spans="1:99">
       <c r="A67" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>68</v>
@@ -12306,22 +12326,25 @@
         <v>0</v>
       </c>
       <c r="AM67" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN67" s="1" t="s">
         <v>135</v>
       </c>
+      <c r="AN67" s="21" t="s">
+        <v>136</v>
+      </c>
       <c r="AO67" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
+      </c>
+      <c r="AP67" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="AY67" s="2">
         <v>2050</v>
       </c>
       <c r="AZ67" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BA67" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BB67" s="2" t="s">
         <v>68</v>
@@ -12432,39 +12455,39 @@
         <v>0</v>
       </c>
       <c r="CL67" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="CM67" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="CO67" s="22">
+        <v>0</v>
+      </c>
+      <c r="CP67" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ67" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="CM67" s="2" t="s">
+      <c r="CR67" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS67" s="22">
+        <v>5</v>
+      </c>
+      <c r="CT67" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="CO67" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP67" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ67" s="21" t="s">
+      <c r="CU67" s="22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" ht="16" spans="1:99">
+      <c r="A68" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="CR67" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS67" s="21">
-        <v>5</v>
-      </c>
-      <c r="CT67" s="21" t="s">
+      <c r="B68" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="CU67" s="21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A68" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>68</v>
@@ -12609,22 +12632,25 @@
         <v>0</v>
       </c>
       <c r="AM68" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN68" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN68" s="21" t="s">
         <v>136</v>
       </c>
       <c r="AO68" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
+      </c>
+      <c r="AP68" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="AY68" s="2">
         <v>2050</v>
       </c>
       <c r="AZ68" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BA68" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BB68" s="2" t="s">
         <v>68</v>
@@ -12735,39 +12761,39 @@
         <v>0</v>
       </c>
       <c r="CL68" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="CM68" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="CO68" s="22">
+        <v>0</v>
+      </c>
+      <c r="CP68" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ68" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="CM68" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="CO68" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP68" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ68" s="21" t="s">
+      <c r="CR68" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS68" s="22">
+        <v>5</v>
+      </c>
+      <c r="CT68" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="CU68" s="22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" ht="16" spans="1:99">
+      <c r="A69" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="CR68" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS68" s="21">
-        <v>5</v>
-      </c>
-      <c r="CT68" s="21" t="s">
+      <c r="B69" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="CU68" s="21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A69" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>68</v>
@@ -12912,22 +12938,25 @@
         <v>0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN69" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
+      </c>
+      <c r="AN69" s="21" t="s">
+        <v>136</v>
       </c>
       <c r="AO69" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
+      </c>
+      <c r="AP69" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="AY69" s="2">
         <v>2050</v>
       </c>
       <c r="AZ69" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BA69" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BB69" s="2" t="s">
         <v>68</v>
@@ -13038,39 +13067,39 @@
         <v>0</v>
       </c>
       <c r="CL69" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="CM69" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="CO69" s="22">
+        <v>0</v>
+      </c>
+      <c r="CP69" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ69" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="CM69" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="CO69" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP69" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ69" s="21" t="s">
+      <c r="CR69" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS69" s="22">
+        <v>5</v>
+      </c>
+      <c r="CT69" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="CU69" s="22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" ht="16" spans="1:99">
+      <c r="A70" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="CR69" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS69" s="21">
-        <v>5</v>
-      </c>
-      <c r="CT69" s="21" t="s">
+      <c r="B70" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="CU69" s="21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A70" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>68</v>
@@ -13214,22 +13243,25 @@
         <v>140000</v>
       </c>
       <c r="AM70" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN70" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
+      </c>
+      <c r="AN70" s="21" t="s">
+        <v>136</v>
       </c>
       <c r="AO70" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
+      </c>
+      <c r="AP70" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="AY70" s="2">
         <v>2050</v>
       </c>
       <c r="AZ70" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BA70" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BB70" s="2" t="s">
         <v>68</v>
@@ -13340,39 +13372,39 @@
         <v>140000</v>
       </c>
       <c r="CL70" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="CM70" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="CO70" s="22">
+        <v>0</v>
+      </c>
+      <c r="CP70" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ70" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="CM70" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="CO70" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP70" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ70" s="21" t="s">
+      <c r="CR70" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS70" s="22">
+        <v>5</v>
+      </c>
+      <c r="CT70" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="CU70" s="22" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" ht="16" spans="1:99">
+      <c r="A71" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="CR70" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS70" s="21">
-        <v>5</v>
-      </c>
-      <c r="CT70" s="21" t="s">
+      <c r="B71" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="CU70" s="21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A71" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>68</v>
@@ -13515,22 +13547,25 @@
         <v>0</v>
       </c>
       <c r="AM71" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN71" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
+      </c>
+      <c r="AN71" s="21" t="s">
+        <v>136</v>
       </c>
       <c r="AO71" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
+      </c>
+      <c r="AP71" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="AY71" s="2">
         <v>2050</v>
       </c>
       <c r="AZ71" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BA71" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BB71" s="2" t="s">
         <v>68</v>
@@ -13641,39 +13676,39 @@
         <v>0</v>
       </c>
       <c r="CL71" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="CM71" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="CO71" s="22">
+        <v>0</v>
+      </c>
+      <c r="CP71" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ71" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="CM71" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="CO71" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP71" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ71" s="21" t="s">
+      <c r="CR71" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS71" s="22">
+        <v>5</v>
+      </c>
+      <c r="CT71" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="CU71" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" ht="16" spans="1:99">
+      <c r="A72" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="CR71" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS71" s="21">
-        <v>5</v>
-      </c>
-      <c r="CT71" s="21" t="s">
+      <c r="B72" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="CU71" s="21" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A72" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>68</v>
@@ -13818,22 +13853,25 @@
         <v>0</v>
       </c>
       <c r="AM72" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN72" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
+      </c>
+      <c r="AN72" s="21" t="s">
+        <v>136</v>
       </c>
       <c r="AO72" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
+      </c>
+      <c r="AP72" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="AY72" s="2">
         <v>2050</v>
       </c>
       <c r="AZ72" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BA72" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BB72" s="2" t="s">
         <v>68</v>
@@ -13944,39 +13982,39 @@
         <v>0</v>
       </c>
       <c r="CL72" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="CM72" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CO72" s="22">
+        <v>0</v>
+      </c>
+      <c r="CP72" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ72" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="CM72" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="CO72" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP72" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ72" s="21" t="s">
+      <c r="CR72" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS72" s="22">
+        <v>5</v>
+      </c>
+      <c r="CT72" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="CU72" s="22" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="16" spans="1:99">
+      <c r="A73" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="CR72" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS72" s="21">
-        <v>5</v>
-      </c>
-      <c r="CT72" s="21" t="s">
+      <c r="B73" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="CU72" s="21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A73" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>68</v>
@@ -14121,22 +14159,25 @@
         <v>0</v>
       </c>
       <c r="AM73" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN73" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
+      </c>
+      <c r="AN73" s="21" t="s">
+        <v>136</v>
       </c>
       <c r="AO73" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
+      </c>
+      <c r="AP73" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="AY73" s="2">
         <v>2050</v>
       </c>
       <c r="AZ73" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BA73" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="BB73" s="2" t="s">
         <v>68</v>
@@ -14247,37 +14288,37 @@
         <v>0</v>
       </c>
       <c r="CL73" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="CM73" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="CO73" s="22">
+        <v>0</v>
+      </c>
+      <c r="CP73" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="CQ73" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="CM73" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="CO73" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP73" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ73" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="CR73" s="21" t="s">
+      <c r="CR73" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="CS73" s="21">
+      <c r="CS73" s="22">
         <v>5</v>
       </c>
-      <c r="CT73" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="CU73" s="12" t="s">
-        <v>141</v>
+      <c r="CT73" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="CU73" s="11" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
@@ -14931,7 +14972,7 @@
     </row>
     <row r="88" spans="2:26">
       <c r="B88" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -15146,7 +15187,7 @@
         <v>118</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E104" s="17">
         <v>7.11384396954065</v>
@@ -15164,7 +15205,7 @@
         <v>118</v>
       </c>
       <c r="N104" s="17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O104" s="17">
         <f>E104*0.313</f>
@@ -15185,7 +15226,7 @@
         <v>118</v>
       </c>
       <c r="Z104" s="17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AA104" s="17">
         <v>5</v>
@@ -15202,7 +15243,7 @@
         <v>118</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E105" s="17">
         <v>7.11384396954065</v>
@@ -15220,7 +15261,7 @@
         <v>118</v>
       </c>
       <c r="N105" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O105" s="17">
         <f t="shared" ref="O105:O124" si="16">E105*0.313</f>
@@ -15241,7 +15282,7 @@
         <v>118</v>
       </c>
       <c r="Z105" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AA105" s="17">
         <v>5</v>
@@ -15258,7 +15299,7 @@
         <v>118</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E106" s="17">
         <v>7.62975445836404</v>
@@ -15276,7 +15317,7 @@
         <v>118</v>
       </c>
       <c r="N106" s="17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O106" s="17">
         <f t="shared" si="16"/>
@@ -15297,7 +15338,7 @@
         <v>118</v>
       </c>
       <c r="Z106" s="17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AA106" s="17">
         <v>5</v>
@@ -15314,7 +15355,7 @@
         <v>118</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E107" s="17">
         <v>7.47097081798084</v>
@@ -15332,7 +15373,7 @@
         <v>118</v>
       </c>
       <c r="N107" s="17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O107" s="17">
         <f t="shared" si="16"/>
@@ -15353,7 +15394,7 @@
         <v>118</v>
       </c>
       <c r="Z107" s="17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AA107" s="17">
         <v>5</v>
@@ -15370,7 +15411,7 @@
         <v>118</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E108" s="17">
         <v>7.51643520019651</v>
@@ -15388,7 +15429,7 @@
         <v>118</v>
       </c>
       <c r="N108" s="17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O108" s="17">
         <f t="shared" si="16"/>
@@ -15409,7 +15450,7 @@
         <v>118</v>
       </c>
       <c r="Z108" s="17" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AA108" s="17">
         <v>5</v>
@@ -15426,7 +15467,7 @@
         <v>118</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E109" s="17">
         <v>7.55036263817244</v>
@@ -15444,7 +15485,7 @@
         <v>118</v>
       </c>
       <c r="N109" s="17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O109" s="17">
         <f t="shared" si="16"/>
@@ -15465,7 +15506,7 @@
         <v>118</v>
       </c>
       <c r="Z109" s="17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AA109" s="17">
         <v>5</v>
@@ -15482,7 +15523,7 @@
         <v>118</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E110" s="17">
         <v>7.62975445836404</v>
@@ -15500,7 +15541,7 @@
         <v>118</v>
       </c>
       <c r="N110" s="17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O110" s="17">
         <f t="shared" si="16"/>
@@ -15521,7 +15562,7 @@
         <v>118</v>
       </c>
       <c r="Z110" s="17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AA110" s="17">
         <v>5</v>
@@ -15538,7 +15579,7 @@
         <v>118</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E111" s="17">
         <v>4.18384600835176</v>
@@ -15556,7 +15597,7 @@
         <v>118</v>
       </c>
       <c r="N111" s="17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O111" s="17">
         <f t="shared" si="16"/>
@@ -15577,7 +15618,7 @@
         <v>118</v>
       </c>
       <c r="Z111" s="17" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AA111" s="17">
         <v>5</v>
@@ -15594,7 +15635,7 @@
         <v>118</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E112" s="17">
         <v>4.18384600835176</v>
@@ -15612,7 +15653,7 @@
         <v>118</v>
       </c>
       <c r="N112" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O112" s="17">
         <f t="shared" si="16"/>
@@ -15633,7 +15674,7 @@
         <v>118</v>
       </c>
       <c r="Z112" s="17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AA112" s="17">
         <v>5</v>
@@ -15650,7 +15691,7 @@
         <v>118</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E113" s="17">
         <v>4.18384600835176</v>
@@ -15668,7 +15709,7 @@
         <v>118</v>
       </c>
       <c r="N113" s="17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O113" s="17">
         <f t="shared" si="16"/>
@@ -15689,7 +15730,7 @@
         <v>118</v>
       </c>
       <c r="Z113" s="17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AA113" s="17">
         <v>5</v>
@@ -15706,7 +15747,7 @@
         <v>118</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E114" s="17">
         <v>4.18384600835176</v>
@@ -15724,7 +15765,7 @@
         <v>118</v>
       </c>
       <c r="N114" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O114" s="17">
         <f t="shared" si="16"/>
@@ -15745,7 +15786,7 @@
         <v>118</v>
       </c>
       <c r="Z114" s="17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AA114" s="17">
         <v>5</v>
@@ -15762,7 +15803,7 @@
         <v>118</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E115" s="17">
         <v>4.18384600835176</v>
@@ -15780,7 +15821,7 @@
         <v>118</v>
       </c>
       <c r="N115" s="17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O115" s="17">
         <f t="shared" si="16"/>
@@ -15801,7 +15842,7 @@
         <v>118</v>
       </c>
       <c r="Z115" s="17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AA115" s="17">
         <v>5</v>
@@ -15818,7 +15859,7 @@
         <v>118</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E116" s="17">
         <v>4.18384600835176</v>
@@ -15836,7 +15877,7 @@
         <v>118</v>
       </c>
       <c r="N116" s="17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O116" s="17">
         <f t="shared" si="16"/>
@@ -15857,7 +15898,7 @@
         <v>118</v>
       </c>
       <c r="Z116" s="17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AA116" s="17">
         <v>5</v>
@@ -15874,7 +15915,7 @@
         <v>118</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E117" s="17">
         <v>4.18384600835176</v>
@@ -15892,7 +15933,7 @@
         <v>118</v>
       </c>
       <c r="N117" s="17" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O117" s="17">
         <f t="shared" si="16"/>
@@ -15913,7 +15954,7 @@
         <v>118</v>
       </c>
       <c r="Z117" s="17" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AA117" s="17">
         <v>5</v>
@@ -15930,7 +15971,7 @@
         <v>118</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E118" s="17">
         <v>3.56556266273643</v>
@@ -15948,7 +15989,7 @@
         <v>118</v>
       </c>
       <c r="N118" s="17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O118" s="17">
         <f t="shared" si="16"/>
@@ -15969,7 +16010,7 @@
         <v>118</v>
       </c>
       <c r="Z118" s="17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AA118" s="17">
         <v>5</v>
@@ -15986,7 +16027,7 @@
         <v>118</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E119" s="17">
         <v>3.60087708179809</v>
@@ -16004,7 +16045,7 @@
         <v>118</v>
       </c>
       <c r="N119" s="17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O119" s="17">
         <f t="shared" si="16"/>
@@ -16025,7 +16066,7 @@
         <v>118</v>
       </c>
       <c r="Z119" s="17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AA119" s="17">
         <v>5</v>
@@ -16042,7 +16083,7 @@
         <v>118</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E120" s="17">
         <v>3.56556266273643</v>
@@ -16060,7 +16101,7 @@
         <v>118</v>
       </c>
       <c r="N120" s="17" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O120" s="17">
         <f t="shared" si="16"/>
@@ -16081,7 +16122,7 @@
         <v>118</v>
       </c>
       <c r="Z120" s="17" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AA120" s="17">
         <v>5</v>
@@ -16098,7 +16139,7 @@
         <v>118</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E121" s="17">
         <v>3.56645369688037</v>
@@ -16116,7 +16157,7 @@
         <v>118</v>
       </c>
       <c r="N121" s="17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O121" s="17">
         <f t="shared" si="16"/>
@@ -16137,7 +16178,7 @@
         <v>118</v>
       </c>
       <c r="Z121" s="17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AA121" s="17">
         <v>5</v>
@@ -16154,7 +16195,7 @@
         <v>118</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E122" s="17">
         <v>3.56585961680177</v>
@@ -16172,7 +16213,7 @@
         <v>118</v>
       </c>
       <c r="N122" s="17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O122" s="17">
         <f t="shared" si="16"/>
@@ -16193,7 +16234,7 @@
         <v>118</v>
       </c>
       <c r="Z122" s="17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AA122" s="17">
         <v>5</v>
@@ -16210,7 +16251,7 @@
         <v>118</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E123" s="17">
         <v>3.56556266273643</v>
@@ -16228,7 +16269,7 @@
         <v>118</v>
       </c>
       <c r="N123" s="17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O123" s="17">
         <f t="shared" si="16"/>
@@ -16249,7 +16290,7 @@
         <v>118</v>
       </c>
       <c r="Z123" s="17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AA123" s="17">
         <v>5</v>
@@ -16266,7 +16307,7 @@
         <v>118</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E124" s="17">
         <v>3.56496890198968</v>
@@ -16284,7 +16325,7 @@
         <v>118</v>
       </c>
       <c r="N124" s="19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O124" s="17">
         <f t="shared" si="16"/>
@@ -16305,7 +16346,7 @@
         <v>118</v>
       </c>
       <c r="Z124" s="17" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AA124" s="17">
         <v>5</v>
@@ -16339,7 +16380,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -16351,25 +16392,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -16491,28 +16532,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -16620,7 +16661,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -16631,31 +16672,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -16763,7 +16804,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -16774,31 +16815,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -16906,7 +16947,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -16920,28 +16961,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -17049,7 +17090,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -17060,31 +17101,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -17192,7 +17233,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -17206,28 +17247,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -17335,7 +17376,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -17346,31 +17387,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G8" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -17478,7 +17519,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -17489,31 +17530,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -17621,7 +17662,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -17632,31 +17673,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -17764,7 +17805,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -17775,31 +17816,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -17907,7 +17948,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -17918,31 +17959,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -18050,7 +18091,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -18061,31 +18102,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -18193,7 +18234,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -18204,31 +18245,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -18336,7 +18377,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -18347,31 +18388,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -18479,7 +18520,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -18490,31 +18531,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -18622,7 +18663,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -18636,28 +18677,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -18765,7 +18806,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -18776,31 +18817,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -18908,7 +18949,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -18919,31 +18960,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -19051,7 +19092,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -19062,31 +19103,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -19194,7 +19235,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -19208,28 +19249,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -19337,7 +19378,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -19348,31 +19389,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -19480,7 +19521,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -19491,31 +19532,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -19623,7 +19664,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -19637,28 +19678,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G24" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H24" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I24" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J24" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K24" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -19766,7 +19807,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -19777,31 +19818,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G25" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -19909,7 +19950,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -19920,31 +19961,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -20052,7 +20093,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -20063,31 +20104,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -20195,7 +20236,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -20206,31 +20247,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -20338,7 +20379,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -20352,28 +20393,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F29" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -20481,7 +20522,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -20492,31 +20533,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
+        <v>177</v>
+      </c>
+      <c r="D30" t="s">
+        <v>174</v>
+      </c>
+      <c r="E30" t="s">
+        <v>174</v>
+      </c>
+      <c r="F30" t="s">
         <v>175</v>
       </c>
-      <c r="D30" t="s">
-        <v>172</v>
-      </c>
-      <c r="E30" t="s">
-        <v>172</v>
-      </c>
-      <c r="F30" t="s">
-        <v>173</v>
-      </c>
       <c r="G30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -20624,7 +20665,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -20635,31 +20676,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
+        <v>178</v>
+      </c>
+      <c r="D31" t="s">
+        <v>174</v>
+      </c>
+      <c r="E31" t="s">
+        <v>174</v>
+      </c>
+      <c r="F31" t="s">
+        <v>175</v>
+      </c>
+      <c r="G31" t="s">
         <v>176</v>
       </c>
-      <c r="D31" t="s">
-        <v>172</v>
-      </c>
-      <c r="E31" t="s">
-        <v>172</v>
-      </c>
-      <c r="F31" t="s">
-        <v>173</v>
-      </c>
-      <c r="G31" t="s">
-        <v>174</v>
-      </c>
       <c r="H31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -20767,7 +20808,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -20781,28 +20822,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F32" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -20910,7 +20951,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -20921,31 +20962,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -21053,7 +21094,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -21067,28 +21108,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F34" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G34" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -21196,7 +21237,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -21207,31 +21248,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F35" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G35" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -21339,7 +21380,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -21350,31 +21391,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G36" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -21482,7 +21523,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -21493,31 +21534,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F37" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G37" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -21625,7 +21666,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -21636,31 +21677,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F38" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G38" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -21768,7 +21809,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -21779,31 +21820,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G39" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -21911,7 +21952,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -21922,31 +21963,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F40" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G40" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -22054,7 +22095,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -22065,31 +22106,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F41" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G41" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -22197,7 +22238,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -22208,31 +22249,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F42" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G42" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -22340,7 +22381,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -22351,31 +22392,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F43" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G43" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -22483,7 +22524,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -22497,28 +22538,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G44" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -22626,7 +22667,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -22637,31 +22678,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F45" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G45" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -22769,7 +22810,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -22780,31 +22821,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D46" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E46" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F46" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G46" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H46" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I46" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J46" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K46" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -22912,7 +22953,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -22923,31 +22964,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F47" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G47" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -23055,7 +23096,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -23069,28 +23110,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E48" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F48" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G48" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H48" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I48" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J48" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K48" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -23198,7 +23239,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -23209,31 +23250,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F49" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G49" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -23341,7 +23382,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -23352,31 +23393,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G50" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -23484,7 +23525,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -23498,28 +23539,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F51" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G51" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -23627,7 +23668,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -23638,31 +23679,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F52" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G52" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -23770,7 +23811,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -23781,31 +23822,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F53" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G53" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -23913,7 +23954,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -23924,31 +23965,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F54" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G54" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -24056,7 +24097,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -24067,31 +24108,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F55" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G55" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -24199,7 +24240,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="197">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -465,9 +465,6 @@
   </si>
   <si>
     <t>Saudi Arabia</t>
-  </si>
-  <si>
-    <t>cset_set</t>
   </si>
   <si>
     <t>annual</t>
@@ -875,7 +872,7 @@
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -897,12 +894,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1251,7 +1242,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1275,16 +1266,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1293,85 +1284,85 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1400,7 +1391,7 @@
     <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -12024,7 +12015,7 @@
         <v>45</v>
       </c>
       <c r="AN66" s="12" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="AO66" s="2" t="s">
         <v>59</v>
@@ -12179,10 +12170,10 @@
     </row>
     <row r="67" s="2" customFormat="1" ht="16" spans="1:99">
       <c r="A67" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>68</v>
@@ -12326,25 +12317,25 @@
         <v>0</v>
       </c>
       <c r="AM67" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN67" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="AN67" s="21" t="s">
+      <c r="AO67" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="AO67" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="AP67" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AY67" s="2">
         <v>2050</v>
       </c>
       <c r="AZ67" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA67" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BA67" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BB67" s="2" t="s">
         <v>68</v>
@@ -12455,19 +12446,19 @@
         <v>0</v>
       </c>
       <c r="CL67" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM67" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="CO67" s="22">
         <v>0</v>
       </c>
       <c r="CP67" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ67" s="22" t="s">
         <v>133</v>
-      </c>
-      <c r="CQ67" s="22" t="s">
-        <v>134</v>
       </c>
       <c r="CR67" s="22" t="s">
         <v>68</v>
@@ -12476,18 +12467,18 @@
         <v>5</v>
       </c>
       <c r="CT67" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CU67" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" ht="16" spans="1:99">
       <c r="A68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>68</v>
@@ -12632,25 +12623,25 @@
         <v>0</v>
       </c>
       <c r="AM68" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN68" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="AN68" s="21" t="s">
-        <v>136</v>
-      </c>
       <c r="AO68" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AP68" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AY68" s="2">
         <v>2050</v>
       </c>
       <c r="AZ68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA68" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BA68" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BB68" s="2" t="s">
         <v>68</v>
@@ -12761,19 +12752,19 @@
         <v>0</v>
       </c>
       <c r="CL68" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM68" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="CO68" s="22">
         <v>0</v>
       </c>
       <c r="CP68" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ68" s="22" t="s">
         <v>133</v>
-      </c>
-      <c r="CQ68" s="22" t="s">
-        <v>134</v>
       </c>
       <c r="CR68" s="22" t="s">
         <v>68</v>
@@ -12782,18 +12773,18 @@
         <v>5</v>
       </c>
       <c r="CT68" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CU68" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" ht="16" spans="1:99">
       <c r="A69" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B69" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>68</v>
@@ -12938,25 +12929,25 @@
         <v>0</v>
       </c>
       <c r="AM69" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN69" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="AN69" s="21" t="s">
-        <v>136</v>
-      </c>
       <c r="AO69" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AP69" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AY69" s="2">
         <v>2050</v>
       </c>
       <c r="AZ69" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA69" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BA69" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BB69" s="2" t="s">
         <v>68</v>
@@ -13067,19 +13058,19 @@
         <v>0</v>
       </c>
       <c r="CL69" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM69" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="CO69" s="22">
         <v>0</v>
       </c>
       <c r="CP69" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ69" s="22" t="s">
         <v>133</v>
-      </c>
-      <c r="CQ69" s="22" t="s">
-        <v>134</v>
       </c>
       <c r="CR69" s="22" t="s">
         <v>68</v>
@@ -13088,18 +13079,18 @@
         <v>5</v>
       </c>
       <c r="CT69" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CU69" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" ht="16" spans="1:99">
       <c r="A70" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B70" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>68</v>
@@ -13243,25 +13234,25 @@
         <v>140000</v>
       </c>
       <c r="AM70" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN70" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="AN70" s="21" t="s">
-        <v>136</v>
-      </c>
       <c r="AO70" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AP70" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AY70" s="2">
         <v>2050</v>
       </c>
       <c r="AZ70" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA70" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BA70" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BB70" s="2" t="s">
         <v>68</v>
@@ -13372,19 +13363,19 @@
         <v>140000</v>
       </c>
       <c r="CL70" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM70" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="CO70" s="22">
         <v>0</v>
       </c>
       <c r="CP70" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ70" s="22" t="s">
         <v>133</v>
-      </c>
-      <c r="CQ70" s="22" t="s">
-        <v>134</v>
       </c>
       <c r="CR70" s="22" t="s">
         <v>68</v>
@@ -13393,18 +13384,18 @@
         <v>5</v>
       </c>
       <c r="CT70" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CU70" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" ht="16" spans="1:99">
       <c r="A71" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B71" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>68</v>
@@ -13547,25 +13538,25 @@
         <v>0</v>
       </c>
       <c r="AM71" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN71" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="AN71" s="21" t="s">
-        <v>136</v>
-      </c>
       <c r="AO71" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AP71" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AY71" s="2">
         <v>2050</v>
       </c>
       <c r="AZ71" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA71" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BA71" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BB71" s="2" t="s">
         <v>68</v>
@@ -13676,19 +13667,19 @@
         <v>0</v>
       </c>
       <c r="CL71" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM71" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="CO71" s="22">
         <v>0</v>
       </c>
       <c r="CP71" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ71" s="22" t="s">
         <v>133</v>
-      </c>
-      <c r="CQ71" s="22" t="s">
-        <v>134</v>
       </c>
       <c r="CR71" s="22" t="s">
         <v>68</v>
@@ -13697,18 +13688,18 @@
         <v>5</v>
       </c>
       <c r="CT71" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CU71" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" ht="16" spans="1:99">
       <c r="A72" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B72" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>68</v>
@@ -13853,25 +13844,25 @@
         <v>0</v>
       </c>
       <c r="AM72" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN72" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="AN72" s="21" t="s">
-        <v>136</v>
-      </c>
       <c r="AO72" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AP72" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AY72" s="2">
         <v>2050</v>
       </c>
       <c r="AZ72" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA72" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="BA72" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="BB72" s="2" t="s">
         <v>68</v>
@@ -13982,19 +13973,19 @@
         <v>0</v>
       </c>
       <c r="CL72" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM72" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="CO72" s="22">
         <v>0</v>
       </c>
       <c r="CP72" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ72" s="22" t="s">
         <v>133</v>
-      </c>
-      <c r="CQ72" s="22" t="s">
-        <v>134</v>
       </c>
       <c r="CR72" s="22" t="s">
         <v>68</v>
@@ -14003,18 +13994,18 @@
         <v>5</v>
       </c>
       <c r="CT72" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CU72" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="16" spans="1:99">
       <c r="A73" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" s="13" t="s">
         <v>133</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>134</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>68</v>
@@ -14159,25 +14150,25 @@
         <v>0</v>
       </c>
       <c r="AM73" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN73" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="AN73" s="21" t="s">
-        <v>136</v>
-      </c>
       <c r="AO73" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AP73" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AY73" s="2">
         <v>2050</v>
       </c>
       <c r="AZ73" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA73" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="BA73" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="BB73" s="2" t="s">
         <v>68</v>
@@ -14288,19 +14279,19 @@
         <v>0</v>
       </c>
       <c r="CL73" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CM73" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="CO73" s="22">
         <v>0</v>
       </c>
       <c r="CP73" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ73" s="11" t="s">
         <v>133</v>
-      </c>
-      <c r="CQ73" s="11" t="s">
-        <v>134</v>
       </c>
       <c r="CR73" s="22" t="s">
         <v>68</v>
@@ -14309,16 +14300,16 @@
         <v>5</v>
       </c>
       <c r="CT73" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="CU73" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
@@ -14972,7 +14963,7 @@
     </row>
     <row r="88" spans="2:26">
       <c r="B88" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -15187,7 +15178,7 @@
         <v>118</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E104" s="17">
         <v>7.11384396954065</v>
@@ -15205,7 +15196,7 @@
         <v>118</v>
       </c>
       <c r="N104" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O104" s="17">
         <f>E104*0.313</f>
@@ -15226,7 +15217,7 @@
         <v>118</v>
       </c>
       <c r="Z104" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AA104" s="17">
         <v>5</v>
@@ -15243,7 +15234,7 @@
         <v>118</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E105" s="17">
         <v>7.11384396954065</v>
@@ -15261,7 +15252,7 @@
         <v>118</v>
       </c>
       <c r="N105" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O105" s="17">
         <f t="shared" ref="O105:O124" si="16">E105*0.313</f>
@@ -15282,7 +15273,7 @@
         <v>118</v>
       </c>
       <c r="Z105" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AA105" s="17">
         <v>5</v>
@@ -15299,7 +15290,7 @@
         <v>118</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E106" s="17">
         <v>7.62975445836404</v>
@@ -15317,7 +15308,7 @@
         <v>118</v>
       </c>
       <c r="N106" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O106" s="17">
         <f t="shared" si="16"/>
@@ -15338,7 +15329,7 @@
         <v>118</v>
       </c>
       <c r="Z106" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA106" s="17">
         <v>5</v>
@@ -15355,7 +15346,7 @@
         <v>118</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E107" s="17">
         <v>7.47097081798084</v>
@@ -15373,7 +15364,7 @@
         <v>118</v>
       </c>
       <c r="N107" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O107" s="17">
         <f t="shared" si="16"/>
@@ -15394,7 +15385,7 @@
         <v>118</v>
       </c>
       <c r="Z107" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA107" s="17">
         <v>5</v>
@@ -15411,7 +15402,7 @@
         <v>118</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E108" s="17">
         <v>7.51643520019651</v>
@@ -15429,7 +15420,7 @@
         <v>118</v>
       </c>
       <c r="N108" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O108" s="17">
         <f t="shared" si="16"/>
@@ -15450,7 +15441,7 @@
         <v>118</v>
       </c>
       <c r="Z108" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AA108" s="17">
         <v>5</v>
@@ -15467,7 +15458,7 @@
         <v>118</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E109" s="17">
         <v>7.55036263817244</v>
@@ -15485,7 +15476,7 @@
         <v>118</v>
       </c>
       <c r="N109" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O109" s="17">
         <f t="shared" si="16"/>
@@ -15506,7 +15497,7 @@
         <v>118</v>
       </c>
       <c r="Z109" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA109" s="17">
         <v>5</v>
@@ -15523,7 +15514,7 @@
         <v>118</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E110" s="17">
         <v>7.62975445836404</v>
@@ -15541,7 +15532,7 @@
         <v>118</v>
       </c>
       <c r="N110" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O110" s="17">
         <f t="shared" si="16"/>
@@ -15562,7 +15553,7 @@
         <v>118</v>
       </c>
       <c r="Z110" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AA110" s="17">
         <v>5</v>
@@ -15579,7 +15570,7 @@
         <v>118</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E111" s="17">
         <v>4.18384600835176</v>
@@ -15597,7 +15588,7 @@
         <v>118</v>
       </c>
       <c r="N111" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O111" s="17">
         <f t="shared" si="16"/>
@@ -15618,7 +15609,7 @@
         <v>118</v>
       </c>
       <c r="Z111" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AA111" s="17">
         <v>5</v>
@@ -15635,7 +15626,7 @@
         <v>118</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E112" s="17">
         <v>4.18384600835176</v>
@@ -15653,7 +15644,7 @@
         <v>118</v>
       </c>
       <c r="N112" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O112" s="17">
         <f t="shared" si="16"/>
@@ -15674,7 +15665,7 @@
         <v>118</v>
       </c>
       <c r="Z112" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AA112" s="17">
         <v>5</v>
@@ -15691,7 +15682,7 @@
         <v>118</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E113" s="17">
         <v>4.18384600835176</v>
@@ -15709,7 +15700,7 @@
         <v>118</v>
       </c>
       <c r="N113" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O113" s="17">
         <f t="shared" si="16"/>
@@ -15730,7 +15721,7 @@
         <v>118</v>
       </c>
       <c r="Z113" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AA113" s="17">
         <v>5</v>
@@ -15747,7 +15738,7 @@
         <v>118</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E114" s="17">
         <v>4.18384600835176</v>
@@ -15765,7 +15756,7 @@
         <v>118</v>
       </c>
       <c r="N114" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O114" s="17">
         <f t="shared" si="16"/>
@@ -15786,7 +15777,7 @@
         <v>118</v>
       </c>
       <c r="Z114" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AA114" s="17">
         <v>5</v>
@@ -15803,7 +15794,7 @@
         <v>118</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E115" s="17">
         <v>4.18384600835176</v>
@@ -15821,7 +15812,7 @@
         <v>118</v>
       </c>
       <c r="N115" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O115" s="17">
         <f t="shared" si="16"/>
@@ -15842,7 +15833,7 @@
         <v>118</v>
       </c>
       <c r="Z115" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA115" s="17">
         <v>5</v>
@@ -15859,7 +15850,7 @@
         <v>118</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E116" s="17">
         <v>4.18384600835176</v>
@@ -15877,7 +15868,7 @@
         <v>118</v>
       </c>
       <c r="N116" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O116" s="17">
         <f t="shared" si="16"/>
@@ -15898,7 +15889,7 @@
         <v>118</v>
       </c>
       <c r="Z116" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA116" s="17">
         <v>5</v>
@@ -15915,7 +15906,7 @@
         <v>118</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E117" s="17">
         <v>4.18384600835176</v>
@@ -15933,7 +15924,7 @@
         <v>118</v>
       </c>
       <c r="N117" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O117" s="17">
         <f t="shared" si="16"/>
@@ -15954,7 +15945,7 @@
         <v>118</v>
       </c>
       <c r="Z117" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA117" s="17">
         <v>5</v>
@@ -15971,7 +15962,7 @@
         <v>118</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E118" s="17">
         <v>3.56556266273643</v>
@@ -15989,7 +15980,7 @@
         <v>118</v>
       </c>
       <c r="N118" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O118" s="17">
         <f t="shared" si="16"/>
@@ -16010,7 +16001,7 @@
         <v>118</v>
       </c>
       <c r="Z118" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA118" s="17">
         <v>5</v>
@@ -16027,7 +16018,7 @@
         <v>118</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E119" s="17">
         <v>3.60087708179809</v>
@@ -16045,7 +16036,7 @@
         <v>118</v>
       </c>
       <c r="N119" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O119" s="17">
         <f t="shared" si="16"/>
@@ -16066,7 +16057,7 @@
         <v>118</v>
       </c>
       <c r="Z119" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA119" s="17">
         <v>5</v>
@@ -16083,7 +16074,7 @@
         <v>118</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E120" s="17">
         <v>3.56556266273643</v>
@@ -16101,7 +16092,7 @@
         <v>118</v>
       </c>
       <c r="N120" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O120" s="17">
         <f t="shared" si="16"/>
@@ -16122,7 +16113,7 @@
         <v>118</v>
       </c>
       <c r="Z120" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AA120" s="17">
         <v>5</v>
@@ -16139,7 +16130,7 @@
         <v>118</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E121" s="17">
         <v>3.56645369688037</v>
@@ -16157,7 +16148,7 @@
         <v>118</v>
       </c>
       <c r="N121" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O121" s="17">
         <f t="shared" si="16"/>
@@ -16178,7 +16169,7 @@
         <v>118</v>
       </c>
       <c r="Z121" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA121" s="17">
         <v>5</v>
@@ -16195,7 +16186,7 @@
         <v>118</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E122" s="17">
         <v>3.56585961680177</v>
@@ -16213,7 +16204,7 @@
         <v>118</v>
       </c>
       <c r="N122" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O122" s="17">
         <f t="shared" si="16"/>
@@ -16234,7 +16225,7 @@
         <v>118</v>
       </c>
       <c r="Z122" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA122" s="17">
         <v>5</v>
@@ -16251,7 +16242,7 @@
         <v>118</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E123" s="17">
         <v>3.56556266273643</v>
@@ -16269,7 +16260,7 @@
         <v>118</v>
       </c>
       <c r="N123" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O123" s="17">
         <f t="shared" si="16"/>
@@ -16290,7 +16281,7 @@
         <v>118</v>
       </c>
       <c r="Z123" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA123" s="17">
         <v>5</v>
@@ -16307,7 +16298,7 @@
         <v>118</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E124" s="17">
         <v>3.56496890198968</v>
@@ -16325,7 +16316,7 @@
         <v>118</v>
       </c>
       <c r="N124" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O124" s="17">
         <f t="shared" si="16"/>
@@ -16346,7 +16337,7 @@
         <v>118</v>
       </c>
       <c r="Z124" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA124" s="17">
         <v>5</v>
@@ -16380,7 +16371,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -16392,25 +16383,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
-      </c>
-      <c r="F1" t="s">
-        <v>169</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1" t="s">
         <v>170</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>171</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>172</v>
-      </c>
-      <c r="K1" t="s">
-        <v>173</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -16532,28 +16523,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G2" t="s">
         <v>175</v>
       </c>
-      <c r="G2" t="s">
-        <v>176</v>
-      </c>
       <c r="H2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -16661,7 +16652,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -16672,31 +16663,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G3" t="s">
         <v>175</v>
       </c>
-      <c r="G3" t="s">
-        <v>176</v>
-      </c>
       <c r="H3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -16804,7 +16795,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -16815,31 +16806,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G4" t="s">
         <v>175</v>
       </c>
-      <c r="G4" t="s">
-        <v>176</v>
-      </c>
       <c r="H4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -16947,7 +16938,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -16961,28 +16952,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G5" t="s">
         <v>175</v>
       </c>
-      <c r="G5" t="s">
-        <v>176</v>
-      </c>
       <c r="H5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -17090,7 +17081,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -17101,31 +17092,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G6" t="s">
         <v>175</v>
       </c>
-      <c r="G6" t="s">
-        <v>176</v>
-      </c>
       <c r="H6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -17233,7 +17224,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -17247,28 +17238,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" t="s">
         <v>175</v>
       </c>
-      <c r="G7" t="s">
-        <v>176</v>
-      </c>
       <c r="H7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -17376,7 +17367,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -17387,31 +17378,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
+        <v>174</v>
+      </c>
+      <c r="G8" t="s">
         <v>175</v>
       </c>
-      <c r="G8" t="s">
-        <v>176</v>
-      </c>
       <c r="H8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -17519,7 +17510,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -17530,31 +17521,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G9" t="s">
         <v>175</v>
       </c>
-      <c r="G9" t="s">
-        <v>176</v>
-      </c>
       <c r="H9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -17662,7 +17653,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -17673,31 +17664,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
+        <v>174</v>
+      </c>
+      <c r="G10" t="s">
         <v>175</v>
       </c>
-      <c r="G10" t="s">
-        <v>176</v>
-      </c>
       <c r="H10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -17805,7 +17796,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -17816,31 +17807,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
+        <v>174</v>
+      </c>
+      <c r="G11" t="s">
         <v>175</v>
       </c>
-      <c r="G11" t="s">
-        <v>176</v>
-      </c>
       <c r="H11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -17948,7 +17939,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -17959,31 +17950,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
+        <v>174</v>
+      </c>
+      <c r="G12" t="s">
         <v>175</v>
       </c>
-      <c r="G12" t="s">
-        <v>176</v>
-      </c>
       <c r="H12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -18091,7 +18082,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -18102,31 +18093,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
+        <v>174</v>
+      </c>
+      <c r="G13" t="s">
         <v>175</v>
       </c>
-      <c r="G13" t="s">
-        <v>176</v>
-      </c>
       <c r="H13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -18234,7 +18225,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -18245,31 +18236,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14" t="s">
         <v>175</v>
       </c>
-      <c r="G14" t="s">
-        <v>176</v>
-      </c>
       <c r="H14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -18377,7 +18368,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -18388,31 +18379,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
+        <v>174</v>
+      </c>
+      <c r="G15" t="s">
         <v>175</v>
       </c>
-      <c r="G15" t="s">
-        <v>176</v>
-      </c>
       <c r="H15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -18520,7 +18511,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -18531,31 +18522,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
+        <v>174</v>
+      </c>
+      <c r="G16" t="s">
         <v>175</v>
       </c>
-      <c r="G16" t="s">
-        <v>176</v>
-      </c>
       <c r="H16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -18663,7 +18654,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -18677,28 +18668,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
+        <v>174</v>
+      </c>
+      <c r="G17" t="s">
         <v>175</v>
       </c>
-      <c r="G17" t="s">
-        <v>176</v>
-      </c>
       <c r="H17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -18806,7 +18797,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -18817,31 +18808,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" t="s">
         <v>175</v>
       </c>
-      <c r="G18" t="s">
-        <v>176</v>
-      </c>
       <c r="H18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -18949,7 +18940,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -18960,31 +18951,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
+        <v>174</v>
+      </c>
+      <c r="G19" t="s">
         <v>175</v>
       </c>
-      <c r="G19" t="s">
-        <v>176</v>
-      </c>
       <c r="H19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -19092,7 +19083,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -19103,31 +19094,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
+        <v>174</v>
+      </c>
+      <c r="G20" t="s">
         <v>175</v>
       </c>
-      <c r="G20" t="s">
-        <v>176</v>
-      </c>
       <c r="H20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -19235,7 +19226,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -19249,28 +19240,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
+        <v>174</v>
+      </c>
+      <c r="G21" t="s">
         <v>175</v>
       </c>
-      <c r="G21" t="s">
-        <v>176</v>
-      </c>
       <c r="H21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -19378,7 +19369,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -19389,31 +19380,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
+        <v>174</v>
+      </c>
+      <c r="G22" t="s">
         <v>175</v>
       </c>
-      <c r="G22" t="s">
-        <v>176</v>
-      </c>
       <c r="H22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -19521,7 +19512,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -19532,31 +19523,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
+        <v>174</v>
+      </c>
+      <c r="G23" t="s">
         <v>175</v>
       </c>
-      <c r="G23" t="s">
-        <v>176</v>
-      </c>
       <c r="H23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -19664,7 +19655,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -19678,28 +19669,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
+        <v>174</v>
+      </c>
+      <c r="G24" t="s">
         <v>175</v>
       </c>
-      <c r="G24" t="s">
-        <v>176</v>
-      </c>
       <c r="H24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -19807,7 +19798,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -19818,31 +19809,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
+        <v>174</v>
+      </c>
+      <c r="G25" t="s">
         <v>175</v>
       </c>
-      <c r="G25" t="s">
-        <v>176</v>
-      </c>
       <c r="H25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -19950,7 +19941,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -19961,31 +19952,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
+        <v>174</v>
+      </c>
+      <c r="G26" t="s">
         <v>175</v>
       </c>
-      <c r="G26" t="s">
-        <v>176</v>
-      </c>
       <c r="H26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -20093,7 +20084,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -20104,31 +20095,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
+        <v>174</v>
+      </c>
+      <c r="G27" t="s">
         <v>175</v>
       </c>
-      <c r="G27" t="s">
-        <v>176</v>
-      </c>
       <c r="H27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -20236,7 +20227,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -20247,31 +20238,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
+        <v>174</v>
+      </c>
+      <c r="G28" t="s">
         <v>175</v>
       </c>
-      <c r="G28" t="s">
-        <v>176</v>
-      </c>
       <c r="H28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -20379,7 +20370,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -20393,28 +20384,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
+        <v>173</v>
+      </c>
+      <c r="E29" t="s">
+        <v>173</v>
+      </c>
+      <c r="F29" t="s">
         <v>174</v>
       </c>
-      <c r="E29" t="s">
-        <v>174</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>175</v>
       </c>
-      <c r="G29" t="s">
-        <v>176</v>
-      </c>
       <c r="H29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -20522,7 +20513,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -20533,31 +20524,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D30" t="s">
+        <v>173</v>
+      </c>
+      <c r="E30" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" t="s">
         <v>174</v>
       </c>
-      <c r="E30" t="s">
-        <v>174</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>175</v>
       </c>
-      <c r="G30" t="s">
-        <v>176</v>
-      </c>
       <c r="H30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -20665,7 +20656,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -20676,31 +20667,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D31" t="s">
+        <v>173</v>
+      </c>
+      <c r="E31" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" t="s">
         <v>174</v>
       </c>
-      <c r="E31" t="s">
-        <v>174</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>175</v>
       </c>
-      <c r="G31" t="s">
-        <v>176</v>
-      </c>
       <c r="H31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -20808,7 +20799,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -20822,28 +20813,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32" t="s">
         <v>174</v>
       </c>
-      <c r="E32" t="s">
-        <v>174</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>175</v>
       </c>
-      <c r="G32" t="s">
-        <v>176</v>
-      </c>
       <c r="H32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -20951,7 +20942,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -20962,31 +20953,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D33" t="s">
+        <v>173</v>
+      </c>
+      <c r="E33" t="s">
+        <v>173</v>
+      </c>
+      <c r="F33" t="s">
         <v>174</v>
       </c>
-      <c r="E33" t="s">
-        <v>174</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>175</v>
       </c>
-      <c r="G33" t="s">
-        <v>176</v>
-      </c>
       <c r="H33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -21094,7 +21085,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -21108,28 +21099,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" t="s">
+        <v>173</v>
+      </c>
+      <c r="F34" t="s">
         <v>174</v>
       </c>
-      <c r="E34" t="s">
-        <v>174</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>175</v>
       </c>
-      <c r="G34" t="s">
-        <v>176</v>
-      </c>
       <c r="H34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -21237,7 +21228,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -21248,31 +21239,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D35" t="s">
+        <v>173</v>
+      </c>
+      <c r="E35" t="s">
+        <v>173</v>
+      </c>
+      <c r="F35" t="s">
         <v>174</v>
       </c>
-      <c r="E35" t="s">
-        <v>174</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>175</v>
       </c>
-      <c r="G35" t="s">
-        <v>176</v>
-      </c>
       <c r="H35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -21380,7 +21371,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -21391,31 +21382,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" t="s">
+        <v>173</v>
+      </c>
+      <c r="F36" t="s">
         <v>174</v>
       </c>
-      <c r="E36" t="s">
-        <v>174</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>175</v>
       </c>
-      <c r="G36" t="s">
-        <v>176</v>
-      </c>
       <c r="H36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -21523,7 +21514,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -21534,31 +21525,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D37" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" t="s">
         <v>174</v>
       </c>
-      <c r="E37" t="s">
-        <v>174</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>175</v>
       </c>
-      <c r="G37" t="s">
-        <v>176</v>
-      </c>
       <c r="H37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -21666,7 +21657,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -21677,31 +21668,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D38" t="s">
+        <v>173</v>
+      </c>
+      <c r="E38" t="s">
+        <v>173</v>
+      </c>
+      <c r="F38" t="s">
         <v>174</v>
       </c>
-      <c r="E38" t="s">
-        <v>174</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>175</v>
       </c>
-      <c r="G38" t="s">
-        <v>176</v>
-      </c>
       <c r="H38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -21809,7 +21800,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -21820,31 +21811,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D39" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" t="s">
+        <v>173</v>
+      </c>
+      <c r="F39" t="s">
         <v>174</v>
       </c>
-      <c r="E39" t="s">
-        <v>174</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>175</v>
       </c>
-      <c r="G39" t="s">
-        <v>176</v>
-      </c>
       <c r="H39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -21952,7 +21943,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -21963,31 +21954,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D40" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" t="s">
+        <v>173</v>
+      </c>
+      <c r="F40" t="s">
         <v>174</v>
       </c>
-      <c r="E40" t="s">
-        <v>174</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>175</v>
       </c>
-      <c r="G40" t="s">
-        <v>176</v>
-      </c>
       <c r="H40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -22095,7 +22086,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -22106,31 +22097,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D41" t="s">
+        <v>173</v>
+      </c>
+      <c r="E41" t="s">
+        <v>173</v>
+      </c>
+      <c r="F41" t="s">
         <v>174</v>
       </c>
-      <c r="E41" t="s">
-        <v>174</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>175</v>
       </c>
-      <c r="G41" t="s">
-        <v>176</v>
-      </c>
       <c r="H41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -22238,7 +22229,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -22249,31 +22240,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D42" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" t="s">
+        <v>173</v>
+      </c>
+      <c r="F42" t="s">
         <v>174</v>
       </c>
-      <c r="E42" t="s">
-        <v>174</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>175</v>
       </c>
-      <c r="G42" t="s">
-        <v>176</v>
-      </c>
       <c r="H42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -22381,7 +22372,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -22392,31 +22383,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D43" t="s">
+        <v>173</v>
+      </c>
+      <c r="E43" t="s">
+        <v>173</v>
+      </c>
+      <c r="F43" t="s">
         <v>174</v>
       </c>
-      <c r="E43" t="s">
-        <v>174</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>175</v>
       </c>
-      <c r="G43" t="s">
-        <v>176</v>
-      </c>
       <c r="H43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -22524,7 +22515,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -22538,28 +22529,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44" t="s">
+        <v>173</v>
+      </c>
+      <c r="F44" t="s">
         <v>174</v>
       </c>
-      <c r="E44" t="s">
-        <v>174</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>175</v>
       </c>
-      <c r="G44" t="s">
-        <v>176</v>
-      </c>
       <c r="H44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -22667,7 +22658,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -22678,31 +22669,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D45" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" t="s">
+        <v>173</v>
+      </c>
+      <c r="F45" t="s">
         <v>174</v>
       </c>
-      <c r="E45" t="s">
-        <v>174</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>175</v>
       </c>
-      <c r="G45" t="s">
-        <v>176</v>
-      </c>
       <c r="H45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -22810,7 +22801,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -22821,31 +22812,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D46" t="s">
+        <v>173</v>
+      </c>
+      <c r="E46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F46" t="s">
         <v>174</v>
       </c>
-      <c r="E46" t="s">
-        <v>174</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>175</v>
       </c>
-      <c r="G46" t="s">
-        <v>176</v>
-      </c>
       <c r="H46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -22953,7 +22944,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -22964,31 +22955,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D47" t="s">
+        <v>173</v>
+      </c>
+      <c r="E47" t="s">
+        <v>173</v>
+      </c>
+      <c r="F47" t="s">
         <v>174</v>
       </c>
-      <c r="E47" t="s">
-        <v>174</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>175</v>
       </c>
-      <c r="G47" t="s">
-        <v>176</v>
-      </c>
       <c r="H47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -23096,7 +23087,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -23110,28 +23101,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
+        <v>173</v>
+      </c>
+      <c r="E48" t="s">
+        <v>173</v>
+      </c>
+      <c r="F48" t="s">
         <v>174</v>
       </c>
-      <c r="E48" t="s">
-        <v>174</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>175</v>
       </c>
-      <c r="G48" t="s">
-        <v>176</v>
-      </c>
       <c r="H48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -23239,7 +23230,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -23250,31 +23241,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D49" t="s">
+        <v>173</v>
+      </c>
+      <c r="E49" t="s">
+        <v>173</v>
+      </c>
+      <c r="F49" t="s">
         <v>174</v>
       </c>
-      <c r="E49" t="s">
-        <v>174</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>175</v>
       </c>
-      <c r="G49" t="s">
-        <v>176</v>
-      </c>
       <c r="H49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -23382,7 +23373,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -23393,31 +23384,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D50" t="s">
+        <v>173</v>
+      </c>
+      <c r="E50" t="s">
+        <v>173</v>
+      </c>
+      <c r="F50" t="s">
         <v>174</v>
       </c>
-      <c r="E50" t="s">
-        <v>174</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>175</v>
       </c>
-      <c r="G50" t="s">
-        <v>176</v>
-      </c>
       <c r="H50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -23525,7 +23516,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -23539,28 +23530,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E51" t="s">
+        <v>173</v>
+      </c>
+      <c r="F51" t="s">
         <v>174</v>
       </c>
-      <c r="E51" t="s">
-        <v>174</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>175</v>
       </c>
-      <c r="G51" t="s">
-        <v>176</v>
-      </c>
       <c r="H51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -23668,7 +23659,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -23679,31 +23670,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D52" t="s">
+        <v>173</v>
+      </c>
+      <c r="E52" t="s">
+        <v>173</v>
+      </c>
+      <c r="F52" t="s">
         <v>174</v>
       </c>
-      <c r="E52" t="s">
-        <v>174</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>175</v>
       </c>
-      <c r="G52" t="s">
-        <v>176</v>
-      </c>
       <c r="H52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -23811,7 +23802,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -23822,31 +23813,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D53" t="s">
+        <v>173</v>
+      </c>
+      <c r="E53" t="s">
+        <v>173</v>
+      </c>
+      <c r="F53" t="s">
         <v>174</v>
       </c>
-      <c r="E53" t="s">
-        <v>174</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>175</v>
       </c>
-      <c r="G53" t="s">
-        <v>176</v>
-      </c>
       <c r="H53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -23954,7 +23945,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -23965,31 +23956,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D54" t="s">
+        <v>173</v>
+      </c>
+      <c r="E54" t="s">
+        <v>173</v>
+      </c>
+      <c r="F54" t="s">
         <v>174</v>
       </c>
-      <c r="E54" t="s">
-        <v>174</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>175</v>
       </c>
-      <c r="G54" t="s">
-        <v>176</v>
-      </c>
       <c r="H54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -24097,7 +24088,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -24108,31 +24099,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D55" t="s">
+        <v>173</v>
+      </c>
+      <c r="E55" t="s">
+        <v>173</v>
+      </c>
+      <c r="F55" t="s">
         <v>174</v>
       </c>
-      <c r="E55" t="s">
-        <v>174</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>175</v>
       </c>
-      <c r="G55" t="s">
-        <v>176</v>
-      </c>
       <c r="H55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -24240,7 +24231,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -8472,7 +8472,8 @@
     <col min="21" max="21" width="7.81818181818182" customWidth="1"/>
     <col min="22" max="24" width="7.13636363636364" customWidth="1"/>
     <col min="25" max="25" width="9.54545454545454" customWidth="1"/>
-    <col min="26" max="33" width="7.13636363636364" customWidth="1"/>
+    <col min="26" max="26" width="17.9090909090909" customWidth="1"/>
+    <col min="27" max="33" width="7.13636363636364" customWidth="1"/>
     <col min="34" max="37" width="6" customWidth="1"/>
     <col min="38" max="39" width="15.5454545454545" customWidth="1"/>
     <col min="40" max="40" width="22.6363636363636" customWidth="1"/>
@@ -12014,8 +12015,8 @@
       <c r="AM66" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AN66" s="12" t="s">
-        <v>124</v>
+      <c r="AN66" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="AO66" s="2" t="s">
         <v>59</v>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="197">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -12018,10 +12018,7 @@
       <c r="AN66" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AO66" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AP66" s="12" t="s">
+      <c r="AO66" s="12" t="s">
         <v>58</v>
       </c>
       <c r="AY66" s="2" t="s">
@@ -12326,9 +12323,6 @@
       <c r="AO67" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="AP67" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="AY67" s="2">
         <v>2050</v>
       </c>
@@ -12632,9 +12626,6 @@
       <c r="AO68" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="AP68" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="AY68" s="2">
         <v>2050</v>
       </c>
@@ -12938,9 +12929,6 @@
       <c r="AO69" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="AP69" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="AY69" s="2">
         <v>2050</v>
       </c>
@@ -13243,9 +13231,6 @@
       <c r="AO70" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AP70" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="AY70" s="2">
         <v>2050</v>
       </c>
@@ -13547,9 +13532,6 @@
       <c r="AO71" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="AP71" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="AY71" s="2">
         <v>2050</v>
       </c>
@@ -13853,9 +13835,6 @@
       <c r="AO72" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="AP72" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="AY72" s="2">
         <v>2050</v>
       </c>
@@ -14157,9 +14136,6 @@
         <v>135</v>
       </c>
       <c r="AO73" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AP73" s="1" t="s">
         <v>142</v>
       </c>
       <c r="AY73" s="2">

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="196">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -476,9 +476,6 @@
     <t>MINBatMaterials</t>
   </si>
   <si>
-    <t>MINBatMaterials_MATO</t>
-  </si>
-  <si>
     <t>m_lithium</t>
   </si>
   <si>
@@ -674,7 +671,7 @@
     <numFmt numFmtId="178" formatCode="0.0"/>
     <numFmt numFmtId="179" formatCode="0.000"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -701,12 +698,6 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.2"/>
-      <color rgb="FF212529"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1221,28 +1212,31 @@
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1251,125 +1245,122 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1391,7 +1382,6 @@
     <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -1880,29 +1870,29 @@
   <dimension ref="A1:AA281"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="23" customWidth="1"/>
-    <col min="2" max="2" width="8.85454545454546" style="23" customWidth="1"/>
-    <col min="3" max="3" width="4.70909090909091" style="23" customWidth="1"/>
-    <col min="4" max="4" width="8.85454545454546" style="23" customWidth="1"/>
-    <col min="5" max="5" width="4.42727272727273" style="23" customWidth="1"/>
-    <col min="6" max="6" width="4.28181818181818" style="23" customWidth="1"/>
-    <col min="7" max="7" width="4.42727272727273" style="23" customWidth="1"/>
-    <col min="8" max="8" width="4.57272727272727" style="23" customWidth="1"/>
-    <col min="9" max="9" width="4" style="23" customWidth="1"/>
-    <col min="10" max="10" width="4.42727272727273" style="23" customWidth="1"/>
-    <col min="11" max="11" width="4.57272727272727" style="23" customWidth="1"/>
-    <col min="12" max="12" width="4.42727272727273" style="23" customWidth="1"/>
-    <col min="13" max="13" width="4" style="23" customWidth="1"/>
-    <col min="14" max="14" width="4.28181818181818" style="23" customWidth="1"/>
-    <col min="15" max="16" width="4.42727272727273" style="23" customWidth="1"/>
-    <col min="17" max="18" width="4.57272727272727" style="23" customWidth="1"/>
-    <col min="19" max="19" width="4.42727272727273" style="23" customWidth="1"/>
-    <col min="20" max="20" width="5" style="23" customWidth="1"/>
-    <col min="21" max="21" width="11.7090909090909" style="23" customWidth="1"/>
-    <col min="22" max="22" width="10.7090909090909" style="23" customWidth="1"/>
-    <col min="23" max="23" width="13.1363636363636" style="23" customWidth="1"/>
-    <col min="24" max="259" width="11.4272727272727" style="23" customWidth="1"/>
-    <col min="260" max="16384" width="9.13636363636364" style="23"/>
+    <col min="1" max="1" width="15" style="22" customWidth="1"/>
+    <col min="2" max="2" width="8.85454545454546" style="22" customWidth="1"/>
+    <col min="3" max="3" width="4.70909090909091" style="22" customWidth="1"/>
+    <col min="4" max="4" width="8.85454545454546" style="22" customWidth="1"/>
+    <col min="5" max="5" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="6" max="6" width="4.28181818181818" style="22" customWidth="1"/>
+    <col min="7" max="7" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="8" max="8" width="4.57272727272727" style="22" customWidth="1"/>
+    <col min="9" max="9" width="4" style="22" customWidth="1"/>
+    <col min="10" max="10" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="11" max="11" width="4.57272727272727" style="22" customWidth="1"/>
+    <col min="12" max="12" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="13" max="13" width="4" style="22" customWidth="1"/>
+    <col min="14" max="14" width="4.28181818181818" style="22" customWidth="1"/>
+    <col min="15" max="16" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="17" max="18" width="4.57272727272727" style="22" customWidth="1"/>
+    <col min="19" max="19" width="4.42727272727273" style="22" customWidth="1"/>
+    <col min="20" max="20" width="5" style="22" customWidth="1"/>
+    <col min="21" max="21" width="11.7090909090909" style="22" customWidth="1"/>
+    <col min="22" max="22" width="10.7090909090909" style="22" customWidth="1"/>
+    <col min="23" max="23" width="13.1363636363636" style="22" customWidth="1"/>
+    <col min="24" max="259" width="11.4272727272727" style="22" customWidth="1"/>
+    <col min="260" max="16384" width="9.13636363636364" style="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.5" spans="1:21">
@@ -2981,7 +2971,7 @@
       <c r="AA34" s="5"/>
     </row>
     <row r="35" ht="12.5" spans="1:27">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="22" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -3009,7 +2999,7 @@
       <c r="AA35" s="5"/>
     </row>
     <row r="36" ht="12.5" spans="1:27">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="22" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -3037,7 +3027,7 @@
       <c r="AA36" s="5"/>
     </row>
     <row r="37" ht="12.5" spans="1:27">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="22" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -3065,7 +3055,7 @@
       <c r="AA37" s="5"/>
     </row>
     <row r="38" ht="12.5" spans="1:27">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="22" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -3093,7 +3083,7 @@
       <c r="AA38" s="5"/>
     </row>
     <row r="39" ht="12.5" spans="1:27">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="22" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -8766,7 +8756,7 @@
       <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="23" t="s">
         <v>92</v>
       </c>
       <c r="F14">
@@ -8825,7 +8815,7 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="23" t="s">
         <v>92</v>
       </c>
       <c r="C18">
@@ -8834,7 +8824,7 @@
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="23" t="s">
         <v>100</v>
       </c>
       <c r="F18" t="s">
@@ -11622,7 +11612,7 @@
       <c r="D45">
         <v>2020</v>
       </c>
-      <c r="E45" s="25" t="s">
+      <c r="E45" s="24" t="s">
         <v>119</v>
       </c>
       <c r="F45" t="s">
@@ -11706,7 +11696,7 @@
       <c r="D55" t="s">
         <v>126</v>
       </c>
-      <c r="E55" s="24" t="s">
+      <c r="E55" s="23" t="s">
         <v>127</v>
       </c>
     </row>
@@ -11839,7 +11829,7 @@
     <row r="65" s="1" customFormat="1" spans="1:99">
       <c r="A65" s="2"/>
       <c r="B65" s="12" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
@@ -11907,119 +11897,113 @@
       <c r="C66" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E66" s="2" t="s">
+      <c r="D66" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="G66" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="H66" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H66" s="2" t="s">
+      <c r="I66" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I66" s="2" t="s">
+      <c r="J66" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="2" t="s">
+      <c r="K66" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K66" s="2" t="s">
+      <c r="L66" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L66" s="2" t="s">
+      <c r="M66" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M66" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="N66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O66" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O66" s="2" t="s">
+      <c r="P66" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P66" s="2" t="s">
+      <c r="Q66" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q66" s="2" t="s">
+      <c r="R66" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R66" s="2" t="s">
+      <c r="S66" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S66" s="2" t="s">
+      <c r="T66" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T66" s="2" t="s">
+      <c r="U66" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U66" s="2" t="s">
+      <c r="V66" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V66" s="2" t="s">
+      <c r="W66" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W66" s="2" t="s">
+      <c r="X66" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X66" s="2" t="s">
+      <c r="Y66" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y66" s="2" t="s">
+      <c r="Z66" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z66" s="2" t="s">
+      <c r="AA66" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA66" s="2" t="s">
+      <c r="AB66" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB66" s="2" t="s">
+      <c r="AC66" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC66" s="2" t="s">
+      <c r="AD66" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD66" s="2" t="s">
+      <c r="AE66" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE66" s="2" t="s">
+      <c r="AF66" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="AF66" s="2" t="s">
+      <c r="AG66" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG66" s="2" t="s">
+      <c r="AH66" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH66" s="2" t="s">
+      <c r="AI66" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI66" s="2" t="s">
+      <c r="AJ66" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ66" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="AK66" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL66" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL66" s="2" t="s">
+      <c r="AM66" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="AM66" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="AN66" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AO66" s="12" t="s">
-        <v>58</v>
       </c>
       <c r="AY66" s="2" t="s">
         <v>79</v>
@@ -12144,29 +12128,29 @@
       <c r="CM66" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="CO66" s="22" t="s">
+      <c r="CO66" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="CP66" s="22" t="s">
+      <c r="CP66" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="CQ66" s="22" t="s">
+      <c r="CQ66" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="CR66" s="22" t="s">
+      <c r="CR66" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="CS66" s="22" t="s">
+      <c r="CS66" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="CT66" s="22" t="s">
+      <c r="CT66" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="CU66" s="22" t="s">
+      <c r="CU66" s="21" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" ht="16" spans="1:99">
+    <row r="67" s="2" customFormat="1" ht="14.5" spans="1:99">
       <c r="A67" s="2" t="s">
         <v>132</v>
       </c>
@@ -12176,25 +12160,24 @@
       <c r="C67" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D67" s="2">
-        <v>0</v>
-      </c>
-      <c r="E67" s="2">
-        <f t="shared" ref="E67:K67" si="2">D77/1000</f>
-        <v>0</v>
+      <c r="D67" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="F67" s="2">
+        <f t="shared" ref="F67:L67" si="2">D77/1000</f>
+        <v>0</v>
+      </c>
+      <c r="G67" s="2">
         <f t="shared" si="2"/>
         <v>310</v>
       </c>
-      <c r="G67" s="2">
+      <c r="H67" s="2">
         <f t="shared" si="2"/>
         <v>6200</v>
       </c>
-      <c r="H67" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="I67" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -12205,17 +12188,17 @@
       </c>
       <c r="K67" s="2">
         <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L67" s="2">
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
-      <c r="L67" s="2">
+      <c r="M67" s="2">
         <v>2000</v>
       </c>
-      <c r="M67" s="2">
-        <f t="shared" ref="M67:AL67" si="3">L77/1000</f>
-        <v>0</v>
-      </c>
       <c r="N67" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="N67:AM67" si="3">L77/1000</f>
         <v>0</v>
       </c>
       <c r="O67" s="2">
@@ -12256,19 +12239,19 @@
       </c>
       <c r="X67" s="2">
         <f t="shared" si="3"/>
-        <v>12250</v>
+        <v>0</v>
       </c>
       <c r="Y67" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>12250</v>
       </c>
       <c r="Z67" s="2">
         <f t="shared" si="3"/>
-        <v>1930</v>
+        <v>0</v>
       </c>
       <c r="AA67" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1930</v>
       </c>
       <c r="AB67" s="2">
         <f t="shared" si="3"/>
@@ -12276,11 +12259,11 @@
       </c>
       <c r="AC67" s="2">
         <f t="shared" si="3"/>
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="AD67" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="AE67" s="2">
         <f t="shared" si="3"/>
@@ -12292,11 +12275,11 @@
       </c>
       <c r="AG67" s="2">
         <f t="shared" si="3"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AH67" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AI67" s="2">
         <f t="shared" si="3"/>
@@ -12314,14 +12297,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AM67" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN67" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="AO67" s="1" t="s">
-        <v>136</v>
+      <c r="AM67" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
       <c r="AY67" s="2">
         <v>2050</v>
@@ -12444,58 +12422,48 @@
         <v>134</v>
       </c>
       <c r="CM67" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="CO67" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP67" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ67" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR67" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS67" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT67" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="CU67" s="21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" ht="14.5" spans="2:99">
+      <c r="B68" s="13"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="CO67" s="22">
-        <v>0</v>
-      </c>
-      <c r="CP67" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ67" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="CR67" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS67" s="22">
-        <v>5</v>
-      </c>
-      <c r="CT67" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="CU67" s="22" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" ht="16" spans="1:99">
-      <c r="A68" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D68" s="2">
-        <v>0</v>
-      </c>
-      <c r="E68" s="2">
-        <f t="shared" ref="E68:L68" si="4">D78/1000</f>
-        <v>0</v>
-      </c>
       <c r="F68" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="F68:M68" si="4">D78/1000</f>
         <v>0</v>
       </c>
       <c r="G68" s="2">
         <f t="shared" si="4"/>
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="H68" s="2">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="I68" s="2">
         <f t="shared" si="4"/>
@@ -12507,18 +12475,18 @@
       </c>
       <c r="K68" s="2">
         <f t="shared" si="4"/>
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2">
         <f t="shared" si="4"/>
+        <v>16000</v>
+      </c>
+      <c r="M68" s="2">
+        <f t="shared" si="4"/>
         <v>2100</v>
       </c>
-      <c r="M68" s="2">
-        <f t="shared" ref="M68:AL68" si="5">L78/1000</f>
-        <v>0</v>
-      </c>
       <c r="N68" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="N68:AM68" si="5">L78/1000</f>
         <v>0</v>
       </c>
       <c r="O68" s="2">
@@ -12559,19 +12527,19 @@
       </c>
       <c r="X68" s="2">
         <f t="shared" si="5"/>
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="Y68" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="Z68" s="2">
         <f t="shared" si="5"/>
-        <v>2570</v>
+        <v>0</v>
       </c>
       <c r="AA68" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2570</v>
       </c>
       <c r="AB68" s="2">
         <f t="shared" si="5"/>
@@ -12579,15 +12547,15 @@
       </c>
       <c r="AC68" s="2">
         <f t="shared" si="5"/>
-        <v>52900</v>
+        <v>0</v>
       </c>
       <c r="AD68" s="2">
         <f t="shared" si="5"/>
-        <v>7500</v>
+        <v>52900</v>
       </c>
       <c r="AE68" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="AF68" s="2">
         <f t="shared" si="5"/>
@@ -12617,14 +12585,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AM68" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN68" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="AO68" s="1" t="s">
-        <v>137</v>
+      <c r="AM68" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="AY68" s="2">
         <v>2050</v>
@@ -12747,59 +12710,49 @@
         <v>134</v>
       </c>
       <c r="CM68" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="CO68" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP68" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ68" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR68" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS68" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT68" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="CU68" s="21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" ht="14.5" spans="2:99">
+      <c r="B69" s="13"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="CO68" s="22">
-        <v>0</v>
-      </c>
-      <c r="CP68" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ68" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="CR68" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS68" s="22">
-        <v>5</v>
-      </c>
-      <c r="CT68" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="CU68" s="22" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" ht="16" spans="1:99">
-      <c r="A69" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D69" s="2">
-        <v>0</v>
-      </c>
-      <c r="E69" s="2">
-        <f t="shared" ref="E69:L69" si="6">D79/1000</f>
+      <c r="F69" s="2">
+        <f t="shared" ref="F69:M69" si="6">D79/1000</f>
         <v>13</v>
       </c>
-      <c r="F69" s="2">
+      <c r="G69" s="2">
         <f t="shared" si="6"/>
         <v>4100</v>
       </c>
-      <c r="G69" s="2">
+      <c r="H69" s="2">
         <f t="shared" si="6"/>
         <v>1500</v>
       </c>
-      <c r="H69" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
       <c r="I69" s="2">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -12814,14 +12767,14 @@
       </c>
       <c r="L69" s="2">
         <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M69" s="2">
+        <f t="shared" si="6"/>
         <v>140</v>
       </c>
-      <c r="M69" s="2">
-        <f t="shared" ref="M69:AL69" si="7">L79/1000</f>
-        <v>0</v>
-      </c>
       <c r="N69" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="N69:AM69" si="7">L79/1000</f>
         <v>0</v>
       </c>
       <c r="O69" s="2">
@@ -12862,19 +12815,19 @@
       </c>
       <c r="X69" s="2">
         <f t="shared" si="7"/>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Y69" s="2">
         <f t="shared" si="7"/>
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="Z69" s="2">
         <f t="shared" si="7"/>
-        <v>289</v>
+        <v>36</v>
       </c>
       <c r="AA69" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="AB69" s="2">
         <f t="shared" si="7"/>
@@ -12882,15 +12835,15 @@
       </c>
       <c r="AC69" s="2">
         <f t="shared" si="7"/>
-        <v>1517</v>
+        <v>0</v>
       </c>
       <c r="AD69" s="2">
         <f t="shared" si="7"/>
-        <v>250</v>
+        <v>1517</v>
       </c>
       <c r="AE69" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AF69" s="2">
         <f t="shared" si="7"/>
@@ -12910,24 +12863,19 @@
       </c>
       <c r="AJ69" s="2">
         <f t="shared" si="7"/>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AK69" s="2">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL69" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM69" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN69" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="AO69" s="1" t="s">
-        <v>138</v>
+      <c r="AM69" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="AY69" s="2">
         <v>2050</v>
@@ -13050,59 +12998,49 @@
         <v>134</v>
       </c>
       <c r="CM69" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="CO69" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP69" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ69" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR69" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS69" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT69" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="CU69" s="21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" ht="14.5" spans="2:99">
+      <c r="B70" s="13"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="CO69" s="22">
-        <v>0</v>
-      </c>
-      <c r="CP69" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ69" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="CR69" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS69" s="22">
-        <v>5</v>
-      </c>
-      <c r="CT69" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="CU69" s="22" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" ht="16" spans="1:99">
-      <c r="A70" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D70" s="2">
-        <v>0</v>
-      </c>
-      <c r="E70" s="2">
-        <f t="shared" ref="E70:L70" si="8">D80/1000</f>
-        <v>0</v>
-      </c>
       <c r="F70" s="2">
+        <f t="shared" ref="F70:M70" si="8">D80/1000</f>
+        <v>0</v>
+      </c>
+      <c r="G70" s="2">
         <f t="shared" si="8"/>
         <v>74000</v>
       </c>
-      <c r="G70" s="2">
+      <c r="H70" s="2">
         <f t="shared" si="8"/>
         <v>270000</v>
       </c>
-      <c r="H70" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
       <c r="I70" s="2">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -13113,18 +13051,18 @@
       </c>
       <c r="K70" s="2">
         <f t="shared" si="8"/>
-        <v>270000</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2">
         <f t="shared" si="8"/>
+        <v>270000</v>
+      </c>
+      <c r="M70" s="2">
+        <f t="shared" si="8"/>
         <v>280000</v>
       </c>
-      <c r="M70" s="2">
-        <f t="shared" ref="M70:AL70" si="9">L80/1000</f>
-        <v>0</v>
-      </c>
       <c r="N70" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="N70:AM70" si="9">L80/1000</f>
         <v>0</v>
       </c>
       <c r="O70" s="2">
@@ -13149,11 +13087,11 @@
       </c>
       <c r="T70" s="2">
         <f t="shared" si="9"/>
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="U70" s="2">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="V70" s="2">
         <f t="shared" si="9"/>
@@ -13165,18 +13103,18 @@
       </c>
       <c r="X70" s="2">
         <f t="shared" si="9"/>
-        <v>275000</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="2">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Z70" s="20">
+        <v>275000</v>
+      </c>
+      <c r="Z70" s="2">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AA70" s="20">
         <v>100</v>
-      </c>
-      <c r="AA70" s="2">
-        <f t="shared" si="9"/>
-        <v>0</v>
       </c>
       <c r="AB70" s="2">
         <f t="shared" si="9"/>
@@ -13184,11 +13122,11 @@
       </c>
       <c r="AC70" s="2">
         <f t="shared" si="9"/>
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AD70" s="2">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AE70" s="2">
         <f t="shared" si="9"/>
@@ -13196,11 +13134,11 @@
       </c>
       <c r="AF70" s="2">
         <f t="shared" si="9"/>
-        <v>640000</v>
+        <v>0</v>
       </c>
       <c r="AG70" s="2">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>640000</v>
       </c>
       <c r="AH70" s="2">
         <f t="shared" si="9"/>
@@ -13220,16 +13158,11 @@
       </c>
       <c r="AL70" s="2">
         <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AM70" s="2">
+        <f t="shared" si="9"/>
         <v>140000</v>
-      </c>
-      <c r="AM70" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN70" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="AO70" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="AY70" s="2">
         <v>2050</v>
@@ -13352,49 +13285,39 @@
         <v>134</v>
       </c>
       <c r="CM70" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="CO70" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP70" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ70" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR70" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS70" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT70" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="CU70" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" ht="14.5" spans="2:99">
+      <c r="B71" s="13"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="CO70" s="22">
-        <v>0</v>
-      </c>
-      <c r="CP70" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ70" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="CR70" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS70" s="22">
-        <v>5</v>
-      </c>
-      <c r="CT70" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="CU70" s="22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" ht="16" spans="1:99">
-      <c r="A71" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D71" s="2">
-        <v>0</v>
-      </c>
-      <c r="E71" s="2">
-        <f t="shared" ref="E71:L71" si="10">D81/1000</f>
-        <v>0</v>
-      </c>
       <c r="F71" s="2">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="F71:M71" si="10">D81/1000</f>
         <v>0</v>
       </c>
       <c r="G71" s="2">
@@ -13417,15 +13340,15 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="L71" s="20">
+      <c r="L71" s="2">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M71" s="20">
         <v>100</v>
       </c>
-      <c r="M71" s="2">
-        <f t="shared" ref="M71:AL71" si="11">L81/1000</f>
-        <v>0</v>
-      </c>
       <c r="N71" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="N71:AM71" si="11">L81/1000</f>
         <v>0</v>
       </c>
       <c r="O71" s="2">
@@ -13472,12 +13395,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Z71" s="20">
+      <c r="Z71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AA71" s="20">
         <v>100</v>
-      </c>
-      <c r="AA71" s="2">
-        <f t="shared" si="11"/>
-        <v>0</v>
       </c>
       <c r="AB71" s="2">
         <f t="shared" si="11"/>
@@ -13523,14 +13446,9 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AM71" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN71" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="AO71" s="1" t="s">
-        <v>140</v>
+      <c r="AM71" s="2">
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
       <c r="AY71" s="2">
         <v>2050</v>
@@ -13653,59 +13571,49 @@
         <v>134</v>
       </c>
       <c r="CM71" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="CO71" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP71" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ71" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR71" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS71" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT71" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="CU71" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" ht="14.5" spans="2:99">
+      <c r="B72" s="13"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="CO71" s="22">
-        <v>0</v>
-      </c>
-      <c r="CP71" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ71" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="CR71" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS71" s="22">
-        <v>5</v>
-      </c>
-      <c r="CT71" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="CU71" s="22" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" ht="16" spans="1:99">
-      <c r="A72" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D72" s="2">
-        <v>0</v>
-      </c>
-      <c r="E72" s="2">
-        <f t="shared" ref="E72:L72" si="12">D82/1000</f>
-        <v>0</v>
-      </c>
       <c r="F72" s="2">
+        <f t="shared" ref="F72:M72" si="12">D82/1000</f>
+        <v>0</v>
+      </c>
+      <c r="G72" s="2">
         <f t="shared" si="12"/>
         <v>50000</v>
       </c>
-      <c r="G72" s="2">
+      <c r="H72" s="2">
         <f t="shared" si="12"/>
         <v>97000</v>
       </c>
-      <c r="H72" s="2">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
       <c r="I72" s="2">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -13720,14 +13628,14 @@
       </c>
       <c r="L72" s="2">
         <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="M72" s="2">
+        <f t="shared" si="12"/>
         <v>27000</v>
       </c>
-      <c r="M72" s="2">
-        <f t="shared" ref="M72:AL72" si="13">L82/1000</f>
-        <v>0</v>
-      </c>
       <c r="N72" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="N72:AM72" si="13">L82/1000</f>
         <v>0</v>
       </c>
       <c r="O72" s="2">
@@ -13768,35 +13676,35 @@
       </c>
       <c r="X72" s="2">
         <f t="shared" si="13"/>
-        <v>324000</v>
+        <v>0</v>
       </c>
       <c r="Y72" s="2">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>324000</v>
       </c>
       <c r="Z72" s="2">
         <f t="shared" si="13"/>
-        <v>51600</v>
+        <v>0</v>
       </c>
       <c r="AA72" s="2">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>51600</v>
       </c>
       <c r="AB72" s="2">
         <f t="shared" si="13"/>
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="AC72" s="2">
         <f t="shared" si="13"/>
-        <v>244000</v>
+        <v>30000</v>
       </c>
       <c r="AD72" s="2">
         <f t="shared" si="13"/>
-        <v>62000</v>
+        <v>244000</v>
       </c>
       <c r="AE72" s="2">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="AF72" s="2">
         <f t="shared" si="13"/>
@@ -13826,14 +13734,9 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AM72" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN72" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="AO72" s="1" t="s">
-        <v>141</v>
+      <c r="AM72" s="2">
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
       <c r="AY72" s="2">
         <v>2050</v>
@@ -13956,55 +13859,46 @@
         <v>134</v>
       </c>
       <c r="CM72" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="CO72" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP72" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="CQ72" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CR72" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="CS72" s="21">
+        <v>5</v>
+      </c>
+      <c r="CT72" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="CU72" s="21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="14.5" spans="1:99">
+      <c r="A73" s="2"/>
+      <c r="B73" s="13"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="CO72" s="22">
-        <v>0</v>
-      </c>
-      <c r="CP72" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="CQ72" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="CR72" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS72" s="22">
-        <v>5</v>
-      </c>
-      <c r="CT72" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="CU72" s="22" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" ht="16" spans="1:99">
-      <c r="A73" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D73" s="2">
-        <v>0</v>
-      </c>
-      <c r="E73" s="2">
-        <f t="shared" ref="E73:L73" si="14">D83/1000</f>
-        <v>0</v>
-      </c>
       <c r="F73" s="2">
+        <f t="shared" ref="F73:M73" si="14">D83/1000</f>
+        <v>0</v>
+      </c>
+      <c r="G73" s="2">
         <f t="shared" si="14"/>
         <v>69000</v>
       </c>
-      <c r="G73" s="2">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
       <c r="H73" s="2">
         <f t="shared" si="14"/>
         <v>0</v>
@@ -14019,18 +13913,18 @@
       </c>
       <c r="K73" s="2">
         <f t="shared" si="14"/>
-        <v>74000</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2">
         <f t="shared" si="14"/>
+        <v>74000</v>
+      </c>
+      <c r="M73" s="2">
+        <f t="shared" si="14"/>
         <v>52000</v>
       </c>
-      <c r="M73" s="2">
-        <f t="shared" ref="M73:AL73" si="15">L83/1000</f>
-        <v>0</v>
-      </c>
       <c r="N73" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="N73:AM73" si="15">L83/1000</f>
         <v>0</v>
       </c>
       <c r="O73" s="2">
@@ -14055,11 +13949,11 @@
       </c>
       <c r="T73" s="2">
         <f t="shared" si="15"/>
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="U73" s="2">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="V73" s="2">
         <f t="shared" si="15"/>
@@ -14071,35 +13965,35 @@
       </c>
       <c r="X73" s="2">
         <f t="shared" si="15"/>
-        <v>77100</v>
+        <v>0</v>
       </c>
       <c r="Y73" s="2">
         <f t="shared" si="15"/>
-        <v>90000</v>
+        <v>77100</v>
       </c>
       <c r="Z73" s="2">
         <f t="shared" si="15"/>
-        <v>5700</v>
+        <v>90000</v>
       </c>
       <c r="AA73" s="2">
         <f t="shared" si="15"/>
-        <v>600</v>
+        <v>5700</v>
       </c>
       <c r="AB73" s="2">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="AC73" s="2">
         <f t="shared" si="15"/>
-        <v>12900</v>
+        <v>0</v>
       </c>
       <c r="AD73" s="2">
         <f t="shared" si="15"/>
-        <v>14000</v>
+        <v>12900</v>
       </c>
       <c r="AE73" s="2">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="AF73" s="2">
         <f t="shared" si="15"/>
@@ -14119,24 +14013,19 @@
       </c>
       <c r="AJ73" s="2">
         <f t="shared" si="15"/>
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="AK73" s="2">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="AL73" s="2">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AM73" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN73" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="AO73" s="1" t="s">
-        <v>142</v>
+      <c r="AM73" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
       </c>
       <c r="AY73" s="2">
         <v>2050</v>
@@ -14259,9 +14148,9 @@
         <v>134</v>
       </c>
       <c r="CM73" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="CO73" s="22">
+        <v>141</v>
+      </c>
+      <c r="CO73" s="21">
         <v>0</v>
       </c>
       <c r="CP73" s="11" t="s">
@@ -14270,23 +14159,23 @@
       <c r="CQ73" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="CR73" s="22" t="s">
+      <c r="CR73" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="CS73" s="22">
+      <c r="CS73" s="21">
         <v>5</v>
       </c>
       <c r="CT73" s="11" t="s">
         <v>134</v>
       </c>
       <c r="CU73" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
@@ -14940,7 +14829,7 @@
     </row>
     <row r="88" spans="2:26">
       <c r="B88" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -15155,7 +15044,7 @@
         <v>118</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E104" s="17">
         <v>7.11384396954065</v>
@@ -15173,7 +15062,7 @@
         <v>118</v>
       </c>
       <c r="N104" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O104" s="17">
         <f>E104*0.313</f>
@@ -15194,7 +15083,7 @@
         <v>118</v>
       </c>
       <c r="Z104" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AA104" s="17">
         <v>5</v>
@@ -15211,7 +15100,7 @@
         <v>118</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E105" s="17">
         <v>7.11384396954065</v>
@@ -15229,7 +15118,7 @@
         <v>118</v>
       </c>
       <c r="N105" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O105" s="17">
         <f t="shared" ref="O105:O124" si="16">E105*0.313</f>
@@ -15250,7 +15139,7 @@
         <v>118</v>
       </c>
       <c r="Z105" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AA105" s="17">
         <v>5</v>
@@ -15267,7 +15156,7 @@
         <v>118</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E106" s="17">
         <v>7.62975445836404</v>
@@ -15285,7 +15174,7 @@
         <v>118</v>
       </c>
       <c r="N106" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O106" s="17">
         <f t="shared" si="16"/>
@@ -15306,7 +15195,7 @@
         <v>118</v>
       </c>
       <c r="Z106" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AA106" s="17">
         <v>5</v>
@@ -15323,7 +15212,7 @@
         <v>118</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E107" s="17">
         <v>7.47097081798084</v>
@@ -15341,7 +15230,7 @@
         <v>118</v>
       </c>
       <c r="N107" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O107" s="17">
         <f t="shared" si="16"/>
@@ -15362,7 +15251,7 @@
         <v>118</v>
       </c>
       <c r="Z107" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA107" s="17">
         <v>5</v>
@@ -15379,7 +15268,7 @@
         <v>118</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E108" s="17">
         <v>7.51643520019651</v>
@@ -15397,7 +15286,7 @@
         <v>118</v>
       </c>
       <c r="N108" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O108" s="17">
         <f t="shared" si="16"/>
@@ -15418,7 +15307,7 @@
         <v>118</v>
       </c>
       <c r="Z108" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA108" s="17">
         <v>5</v>
@@ -15435,7 +15324,7 @@
         <v>118</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E109" s="17">
         <v>7.55036263817244</v>
@@ -15453,7 +15342,7 @@
         <v>118</v>
       </c>
       <c r="N109" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O109" s="17">
         <f t="shared" si="16"/>
@@ -15474,7 +15363,7 @@
         <v>118</v>
       </c>
       <c r="Z109" s="17" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AA109" s="17">
         <v>5</v>
@@ -15491,7 +15380,7 @@
         <v>118</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E110" s="17">
         <v>7.62975445836404</v>
@@ -15509,7 +15398,7 @@
         <v>118</v>
       </c>
       <c r="N110" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O110" s="17">
         <f t="shared" si="16"/>
@@ -15530,7 +15419,7 @@
         <v>118</v>
       </c>
       <c r="Z110" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA110" s="17">
         <v>5</v>
@@ -15547,7 +15436,7 @@
         <v>118</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E111" s="17">
         <v>4.18384600835176</v>
@@ -15565,7 +15454,7 @@
         <v>118</v>
       </c>
       <c r="N111" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O111" s="17">
         <f t="shared" si="16"/>
@@ -15586,7 +15475,7 @@
         <v>118</v>
       </c>
       <c r="Z111" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AA111" s="17">
         <v>5</v>
@@ -15603,7 +15492,7 @@
         <v>118</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E112" s="17">
         <v>4.18384600835176</v>
@@ -15621,7 +15510,7 @@
         <v>118</v>
       </c>
       <c r="N112" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O112" s="17">
         <f t="shared" si="16"/>
@@ -15642,7 +15531,7 @@
         <v>118</v>
       </c>
       <c r="Z112" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AA112" s="17">
         <v>5</v>
@@ -15659,7 +15548,7 @@
         <v>118</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E113" s="17">
         <v>4.18384600835176</v>
@@ -15677,7 +15566,7 @@
         <v>118</v>
       </c>
       <c r="N113" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O113" s="17">
         <f t="shared" si="16"/>
@@ -15698,7 +15587,7 @@
         <v>118</v>
       </c>
       <c r="Z113" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AA113" s="17">
         <v>5</v>
@@ -15715,7 +15604,7 @@
         <v>118</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E114" s="17">
         <v>4.18384600835176</v>
@@ -15733,7 +15622,7 @@
         <v>118</v>
       </c>
       <c r="N114" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O114" s="17">
         <f t="shared" si="16"/>
@@ -15754,7 +15643,7 @@
         <v>118</v>
       </c>
       <c r="Z114" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AA114" s="17">
         <v>5</v>
@@ -15771,7 +15660,7 @@
         <v>118</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E115" s="17">
         <v>4.18384600835176</v>
@@ -15789,7 +15678,7 @@
         <v>118</v>
       </c>
       <c r="N115" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O115" s="17">
         <f t="shared" si="16"/>
@@ -15810,7 +15699,7 @@
         <v>118</v>
       </c>
       <c r="Z115" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AA115" s="17">
         <v>5</v>
@@ -15827,7 +15716,7 @@
         <v>118</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E116" s="17">
         <v>4.18384600835176</v>
@@ -15845,7 +15734,7 @@
         <v>118</v>
       </c>
       <c r="N116" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O116" s="17">
         <f t="shared" si="16"/>
@@ -15866,7 +15755,7 @@
         <v>118</v>
       </c>
       <c r="Z116" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA116" s="17">
         <v>5</v>
@@ -15883,7 +15772,7 @@
         <v>118</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E117" s="17">
         <v>4.18384600835176</v>
@@ -15901,7 +15790,7 @@
         <v>118</v>
       </c>
       <c r="N117" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O117" s="17">
         <f t="shared" si="16"/>
@@ -15922,7 +15811,7 @@
         <v>118</v>
       </c>
       <c r="Z117" s="17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA117" s="17">
         <v>5</v>
@@ -15939,7 +15828,7 @@
         <v>118</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E118" s="17">
         <v>3.56556266273643</v>
@@ -15957,7 +15846,7 @@
         <v>118</v>
       </c>
       <c r="N118" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O118" s="17">
         <f t="shared" si="16"/>
@@ -15978,7 +15867,7 @@
         <v>118</v>
       </c>
       <c r="Z118" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AA118" s="17">
         <v>5</v>
@@ -15995,7 +15884,7 @@
         <v>118</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E119" s="17">
         <v>3.60087708179809</v>
@@ -16013,7 +15902,7 @@
         <v>118</v>
       </c>
       <c r="N119" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O119" s="17">
         <f t="shared" si="16"/>
@@ -16034,7 +15923,7 @@
         <v>118</v>
       </c>
       <c r="Z119" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA119" s="17">
         <v>5</v>
@@ -16051,7 +15940,7 @@
         <v>118</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E120" s="17">
         <v>3.56556266273643</v>
@@ -16069,7 +15958,7 @@
         <v>118</v>
       </c>
       <c r="N120" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O120" s="17">
         <f t="shared" si="16"/>
@@ -16090,7 +15979,7 @@
         <v>118</v>
       </c>
       <c r="Z120" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA120" s="17">
         <v>5</v>
@@ -16107,7 +15996,7 @@
         <v>118</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E121" s="17">
         <v>3.56645369688037</v>
@@ -16125,7 +16014,7 @@
         <v>118</v>
       </c>
       <c r="N121" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O121" s="17">
         <f t="shared" si="16"/>
@@ -16146,7 +16035,7 @@
         <v>118</v>
       </c>
       <c r="Z121" s="17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AA121" s="17">
         <v>5</v>
@@ -16163,7 +16052,7 @@
         <v>118</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E122" s="17">
         <v>3.56585961680177</v>
@@ -16181,7 +16070,7 @@
         <v>118</v>
       </c>
       <c r="N122" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O122" s="17">
         <f t="shared" si="16"/>
@@ -16202,7 +16091,7 @@
         <v>118</v>
       </c>
       <c r="Z122" s="17" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA122" s="17">
         <v>5</v>
@@ -16219,7 +16108,7 @@
         <v>118</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E123" s="17">
         <v>3.56556266273643</v>
@@ -16237,7 +16126,7 @@
         <v>118</v>
       </c>
       <c r="N123" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O123" s="17">
         <f t="shared" si="16"/>
@@ -16258,7 +16147,7 @@
         <v>118</v>
       </c>
       <c r="Z123" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA123" s="17">
         <v>5</v>
@@ -16275,7 +16164,7 @@
         <v>118</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E124" s="17">
         <v>3.56496890198968</v>
@@ -16293,7 +16182,7 @@
         <v>118</v>
       </c>
       <c r="N124" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O124" s="17">
         <f t="shared" si="16"/>
@@ -16314,7 +16203,7 @@
         <v>118</v>
       </c>
       <c r="Z124" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA124" s="17">
         <v>5</v>
@@ -16348,7 +16237,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -16360,25 +16249,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F1" t="s">
         <v>167</v>
-      </c>
-      <c r="F1" t="s">
-        <v>168</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1" t="s">
         <v>169</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>170</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>171</v>
-      </c>
-      <c r="K1" t="s">
-        <v>172</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -16500,28 +16389,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G2" t="s">
         <v>174</v>
       </c>
-      <c r="G2" t="s">
-        <v>175</v>
-      </c>
       <c r="H2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -16629,7 +16518,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -16640,31 +16529,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G3" t="s">
         <v>174</v>
       </c>
-      <c r="G3" t="s">
-        <v>175</v>
-      </c>
       <c r="H3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -16772,7 +16661,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -16783,31 +16672,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G4" t="s">
         <v>174</v>
       </c>
-      <c r="G4" t="s">
-        <v>175</v>
-      </c>
       <c r="H4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -16915,7 +16804,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -16929,28 +16818,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G5" t="s">
         <v>174</v>
       </c>
-      <c r="G5" t="s">
-        <v>175</v>
-      </c>
       <c r="H5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -17058,7 +16947,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -17069,31 +16958,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G6" t="s">
         <v>174</v>
       </c>
-      <c r="G6" t="s">
-        <v>175</v>
-      </c>
       <c r="H6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -17201,7 +17090,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -17215,28 +17104,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" t="s">
         <v>174</v>
       </c>
-      <c r="G7" t="s">
-        <v>175</v>
-      </c>
       <c r="H7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -17344,7 +17233,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -17355,31 +17244,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" t="s">
         <v>174</v>
       </c>
-      <c r="G8" t="s">
-        <v>175</v>
-      </c>
       <c r="H8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -17487,7 +17376,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -17498,31 +17387,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" t="s">
         <v>174</v>
       </c>
-      <c r="G9" t="s">
-        <v>175</v>
-      </c>
       <c r="H9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -17630,7 +17519,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -17641,31 +17530,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" t="s">
         <v>174</v>
       </c>
-      <c r="G10" t="s">
-        <v>175</v>
-      </c>
       <c r="H10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -17773,7 +17662,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -17784,31 +17673,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G11" t="s">
         <v>174</v>
       </c>
-      <c r="G11" t="s">
-        <v>175</v>
-      </c>
       <c r="H11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -17916,7 +17805,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -17927,31 +17816,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" t="s">
         <v>174</v>
       </c>
-      <c r="G12" t="s">
-        <v>175</v>
-      </c>
       <c r="H12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -18059,7 +17948,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -18070,31 +17959,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" t="s">
         <v>174</v>
       </c>
-      <c r="G13" t="s">
-        <v>175</v>
-      </c>
       <c r="H13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -18202,7 +18091,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -18213,31 +18102,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G14" t="s">
         <v>174</v>
       </c>
-      <c r="G14" t="s">
-        <v>175</v>
-      </c>
       <c r="H14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -18345,7 +18234,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -18356,31 +18245,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
+        <v>173</v>
+      </c>
+      <c r="G15" t="s">
         <v>174</v>
       </c>
-      <c r="G15" t="s">
-        <v>175</v>
-      </c>
       <c r="H15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -18488,7 +18377,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -18499,31 +18388,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
+        <v>173</v>
+      </c>
+      <c r="G16" t="s">
         <v>174</v>
       </c>
-      <c r="G16" t="s">
-        <v>175</v>
-      </c>
       <c r="H16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -18631,7 +18520,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -18645,28 +18534,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
+        <v>173</v>
+      </c>
+      <c r="G17" t="s">
         <v>174</v>
       </c>
-      <c r="G17" t="s">
-        <v>175</v>
-      </c>
       <c r="H17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -18774,7 +18663,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -18785,31 +18674,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
+        <v>173</v>
+      </c>
+      <c r="G18" t="s">
         <v>174</v>
       </c>
-      <c r="G18" t="s">
-        <v>175</v>
-      </c>
       <c r="H18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -18917,7 +18806,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -18928,31 +18817,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
+        <v>173</v>
+      </c>
+      <c r="G19" t="s">
         <v>174</v>
       </c>
-      <c r="G19" t="s">
-        <v>175</v>
-      </c>
       <c r="H19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -19060,7 +18949,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -19071,31 +18960,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
+        <v>173</v>
+      </c>
+      <c r="G20" t="s">
         <v>174</v>
       </c>
-      <c r="G20" t="s">
-        <v>175</v>
-      </c>
       <c r="H20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -19203,7 +19092,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -19217,28 +19106,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
+        <v>173</v>
+      </c>
+      <c r="G21" t="s">
         <v>174</v>
       </c>
-      <c r="G21" t="s">
-        <v>175</v>
-      </c>
       <c r="H21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -19346,7 +19235,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -19357,31 +19246,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" t="s">
         <v>174</v>
       </c>
-      <c r="G22" t="s">
-        <v>175</v>
-      </c>
       <c r="H22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -19489,7 +19378,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -19500,31 +19389,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" t="s">
         <v>174</v>
       </c>
-      <c r="G23" t="s">
-        <v>175</v>
-      </c>
       <c r="H23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -19632,7 +19521,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -19646,28 +19535,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
+        <v>173</v>
+      </c>
+      <c r="G24" t="s">
         <v>174</v>
       </c>
-      <c r="G24" t="s">
-        <v>175</v>
-      </c>
       <c r="H24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -19775,7 +19664,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -19786,31 +19675,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
+        <v>173</v>
+      </c>
+      <c r="G25" t="s">
         <v>174</v>
       </c>
-      <c r="G25" t="s">
-        <v>175</v>
-      </c>
       <c r="H25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -19918,7 +19807,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -19929,31 +19818,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
+        <v>173</v>
+      </c>
+      <c r="G26" t="s">
         <v>174</v>
       </c>
-      <c r="G26" t="s">
-        <v>175</v>
-      </c>
       <c r="H26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -20061,7 +19950,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -20072,31 +19961,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
+        <v>173</v>
+      </c>
+      <c r="G27" t="s">
         <v>174</v>
       </c>
-      <c r="G27" t="s">
-        <v>175</v>
-      </c>
       <c r="H27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -20204,7 +20093,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -20215,31 +20104,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
+        <v>173</v>
+      </c>
+      <c r="G28" t="s">
         <v>174</v>
       </c>
-      <c r="G28" t="s">
-        <v>175</v>
-      </c>
       <c r="H28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -20347,7 +20236,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -20361,28 +20250,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
+        <v>172</v>
+      </c>
+      <c r="E29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F29" t="s">
         <v>173</v>
       </c>
-      <c r="E29" t="s">
-        <v>173</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>174</v>
       </c>
-      <c r="G29" t="s">
-        <v>175</v>
-      </c>
       <c r="H29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -20490,7 +20379,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -20501,31 +20390,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D30" t="s">
+        <v>172</v>
+      </c>
+      <c r="E30" t="s">
+        <v>172</v>
+      </c>
+      <c r="F30" t="s">
         <v>173</v>
       </c>
-      <c r="E30" t="s">
-        <v>173</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>174</v>
       </c>
-      <c r="G30" t="s">
-        <v>175</v>
-      </c>
       <c r="H30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -20633,7 +20522,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -20644,31 +20533,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D31" t="s">
+        <v>172</v>
+      </c>
+      <c r="E31" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31" t="s">
         <v>173</v>
       </c>
-      <c r="E31" t="s">
-        <v>173</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>174</v>
       </c>
-      <c r="G31" t="s">
-        <v>175</v>
-      </c>
       <c r="H31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -20776,7 +20665,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -20790,28 +20679,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
+        <v>172</v>
+      </c>
+      <c r="E32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F32" t="s">
         <v>173</v>
       </c>
-      <c r="E32" t="s">
-        <v>173</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>174</v>
       </c>
-      <c r="G32" t="s">
-        <v>175</v>
-      </c>
       <c r="H32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -20919,7 +20808,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -20930,31 +20819,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" t="s">
         <v>173</v>
       </c>
-      <c r="E33" t="s">
-        <v>173</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>174</v>
       </c>
-      <c r="G33" t="s">
-        <v>175</v>
-      </c>
       <c r="H33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -21062,7 +20951,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -21076,28 +20965,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
+        <v>172</v>
+      </c>
+      <c r="E34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F34" t="s">
         <v>173</v>
       </c>
-      <c r="E34" t="s">
-        <v>173</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>174</v>
       </c>
-      <c r="G34" t="s">
-        <v>175</v>
-      </c>
       <c r="H34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -21205,7 +21094,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -21216,31 +21105,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D35" t="s">
+        <v>172</v>
+      </c>
+      <c r="E35" t="s">
+        <v>172</v>
+      </c>
+      <c r="F35" t="s">
         <v>173</v>
       </c>
-      <c r="E35" t="s">
-        <v>173</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>174</v>
       </c>
-      <c r="G35" t="s">
-        <v>175</v>
-      </c>
       <c r="H35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -21348,7 +21237,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -21359,31 +21248,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D36" t="s">
+        <v>172</v>
+      </c>
+      <c r="E36" t="s">
+        <v>172</v>
+      </c>
+      <c r="F36" t="s">
         <v>173</v>
       </c>
-      <c r="E36" t="s">
-        <v>173</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>174</v>
       </c>
-      <c r="G36" t="s">
-        <v>175</v>
-      </c>
       <c r="H36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -21491,7 +21380,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -21502,31 +21391,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D37" t="s">
+        <v>172</v>
+      </c>
+      <c r="E37" t="s">
+        <v>172</v>
+      </c>
+      <c r="F37" t="s">
         <v>173</v>
       </c>
-      <c r="E37" t="s">
-        <v>173</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>174</v>
       </c>
-      <c r="G37" t="s">
-        <v>175</v>
-      </c>
       <c r="H37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -21634,7 +21523,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -21645,31 +21534,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s">
+        <v>172</v>
+      </c>
+      <c r="E38" t="s">
+        <v>172</v>
+      </c>
+      <c r="F38" t="s">
         <v>173</v>
       </c>
-      <c r="E38" t="s">
-        <v>173</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>174</v>
       </c>
-      <c r="G38" t="s">
-        <v>175</v>
-      </c>
       <c r="H38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -21777,7 +21666,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -21788,31 +21677,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D39" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" t="s">
         <v>173</v>
       </c>
-      <c r="E39" t="s">
-        <v>173</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>174</v>
       </c>
-      <c r="G39" t="s">
-        <v>175</v>
-      </c>
       <c r="H39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -21920,7 +21809,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -21931,31 +21820,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D40" t="s">
+        <v>172</v>
+      </c>
+      <c r="E40" t="s">
+        <v>172</v>
+      </c>
+      <c r="F40" t="s">
         <v>173</v>
       </c>
-      <c r="E40" t="s">
-        <v>173</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>174</v>
       </c>
-      <c r="G40" t="s">
-        <v>175</v>
-      </c>
       <c r="H40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -22063,7 +21952,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -22074,31 +21963,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D41" t="s">
+        <v>172</v>
+      </c>
+      <c r="E41" t="s">
+        <v>172</v>
+      </c>
+      <c r="F41" t="s">
         <v>173</v>
       </c>
-      <c r="E41" t="s">
-        <v>173</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>174</v>
       </c>
-      <c r="G41" t="s">
-        <v>175</v>
-      </c>
       <c r="H41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -22206,7 +22095,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -22217,31 +22106,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D42" t="s">
+        <v>172</v>
+      </c>
+      <c r="E42" t="s">
+        <v>172</v>
+      </c>
+      <c r="F42" t="s">
         <v>173</v>
       </c>
-      <c r="E42" t="s">
-        <v>173</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>174</v>
       </c>
-      <c r="G42" t="s">
-        <v>175</v>
-      </c>
       <c r="H42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -22349,7 +22238,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -22360,31 +22249,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D43" t="s">
+        <v>172</v>
+      </c>
+      <c r="E43" t="s">
+        <v>172</v>
+      </c>
+      <c r="F43" t="s">
         <v>173</v>
       </c>
-      <c r="E43" t="s">
-        <v>173</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>174</v>
       </c>
-      <c r="G43" t="s">
-        <v>175</v>
-      </c>
       <c r="H43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -22492,7 +22381,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -22506,28 +22395,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
+        <v>172</v>
+      </c>
+      <c r="E44" t="s">
+        <v>172</v>
+      </c>
+      <c r="F44" t="s">
         <v>173</v>
       </c>
-      <c r="E44" t="s">
-        <v>173</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>174</v>
       </c>
-      <c r="G44" t="s">
-        <v>175</v>
-      </c>
       <c r="H44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -22635,7 +22524,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -22646,31 +22535,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D45" t="s">
+        <v>172</v>
+      </c>
+      <c r="E45" t="s">
+        <v>172</v>
+      </c>
+      <c r="F45" t="s">
         <v>173</v>
       </c>
-      <c r="E45" t="s">
-        <v>173</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>174</v>
       </c>
-      <c r="G45" t="s">
-        <v>175</v>
-      </c>
       <c r="H45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -22778,7 +22667,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -22789,31 +22678,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D46" t="s">
+        <v>172</v>
+      </c>
+      <c r="E46" t="s">
+        <v>172</v>
+      </c>
+      <c r="F46" t="s">
         <v>173</v>
       </c>
-      <c r="E46" t="s">
-        <v>173</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>174</v>
       </c>
-      <c r="G46" t="s">
-        <v>175</v>
-      </c>
       <c r="H46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -22921,7 +22810,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -22932,31 +22821,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D47" t="s">
+        <v>172</v>
+      </c>
+      <c r="E47" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" t="s">
         <v>173</v>
       </c>
-      <c r="E47" t="s">
-        <v>173</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>174</v>
       </c>
-      <c r="G47" t="s">
-        <v>175</v>
-      </c>
       <c r="H47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -23064,7 +22953,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -23078,28 +22967,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
+        <v>172</v>
+      </c>
+      <c r="E48" t="s">
+        <v>172</v>
+      </c>
+      <c r="F48" t="s">
         <v>173</v>
       </c>
-      <c r="E48" t="s">
-        <v>173</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>174</v>
       </c>
-      <c r="G48" t="s">
-        <v>175</v>
-      </c>
       <c r="H48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -23207,7 +23096,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -23218,31 +23107,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D49" t="s">
+        <v>172</v>
+      </c>
+      <c r="E49" t="s">
+        <v>172</v>
+      </c>
+      <c r="F49" t="s">
         <v>173</v>
       </c>
-      <c r="E49" t="s">
-        <v>173</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>174</v>
       </c>
-      <c r="G49" t="s">
-        <v>175</v>
-      </c>
       <c r="H49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -23350,7 +23239,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -23361,31 +23250,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E50" t="s">
+        <v>172</v>
+      </c>
+      <c r="F50" t="s">
         <v>173</v>
       </c>
-      <c r="E50" t="s">
-        <v>173</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>174</v>
       </c>
-      <c r="G50" t="s">
-        <v>175</v>
-      </c>
       <c r="H50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -23493,7 +23382,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -23507,28 +23396,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
+        <v>172</v>
+      </c>
+      <c r="E51" t="s">
+        <v>172</v>
+      </c>
+      <c r="F51" t="s">
         <v>173</v>
       </c>
-      <c r="E51" t="s">
-        <v>173</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>174</v>
       </c>
-      <c r="G51" t="s">
-        <v>175</v>
-      </c>
       <c r="H51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -23636,7 +23525,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -23647,31 +23536,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D52" t="s">
+        <v>172</v>
+      </c>
+      <c r="E52" t="s">
+        <v>172</v>
+      </c>
+      <c r="F52" t="s">
         <v>173</v>
       </c>
-      <c r="E52" t="s">
-        <v>173</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>174</v>
       </c>
-      <c r="G52" t="s">
-        <v>175</v>
-      </c>
       <c r="H52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -23779,7 +23668,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -23790,31 +23679,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D53" t="s">
+        <v>172</v>
+      </c>
+      <c r="E53" t="s">
+        <v>172</v>
+      </c>
+      <c r="F53" t="s">
         <v>173</v>
       </c>
-      <c r="E53" t="s">
-        <v>173</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>174</v>
       </c>
-      <c r="G53" t="s">
-        <v>175</v>
-      </c>
       <c r="H53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -23922,7 +23811,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -23933,31 +23822,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D54" t="s">
+        <v>172</v>
+      </c>
+      <c r="E54" t="s">
+        <v>172</v>
+      </c>
+      <c r="F54" t="s">
         <v>173</v>
       </c>
-      <c r="E54" t="s">
-        <v>173</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>174</v>
       </c>
-      <c r="G54" t="s">
-        <v>175</v>
-      </c>
       <c r="H54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -24065,7 +23954,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -24076,31 +23965,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D55" t="s">
+        <v>172</v>
+      </c>
+      <c r="E55" t="s">
+        <v>172</v>
+      </c>
+      <c r="F55" t="s">
         <v>173</v>
       </c>
-      <c r="E55" t="s">
-        <v>173</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>174</v>
       </c>
-      <c r="G55" t="s">
-        <v>175</v>
-      </c>
       <c r="H55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -24208,7 +24097,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="196">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -1372,8 +1372,8 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -11794,7 +11794,9 @@
       <c r="Z62" s="9"/>
     </row>
     <row r="63" spans="2:95">
-      <c r="B63" s="9"/>
+      <c r="B63" s="11" t="s">
+        <v>108</v>
+      </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
@@ -11822,15 +11824,12 @@
       <c r="BA63" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="CQ63" s="11" t="s">
+      <c r="CQ63" s="12" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:99">
       <c r="A65" s="2"/>
-      <c r="B65" s="12" t="s">
-        <v>108</v>
-      </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
@@ -11880,12 +11879,12 @@
       <c r="BG65" s="2"/>
       <c r="BH65" s="2"/>
       <c r="BI65" s="2"/>
-      <c r="CO65" s="11"/>
-      <c r="CP65" s="11"/>
-      <c r="CR65" s="11"/>
-      <c r="CS65" s="11"/>
-      <c r="CT65" s="11"/>
-      <c r="CU65" s="11"/>
+      <c r="CO65" s="12"/>
+      <c r="CP65" s="12"/>
+      <c r="CR65" s="12"/>
+      <c r="CS65" s="12"/>
+      <c r="CT65" s="12"/>
+      <c r="CU65" s="12"/>
     </row>
     <row r="66" s="2" customFormat="1" spans="1:99">
       <c r="A66" s="2" t="s">
@@ -11897,10 +11896,10 @@
       <c r="C66" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E66" s="12" t="s">
+      <c r="E66" s="11" t="s">
         <v>58</v>
       </c>
       <c r="F66" s="2" t="s">
@@ -12446,10 +12445,19 @@
         <v>135</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1" ht="14.5" spans="2:99">
-      <c r="B68" s="13"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
+    <row r="68" s="2" customFormat="1" ht="14.5" spans="1:99">
+      <c r="A68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="E68" s="1" t="s">
         <v>136</v>
       </c>
@@ -12734,10 +12742,19 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" s="2" customFormat="1" ht="14.5" spans="2:99">
-      <c r="B69" s="13"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
+    <row r="69" s="2" customFormat="1" ht="14.5" spans="1:99">
+      <c r="A69" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="E69" s="1" t="s">
         <v>137</v>
       </c>
@@ -13022,10 +13039,19 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" s="2" customFormat="1" ht="14.5" spans="2:99">
-      <c r="B70" s="13"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
+    <row r="70" s="2" customFormat="1" ht="14.5" spans="1:99">
+      <c r="A70" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="E70" s="1" t="s">
         <v>138</v>
       </c>
@@ -13309,10 +13335,19 @@
         <v>138</v>
       </c>
     </row>
-    <row r="71" s="2" customFormat="1" ht="14.5" spans="2:99">
-      <c r="B71" s="13"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
+    <row r="71" s="2" customFormat="1" ht="14.5" spans="1:99">
+      <c r="A71" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="E71" s="1" t="s">
         <v>139</v>
       </c>
@@ -13595,10 +13630,19 @@
         <v>139</v>
       </c>
     </row>
-    <row r="72" s="2" customFormat="1" ht="14.5" spans="2:99">
-      <c r="B72" s="13"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
+    <row r="72" s="2" customFormat="1" ht="14.5" spans="1:99">
+      <c r="A72" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="E72" s="1" t="s">
         <v>140</v>
       </c>
@@ -13884,10 +13928,18 @@
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A73" s="2"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
+      <c r="A73" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="E73" s="1" t="s">
         <v>141</v>
       </c>
@@ -14153,10 +14205,10 @@
       <c r="CO73" s="21">
         <v>0</v>
       </c>
-      <c r="CP73" s="11" t="s">
+      <c r="CP73" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="CQ73" s="11" t="s">
+      <c r="CQ73" s="12" t="s">
         <v>133</v>
       </c>
       <c r="CR73" s="21" t="s">
@@ -14165,10 +14217,10 @@
       <c r="CS73" s="21">
         <v>5</v>
       </c>
-      <c r="CT73" s="11" t="s">
+      <c r="CT73" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="CU73" s="11" t="s">
+      <c r="CU73" s="12" t="s">
         <v>141</v>
       </c>
     </row>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="196">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -461,13 +461,10 @@
     <t>AuxStoIN</t>
   </si>
   <si>
-    <t>timeslice</t>
-  </si>
-  <si>
     <t>Saudi Arabia</t>
   </si>
   <si>
-    <t>annual</t>
+    <t>timeslice</t>
   </si>
   <si>
     <t>FLO_BND</t>
@@ -477,6 +474,9 @@
   </si>
   <si>
     <t>m_lithium</t>
+  </si>
+  <si>
+    <t>annual</t>
   </si>
   <si>
     <t>m_nickel</t>
@@ -1372,8 +1372,8 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -11793,10 +11793,7 @@
       <c r="Y62" s="9"/>
       <c r="Z62" s="9"/>
     </row>
-    <row r="63" spans="2:95">
-      <c r="B63" s="11" t="s">
-        <v>108</v>
-      </c>
+    <row r="63" spans="3:95">
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
@@ -11824,12 +11821,15 @@
       <c r="BA63" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="CQ63" s="12" t="s">
+      <c r="CQ63" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:99">
       <c r="A65" s="2"/>
+      <c r="B65" s="12" t="s">
+        <v>108</v>
+      </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
@@ -11879,28 +11879,25 @@
       <c r="BG65" s="2"/>
       <c r="BH65" s="2"/>
       <c r="BI65" s="2"/>
-      <c r="CO65" s="12"/>
-      <c r="CP65" s="12"/>
-      <c r="CR65" s="12"/>
-      <c r="CS65" s="12"/>
-      <c r="CT65" s="12"/>
-      <c r="CU65" s="12"/>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="1:99">
-      <c r="A66" s="2" t="s">
-        <v>130</v>
-      </c>
+      <c r="CO65" s="11"/>
+      <c r="CP65" s="11"/>
+      <c r="CR65" s="11"/>
+      <c r="CS65" s="11"/>
+      <c r="CT65" s="11"/>
+      <c r="CU65" s="11"/>
+    </row>
+    <row r="66" s="2" customFormat="1" spans="2:99">
       <c r="B66" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E66" s="11" t="s">
-        <v>58</v>
+      <c r="E66" t="s">
+        <v>59</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>3</v>
@@ -11981,7 +11978,7 @@
         <v>29</v>
       </c>
       <c r="AF66" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG66" s="2" t="s">
         <v>31</v>
@@ -12008,7 +12005,7 @@
         <v>79</v>
       </c>
       <c r="AZ66" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BA66" s="2" t="s">
         <v>56</v>
@@ -12098,7 +12095,7 @@
         <v>29</v>
       </c>
       <c r="CD66" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="CE66" s="2" t="s">
         <v>31</v>
@@ -12131,7 +12128,7 @@
         <v>79</v>
       </c>
       <c r="CP66" s="21" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="CQ66" s="21" t="s">
         <v>56</v>
@@ -12149,21 +12146,18 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A67" s="2" t="s">
+    <row r="67" s="2" customFormat="1" ht="14.5" spans="2:99">
+      <c r="B67" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D67" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E67" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="F67" s="2">
         <f t="shared" ref="F67:L67" si="2">D77/1000</f>
@@ -12304,10 +12298,10 @@
         <v>2050</v>
       </c>
       <c r="AZ67" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BA67" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="BA67" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="BB67" s="2" t="s">
         <v>68</v>
@@ -12418,19 +12412,19 @@
         <v>0</v>
       </c>
       <c r="CL67" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="CM67" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="CM67" s="2" t="s">
+      <c r="CO67" s="21">
+        <v>0</v>
+      </c>
+      <c r="CP67" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="CO67" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP67" s="21" t="s">
+      <c r="CQ67" s="21" t="s">
         <v>132</v>
-      </c>
-      <c r="CQ67" s="21" t="s">
-        <v>133</v>
       </c>
       <c r="CR67" s="21" t="s">
         <v>68</v>
@@ -12439,24 +12433,21 @@
         <v>5</v>
       </c>
       <c r="CT67" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="CU67" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="CU67" s="21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A68" s="2" t="s">
+    </row>
+    <row r="68" s="2" customFormat="1" ht="14.5" spans="2:99">
+      <c r="B68" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>136</v>
@@ -12601,10 +12592,10 @@
         <v>2050</v>
       </c>
       <c r="AZ68" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BA68" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="BA68" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="BB68" s="2" t="s">
         <v>68</v>
@@ -12715,7 +12706,7 @@
         <v>0</v>
       </c>
       <c r="CL68" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CM68" s="2" t="s">
         <v>136</v>
@@ -12724,10 +12715,10 @@
         <v>0</v>
       </c>
       <c r="CP68" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="CQ68" s="21" t="s">
         <v>132</v>
-      </c>
-      <c r="CQ68" s="21" t="s">
-        <v>133</v>
       </c>
       <c r="CR68" s="21" t="s">
         <v>68</v>
@@ -12736,24 +12727,21 @@
         <v>5</v>
       </c>
       <c r="CT68" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CU68" s="21" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="69" s="2" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A69" s="2" t="s">
+    <row r="69" s="2" customFormat="1" ht="14.5" spans="2:99">
+      <c r="B69" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>137</v>
@@ -12898,10 +12886,10 @@
         <v>2050</v>
       </c>
       <c r="AZ69" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BA69" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="BA69" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="BB69" s="2" t="s">
         <v>68</v>
@@ -13012,7 +13000,7 @@
         <v>0</v>
       </c>
       <c r="CL69" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CM69" s="2" t="s">
         <v>137</v>
@@ -13021,10 +13009,10 @@
         <v>0</v>
       </c>
       <c r="CP69" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="CQ69" s="21" t="s">
         <v>132</v>
-      </c>
-      <c r="CQ69" s="21" t="s">
-        <v>133</v>
       </c>
       <c r="CR69" s="21" t="s">
         <v>68</v>
@@ -13033,24 +13021,21 @@
         <v>5</v>
       </c>
       <c r="CT69" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CU69" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="70" s="2" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A70" s="2" t="s">
+    <row r="70" s="2" customFormat="1" ht="14.5" spans="2:99">
+      <c r="B70" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>138</v>
@@ -13194,10 +13179,10 @@
         <v>2050</v>
       </c>
       <c r="AZ70" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BA70" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="BA70" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="BB70" s="2" t="s">
         <v>68</v>
@@ -13308,7 +13293,7 @@
         <v>140000</v>
       </c>
       <c r="CL70" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CM70" s="2" t="s">
         <v>138</v>
@@ -13317,10 +13302,10 @@
         <v>0</v>
       </c>
       <c r="CP70" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="CQ70" s="21" t="s">
         <v>132</v>
-      </c>
-      <c r="CQ70" s="21" t="s">
-        <v>133</v>
       </c>
       <c r="CR70" s="21" t="s">
         <v>68</v>
@@ -13329,24 +13314,21 @@
         <v>5</v>
       </c>
       <c r="CT70" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CU70" s="21" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="71" s="2" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A71" s="2" t="s">
+    <row r="71" s="2" customFormat="1" ht="14.5" spans="2:99">
+      <c r="B71" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>139</v>
@@ -13489,10 +13471,10 @@
         <v>2050</v>
       </c>
       <c r="AZ71" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BA71" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="BA71" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="BB71" s="2" t="s">
         <v>68</v>
@@ -13603,7 +13585,7 @@
         <v>0</v>
       </c>
       <c r="CL71" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CM71" s="2" t="s">
         <v>139</v>
@@ -13612,10 +13594,10 @@
         <v>0</v>
       </c>
       <c r="CP71" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="CQ71" s="21" t="s">
         <v>132</v>
-      </c>
-      <c r="CQ71" s="21" t="s">
-        <v>133</v>
       </c>
       <c r="CR71" s="21" t="s">
         <v>68</v>
@@ -13624,24 +13606,21 @@
         <v>5</v>
       </c>
       <c r="CT71" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CU71" s="21" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="72" s="2" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A72" s="2" t="s">
+    <row r="72" s="2" customFormat="1" ht="14.5" spans="2:99">
+      <c r="B72" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>140</v>
@@ -13786,10 +13765,10 @@
         <v>2050</v>
       </c>
       <c r="AZ72" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BA72" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="BA72" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="BB72" s="2" t="s">
         <v>68</v>
@@ -13900,7 +13879,7 @@
         <v>0</v>
       </c>
       <c r="CL72" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CM72" s="2" t="s">
         <v>140</v>
@@ -13909,10 +13888,10 @@
         <v>0</v>
       </c>
       <c r="CP72" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="CQ72" s="21" t="s">
         <v>132</v>
-      </c>
-      <c r="CQ72" s="21" t="s">
-        <v>133</v>
       </c>
       <c r="CR72" s="21" t="s">
         <v>68</v>
@@ -13921,24 +13900,22 @@
         <v>5</v>
       </c>
       <c r="CT72" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CU72" s="21" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="2"/>
+      <c r="B73" s="13" t="s">
         <v>132</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>133</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>141</v>
@@ -14083,10 +14060,10 @@
         <v>2050</v>
       </c>
       <c r="AZ73" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="BA73" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="BA73" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="BB73" s="2" t="s">
         <v>68</v>
@@ -14197,7 +14174,7 @@
         <v>0</v>
       </c>
       <c r="CL73" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="CM73" s="1" t="s">
         <v>141</v>
@@ -14205,11 +14182,11 @@
       <c r="CO73" s="21">
         <v>0</v>
       </c>
-      <c r="CP73" s="12" t="s">
+      <c r="CP73" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="CQ73" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="CQ73" s="12" t="s">
-        <v>133</v>
       </c>
       <c r="CR73" s="21" t="s">
         <v>68</v>
@@ -14217,10 +14194,10 @@
       <c r="CS73" s="21">
         <v>5</v>
       </c>
-      <c r="CT73" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="CU73" s="12" t="s">
+      <c r="CT73" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="CU73" s="11" t="s">
         <v>141</v>
       </c>
     </row>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="194">
   <si>
     <t>~TFM_AVA</t>
   </si>
@@ -464,9 +464,6 @@
     <t>Saudi Arabia</t>
   </si>
   <si>
-    <t>timeslice</t>
-  </si>
-  <si>
     <t>FLO_BND</t>
   </si>
   <si>
@@ -474,9 +471,6 @@
   </si>
   <si>
     <t>m_lithium</t>
-  </si>
-  <si>
-    <t>annual</t>
   </si>
   <si>
     <t>m_nickel</t>
@@ -671,7 +665,7 @@
     <numFmt numFmtId="178" formatCode="0.0"/>
     <numFmt numFmtId="179" formatCode="0.000"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -695,6 +689,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
@@ -863,7 +870,7 @@
       <charset val="0"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -873,6 +880,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1212,28 +1231,19 @@
   </borders>
   <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1242,43 +1252,46 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1290,77 +1303,83 @@
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1372,17 +1391,30 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="51" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="51" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="6" borderId="1" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="51" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="51" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="51" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="51" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
@@ -1870,29 +1902,29 @@
   <dimension ref="A1:AA281"/>
   <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="11.5"/>
   <cols>
-    <col min="1" max="1" width="15" style="22" customWidth="1"/>
-    <col min="2" max="2" width="8.85454545454546" style="22" customWidth="1"/>
-    <col min="3" max="3" width="4.70909090909091" style="22" customWidth="1"/>
-    <col min="4" max="4" width="8.85454545454546" style="22" customWidth="1"/>
-    <col min="5" max="5" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="6" max="6" width="4.28181818181818" style="22" customWidth="1"/>
-    <col min="7" max="7" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="8" max="8" width="4.57272727272727" style="22" customWidth="1"/>
-    <col min="9" max="9" width="4" style="22" customWidth="1"/>
-    <col min="10" max="10" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="11" max="11" width="4.57272727272727" style="22" customWidth="1"/>
-    <col min="12" max="12" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="13" max="13" width="4" style="22" customWidth="1"/>
-    <col min="14" max="14" width="4.28181818181818" style="22" customWidth="1"/>
-    <col min="15" max="16" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="17" max="18" width="4.57272727272727" style="22" customWidth="1"/>
-    <col min="19" max="19" width="4.42727272727273" style="22" customWidth="1"/>
-    <col min="20" max="20" width="5" style="22" customWidth="1"/>
-    <col min="21" max="21" width="11.7090909090909" style="22" customWidth="1"/>
-    <col min="22" max="22" width="10.7090909090909" style="22" customWidth="1"/>
-    <col min="23" max="23" width="13.1363636363636" style="22" customWidth="1"/>
-    <col min="24" max="259" width="11.4272727272727" style="22" customWidth="1"/>
-    <col min="260" max="16384" width="9.13636363636364" style="22"/>
+    <col min="1" max="1" width="15" style="35" customWidth="1"/>
+    <col min="2" max="2" width="8.85454545454546" style="35" customWidth="1"/>
+    <col min="3" max="3" width="4.70909090909091" style="35" customWidth="1"/>
+    <col min="4" max="4" width="8.85454545454546" style="35" customWidth="1"/>
+    <col min="5" max="5" width="4.42727272727273" style="35" customWidth="1"/>
+    <col min="6" max="6" width="4.28181818181818" style="35" customWidth="1"/>
+    <col min="7" max="7" width="4.42727272727273" style="35" customWidth="1"/>
+    <col min="8" max="8" width="4.57272727272727" style="35" customWidth="1"/>
+    <col min="9" max="9" width="4" style="35" customWidth="1"/>
+    <col min="10" max="10" width="4.42727272727273" style="35" customWidth="1"/>
+    <col min="11" max="11" width="4.57272727272727" style="35" customWidth="1"/>
+    <col min="12" max="12" width="4.42727272727273" style="35" customWidth="1"/>
+    <col min="13" max="13" width="4" style="35" customWidth="1"/>
+    <col min="14" max="14" width="4.28181818181818" style="35" customWidth="1"/>
+    <col min="15" max="16" width="4.42727272727273" style="35" customWidth="1"/>
+    <col min="17" max="18" width="4.57272727272727" style="35" customWidth="1"/>
+    <col min="19" max="19" width="4.42727272727273" style="35" customWidth="1"/>
+    <col min="20" max="20" width="5" style="35" customWidth="1"/>
+    <col min="21" max="21" width="11.7090909090909" style="35" customWidth="1"/>
+    <col min="22" max="22" width="10.7090909090909" style="35" customWidth="1"/>
+    <col min="23" max="23" width="13.1363636363636" style="35" customWidth="1"/>
+    <col min="24" max="259" width="11.4272727272727" style="35" customWidth="1"/>
+    <col min="260" max="16384" width="9.13636363636364" style="35"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.5" spans="1:21">
@@ -2971,7 +3003,7 @@
       <c r="AA34" s="5"/>
     </row>
     <row r="35" ht="12.5" spans="1:27">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="35" t="s">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -2999,7 +3031,7 @@
       <c r="AA35" s="5"/>
     </row>
     <row r="36" ht="12.5" spans="1:27">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="35" t="s">
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -3027,7 +3059,7 @@
       <c r="AA36" s="5"/>
     </row>
     <row r="37" ht="12.5" spans="1:27">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="35" t="s">
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -3055,7 +3087,7 @@
       <c r="AA37" s="5"/>
     </row>
     <row r="38" ht="12.5" spans="1:27">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -3083,7 +3115,7 @@
       <c r="AA38" s="5"/>
     </row>
     <row r="39" ht="12.5" spans="1:27">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="35" t="s">
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -8444,7 +8476,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:CU124"/>
+  <dimension ref="A2:DB124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="2" max="2" width="21.3727272727273" customWidth="1"/>
@@ -8463,7 +8495,8 @@
     <col min="22" max="24" width="7.13636363636364" customWidth="1"/>
     <col min="25" max="25" width="9.54545454545454" customWidth="1"/>
     <col min="26" max="26" width="17.9090909090909" customWidth="1"/>
-    <col min="27" max="33" width="7.13636363636364" customWidth="1"/>
+    <col min="27" max="27" width="9.90909090909091" customWidth="1"/>
+    <col min="28" max="33" width="7.13636363636364" customWidth="1"/>
     <col min="34" max="37" width="6" customWidth="1"/>
     <col min="38" max="39" width="15.5454545454545" customWidth="1"/>
     <col min="40" max="40" width="22.6363636363636" customWidth="1"/>
@@ -8756,7 +8789,7 @@
       <c r="C14" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="36" t="s">
         <v>92</v>
       </c>
       <c r="F14">
@@ -8815,7 +8848,7 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="36" t="s">
         <v>92</v>
       </c>
       <c r="C18">
@@ -8824,7 +8857,7 @@
       <c r="D18">
         <v>3</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="36" t="s">
         <v>100</v>
       </c>
       <c r="F18" t="s">
@@ -11612,7 +11645,7 @@
       <c r="D45">
         <v>2020</v>
       </c>
-      <c r="E45" s="24" t="s">
+      <c r="E45" s="37" t="s">
         <v>119</v>
       </c>
       <c r="F45" t="s">
@@ -11696,7 +11729,7 @@
       <c r="D55" t="s">
         <v>126</v>
       </c>
-      <c r="E55" s="23" t="s">
+      <c r="E55" s="36" t="s">
         <v>127</v>
       </c>
     </row>
@@ -11793,7 +11826,7 @@
       <c r="Y62" s="9"/>
       <c r="Z62" s="9"/>
     </row>
-    <row r="63" spans="3:95">
+    <row r="63" spans="3:53">
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
@@ -11818,20 +11851,16 @@
       <c r="X63" s="9"/>
       <c r="Y63" s="9"/>
       <c r="Z63" s="9"/>
-      <c r="BA63" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="CQ63" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="1:99">
+      <c r="BA63" s="2"/>
+    </row>
+    <row r="65" s="1" customFormat="1" spans="1:106">
       <c r="A65" s="2"/>
-      <c r="B65" s="12" t="s">
+      <c r="B65" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -11879,24 +11908,32 @@
       <c r="BG65" s="2"/>
       <c r="BH65" s="2"/>
       <c r="BI65" s="2"/>
-      <c r="CO65" s="11"/>
-      <c r="CP65" s="11"/>
-      <c r="CR65" s="11"/>
-      <c r="CS65" s="11"/>
-      <c r="CT65" s="11"/>
-      <c r="CU65" s="11"/>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="2:99">
-      <c r="B66" s="2" t="s">
+      <c r="CO65" s="26"/>
+      <c r="CP65" s="26"/>
+      <c r="CR65" s="26"/>
+      <c r="CS65" s="26"/>
+      <c r="CT65" s="26"/>
+      <c r="CU65" s="26"/>
+      <c r="CW65" s="28"/>
+      <c r="CX65" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="CY65" s="28"/>
+      <c r="CZ65" s="28"/>
+      <c r="DA65" s="28"/>
+      <c r="DB65" s="28"/>
+    </row>
+    <row r="66" s="2" customFormat="1" spans="2:106">
+      <c r="B66" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="14" t="s">
         <v>59</v>
       </c>
       <c r="F66" s="2" t="s">
@@ -12001,163 +12038,41 @@
       <c r="AM66" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AY66" s="2" t="s">
+      <c r="CQ66" s="27"/>
+      <c r="CR66" s="27"/>
+      <c r="CT66" s="27"/>
+      <c r="CU66" s="27"/>
+      <c r="CW66" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="CX66" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="CY66" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="CZ66" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="DA66" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="AZ66" s="2" t="s">
+      <c r="DB66" s="34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" ht="14.5" spans="2:106">
+      <c r="B67" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="BA66" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="BB66" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="BC66" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="BD66" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="BE66" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="BF66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="BG66" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="BH66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="BI66" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="BJ66" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="BK66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="BL66" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="BM66" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="BN66" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="BO66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="BP66" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="BQ66" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BR66" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="BS66" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="BT66" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="BU66" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="BV66" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="BW66" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="BX66" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="BY66" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="BZ66" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="CA66" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="CB66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="CC66" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="CD66" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="CE66" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="CF66" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="CG66" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="CH66" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="CI66" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="CJ66" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="CK66" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="CL66" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="CM66" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="CO66" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="CP66" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="CQ66" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="CR66" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="CS66" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="CT66" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="CU66" s="21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="67" s="2" customFormat="1" ht="14.5" spans="2:99">
-      <c r="B67" s="13" t="s">
+      <c r="C67" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D67" s="1" t="s">
+      <c r="E67" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="F67" s="2">
         <f t="shared" ref="F67:L67" si="2">D77/1000</f>
@@ -12294,163 +12209,41 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AY67" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AZ67" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BA67" s="2" t="s">
+      <c r="CQ67" s="27"/>
+      <c r="CR67" s="27"/>
+      <c r="CT67" s="27"/>
+      <c r="CU67" s="27"/>
+      <c r="CW67" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="CX67" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="CY67" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="BB67" s="2" t="s">
+      <c r="CZ67" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="DA67" s="34">
+        <v>0</v>
+      </c>
+      <c r="DB67" s="34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" ht="14.5" spans="2:106">
+      <c r="B68" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C68" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="BC67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE67" s="2">
-        <v>310</v>
-      </c>
-      <c r="BF67" s="2">
-        <v>6200</v>
-      </c>
-      <c r="BG67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ67" s="2">
-        <v>250</v>
-      </c>
-      <c r="BK67" s="2">
-        <v>2000</v>
-      </c>
-      <c r="BL67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW67" s="2">
-        <v>12250</v>
-      </c>
-      <c r="BX67" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY67" s="2">
-        <v>1930</v>
-      </c>
-      <c r="BZ67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB67" s="2">
-        <v>3300</v>
-      </c>
-      <c r="CC67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF67" s="2">
-        <v>60</v>
-      </c>
-      <c r="CG67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK67" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL67" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="CM67" s="2" t="s">
+      <c r="D68" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E68" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="CO67" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP67" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="CQ67" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="CR67" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS67" s="21">
-        <v>5</v>
-      </c>
-      <c r="CT67" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="CU67" s="21" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" ht="14.5" spans="2:99">
-      <c r="B68" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="F68" s="2">
         <f t="shared" ref="F68:M68" si="4">D78/1000</f>
@@ -12588,163 +12381,41 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY68" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AZ68" s="2" t="s">
+      <c r="CQ68" s="27"/>
+      <c r="CR68" s="27"/>
+      <c r="CT68" s="27"/>
+      <c r="CU68" s="27"/>
+      <c r="CW68" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="CX68" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="CY68" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="CZ68" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="DA68" s="34">
+        <v>0</v>
+      </c>
+      <c r="DB68" s="34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" ht="14.5" spans="2:106">
+      <c r="B69" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E69" s="12" t="s">
         <v>135</v>
-      </c>
-      <c r="BA68" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BB68" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="BC68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF68" s="2">
-        <v>21000</v>
-      </c>
-      <c r="BG68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ68" s="2">
-        <v>16000</v>
-      </c>
-      <c r="BK68" s="2">
-        <v>2100</v>
-      </c>
-      <c r="BL68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW68" s="2">
-        <v>16000</v>
-      </c>
-      <c r="BX68" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY68" s="2">
-        <v>2570</v>
-      </c>
-      <c r="BZ68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB68" s="2">
-        <v>52900</v>
-      </c>
-      <c r="CC68" s="2">
-        <v>7500</v>
-      </c>
-      <c r="CD68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK68" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL68" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="CM68" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="CO68" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP68" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="CQ68" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="CR68" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS68" s="21">
-        <v>5</v>
-      </c>
-      <c r="CT68" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="CU68" s="21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" ht="14.5" spans="2:99">
-      <c r="B69" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="F69" s="2">
         <f t="shared" ref="F69:M69" si="6">D79/1000</f>
@@ -12882,249 +12553,127 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AY69" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AZ69" s="2" t="s">
+      <c r="CQ69" s="27"/>
+      <c r="CR69" s="27"/>
+      <c r="CT69" s="27"/>
+      <c r="CU69" s="27"/>
+      <c r="CW69" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="CX69" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="CY69" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="CZ69" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="BA69" s="2" t="s">
+      <c r="DA69" s="34">
+        <v>0</v>
+      </c>
+      <c r="DB69" s="34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" ht="14.5" spans="2:106">
+      <c r="B70" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="BB69" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="BC69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD69" s="2">
-        <v>13</v>
-      </c>
-      <c r="BE69" s="2">
-        <v>4100</v>
-      </c>
-      <c r="BF69" s="2">
-        <v>1500</v>
-      </c>
-      <c r="BG69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK69" s="2">
-        <v>140</v>
-      </c>
-      <c r="BL69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV69" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW69" s="2">
-        <v>500</v>
-      </c>
-      <c r="BX69" s="2">
-        <v>36</v>
-      </c>
-      <c r="BY69" s="2">
-        <v>289</v>
-      </c>
-      <c r="BZ69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB69" s="2">
-        <v>1517</v>
-      </c>
-      <c r="CC69" s="2">
-        <v>250</v>
-      </c>
-      <c r="CD69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI69" s="2">
-        <v>36</v>
-      </c>
-      <c r="CJ69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK69" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL69" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="CM69" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="CO69" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP69" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="CQ69" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="CR69" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS69" s="21">
-        <v>5</v>
-      </c>
-      <c r="CT69" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="CU69" s="21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" ht="14.5" spans="2:99">
-      <c r="B70" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F70" s="2">
+      <c r="E70" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F70" s="17">
         <f t="shared" ref="F70:M70" si="8">D80/1000</f>
         <v>0</v>
       </c>
-      <c r="G70" s="2">
+      <c r="G70" s="17">
         <f t="shared" si="8"/>
         <v>74000</v>
       </c>
-      <c r="H70" s="2">
+      <c r="H70" s="17">
         <f t="shared" si="8"/>
         <v>270000</v>
       </c>
-      <c r="I70" s="2">
+      <c r="I70" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="J70" s="2">
+      <c r="J70" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="K70" s="2">
+      <c r="K70" s="17">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="L70" s="2">
+      <c r="L70" s="17">
         <f t="shared" si="8"/>
         <v>270000</v>
       </c>
-      <c r="M70" s="2">
+      <c r="M70" s="17">
         <f t="shared" si="8"/>
         <v>280000</v>
       </c>
-      <c r="N70" s="2">
+      <c r="N70" s="17">
         <f t="shared" ref="N70:AM70" si="9">L80/1000</f>
         <v>0</v>
       </c>
-      <c r="O70" s="2">
+      <c r="O70" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="P70" s="2">
+      <c r="P70" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="Q70" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="R70" s="2">
+      <c r="R70" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="S70" s="2">
+      <c r="S70" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T70" s="2">
+      <c r="T70" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U70" s="2">
+      <c r="U70" s="17">
         <f t="shared" si="9"/>
         <v>34000</v>
       </c>
-      <c r="V70" s="2">
+      <c r="V70" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="W70" s="2">
+      <c r="W70" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X70" s="2">
+      <c r="X70" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Y70" s="2">
+      <c r="Y70" s="17">
         <f t="shared" si="9"/>
         <v>275000</v>
       </c>
-      <c r="Z70" s="2">
+      <c r="Z70" s="17">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AA70" s="20">
+      <c r="AA70" s="25">
         <v>100</v>
       </c>
       <c r="AB70" s="2">
@@ -13175,163 +12724,41 @@
         <f t="shared" si="9"/>
         <v>140000</v>
       </c>
-      <c r="AY70" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AZ70" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BA70" s="2" t="s">
+      <c r="CQ70" s="27"/>
+      <c r="CR70" s="27"/>
+      <c r="CT70" s="27"/>
+      <c r="CU70" s="27"/>
+      <c r="CW70" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="CX70" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="CY70" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="BB70" s="2" t="s">
+      <c r="CZ70" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="DA70" s="34">
+        <v>0</v>
+      </c>
+      <c r="DB70" s="34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" ht="14.5" spans="2:106">
+      <c r="B71" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="BC70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE70" s="2">
-        <v>74000</v>
-      </c>
-      <c r="BF70" s="2">
-        <v>270000</v>
-      </c>
-      <c r="BG70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ70" s="2">
-        <v>270000</v>
-      </c>
-      <c r="BK70" s="2">
-        <v>280000</v>
-      </c>
-      <c r="BL70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS70" s="2">
-        <v>34000</v>
-      </c>
-      <c r="BT70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW70" s="2">
-        <v>275000</v>
-      </c>
-      <c r="BX70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY70" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB70" s="2">
-        <v>5000</v>
-      </c>
-      <c r="CC70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE70" s="2">
-        <v>640000</v>
-      </c>
-      <c r="CF70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ70" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK70" s="2">
-        <v>140000</v>
-      </c>
-      <c r="CL70" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="CM70" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="CO70" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP70" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="CQ70" s="21" t="s">
+      <c r="D71" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="CR70" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS70" s="21">
-        <v>5</v>
-      </c>
-      <c r="CT70" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="CU70" s="21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" ht="14.5" spans="2:99">
-      <c r="B71" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>139</v>
+      <c r="E71" s="12" t="s">
+        <v>137</v>
       </c>
       <c r="F71" s="2">
         <f t="shared" ref="F71:M71" si="10">D81/1000</f>
@@ -13361,7 +12788,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M71" s="20">
+      <c r="M71" s="24">
         <v>100</v>
       </c>
       <c r="N71" s="2">
@@ -13416,7 +12843,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AA71" s="20">
+      <c r="AA71" s="24">
         <v>100</v>
       </c>
       <c r="AB71" s="2">
@@ -13467,163 +12894,41 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AY71" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AZ71" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BA71" s="2" t="s">
+      <c r="CQ71" s="27"/>
+      <c r="CR71" s="27"/>
+      <c r="CT71" s="27"/>
+      <c r="CU71" s="27"/>
+      <c r="CW71" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="CX71" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="CY71" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="BB71" s="2" t="s">
+      <c r="CZ71" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="DA71" s="34">
+        <v>0</v>
+      </c>
+      <c r="DB71" s="34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" ht="14.5" spans="2:106">
+      <c r="B72" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C72" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="BC71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY71" s="2">
-        <v>0</v>
-      </c>
-      <c r="BZ71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CB71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK71" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL71" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="CM71" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="CO71" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP71" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="CQ71" s="21" t="s">
+      <c r="D72" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="CR71" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS71" s="21">
-        <v>5</v>
-      </c>
-      <c r="CT71" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="CU71" s="21" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" ht="14.5" spans="2:99">
-      <c r="B72" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>140</v>
+      <c r="E72" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="F72" s="2">
         <f t="shared" ref="F72:M72" si="12">D82/1000</f>
@@ -13761,164 +13066,42 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AY72" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AZ72" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BA72" s="2" t="s">
+      <c r="CQ72" s="27"/>
+      <c r="CR72" s="27"/>
+      <c r="CT72" s="27"/>
+      <c r="CU72" s="27"/>
+      <c r="CW72" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="CX72" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="CY72" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="BB72" s="2" t="s">
+      <c r="CZ72" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="DA72" s="34">
+        <v>0</v>
+      </c>
+      <c r="DB72" s="34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" ht="14.5" spans="1:106">
+      <c r="A73" s="2"/>
+      <c r="B73" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C73" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="BC72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE72" s="2">
-        <v>50000</v>
-      </c>
-      <c r="BF72" s="2">
-        <v>97000</v>
-      </c>
-      <c r="BG72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK72" s="2">
-        <v>27000</v>
-      </c>
-      <c r="BL72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BV72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BW72" s="2">
-        <v>324000</v>
-      </c>
-      <c r="BX72" s="2">
-        <v>0</v>
-      </c>
-      <c r="BY72" s="2">
-        <v>51600</v>
-      </c>
-      <c r="BZ72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CA72" s="2">
-        <v>30000</v>
-      </c>
-      <c r="CB72" s="2">
-        <v>244000</v>
-      </c>
-      <c r="CC72" s="2">
-        <v>62000</v>
-      </c>
-      <c r="CD72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CF72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK72" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL72" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="CM72" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="CO72" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP72" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="CQ72" s="21" t="s">
+      <c r="D73" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="CR72" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS72" s="21">
-        <v>5</v>
-      </c>
-      <c r="CT72" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="CU72" s="21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" ht="14.5" spans="1:99">
-      <c r="A73" s="2"/>
-      <c r="B73" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>141</v>
+      <c r="E73" s="12" t="s">
+        <v>139</v>
       </c>
       <c r="F73" s="2">
         <f t="shared" ref="F73:M73" si="14">D83/1000</f>
@@ -14056,721 +13239,640 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AY73" s="2">
-        <v>2050</v>
-      </c>
-      <c r="AZ73" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="BA73" s="1" t="s">
+      <c r="AY73" s="2"/>
+      <c r="AZ73" s="1"/>
+      <c r="BA73" s="1"/>
+      <c r="BB73" s="2"/>
+      <c r="BC73" s="1"/>
+      <c r="BD73" s="1"/>
+      <c r="BE73" s="1"/>
+      <c r="BF73" s="1"/>
+      <c r="BG73" s="1"/>
+      <c r="BH73" s="1"/>
+      <c r="BI73" s="1"/>
+      <c r="BJ73" s="1"/>
+      <c r="BK73" s="1"/>
+      <c r="BL73" s="1"/>
+      <c r="BM73" s="1"/>
+      <c r="BN73" s="1"/>
+      <c r="BO73" s="1"/>
+      <c r="BP73" s="1"/>
+      <c r="BQ73" s="1"/>
+      <c r="BR73" s="1"/>
+      <c r="BS73" s="1"/>
+      <c r="BT73" s="1"/>
+      <c r="BU73" s="1"/>
+      <c r="BV73" s="1"/>
+      <c r="BW73" s="1"/>
+      <c r="BX73" s="1"/>
+      <c r="BY73" s="1"/>
+      <c r="BZ73" s="1"/>
+      <c r="CA73" s="1"/>
+      <c r="CB73" s="1"/>
+      <c r="CC73" s="1"/>
+      <c r="CD73" s="1"/>
+      <c r="CE73" s="1"/>
+      <c r="CF73" s="1"/>
+      <c r="CG73" s="1"/>
+      <c r="CH73" s="1"/>
+      <c r="CI73" s="1"/>
+      <c r="CJ73" s="1"/>
+      <c r="CK73" s="1"/>
+      <c r="CL73" s="1"/>
+      <c r="CM73" s="1"/>
+      <c r="CQ73" s="26"/>
+      <c r="CR73" s="27"/>
+      <c r="CT73" s="26"/>
+      <c r="CU73" s="26"/>
+      <c r="CW73" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="CX73" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="CY73" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="BB73" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="BC73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BD73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE73" s="1">
-        <v>69000</v>
-      </c>
-      <c r="BF73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BG73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BH73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ73" s="1">
-        <v>74000</v>
-      </c>
-      <c r="BK73" s="1">
-        <v>52000</v>
-      </c>
-      <c r="BL73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BM73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BP73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BQ73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BS73" s="1">
-        <v>8000</v>
-      </c>
-      <c r="BT73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BU73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BV73" s="1">
-        <v>0</v>
-      </c>
-      <c r="BW73" s="1">
-        <v>77100</v>
-      </c>
-      <c r="BX73" s="1">
-        <v>90000</v>
-      </c>
-      <c r="BY73" s="1">
-        <v>5700</v>
-      </c>
-      <c r="BZ73" s="1">
-        <v>600</v>
-      </c>
-      <c r="CA73" s="1">
-        <v>0</v>
-      </c>
-      <c r="CB73" s="1">
-        <v>12900</v>
-      </c>
-      <c r="CC73" s="1">
-        <v>14000</v>
-      </c>
-      <c r="CD73" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE73" s="1">
-        <v>0</v>
-      </c>
-      <c r="CF73" s="1">
-        <v>0</v>
-      </c>
-      <c r="CG73" s="1">
-        <v>0</v>
-      </c>
-      <c r="CH73" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI73" s="1">
-        <v>90000</v>
-      </c>
-      <c r="CJ73" s="1">
-        <v>0</v>
-      </c>
-      <c r="CK73" s="1">
-        <v>0</v>
-      </c>
-      <c r="CL73" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="CM73" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="CO73" s="21">
-        <v>0</v>
-      </c>
-      <c r="CP73" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="CQ73" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="CR73" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="CS73" s="21">
+      <c r="CZ73" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="DA73" s="34">
+        <v>0</v>
+      </c>
+      <c r="DB73" s="34">
         <v>5</v>
-      </c>
-      <c r="CT73" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="CU73" s="11" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1"/>
     <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1"/>
     <row r="77" s="3" customFormat="1" spans="4:37">
-      <c r="D77" s="14">
-        <v>0</v>
-      </c>
-      <c r="E77" s="14">
+      <c r="D77" s="18">
+        <v>0</v>
+      </c>
+      <c r="E77" s="18">
         <v>310000</v>
       </c>
-      <c r="F77" s="14">
+      <c r="F77" s="18">
         <v>6200000</v>
       </c>
-      <c r="G77" s="14">
-        <v>0</v>
-      </c>
-      <c r="H77" s="14"/>
-      <c r="I77" s="14"/>
-      <c r="J77" s="14">
+      <c r="G77" s="18">
+        <v>0</v>
+      </c>
+      <c r="H77" s="18"/>
+      <c r="I77" s="18"/>
+      <c r="J77" s="18">
         <v>250000</v>
       </c>
-      <c r="K77" s="14">
+      <c r="K77" s="18">
         <v>2000000</v>
       </c>
-      <c r="L77" s="14"/>
-      <c r="M77" s="14">
-        <v>0</v>
-      </c>
-      <c r="N77" s="14">
-        <v>0</v>
-      </c>
-      <c r="O77" s="14">
-        <v>0</v>
-      </c>
-      <c r="P77" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="14"/>
-      <c r="R77" s="14"/>
-      <c r="S77" s="14">
-        <v>0</v>
-      </c>
-      <c r="T77" s="14"/>
-      <c r="U77" s="14"/>
-      <c r="V77" s="14">
-        <v>0</v>
-      </c>
-      <c r="W77" s="14">
+      <c r="L77" s="18"/>
+      <c r="M77" s="18">
+        <v>0</v>
+      </c>
+      <c r="N77" s="18">
+        <v>0</v>
+      </c>
+      <c r="O77" s="18">
+        <v>0</v>
+      </c>
+      <c r="P77" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="18"/>
+      <c r="R77" s="18"/>
+      <c r="S77" s="18">
+        <v>0</v>
+      </c>
+      <c r="T77" s="18"/>
+      <c r="U77" s="18"/>
+      <c r="V77" s="18">
+        <v>0</v>
+      </c>
+      <c r="W77" s="18">
         <v>12250000</v>
       </c>
-      <c r="X77" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y77" s="14">
+      <c r="X77" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="18">
         <v>1930000</v>
       </c>
-      <c r="Z77" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB77" s="14">
+      <c r="Z77" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="18">
         <v>3300000</v>
       </c>
-      <c r="AC77" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD77" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE77" s="14">
-        <v>0</v>
-      </c>
-      <c r="AF77" s="14">
+      <c r="AC77" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="18">
         <v>60000</v>
       </c>
-      <c r="AG77" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH77" s="14"/>
-      <c r="AI77" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ77" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK77" s="14">
+      <c r="AG77" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="18"/>
+      <c r="AI77" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="78" s="3" customFormat="1" spans="4:37">
-      <c r="D78" s="14">
-        <v>0</v>
-      </c>
-      <c r="E78" s="14">
-        <v>0</v>
-      </c>
-      <c r="F78" s="14">
+      <c r="D78" s="18">
+        <v>0</v>
+      </c>
+      <c r="E78" s="18">
+        <v>0</v>
+      </c>
+      <c r="F78" s="18">
         <v>21000000</v>
       </c>
-      <c r="G78" s="14">
-        <v>0</v>
-      </c>
-      <c r="H78" s="14"/>
-      <c r="I78" s="14"/>
-      <c r="J78" s="14">
+      <c r="G78" s="18">
+        <v>0</v>
+      </c>
+      <c r="H78" s="18"/>
+      <c r="I78" s="18"/>
+      <c r="J78" s="18">
         <v>16000000</v>
       </c>
-      <c r="K78" s="14">
+      <c r="K78" s="18">
         <v>2100000</v>
       </c>
-      <c r="L78" s="14"/>
-      <c r="M78" s="14">
-        <v>0</v>
-      </c>
-      <c r="N78" s="14">
-        <v>0</v>
-      </c>
-      <c r="O78" s="14">
-        <v>0</v>
-      </c>
-      <c r="P78" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="14"/>
-      <c r="R78" s="14"/>
-      <c r="S78" s="14">
-        <v>0</v>
-      </c>
-      <c r="T78" s="14"/>
-      <c r="U78" s="14"/>
-      <c r="V78" s="14">
-        <v>0</v>
-      </c>
-      <c r="W78" s="14">
+      <c r="L78" s="18"/>
+      <c r="M78" s="18">
+        <v>0</v>
+      </c>
+      <c r="N78" s="18">
+        <v>0</v>
+      </c>
+      <c r="O78" s="18">
+        <v>0</v>
+      </c>
+      <c r="P78" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="18"/>
+      <c r="R78" s="18"/>
+      <c r="S78" s="18">
+        <v>0</v>
+      </c>
+      <c r="T78" s="18"/>
+      <c r="U78" s="18"/>
+      <c r="V78" s="18">
+        <v>0</v>
+      </c>
+      <c r="W78" s="18">
         <v>16000000</v>
       </c>
-      <c r="X78" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y78" s="14">
+      <c r="X78" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="18">
         <v>2570000</v>
       </c>
-      <c r="Z78" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB78" s="14">
+      <c r="Z78" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="18">
         <v>52900000</v>
       </c>
-      <c r="AC78" s="14">
+      <c r="AC78" s="18">
         <v>7500000</v>
       </c>
-      <c r="AD78" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE78" s="14">
-        <v>0</v>
-      </c>
-      <c r="AF78" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG78" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH78" s="14"/>
-      <c r="AI78" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ78" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK78" s="14">
+      <c r="AD78" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF78" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH78" s="18"/>
+      <c r="AI78" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="79" s="3" customFormat="1" spans="4:37">
-      <c r="D79" s="14">
+      <c r="D79" s="18">
         <v>13000</v>
       </c>
-      <c r="E79" s="14">
+      <c r="E79" s="18">
         <v>4100000</v>
       </c>
-      <c r="F79" s="14">
+      <c r="F79" s="18">
         <v>1500000</v>
       </c>
-      <c r="G79" s="14">
-        <v>0</v>
-      </c>
-      <c r="H79" s="14"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14">
-        <v>0</v>
-      </c>
-      <c r="K79" s="14">
+      <c r="G79" s="18">
+        <v>0</v>
+      </c>
+      <c r="H79" s="18"/>
+      <c r="I79" s="18"/>
+      <c r="J79" s="18">
+        <v>0</v>
+      </c>
+      <c r="K79" s="18">
         <v>140000</v>
       </c>
-      <c r="L79" s="14"/>
-      <c r="M79" s="14">
-        <v>0</v>
-      </c>
-      <c r="N79" s="14">
-        <v>0</v>
-      </c>
-      <c r="O79" s="14">
-        <v>0</v>
-      </c>
-      <c r="P79" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="14"/>
-      <c r="R79" s="14"/>
-      <c r="S79" s="14">
-        <v>0</v>
-      </c>
-      <c r="T79" s="14"/>
-      <c r="U79" s="14"/>
-      <c r="V79" s="14">
-        <v>0</v>
-      </c>
-      <c r="W79" s="14">
+      <c r="L79" s="18"/>
+      <c r="M79" s="18">
+        <v>0</v>
+      </c>
+      <c r="N79" s="18">
+        <v>0</v>
+      </c>
+      <c r="O79" s="18">
+        <v>0</v>
+      </c>
+      <c r="P79" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="18"/>
+      <c r="R79" s="18"/>
+      <c r="S79" s="18">
+        <v>0</v>
+      </c>
+      <c r="T79" s="18"/>
+      <c r="U79" s="18"/>
+      <c r="V79" s="18">
+        <v>0</v>
+      </c>
+      <c r="W79" s="18">
         <v>500000</v>
       </c>
-      <c r="X79" s="14">
+      <c r="X79" s="18">
         <v>36000</v>
       </c>
-      <c r="Y79" s="14">
+      <c r="Y79" s="18">
         <v>289000</v>
       </c>
-      <c r="Z79" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA79" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB79" s="14">
+      <c r="Z79" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="18">
         <v>1517000</v>
       </c>
-      <c r="AC79" s="14">
+      <c r="AC79" s="18">
         <v>250000</v>
       </c>
-      <c r="AD79" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE79" s="14">
-        <v>0</v>
-      </c>
-      <c r="AF79" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG79" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH79" s="14"/>
-      <c r="AI79" s="14">
+      <c r="AD79" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF79" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="18"/>
+      <c r="AI79" s="18">
         <v>36000</v>
       </c>
-      <c r="AJ79" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK79" s="14">
+      <c r="AJ79" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="80" s="3" customFormat="1" spans="4:37">
-      <c r="D80" s="14">
-        <v>0</v>
-      </c>
-      <c r="E80" s="14">
+      <c r="D80" s="18">
+        <v>0</v>
+      </c>
+      <c r="E80" s="18">
         <v>74000000</v>
       </c>
-      <c r="F80" s="14">
+      <c r="F80" s="18">
         <v>270000000</v>
       </c>
-      <c r="G80" s="14">
-        <v>0</v>
-      </c>
-      <c r="H80" s="14"/>
-      <c r="I80" s="14"/>
-      <c r="J80" s="14">
+      <c r="G80" s="18">
+        <v>0</v>
+      </c>
+      <c r="H80" s="18"/>
+      <c r="I80" s="18"/>
+      <c r="J80" s="18">
         <v>270000000</v>
       </c>
-      <c r="K80" s="14">
+      <c r="K80" s="18">
         <v>280000000</v>
       </c>
-      <c r="L80" s="14"/>
-      <c r="M80" s="14">
-        <v>0</v>
-      </c>
-      <c r="N80" s="14">
-        <v>0</v>
-      </c>
-      <c r="O80" s="14">
-        <v>0</v>
-      </c>
-      <c r="P80" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="14"/>
-      <c r="R80" s="14"/>
-      <c r="S80" s="14">
+      <c r="L80" s="18"/>
+      <c r="M80" s="18">
+        <v>0</v>
+      </c>
+      <c r="N80" s="18">
+        <v>0</v>
+      </c>
+      <c r="O80" s="18">
+        <v>0</v>
+      </c>
+      <c r="P80" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="18"/>
+      <c r="R80" s="18"/>
+      <c r="S80" s="18">
         <v>34000000</v>
       </c>
-      <c r="T80" s="14"/>
-      <c r="U80" s="14"/>
-      <c r="V80" s="14">
-        <v>0</v>
-      </c>
-      <c r="W80" s="14">
+      <c r="T80" s="18"/>
+      <c r="U80" s="18"/>
+      <c r="V80" s="18">
+        <v>0</v>
+      </c>
+      <c r="W80" s="18">
         <v>275000000</v>
       </c>
-      <c r="X80" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y80" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z80" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="14">
+      <c r="X80" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="18">
         <v>5000000</v>
       </c>
-      <c r="AC80" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD80" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE80" s="14">
+      <c r="AC80" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="18">
         <v>640000000</v>
       </c>
-      <c r="AF80" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG80" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH80" s="14"/>
-      <c r="AI80" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ80" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK80" s="14">
+      <c r="AF80" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="18"/>
+      <c r="AI80" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK80" s="18">
         <v>140000000</v>
       </c>
     </row>
     <row r="81" s="3" customFormat="1" spans="4:37">
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="14"/>
-      <c r="J81" s="14"/>
-      <c r="K81" s="14"/>
-      <c r="L81" s="14"/>
-      <c r="M81" s="14"/>
-      <c r="N81" s="14"/>
-      <c r="O81" s="14"/>
-      <c r="P81" s="14"/>
-      <c r="Q81" s="14"/>
-      <c r="R81" s="14"/>
-      <c r="S81" s="14"/>
-      <c r="T81" s="14"/>
-      <c r="U81" s="14"/>
-      <c r="V81" s="14"/>
-      <c r="W81" s="14"/>
-      <c r="X81" s="14"/>
-      <c r="Y81" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z81" s="14"/>
-      <c r="AA81" s="14"/>
-      <c r="AB81" s="14"/>
-      <c r="AC81" s="14"/>
-      <c r="AD81" s="14"/>
-      <c r="AE81" s="14"/>
-      <c r="AF81" s="14"/>
-      <c r="AG81" s="14"/>
-      <c r="AH81" s="14"/>
-      <c r="AI81" s="14"/>
-      <c r="AJ81" s="14"/>
-      <c r="AK81" s="14"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="18"/>
+      <c r="H81" s="18"/>
+      <c r="I81" s="18"/>
+      <c r="J81" s="18"/>
+      <c r="K81" s="18"/>
+      <c r="L81" s="18"/>
+      <c r="M81" s="18"/>
+      <c r="N81" s="18"/>
+      <c r="O81" s="18"/>
+      <c r="P81" s="18"/>
+      <c r="Q81" s="18"/>
+      <c r="R81" s="18"/>
+      <c r="S81" s="18"/>
+      <c r="T81" s="18"/>
+      <c r="U81" s="18"/>
+      <c r="V81" s="18"/>
+      <c r="W81" s="18"/>
+      <c r="X81" s="18"/>
+      <c r="Y81" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="18"/>
+      <c r="AA81" s="18"/>
+      <c r="AB81" s="18"/>
+      <c r="AC81" s="18"/>
+      <c r="AD81" s="18"/>
+      <c r="AE81" s="18"/>
+      <c r="AF81" s="18"/>
+      <c r="AG81" s="18"/>
+      <c r="AH81" s="18"/>
+      <c r="AI81" s="18"/>
+      <c r="AJ81" s="18"/>
+      <c r="AK81" s="18"/>
     </row>
     <row r="82" s="3" customFormat="1" spans="4:37">
-      <c r="D82" s="14">
-        <v>0</v>
-      </c>
-      <c r="E82" s="14">
+      <c r="D82" s="18">
+        <v>0</v>
+      </c>
+      <c r="E82" s="18">
         <v>50000000</v>
       </c>
-      <c r="F82" s="14">
+      <c r="F82" s="18">
         <v>97000000</v>
       </c>
-      <c r="G82" s="14">
-        <v>0</v>
-      </c>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="14">
-        <v>0</v>
-      </c>
-      <c r="K82" s="14">
+      <c r="G82" s="18">
+        <v>0</v>
+      </c>
+      <c r="H82" s="18"/>
+      <c r="I82" s="18"/>
+      <c r="J82" s="18">
+        <v>0</v>
+      </c>
+      <c r="K82" s="18">
         <v>27000000</v>
       </c>
-      <c r="L82" s="14"/>
-      <c r="M82" s="14">
-        <v>0</v>
-      </c>
-      <c r="N82" s="14">
-        <v>0</v>
-      </c>
-      <c r="O82" s="14">
-        <v>0</v>
-      </c>
-      <c r="P82" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q82" s="14"/>
-      <c r="R82" s="14"/>
-      <c r="S82" s="14">
-        <v>0</v>
-      </c>
-      <c r="T82" s="14"/>
-      <c r="U82" s="14"/>
-      <c r="V82" s="14">
-        <v>0</v>
-      </c>
-      <c r="W82" s="14">
+      <c r="L82" s="18"/>
+      <c r="M82" s="18">
+        <v>0</v>
+      </c>
+      <c r="N82" s="18">
+        <v>0</v>
+      </c>
+      <c r="O82" s="18">
+        <v>0</v>
+      </c>
+      <c r="P82" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="18"/>
+      <c r="R82" s="18"/>
+      <c r="S82" s="18">
+        <v>0</v>
+      </c>
+      <c r="T82" s="18"/>
+      <c r="U82" s="18"/>
+      <c r="V82" s="18">
+        <v>0</v>
+      </c>
+      <c r="W82" s="18">
         <v>324000000</v>
       </c>
-      <c r="X82" s="14">
-        <v>0</v>
-      </c>
-      <c r="Y82" s="14">
+      <c r="X82" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="18">
         <v>51600000</v>
       </c>
-      <c r="Z82" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA82" s="14">
+      <c r="Z82" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="18">
         <v>30000000</v>
       </c>
-      <c r="AB82" s="14">
+      <c r="AB82" s="18">
         <v>244000000</v>
       </c>
-      <c r="AC82" s="14">
+      <c r="AC82" s="18">
         <v>62000000</v>
       </c>
-      <c r="AD82" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE82" s="14">
-        <v>0</v>
-      </c>
-      <c r="AF82" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG82" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH82" s="14"/>
-      <c r="AI82" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ82" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK82" s="14">
+      <c r="AD82" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="18"/>
+      <c r="AI82" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ82" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK82" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="83" s="3" customFormat="1" spans="4:37">
-      <c r="D83" s="14">
-        <v>0</v>
-      </c>
-      <c r="E83" s="14">
+      <c r="D83" s="18">
+        <v>0</v>
+      </c>
+      <c r="E83" s="18">
         <v>69000000</v>
       </c>
-      <c r="F83" s="14">
-        <v>0</v>
-      </c>
-      <c r="G83" s="14">
-        <v>0</v>
-      </c>
-      <c r="H83" s="14"/>
-      <c r="I83" s="14"/>
-      <c r="J83" s="14">
+      <c r="F83" s="18">
+        <v>0</v>
+      </c>
+      <c r="G83" s="18">
+        <v>0</v>
+      </c>
+      <c r="H83" s="18"/>
+      <c r="I83" s="18"/>
+      <c r="J83" s="18">
         <v>74000000</v>
       </c>
-      <c r="K83" s="14">
+      <c r="K83" s="18">
         <v>52000000</v>
       </c>
-      <c r="L83" s="14"/>
-      <c r="M83" s="14">
-        <v>0</v>
-      </c>
-      <c r="N83" s="14">
-        <v>0</v>
-      </c>
-      <c r="O83" s="14">
-        <v>0</v>
-      </c>
-      <c r="P83" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="14"/>
-      <c r="R83" s="14"/>
-      <c r="S83" s="14">
+      <c r="L83" s="18"/>
+      <c r="M83" s="18">
+        <v>0</v>
+      </c>
+      <c r="N83" s="18">
+        <v>0</v>
+      </c>
+      <c r="O83" s="18">
+        <v>0</v>
+      </c>
+      <c r="P83" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="18"/>
+      <c r="R83" s="18"/>
+      <c r="S83" s="18">
         <v>8000000</v>
       </c>
-      <c r="T83" s="14"/>
-      <c r="U83" s="14"/>
-      <c r="V83" s="14">
-        <v>0</v>
-      </c>
-      <c r="W83" s="14">
+      <c r="T83" s="18"/>
+      <c r="U83" s="18"/>
+      <c r="V83" s="18">
+        <v>0</v>
+      </c>
+      <c r="W83" s="18">
         <v>77100000</v>
       </c>
-      <c r="X83" s="14">
+      <c r="X83" s="18">
         <v>90000000</v>
       </c>
-      <c r="Y83" s="14">
+      <c r="Y83" s="18">
         <v>5700000</v>
       </c>
-      <c r="Z83" s="14">
+      <c r="Z83" s="18">
         <v>600000</v>
       </c>
-      <c r="AA83" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="14">
+      <c r="AA83" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="18">
         <v>12900000</v>
       </c>
-      <c r="AC83" s="14">
+      <c r="AC83" s="18">
         <v>14000000</v>
       </c>
-      <c r="AD83" s="14">
-        <v>0</v>
-      </c>
-      <c r="AE83" s="14">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="14">
-        <v>0</v>
-      </c>
-      <c r="AG83" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH83" s="14"/>
-      <c r="AI83" s="14">
+      <c r="AD83" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="18"/>
+      <c r="AI83" s="18">
         <v>90000000</v>
       </c>
-      <c r="AJ83" s="14">
-        <v>0</v>
-      </c>
-      <c r="AK83" s="14">
+      <c r="AJ83" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="18">
         <v>0</v>
       </c>
     </row>
@@ -14858,7 +13960,7 @@
     </row>
     <row r="88" spans="2:26">
       <c r="B88" s="9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="9"/>
@@ -14914,1333 +14016,1333 @@
     </row>
     <row r="90" s="4" customFormat="1"/>
     <row r="91" s="4" customFormat="1" spans="5:12">
-      <c r="E91" s="15"/>
-      <c r="H91" s="16"/>
-      <c r="I91" s="16"/>
-      <c r="J91" s="16"/>
-      <c r="K91" s="16"/>
-      <c r="L91" s="16"/>
+      <c r="E91" s="19"/>
+      <c r="H91" s="20"/>
+      <c r="I91" s="20"/>
+      <c r="J91" s="20"/>
+      <c r="K91" s="20"/>
+      <c r="L91" s="20"/>
     </row>
     <row r="92" s="4" customFormat="1" spans="4:12">
-      <c r="D92" s="16"/>
-      <c r="H92" s="16"/>
-      <c r="I92" s="16"/>
-      <c r="J92" s="16"/>
-      <c r="K92" s="16"/>
-      <c r="L92" s="16"/>
+      <c r="D92" s="20"/>
+      <c r="H92" s="20"/>
+      <c r="I92" s="20"/>
+      <c r="J92" s="20"/>
+      <c r="K92" s="20"/>
+      <c r="L92" s="20"/>
     </row>
     <row r="93" s="4" customFormat="1" spans="3:12">
-      <c r="C93" s="16"/>
-      <c r="D93" s="16"/>
-      <c r="F93" s="16"/>
-      <c r="H93" s="16"/>
-      <c r="I93" s="16"/>
-      <c r="J93" s="16"/>
-      <c r="K93" s="16"/>
-      <c r="L93" s="16"/>
+      <c r="C93" s="20"/>
+      <c r="D93" s="20"/>
+      <c r="F93" s="20"/>
+      <c r="H93" s="20"/>
+      <c r="I93" s="20"/>
+      <c r="J93" s="20"/>
+      <c r="K93" s="20"/>
+      <c r="L93" s="20"/>
     </row>
     <row r="94" s="4" customFormat="1" spans="3:12">
-      <c r="C94" s="16"/>
-      <c r="D94" s="16"/>
-      <c r="H94" s="16"/>
-      <c r="I94" s="16"/>
-      <c r="J94" s="16"/>
-      <c r="K94" s="16"/>
-      <c r="L94" s="16"/>
+      <c r="C94" s="20"/>
+      <c r="D94" s="20"/>
+      <c r="H94" s="20"/>
+      <c r="I94" s="20"/>
+      <c r="J94" s="20"/>
+      <c r="K94" s="20"/>
+      <c r="L94" s="20"/>
     </row>
     <row r="95" s="4" customFormat="1" spans="3:12">
-      <c r="C95" s="16"/>
-      <c r="D95" s="16"/>
-      <c r="F95" s="16"/>
-      <c r="H95" s="16"/>
-      <c r="I95" s="16"/>
-      <c r="J95" s="16"/>
-      <c r="K95" s="16"/>
-      <c r="L95" s="16"/>
+      <c r="C95" s="20"/>
+      <c r="D95" s="20"/>
+      <c r="F95" s="20"/>
+      <c r="H95" s="20"/>
+      <c r="I95" s="20"/>
+      <c r="J95" s="20"/>
+      <c r="K95" s="20"/>
+      <c r="L95" s="20"/>
     </row>
     <row r="96" s="4" customFormat="1" spans="3:12">
-      <c r="C96" s="16"/>
-      <c r="D96" s="16"/>
-      <c r="H96" s="16"/>
-      <c r="I96" s="16"/>
-      <c r="J96" s="16"/>
-      <c r="K96" s="16"/>
-      <c r="L96" s="16"/>
+      <c r="C96" s="20"/>
+      <c r="D96" s="20"/>
+      <c r="H96" s="20"/>
+      <c r="I96" s="20"/>
+      <c r="J96" s="20"/>
+      <c r="K96" s="20"/>
+      <c r="L96" s="20"/>
     </row>
     <row r="97" s="4" customFormat="1" spans="3:12">
-      <c r="C97" s="16"/>
-      <c r="D97" s="16"/>
-      <c r="F97" s="16"/>
-      <c r="H97" s="16"/>
-      <c r="I97" s="16"/>
-      <c r="J97" s="16"/>
-      <c r="K97" s="16"/>
-      <c r="L97" s="16"/>
+      <c r="C97" s="20"/>
+      <c r="D97" s="20"/>
+      <c r="F97" s="20"/>
+      <c r="H97" s="20"/>
+      <c r="I97" s="20"/>
+      <c r="J97" s="20"/>
+      <c r="K97" s="20"/>
+      <c r="L97" s="20"/>
     </row>
     <row r="98" s="4" customFormat="1" spans="3:12">
-      <c r="C98" s="16"/>
-      <c r="D98" s="16"/>
-      <c r="H98" s="16"/>
-      <c r="I98" s="16"/>
-      <c r="J98" s="16"/>
-      <c r="K98" s="16"/>
-      <c r="L98" s="16"/>
+      <c r="C98" s="20"/>
+      <c r="D98" s="20"/>
+      <c r="H98" s="20"/>
+      <c r="I98" s="20"/>
+      <c r="J98" s="20"/>
+      <c r="K98" s="20"/>
+      <c r="L98" s="20"/>
     </row>
     <row r="99" s="4" customFormat="1" spans="3:6">
-      <c r="C99" s="16"/>
-      <c r="F99" s="16"/>
+      <c r="C99" s="20"/>
+      <c r="F99" s="20"/>
     </row>
     <row r="100" s="4" customFormat="1" spans="3:4">
-      <c r="C100" s="16"/>
-      <c r="D100" s="16"/>
+      <c r="C100" s="20"/>
+      <c r="D100" s="20"/>
     </row>
     <row r="101" s="4" customFormat="1" spans="3:7">
-      <c r="C101" s="16"/>
-      <c r="D101" s="17"/>
-      <c r="E101" s="17"/>
-      <c r="F101" s="17"/>
-      <c r="G101" s="17"/>
+      <c r="C101" s="20"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="21"/>
+      <c r="G101" s="21"/>
     </row>
     <row r="102" s="4" customFormat="1" spans="3:26">
-      <c r="C102" s="16"/>
+      <c r="C102" s="20"/>
       <c r="D102" t="s">
         <v>73</v>
       </c>
-      <c r="M102" s="16"/>
+      <c r="M102" s="20"/>
       <c r="N102" t="s">
         <v>73</v>
       </c>
-      <c r="Y102" s="16"/>
+      <c r="Y102" s="20"/>
       <c r="Z102" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="103" s="4" customFormat="1" spans="3:29">
-      <c r="C103" s="16" t="s">
+      <c r="C103" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D103" s="17" t="s">
+      <c r="D103" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E103" s="17" t="s">
+      <c r="E103" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="F103" s="17" t="s">
+      <c r="F103" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G103" s="17" t="s">
+      <c r="G103" s="21" t="s">
         <v>25</v>
       </c>
       <c r="L103" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="M103" s="16" t="s">
+      <c r="M103" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="N103" s="17" t="s">
+      <c r="N103" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="O103" s="17" t="s">
+      <c r="O103" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="P103" s="17" t="s">
+      <c r="P103" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="Q103" s="17" t="s">
+      <c r="Q103" s="21" t="s">
         <v>25</v>
       </c>
       <c r="X103" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="Y103" s="16" t="s">
+      <c r="Y103" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="Z103" s="17" t="s">
+      <c r="Z103" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="AA103" s="17" t="s">
+      <c r="AA103" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="AB103" s="17" t="s">
+      <c r="AB103" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="AC103" s="17" t="s">
+      <c r="AC103" s="21" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="104" s="4" customFormat="1" spans="3:29">
-      <c r="C104" s="16" t="s">
+      <c r="C104" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D104" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="E104" s="17">
+      <c r="D104" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="E104" s="21">
         <v>7.11384396954065</v>
       </c>
-      <c r="F104" s="18">
+      <c r="F104" s="22">
         <v>5.40179852616065</v>
       </c>
-      <c r="G104" s="18">
+      <c r="G104" s="22">
         <v>8.85540744288872</v>
       </c>
       <c r="L104" s="4">
         <v>2050</v>
       </c>
-      <c r="M104" s="16" t="s">
+      <c r="M104" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N104" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="O104" s="17">
+      <c r="N104" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="O104" s="21">
         <f>E104*0.313</f>
         <v>2.22663316246622</v>
       </c>
-      <c r="P104" s="17">
+      <c r="P104" s="21">
         <f>F104*0.313</f>
         <v>1.69076293868828</v>
       </c>
-      <c r="Q104" s="17">
+      <c r="Q104" s="21">
         <f>G104*0.313</f>
         <v>2.77174252962417</v>
       </c>
       <c r="X104" s="4">
         <v>0</v>
       </c>
-      <c r="Y104" s="16" t="s">
+      <c r="Y104" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z104" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA104" s="17">
+      <c r="Z104" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA104" s="21">
         <v>5</v>
       </c>
-      <c r="AB104" s="17">
+      <c r="AB104" s="21">
         <v>5</v>
       </c>
-      <c r="AC104" s="17">
+      <c r="AC104" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="105" s="4" customFormat="1" spans="3:29">
-      <c r="C105" s="16" t="s">
+      <c r="C105" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D105" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="E105" s="17">
+      <c r="D105" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="E105" s="21">
         <v>7.11384396954065</v>
       </c>
-      <c r="F105" s="18">
+      <c r="F105" s="22">
         <v>5.40179852616065</v>
       </c>
-      <c r="G105" s="18">
+      <c r="G105" s="22">
         <v>8.85540744288872</v>
       </c>
       <c r="L105" s="4">
         <v>2050</v>
       </c>
-      <c r="M105" s="16" t="s">
+      <c r="M105" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N105" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="O105" s="17">
+      <c r="N105" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="O105" s="21">
         <f t="shared" ref="O105:O124" si="16">E105*0.313</f>
         <v>2.22663316246622</v>
       </c>
-      <c r="P105" s="17">
+      <c r="P105" s="21">
         <f t="shared" ref="P105:P124" si="17">F105*0.313</f>
         <v>1.69076293868828</v>
       </c>
-      <c r="Q105" s="17">
+      <c r="Q105" s="21">
         <f t="shared" ref="Q105:Q124" si="18">G105*0.313</f>
         <v>2.77174252962417</v>
       </c>
       <c r="X105" s="4">
         <v>0</v>
       </c>
-      <c r="Y105" s="16" t="s">
+      <c r="Y105" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z105" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA105" s="17">
+      <c r="Z105" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="AA105" s="21">
         <v>5</v>
       </c>
-      <c r="AB105" s="17">
+      <c r="AB105" s="21">
         <v>5</v>
       </c>
-      <c r="AC105" s="17">
+      <c r="AC105" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="106" spans="3:29">
-      <c r="C106" s="16" t="s">
+      <c r="C106" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D106" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="E106" s="17">
+      <c r="D106" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="E106" s="21">
         <v>7.62975445836404</v>
       </c>
-      <c r="F106" s="18">
+      <c r="F106" s="22">
         <v>5.79354797347089</v>
       </c>
-      <c r="G106" s="18">
+      <c r="G106" s="22">
         <v>9.49761967575534</v>
       </c>
       <c r="L106" s="4">
         <v>2050</v>
       </c>
-      <c r="M106" s="16" t="s">
+      <c r="M106" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N106" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="O106" s="17">
+      <c r="N106" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="O106" s="21">
         <f t="shared" si="16"/>
         <v>2.38811314546794</v>
       </c>
-      <c r="P106" s="17">
+      <c r="P106" s="21">
         <f t="shared" si="17"/>
         <v>1.81338051569639</v>
       </c>
-      <c r="Q106" s="17">
+      <c r="Q106" s="21">
         <f t="shared" si="18"/>
         <v>2.97275495851142</v>
       </c>
       <c r="X106" s="4">
         <v>0</v>
       </c>
-      <c r="Y106" s="16" t="s">
+      <c r="Y106" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z106" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA106" s="17">
+      <c r="Z106" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA106" s="21">
         <v>5</v>
       </c>
-      <c r="AB106" s="17">
+      <c r="AB106" s="21">
         <v>5</v>
       </c>
-      <c r="AC106" s="17">
+      <c r="AC106" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="107" spans="3:29">
-      <c r="C107" s="16" t="s">
+      <c r="C107" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D107" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="E107" s="17">
+      <c r="D107" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E107" s="21">
         <v>7.47097081798084</v>
       </c>
-      <c r="F107" s="18">
+      <c r="F107" s="22">
         <v>5.67297781871776</v>
       </c>
-      <c r="G107" s="18">
+      <c r="G107" s="22">
         <v>9.29996366985999</v>
       </c>
       <c r="L107" s="4">
         <v>2050</v>
       </c>
-      <c r="M107" s="16" t="s">
+      <c r="M107" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N107" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="O107" s="17">
+      <c r="N107" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="O107" s="21">
         <f t="shared" si="16"/>
         <v>2.338413866028</v>
       </c>
-      <c r="P107" s="17">
+      <c r="P107" s="21">
         <f t="shared" si="17"/>
         <v>1.77564205725866</v>
       </c>
-      <c r="Q107" s="17">
+      <c r="Q107" s="21">
         <f t="shared" si="18"/>
         <v>2.91088862866618</v>
       </c>
       <c r="X107" s="4">
         <v>0</v>
       </c>
-      <c r="Y107" s="16" t="s">
+      <c r="Y107" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z107" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="AA107" s="17">
+      <c r="Z107" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA107" s="21">
         <v>5</v>
       </c>
-      <c r="AB107" s="17">
+      <c r="AB107" s="21">
         <v>5</v>
       </c>
-      <c r="AC107" s="17">
+      <c r="AC107" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="108" spans="3:29">
-      <c r="C108" s="16" t="s">
+      <c r="C108" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D108" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="E108" s="17">
+      <c r="D108" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="E108" s="21">
         <v>7.51643520019651</v>
       </c>
-      <c r="F108" s="18">
+      <c r="F108" s="22">
         <v>5.70750058953574</v>
       </c>
-      <c r="G108" s="18">
+      <c r="G108" s="22">
         <v>9.35655836403832</v>
       </c>
       <c r="L108" s="4">
         <v>2050</v>
       </c>
-      <c r="M108" s="16" t="s">
+      <c r="M108" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N108" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="O108" s="17">
+      <c r="N108" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="O108" s="21">
         <f t="shared" si="16"/>
         <v>2.35264421766151</v>
       </c>
-      <c r="P108" s="17">
+      <c r="P108" s="21">
         <f t="shared" si="17"/>
         <v>1.78644768452469</v>
       </c>
-      <c r="Q108" s="17">
+      <c r="Q108" s="21">
         <f t="shared" si="18"/>
         <v>2.92860276794399</v>
       </c>
       <c r="X108" s="4">
         <v>0</v>
       </c>
-      <c r="Y108" s="16" t="s">
+      <c r="Y108" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z108" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="AA108" s="17">
+      <c r="Z108" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA108" s="21">
         <v>5</v>
       </c>
-      <c r="AB108" s="17">
+      <c r="AB108" s="21">
         <v>5</v>
       </c>
-      <c r="AC108" s="17">
+      <c r="AC108" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="109" spans="3:29">
-      <c r="C109" s="16" t="s">
+      <c r="C109" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D109" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="E109" s="17">
+      <c r="D109" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="E109" s="21">
         <v>7.55036263817244</v>
       </c>
-      <c r="F109" s="18">
+      <c r="F109" s="22">
         <v>5.73326293294031</v>
       </c>
-      <c r="G109" s="18">
+      <c r="G109" s="22">
         <v>9.39879167280766</v>
       </c>
       <c r="L109" s="4">
         <v>2050</v>
       </c>
-      <c r="M109" s="16" t="s">
+      <c r="M109" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N109" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="O109" s="17">
+      <c r="N109" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="O109" s="21">
         <f t="shared" si="16"/>
         <v>2.36326350574797</v>
       </c>
-      <c r="P109" s="17">
+      <c r="P109" s="21">
         <f t="shared" si="17"/>
         <v>1.79451129801032</v>
       </c>
-      <c r="Q109" s="17">
+      <c r="Q109" s="21">
         <f t="shared" si="18"/>
         <v>2.9418217935888</v>
       </c>
       <c r="X109" s="4">
         <v>0</v>
       </c>
-      <c r="Y109" s="16" t="s">
+      <c r="Y109" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z109" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA109" s="17">
+      <c r="Z109" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA109" s="21">
         <v>5</v>
       </c>
-      <c r="AB109" s="17">
+      <c r="AB109" s="21">
         <v>5</v>
       </c>
-      <c r="AC109" s="17">
+      <c r="AC109" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="110" spans="3:29">
-      <c r="C110" s="16" t="s">
+      <c r="C110" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D110" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="E110" s="17">
+      <c r="D110" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="E110" s="21">
         <v>7.62975445836404</v>
       </c>
-      <c r="F110" s="18">
+      <c r="F110" s="22">
         <v>5.79354797347089</v>
       </c>
-      <c r="G110" s="18">
+      <c r="G110" s="22">
         <v>9.49761967575534</v>
       </c>
       <c r="L110" s="4">
         <v>2050</v>
       </c>
-      <c r="M110" s="16" t="s">
+      <c r="M110" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N110" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="O110" s="17">
+      <c r="N110" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="O110" s="21">
         <f t="shared" si="16"/>
         <v>2.38811314546794</v>
       </c>
-      <c r="P110" s="17">
+      <c r="P110" s="21">
         <f t="shared" si="17"/>
         <v>1.81338051569639</v>
       </c>
-      <c r="Q110" s="17">
+      <c r="Q110" s="21">
         <f t="shared" si="18"/>
         <v>2.97275495851142</v>
       </c>
       <c r="X110" s="4">
         <v>0</v>
       </c>
-      <c r="Y110" s="16" t="s">
+      <c r="Y110" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z110" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA110" s="17">
+      <c r="Z110" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA110" s="21">
         <v>5</v>
       </c>
-      <c r="AB110" s="17">
+      <c r="AB110" s="21">
         <v>5</v>
       </c>
-      <c r="AC110" s="17">
+      <c r="AC110" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="111" spans="3:29">
-      <c r="C111" s="16" t="s">
+      <c r="C111" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D111" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E111" s="17">
+      <c r="D111" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E111" s="21">
         <v>4.18384600835176</v>
       </c>
-      <c r="F111" s="18">
+      <c r="F111" s="22">
         <v>3.17694532056006</v>
       </c>
-      <c r="G111" s="18">
+      <c r="G111" s="22">
         <v>5.20810707442889</v>
       </c>
       <c r="L111" s="4">
         <v>2050</v>
       </c>
-      <c r="M111" s="16" t="s">
+      <c r="M111" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N111" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="O111" s="17">
+      <c r="N111" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="O111" s="21">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="P111" s="17">
+      <c r="P111" s="21">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="Q111" s="17">
+      <c r="Q111" s="21">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
       <c r="X111" s="4">
         <v>0</v>
       </c>
-      <c r="Y111" s="16" t="s">
+      <c r="Y111" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z111" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="AA111" s="17">
+      <c r="Z111" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA111" s="21">
         <v>5</v>
       </c>
-      <c r="AB111" s="17">
+      <c r="AB111" s="21">
         <v>5</v>
       </c>
-      <c r="AC111" s="17">
+      <c r="AC111" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="112" spans="3:29">
-      <c r="C112" s="16" t="s">
+      <c r="C112" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D112" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="E112" s="17">
+      <c r="D112" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="E112" s="21">
         <v>4.18384600835176</v>
       </c>
-      <c r="F112" s="18">
+      <c r="F112" s="22">
         <v>3.17694532056006</v>
       </c>
-      <c r="G112" s="18">
+      <c r="G112" s="22">
         <v>5.20810707442889</v>
       </c>
       <c r="L112" s="4">
         <v>2050</v>
       </c>
-      <c r="M112" s="16" t="s">
+      <c r="M112" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N112" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="O112" s="17">
+      <c r="N112" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="O112" s="21">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="P112" s="17">
+      <c r="P112" s="21">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="Q112" s="17">
+      <c r="Q112" s="21">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
       <c r="X112" s="4">
         <v>0</v>
       </c>
-      <c r="Y112" s="16" t="s">
+      <c r="Y112" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z112" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA112" s="17">
+      <c r="Z112" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="AA112" s="21">
         <v>5</v>
       </c>
-      <c r="AB112" s="17">
+      <c r="AB112" s="21">
         <v>5</v>
       </c>
-      <c r="AC112" s="17">
+      <c r="AC112" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="113" spans="3:29">
-      <c r="C113" s="16" t="s">
+      <c r="C113" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D113" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="E113" s="17">
+      <c r="D113" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="E113" s="21">
         <v>4.18384600835176</v>
       </c>
-      <c r="F113" s="18">
+      <c r="F113" s="22">
         <v>3.17694532056006</v>
       </c>
-      <c r="G113" s="18">
+      <c r="G113" s="22">
         <v>5.20810707442889</v>
       </c>
       <c r="L113" s="4">
         <v>2050</v>
       </c>
-      <c r="M113" s="16" t="s">
+      <c r="M113" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N113" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="O113" s="17">
+      <c r="N113" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="O113" s="21">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="P113" s="17">
+      <c r="P113" s="21">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="Q113" s="17">
+      <c r="Q113" s="21">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
       <c r="X113" s="4">
         <v>0</v>
       </c>
-      <c r="Y113" s="16" t="s">
+      <c r="Y113" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z113" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA113" s="17">
+      <c r="Z113" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="AA113" s="21">
         <v>5</v>
       </c>
-      <c r="AB113" s="17">
+      <c r="AB113" s="21">
         <v>5</v>
       </c>
-      <c r="AC113" s="17">
+      <c r="AC113" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="114" spans="3:29">
-      <c r="C114" s="16" t="s">
+      <c r="C114" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D114" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="E114" s="17">
+      <c r="D114" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="E114" s="21">
         <v>4.18384600835176</v>
       </c>
-      <c r="F114" s="18">
+      <c r="F114" s="22">
         <v>3.17694532056006</v>
       </c>
-      <c r="G114" s="18">
+      <c r="G114" s="22">
         <v>5.20810707442889</v>
       </c>
       <c r="L114" s="4">
         <v>2050</v>
       </c>
-      <c r="M114" s="16" t="s">
+      <c r="M114" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N114" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="O114" s="17">
+      <c r="N114" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="O114" s="21">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="P114" s="17">
+      <c r="P114" s="21">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="Q114" s="17">
+      <c r="Q114" s="21">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
       <c r="X114" s="4">
         <v>0</v>
       </c>
-      <c r="Y114" s="16" t="s">
+      <c r="Y114" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z114" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="AA114" s="17">
+      <c r="Z114" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA114" s="21">
         <v>5</v>
       </c>
-      <c r="AB114" s="17">
+      <c r="AB114" s="21">
         <v>5</v>
       </c>
-      <c r="AC114" s="17">
+      <c r="AC114" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="115" spans="3:29">
-      <c r="C115" s="16" t="s">
+      <c r="C115" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D115" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="E115" s="17">
+      <c r="D115" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E115" s="21">
         <v>4.18384600835176</v>
       </c>
-      <c r="F115" s="18">
+      <c r="F115" s="22">
         <v>3.17694532056006</v>
       </c>
-      <c r="G115" s="18">
+      <c r="G115" s="22">
         <v>5.20810707442889</v>
       </c>
       <c r="L115" s="4">
         <v>2050</v>
       </c>
-      <c r="M115" s="16" t="s">
+      <c r="M115" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N115" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="O115" s="17">
+      <c r="N115" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="O115" s="21">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="P115" s="17">
+      <c r="P115" s="21">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="Q115" s="17">
+      <c r="Q115" s="21">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
       <c r="X115" s="4">
         <v>0</v>
       </c>
-      <c r="Y115" s="16" t="s">
+      <c r="Y115" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z115" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA115" s="17">
+      <c r="Z115" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA115" s="21">
         <v>5</v>
       </c>
-      <c r="AB115" s="17">
+      <c r="AB115" s="21">
         <v>5</v>
       </c>
-      <c r="AC115" s="17">
+      <c r="AC115" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="116" spans="3:29">
-      <c r="C116" s="16" t="s">
+      <c r="C116" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D116" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="E116" s="17">
+      <c r="D116" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="E116" s="21">
         <v>4.18384600835176</v>
       </c>
-      <c r="F116" s="18">
+      <c r="F116" s="22">
         <v>3.17694532056006</v>
       </c>
-      <c r="G116" s="18">
+      <c r="G116" s="22">
         <v>5.20810707442889</v>
       </c>
       <c r="L116" s="4">
         <v>2050</v>
       </c>
-      <c r="M116" s="16" t="s">
+      <c r="M116" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N116" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="O116" s="17">
+      <c r="N116" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="O116" s="21">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="P116" s="17">
+      <c r="P116" s="21">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="Q116" s="17">
+      <c r="Q116" s="21">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
       <c r="X116" s="4">
         <v>0</v>
       </c>
-      <c r="Y116" s="16" t="s">
+      <c r="Y116" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z116" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA116" s="17">
+      <c r="Z116" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA116" s="21">
         <v>5</v>
       </c>
-      <c r="AB116" s="17">
+      <c r="AB116" s="21">
         <v>5</v>
       </c>
-      <c r="AC116" s="17">
+      <c r="AC116" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="117" spans="3:29">
-      <c r="C117" s="16" t="s">
+      <c r="C117" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D117" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="E117" s="17">
+      <c r="D117" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="E117" s="21">
         <v>4.18384600835176</v>
       </c>
-      <c r="F117" s="18">
+      <c r="F117" s="22">
         <v>3.17694532056006</v>
       </c>
-      <c r="G117" s="18">
+      <c r="G117" s="22">
         <v>5.20810707442889</v>
       </c>
       <c r="L117" s="4">
         <v>2050</v>
       </c>
-      <c r="M117" s="16" t="s">
+      <c r="M117" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N117" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="O117" s="17">
+      <c r="N117" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="O117" s="21">
         <f t="shared" si="16"/>
         <v>1.3095438006141</v>
       </c>
-      <c r="P117" s="17">
+      <c r="P117" s="21">
         <f t="shared" si="17"/>
         <v>0.994383885335299</v>
       </c>
-      <c r="Q117" s="17">
+      <c r="Q117" s="21">
         <f t="shared" si="18"/>
         <v>1.63013751429624</v>
       </c>
       <c r="X117" s="4">
         <v>0</v>
       </c>
-      <c r="Y117" s="16" t="s">
+      <c r="Y117" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z117" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="AA117" s="17">
+      <c r="Z117" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA117" s="21">
         <v>5</v>
       </c>
-      <c r="AB117" s="17">
+      <c r="AB117" s="21">
         <v>5</v>
       </c>
-      <c r="AC117" s="17">
+      <c r="AC117" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="118" spans="3:29">
-      <c r="C118" s="16" t="s">
+      <c r="C118" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D118" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="E118" s="17">
+      <c r="D118" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E118" s="21">
         <v>3.56556266273643</v>
       </c>
-      <c r="F118" s="18">
+      <c r="F118" s="22">
         <v>2.70746042741341</v>
       </c>
-      <c r="G118" s="18">
+      <c r="G118" s="22">
         <v>4.4384597641857</v>
       </c>
       <c r="L118" s="4">
         <v>2050</v>
       </c>
-      <c r="M118" s="16" t="s">
+      <c r="M118" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N118" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="O118" s="17">
+      <c r="N118" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="O118" s="21">
         <f t="shared" si="16"/>
         <v>1.1160211134365</v>
       </c>
-      <c r="P118" s="17">
+      <c r="P118" s="21">
         <f t="shared" si="17"/>
         <v>0.847435113780397</v>
       </c>
-      <c r="Q118" s="17">
+      <c r="Q118" s="21">
         <f t="shared" si="18"/>
         <v>1.38923790619012</v>
       </c>
       <c r="X118" s="4">
         <v>0</v>
       </c>
-      <c r="Y118" s="16" t="s">
+      <c r="Y118" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z118" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="AA118" s="17">
+      <c r="Z118" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA118" s="21">
         <v>5</v>
       </c>
-      <c r="AB118" s="17">
+      <c r="AB118" s="21">
         <v>5</v>
       </c>
-      <c r="AC118" s="17">
+      <c r="AC118" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="119" spans="3:29">
-      <c r="C119" s="16" t="s">
+      <c r="C119" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D119" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="E119" s="17">
+      <c r="D119" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="E119" s="21">
         <v>3.60087708179809</v>
       </c>
-      <c r="F119" s="18">
+      <c r="F119" s="22">
         <v>2.73427597641857</v>
       </c>
-      <c r="G119" s="18">
+      <c r="G119" s="22">
         <v>4.48241960206338</v>
       </c>
       <c r="L119" s="4">
         <v>2050</v>
       </c>
-      <c r="M119" s="16" t="s">
+      <c r="M119" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N119" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="O119" s="17">
+      <c r="N119" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="O119" s="21">
         <f t="shared" si="16"/>
         <v>1.1270745266028</v>
       </c>
-      <c r="P119" s="17">
+      <c r="P119" s="21">
         <f t="shared" si="17"/>
         <v>0.855828380619012</v>
       </c>
-      <c r="Q119" s="17">
+      <c r="Q119" s="21">
         <f t="shared" si="18"/>
         <v>1.40299733544584</v>
       </c>
       <c r="X119" s="4">
         <v>0</v>
       </c>
-      <c r="Y119" s="16" t="s">
+      <c r="Y119" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z119" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="AA119" s="17">
+      <c r="Z119" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="AA119" s="21">
         <v>5</v>
       </c>
-      <c r="AB119" s="17">
+      <c r="AB119" s="21">
         <v>5</v>
       </c>
-      <c r="AC119" s="17">
+      <c r="AC119" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="120" spans="3:29">
-      <c r="C120" s="16" t="s">
+      <c r="C120" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D120" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="E120" s="17">
+      <c r="D120" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="E120" s="21">
         <v>3.56556266273643</v>
       </c>
-      <c r="F120" s="18">
+      <c r="F120" s="22">
         <v>2.70746042741341</v>
       </c>
-      <c r="G120" s="18">
+      <c r="G120" s="22">
         <v>4.4384597641857</v>
       </c>
       <c r="L120" s="4">
         <v>2050</v>
       </c>
-      <c r="M120" s="16" t="s">
+      <c r="M120" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N120" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="O120" s="17">
+      <c r="N120" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="O120" s="21">
         <f t="shared" si="16"/>
         <v>1.1160211134365</v>
       </c>
-      <c r="P120" s="17">
+      <c r="P120" s="21">
         <f t="shared" si="17"/>
         <v>0.847435113780397</v>
       </c>
-      <c r="Q120" s="17">
+      <c r="Q120" s="21">
         <f t="shared" si="18"/>
         <v>1.38923790619012</v>
       </c>
       <c r="X120" s="4">
         <v>0</v>
       </c>
-      <c r="Y120" s="16" t="s">
+      <c r="Y120" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z120" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA120" s="17">
+      <c r="Z120" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA120" s="21">
         <v>5</v>
       </c>
-      <c r="AB120" s="17">
+      <c r="AB120" s="21">
         <v>5</v>
       </c>
-      <c r="AC120" s="17">
+      <c r="AC120" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="121" spans="3:29">
-      <c r="C121" s="16" t="s">
+      <c r="C121" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D121" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="E121" s="17">
+      <c r="D121" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E121" s="21">
         <v>3.56645369688037</v>
       </c>
-      <c r="F121" s="18">
+      <c r="F121" s="22">
         <v>2.70813706705969</v>
       </c>
-      <c r="G121" s="18">
+      <c r="G121" s="22">
         <v>4.43956890198968</v>
       </c>
       <c r="L121" s="4">
         <v>2050</v>
       </c>
-      <c r="M121" s="16" t="s">
+      <c r="M121" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N121" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="O121" s="17">
+      <c r="N121" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="O121" s="21">
         <f t="shared" si="16"/>
         <v>1.11630000712356</v>
       </c>
-      <c r="P121" s="17">
+      <c r="P121" s="21">
         <f t="shared" si="17"/>
         <v>0.847646901989683</v>
       </c>
-      <c r="Q121" s="17">
+      <c r="Q121" s="21">
         <f t="shared" si="18"/>
         <v>1.38958506632277</v>
       </c>
       <c r="X121" s="4">
         <v>0</v>
       </c>
-      <c r="Y121" s="16" t="s">
+      <c r="Y121" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z121" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA121" s="17">
+      <c r="Z121" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA121" s="21">
         <v>5</v>
       </c>
-      <c r="AB121" s="17">
+      <c r="AB121" s="21">
         <v>5</v>
       </c>
-      <c r="AC121" s="17">
+      <c r="AC121" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="122" spans="3:29">
-      <c r="C122" s="16" t="s">
+      <c r="C122" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D122" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="E122" s="17">
+      <c r="D122" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E122" s="21">
         <v>3.56585961680177</v>
       </c>
-      <c r="F122" s="18">
+      <c r="F122" s="22">
         <v>2.70768592483419</v>
       </c>
-      <c r="G122" s="18">
+      <c r="G122" s="22">
         <v>4.43882940309506</v>
       </c>
       <c r="L122" s="4">
         <v>2050</v>
       </c>
-      <c r="M122" s="16" t="s">
+      <c r="M122" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N122" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="O122" s="17">
+      <c r="N122" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="O122" s="21">
         <f t="shared" si="16"/>
         <v>1.11611406005895</v>
       </c>
-      <c r="P122" s="17">
+      <c r="P122" s="21">
         <f t="shared" si="17"/>
         <v>0.847505694473101</v>
       </c>
-      <c r="Q122" s="17">
+      <c r="Q122" s="21">
         <f t="shared" si="18"/>
         <v>1.38935360316875</v>
       </c>
       <c r="X122" s="4">
         <v>0</v>
       </c>
-      <c r="Y122" s="16" t="s">
+      <c r="Y122" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z122" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA122" s="17">
+      <c r="Z122" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA122" s="21">
         <v>5</v>
       </c>
-      <c r="AB122" s="17">
+      <c r="AB122" s="21">
         <v>5</v>
       </c>
-      <c r="AC122" s="17">
+      <c r="AC122" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="123" spans="3:29">
-      <c r="C123" s="16" t="s">
+      <c r="C123" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D123" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="E123" s="17">
+      <c r="D123" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="E123" s="21">
         <v>3.56556266273643</v>
       </c>
-      <c r="F123" s="18">
+      <c r="F123" s="22">
         <v>2.70746042741341</v>
       </c>
-      <c r="G123" s="18">
+      <c r="G123" s="22">
         <v>4.4384597641857</v>
       </c>
       <c r="L123" s="4">
         <v>2050</v>
       </c>
-      <c r="M123" s="16" t="s">
+      <c r="M123" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N123" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="O123" s="17">
+      <c r="N123" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="O123" s="21">
         <f t="shared" si="16"/>
         <v>1.1160211134365</v>
       </c>
-      <c r="P123" s="17">
+      <c r="P123" s="21">
         <f t="shared" si="17"/>
         <v>0.847435113780397</v>
       </c>
-      <c r="Q123" s="17">
+      <c r="Q123" s="21">
         <f t="shared" si="18"/>
         <v>1.38923790619012</v>
       </c>
       <c r="X123" s="4">
         <v>0</v>
       </c>
-      <c r="Y123" s="16" t="s">
+      <c r="Y123" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z123" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA123" s="17">
+      <c r="Z123" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="AA123" s="21">
         <v>5</v>
       </c>
-      <c r="AB123" s="17">
+      <c r="AB123" s="21">
         <v>5</v>
       </c>
-      <c r="AC123" s="17">
+      <c r="AC123" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="124" spans="3:29">
-      <c r="C124" s="16" t="s">
+      <c r="C124" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D124" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="E124" s="17">
+      <c r="D124" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="E124" s="21">
         <v>3.56496890198968</v>
       </c>
-      <c r="F124" s="18">
+      <c r="F124" s="22">
         <v>2.70700957995578</v>
       </c>
-      <c r="G124" s="18">
+      <c r="G124" s="22">
         <v>4.43772063375092</v>
       </c>
       <c r="L124" s="4">
         <v>2050</v>
       </c>
-      <c r="M124" s="16" t="s">
+      <c r="M124" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="N124" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="O124" s="17">
+      <c r="N124" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="O124" s="21">
         <f t="shared" si="16"/>
         <v>1.11583526632277</v>
       </c>
-      <c r="P124" s="17">
+      <c r="P124" s="21">
         <f t="shared" si="17"/>
         <v>0.847293998526159</v>
       </c>
-      <c r="Q124" s="17">
+      <c r="Q124" s="21">
         <f t="shared" si="18"/>
         <v>1.38900655836404</v>
       </c>
       <c r="X124" s="4">
         <v>0</v>
       </c>
-      <c r="Y124" s="16" t="s">
+      <c r="Y124" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="Z124" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA124" s="17">
+      <c r="Z124" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA124" s="21">
         <v>5</v>
       </c>
-      <c r="AB124" s="17">
+      <c r="AB124" s="21">
         <v>5</v>
       </c>
-      <c r="AC124" s="17">
+      <c r="AC124" s="21">
         <v>5</v>
       </c>
     </row>
@@ -16266,7 +15368,7 @@
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -16278,25 +15380,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1" t="s">
         <v>168</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>169</v>
-      </c>
-      <c r="J1" t="s">
-        <v>170</v>
-      </c>
-      <c r="K1" t="s">
-        <v>171</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -16418,28 +15520,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -16547,7 +15649,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -16558,31 +15660,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -16690,7 +15792,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -16701,31 +15803,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -16833,7 +15935,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -16847,28 +15949,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -16976,7 +16078,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -16987,31 +16089,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -17119,7 +16221,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -17133,28 +16235,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -17262,7 +16364,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -17273,31 +16375,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -17405,7 +16507,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -17416,31 +16518,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -17548,7 +16650,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -17559,31 +16661,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -17691,7 +16793,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -17702,31 +16804,31 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -17834,7 +16936,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -17845,31 +16947,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -17977,7 +17079,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -17988,31 +17090,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -18120,7 +17222,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -18131,31 +17233,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -18263,7 +17365,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -18274,31 +17376,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -18406,7 +17508,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -18417,31 +17519,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -18549,7 +17651,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -18563,28 +17665,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -18692,7 +17794,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -18703,31 +17805,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G18" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -18835,7 +17937,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -18846,31 +17948,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -18978,7 +18080,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:47">
@@ -18989,31 +18091,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -19121,7 +18223,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:47">
@@ -19135,28 +18237,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -19264,7 +18366,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:47">
@@ -19275,31 +18377,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -19407,7 +18509,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:47">
@@ -19418,31 +18520,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -19550,7 +18652,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:47">
@@ -19564,28 +18666,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G24" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -19693,7 +18795,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:47">
@@ -19704,31 +18806,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G25" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -19836,7 +18938,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:47">
@@ -19847,31 +18949,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -19979,7 +19081,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -19990,31 +19092,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -20122,7 +19224,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -20133,31 +19235,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -20265,7 +19367,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -20279,28 +19381,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
+        <v>170</v>
+      </c>
+      <c r="E29" t="s">
+        <v>170</v>
+      </c>
+      <c r="F29" t="s">
+        <v>171</v>
+      </c>
+      <c r="G29" t="s">
         <v>172</v>
       </c>
-      <c r="E29" t="s">
-        <v>172</v>
-      </c>
-      <c r="F29" t="s">
-        <v>173</v>
-      </c>
-      <c r="G29" t="s">
-        <v>174</v>
-      </c>
       <c r="H29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L29">
         <v>0.99</v>
@@ -20408,7 +19510,7 @@
         <v>0.99</v>
       </c>
       <c r="AU29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -20419,31 +19521,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D30" t="s">
+        <v>170</v>
+      </c>
+      <c r="E30" t="s">
+        <v>170</v>
+      </c>
+      <c r="F30" t="s">
+        <v>171</v>
+      </c>
+      <c r="G30" t="s">
         <v>172</v>
       </c>
-      <c r="E30" t="s">
-        <v>172</v>
-      </c>
-      <c r="F30" t="s">
-        <v>173</v>
-      </c>
-      <c r="G30" t="s">
-        <v>174</v>
-      </c>
       <c r="H30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L30">
         <v>0.58697</v>
@@ -20551,7 +19653,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -20562,31 +19664,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D31" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31" t="s">
+        <v>170</v>
+      </c>
+      <c r="F31" t="s">
+        <v>171</v>
+      </c>
+      <c r="G31" t="s">
         <v>172</v>
       </c>
-      <c r="E31" t="s">
-        <v>172</v>
-      </c>
-      <c r="F31" t="s">
-        <v>173</v>
-      </c>
-      <c r="G31" t="s">
-        <v>174</v>
-      </c>
       <c r="H31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L31">
         <v>0.58697</v>
@@ -20694,7 +19796,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -20708,28 +19810,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
+        <v>170</v>
+      </c>
+      <c r="E32" t="s">
+        <v>170</v>
+      </c>
+      <c r="F32" t="s">
+        <v>171</v>
+      </c>
+      <c r="G32" t="s">
         <v>172</v>
       </c>
-      <c r="E32" t="s">
-        <v>172</v>
-      </c>
-      <c r="F32" t="s">
-        <v>173</v>
-      </c>
-      <c r="G32" t="s">
-        <v>174</v>
-      </c>
       <c r="H32" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I32" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J32" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K32" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L32">
         <v>0.58697</v>
@@ -20837,7 +19939,7 @@
         <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:47">
@@ -20848,31 +19950,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D33" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33" t="s">
+        <v>170</v>
+      </c>
+      <c r="F33" t="s">
+        <v>171</v>
+      </c>
+      <c r="G33" t="s">
         <v>172</v>
       </c>
-      <c r="E33" t="s">
-        <v>172</v>
-      </c>
-      <c r="F33" t="s">
-        <v>173</v>
-      </c>
-      <c r="G33" t="s">
-        <v>174</v>
-      </c>
       <c r="H33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L33">
         <v>0.07207</v>
@@ -20980,7 +20082,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:47">
@@ -20994,28 +20096,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
+        <v>170</v>
+      </c>
+      <c r="E34" t="s">
+        <v>170</v>
+      </c>
+      <c r="F34" t="s">
+        <v>171</v>
+      </c>
+      <c r="G34" t="s">
         <v>172</v>
       </c>
-      <c r="E34" t="s">
-        <v>172</v>
-      </c>
-      <c r="F34" t="s">
-        <v>173</v>
-      </c>
-      <c r="G34" t="s">
-        <v>174</v>
-      </c>
       <c r="H34" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I34" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J34" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K34" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L34">
         <v>0.07207</v>
@@ -21123,7 +20225,7 @@
         <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:47">
@@ -21134,31 +20236,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D35" t="s">
+        <v>170</v>
+      </c>
+      <c r="E35" t="s">
+        <v>170</v>
+      </c>
+      <c r="F35" t="s">
+        <v>171</v>
+      </c>
+      <c r="G35" t="s">
         <v>172</v>
       </c>
-      <c r="E35" t="s">
-        <v>172</v>
-      </c>
-      <c r="F35" t="s">
-        <v>173</v>
-      </c>
-      <c r="G35" t="s">
-        <v>174</v>
-      </c>
       <c r="H35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -21266,7 +20368,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -21277,31 +20379,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D36" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" t="s">
+        <v>170</v>
+      </c>
+      <c r="F36" t="s">
+        <v>171</v>
+      </c>
+      <c r="G36" t="s">
         <v>172</v>
       </c>
-      <c r="E36" t="s">
-        <v>172</v>
-      </c>
-      <c r="F36" t="s">
-        <v>173</v>
-      </c>
-      <c r="G36" t="s">
-        <v>174</v>
-      </c>
       <c r="H36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L36">
         <v>0.08</v>
@@ -21409,7 +20511,7 @@
         <v>0.08</v>
       </c>
       <c r="AU36" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -21420,31 +20522,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D37" t="s">
+        <v>170</v>
+      </c>
+      <c r="E37" t="s">
+        <v>170</v>
+      </c>
+      <c r="F37" t="s">
+        <v>171</v>
+      </c>
+      <c r="G37" t="s">
         <v>172</v>
       </c>
-      <c r="E37" t="s">
-        <v>172</v>
-      </c>
-      <c r="F37" t="s">
-        <v>173</v>
-      </c>
-      <c r="G37" t="s">
-        <v>174</v>
-      </c>
       <c r="H37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L37">
         <v>0.08</v>
@@ -21552,7 +20654,7 @@
         <v>0.08</v>
       </c>
       <c r="AU37" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -21563,31 +20665,31 @@
         <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D38" t="s">
+        <v>170</v>
+      </c>
+      <c r="E38" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" t="s">
+        <v>171</v>
+      </c>
+      <c r="G38" t="s">
         <v>172</v>
       </c>
-      <c r="E38" t="s">
-        <v>172</v>
-      </c>
-      <c r="F38" t="s">
-        <v>173</v>
-      </c>
-      <c r="G38" t="s">
-        <v>174</v>
-      </c>
       <c r="H38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L38">
         <v>0.076</v>
@@ -21695,7 +20797,7 @@
         <v>0.076</v>
       </c>
       <c r="AU38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -21706,31 +20808,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E39" t="s">
+        <v>170</v>
+      </c>
+      <c r="F39" t="s">
+        <v>171</v>
+      </c>
+      <c r="G39" t="s">
         <v>172</v>
       </c>
-      <c r="E39" t="s">
-        <v>172</v>
-      </c>
-      <c r="F39" t="s">
-        <v>173</v>
-      </c>
-      <c r="G39" t="s">
-        <v>174</v>
-      </c>
       <c r="H39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L39">
         <v>0.0612</v>
@@ -21838,7 +20940,7 @@
         <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -21849,31 +20951,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D40" t="s">
+        <v>170</v>
+      </c>
+      <c r="E40" t="s">
+        <v>170</v>
+      </c>
+      <c r="F40" t="s">
+        <v>171</v>
+      </c>
+      <c r="G40" t="s">
         <v>172</v>
       </c>
-      <c r="E40" t="s">
-        <v>172</v>
-      </c>
-      <c r="F40" t="s">
-        <v>173</v>
-      </c>
-      <c r="G40" t="s">
-        <v>174</v>
-      </c>
       <c r="H40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L40">
         <v>0.527722806887128</v>
@@ -21981,7 +21083,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -21992,31 +21094,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D41" t="s">
+        <v>170</v>
+      </c>
+      <c r="E41" t="s">
+        <v>170</v>
+      </c>
+      <c r="F41" t="s">
+        <v>171</v>
+      </c>
+      <c r="G41" t="s">
         <v>172</v>
       </c>
-      <c r="E41" t="s">
-        <v>172</v>
-      </c>
-      <c r="F41" t="s">
-        <v>173</v>
-      </c>
-      <c r="G41" t="s">
-        <v>174</v>
-      </c>
       <c r="H41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L41">
         <v>0.527722806887128</v>
@@ -22124,7 +21226,7 @@
         <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -22135,31 +21237,31 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D42" t="s">
+        <v>170</v>
+      </c>
+      <c r="E42" t="s">
+        <v>170</v>
+      </c>
+      <c r="F42" t="s">
+        <v>171</v>
+      </c>
+      <c r="G42" t="s">
         <v>172</v>
       </c>
-      <c r="E42" t="s">
-        <v>172</v>
-      </c>
-      <c r="F42" t="s">
-        <v>173</v>
-      </c>
-      <c r="G42" t="s">
-        <v>174</v>
-      </c>
       <c r="H42" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I42" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J42" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K42" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L42">
         <v>1.16513217002889</v>
@@ -22267,7 +21369,7 @@
         <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -22278,31 +21380,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D43" t="s">
+        <v>170</v>
+      </c>
+      <c r="E43" t="s">
+        <v>170</v>
+      </c>
+      <c r="F43" t="s">
+        <v>171</v>
+      </c>
+      <c r="G43" t="s">
         <v>172</v>
       </c>
-      <c r="E43" t="s">
-        <v>172</v>
-      </c>
-      <c r="F43" t="s">
-        <v>173</v>
-      </c>
-      <c r="G43" t="s">
-        <v>174</v>
-      </c>
       <c r="H43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L43">
         <v>0.466052868011556</v>
@@ -22410,7 +21512,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -22424,28 +21526,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
+        <v>170</v>
+      </c>
+      <c r="E44" t="s">
+        <v>170</v>
+      </c>
+      <c r="F44" t="s">
+        <v>171</v>
+      </c>
+      <c r="G44" t="s">
         <v>172</v>
       </c>
-      <c r="E44" t="s">
-        <v>172</v>
-      </c>
-      <c r="F44" t="s">
-        <v>173</v>
-      </c>
-      <c r="G44" t="s">
-        <v>174</v>
-      </c>
       <c r="H44" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I44" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J44" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K44" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L44">
         <v>0.466052868011556</v>
@@ -22553,7 +21655,7 @@
         <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -22564,31 +21666,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D45" t="s">
+        <v>170</v>
+      </c>
+      <c r="E45" t="s">
+        <v>170</v>
+      </c>
+      <c r="F45" t="s">
+        <v>171</v>
+      </c>
+      <c r="G45" t="s">
         <v>172</v>
       </c>
-      <c r="E45" t="s">
-        <v>172</v>
-      </c>
-      <c r="F45" t="s">
-        <v>173</v>
-      </c>
-      <c r="G45" t="s">
-        <v>174</v>
-      </c>
       <c r="H45" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I45" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J45" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K45" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L45">
         <v>0.475531491178995</v>
@@ -22696,7 +21798,7 @@
         <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -22707,31 +21809,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D46" t="s">
+        <v>170</v>
+      </c>
+      <c r="E46" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" t="s">
+        <v>171</v>
+      </c>
+      <c r="G46" t="s">
         <v>172</v>
       </c>
-      <c r="E46" t="s">
-        <v>172</v>
-      </c>
-      <c r="F46" t="s">
-        <v>173</v>
-      </c>
-      <c r="G46" t="s">
-        <v>174</v>
-      </c>
       <c r="H46" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I46" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J46" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K46" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -22839,7 +21941,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -22850,31 +21952,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D47" t="s">
+        <v>170</v>
+      </c>
+      <c r="E47" t="s">
+        <v>170</v>
+      </c>
+      <c r="F47" t="s">
+        <v>171</v>
+      </c>
+      <c r="G47" t="s">
         <v>172</v>
       </c>
-      <c r="E47" t="s">
-        <v>172</v>
-      </c>
-      <c r="F47" t="s">
-        <v>173</v>
-      </c>
-      <c r="G47" t="s">
-        <v>174</v>
-      </c>
       <c r="H47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -22982,7 +22084,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -22996,28 +22098,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
+        <v>170</v>
+      </c>
+      <c r="E48" t="s">
+        <v>170</v>
+      </c>
+      <c r="F48" t="s">
+        <v>171</v>
+      </c>
+      <c r="G48" t="s">
         <v>172</v>
       </c>
-      <c r="E48" t="s">
-        <v>172</v>
-      </c>
-      <c r="F48" t="s">
-        <v>173</v>
-      </c>
-      <c r="G48" t="s">
-        <v>174</v>
-      </c>
       <c r="H48" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I48" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J48" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K48" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -23125,7 +22227,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -23136,31 +22238,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D49" t="s">
+        <v>170</v>
+      </c>
+      <c r="E49" t="s">
+        <v>170</v>
+      </c>
+      <c r="F49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G49" t="s">
         <v>172</v>
       </c>
-      <c r="E49" t="s">
-        <v>172</v>
-      </c>
-      <c r="F49" t="s">
-        <v>173</v>
-      </c>
-      <c r="G49" t="s">
-        <v>174</v>
-      </c>
       <c r="H49" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I49" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J49" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K49" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -23268,7 +22370,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -23279,31 +22381,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D50" t="s">
+        <v>170</v>
+      </c>
+      <c r="E50" t="s">
+        <v>170</v>
+      </c>
+      <c r="F50" t="s">
+        <v>171</v>
+      </c>
+      <c r="G50" t="s">
         <v>172</v>
       </c>
-      <c r="E50" t="s">
-        <v>172</v>
-      </c>
-      <c r="F50" t="s">
-        <v>173</v>
-      </c>
-      <c r="G50" t="s">
-        <v>174</v>
-      </c>
       <c r="H50" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I50" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J50" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K50" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -23411,7 +22513,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -23425,28 +22527,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
+        <v>170</v>
+      </c>
+      <c r="E51" t="s">
+        <v>170</v>
+      </c>
+      <c r="F51" t="s">
+        <v>171</v>
+      </c>
+      <c r="G51" t="s">
         <v>172</v>
       </c>
-      <c r="E51" t="s">
-        <v>172</v>
-      </c>
-      <c r="F51" t="s">
-        <v>173</v>
-      </c>
-      <c r="G51" t="s">
-        <v>174</v>
-      </c>
       <c r="H51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -23554,7 +22656,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -23565,31 +22667,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D52" t="s">
+        <v>170</v>
+      </c>
+      <c r="E52" t="s">
+        <v>170</v>
+      </c>
+      <c r="F52" t="s">
+        <v>171</v>
+      </c>
+      <c r="G52" t="s">
         <v>172</v>
       </c>
-      <c r="E52" t="s">
-        <v>172</v>
-      </c>
-      <c r="F52" t="s">
-        <v>173</v>
-      </c>
-      <c r="G52" t="s">
-        <v>174</v>
-      </c>
       <c r="H52" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I52" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J52" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K52" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L52">
         <v>0.745426473864409</v>
@@ -23697,7 +22799,7 @@
         <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" spans="1:47">
@@ -23708,31 +22810,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D53" t="s">
+        <v>170</v>
+      </c>
+      <c r="E53" t="s">
+        <v>170</v>
+      </c>
+      <c r="F53" t="s">
+        <v>171</v>
+      </c>
+      <c r="G53" t="s">
         <v>172</v>
       </c>
-      <c r="E53" t="s">
-        <v>172</v>
-      </c>
-      <c r="F53" t="s">
-        <v>173</v>
-      </c>
-      <c r="G53" t="s">
-        <v>174</v>
-      </c>
       <c r="H53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L53">
         <v>0.372713236932204</v>
@@ -23840,7 +22942,7 @@
         <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:47">
@@ -23851,31 +22953,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D54" t="s">
+        <v>170</v>
+      </c>
+      <c r="E54" t="s">
+        <v>170</v>
+      </c>
+      <c r="F54" t="s">
+        <v>171</v>
+      </c>
+      <c r="G54" t="s">
         <v>172</v>
       </c>
-      <c r="E54" t="s">
-        <v>172</v>
-      </c>
-      <c r="F54" t="s">
-        <v>173</v>
-      </c>
-      <c r="G54" t="s">
-        <v>174</v>
-      </c>
       <c r="H54" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I54" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J54" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K54" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L54">
         <v>0.440757335287194</v>
@@ -23983,7 +23085,7 @@
         <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:47">
@@ -23994,31 +23096,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D55" t="s">
+        <v>170</v>
+      </c>
+      <c r="E55" t="s">
+        <v>170</v>
+      </c>
+      <c r="F55" t="s">
+        <v>171</v>
+      </c>
+      <c r="G55" t="s">
         <v>172</v>
       </c>
-      <c r="E55" t="s">
-        <v>172</v>
-      </c>
-      <c r="F55" t="s">
-        <v>173</v>
-      </c>
-      <c r="G55" t="s">
-        <v>174</v>
-      </c>
       <c r="H55" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I55" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J55" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K55" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L55">
         <v>0.329484430322726</v>
@@ -24126,7 +23228,7 @@
         <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
-  <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\KiNESYS_BattCircularity-main\SubRes_Tmpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E4A0E2-2C5D-4736-8117-28B0F8B1E850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr codeName="ThisWorkbook" updateLinks="never"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="18340" windowHeight="8720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TechSelection" sheetId="21" r:id="rId1"/>
@@ -43,18 +37,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>xli9</author>
   </authors>
   <commentList>
-    <comment ref="D101" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="D101" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Times New Roman"/>
+            <charset val="134"/>
           </rPr>
           <t>xli9:</t>
         </r>
@@ -62,6 +57,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Times New Roman"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 Bca its cap with unit of GW, which means this block defines how many costs for recycling 1Gwh of EV-Bat so do not need to multiplyy ktonne/GWh</t>
@@ -420,12 +416,6 @@
     <t>Trd_lcv_dsl</t>
   </si>
   <si>
-    <t>year2</t>
-  </si>
-  <si>
-    <t>NCAP_COST</t>
-  </si>
-  <si>
     <t>tempering the Eff improvement in smaller Evs</t>
   </si>
   <si>
@@ -487,6 +477,9 @@
   </si>
   <si>
     <t>*According to BloomBerg that ~2.5times more demand in 2024 vs. 2017 [means that 2.5 times higher demand every seven years] [https://about.bnef.com/blog/lithium-ion-battery-pack-prices-see-largest-drop-since-2017-falling-to-115-per-kilowatt-hour-bloombergnef/]; and a 18% learning rate also from Bloomberg</t>
+  </si>
+  <si>
+    <t>NCAP_COST</t>
   </si>
   <si>
     <t>PyroRecy-LFP</t>
@@ -573,6 +566,9 @@
     <t>sow</t>
   </si>
   <si>
+    <t>year2</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
@@ -648,12 +644,16 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* \-??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="0.0"/>
+    <numFmt numFmtId="179" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="29">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -696,21 +696,169 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -731,24 +879,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="3" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
+        <fgColor theme="3" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -784,64 +1112,349 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="49" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="3" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="49" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="3" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="9" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="49" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="5" borderId="1" xfId="49" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="49" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="52">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="Normal 3 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal 10" xfId="49"/>
+    <cellStyle name="Normal 3" xfId="50"/>
+    <cellStyle name="Normal 3 2" xfId="51"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="IEA Data"/>
@@ -954,7 +1567,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="New Microsoft Excel Worksheet"/>
@@ -1251,42 +1864,41 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AA281"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="9.13636363636364" defaultRowHeight="11.5"/>
   <cols>
     <col min="1" max="1" width="15" style="25" customWidth="1"/>
-    <col min="2" max="2" width="8.86328125" style="25" customWidth="1"/>
-    <col min="3" max="3" width="4.73046875" style="25" customWidth="1"/>
-    <col min="4" max="4" width="8.86328125" style="25" customWidth="1"/>
-    <col min="5" max="5" width="4.3984375" style="25" customWidth="1"/>
-    <col min="6" max="6" width="4.265625" style="25" customWidth="1"/>
-    <col min="7" max="7" width="4.3984375" style="25" customWidth="1"/>
-    <col min="8" max="8" width="4.59765625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="8.86363636363636" style="25" customWidth="1"/>
+    <col min="3" max="3" width="4.72727272727273" style="25" customWidth="1"/>
+    <col min="4" max="4" width="8.86363636363636" style="25" customWidth="1"/>
+    <col min="5" max="5" width="4.4" style="25" customWidth="1"/>
+    <col min="6" max="6" width="4.26363636363636" style="25" customWidth="1"/>
+    <col min="7" max="7" width="4.4" style="25" customWidth="1"/>
+    <col min="8" max="8" width="4.6" style="25" customWidth="1"/>
     <col min="9" max="9" width="4" style="25" customWidth="1"/>
-    <col min="10" max="10" width="4.3984375" style="25" customWidth="1"/>
-    <col min="11" max="11" width="4.59765625" style="25" customWidth="1"/>
-    <col min="12" max="12" width="4.3984375" style="25" customWidth="1"/>
+    <col min="10" max="10" width="4.4" style="25" customWidth="1"/>
+    <col min="11" max="11" width="4.6" style="25" customWidth="1"/>
+    <col min="12" max="12" width="4.4" style="25" customWidth="1"/>
     <col min="13" max="13" width="4" style="25" customWidth="1"/>
-    <col min="14" max="14" width="4.265625" style="25" customWidth="1"/>
-    <col min="15" max="16" width="4.3984375" style="25" customWidth="1"/>
-    <col min="17" max="18" width="4.59765625" style="25" customWidth="1"/>
-    <col min="19" max="19" width="4.3984375" style="25" customWidth="1"/>
+    <col min="14" max="14" width="4.26363636363636" style="25" customWidth="1"/>
+    <col min="15" max="16" width="4.4" style="25" customWidth="1"/>
+    <col min="17" max="18" width="4.6" style="25" customWidth="1"/>
+    <col min="19" max="19" width="4.4" style="25" customWidth="1"/>
     <col min="20" max="20" width="5" style="25" customWidth="1"/>
-    <col min="21" max="21" width="11.73046875" style="25" customWidth="1"/>
-    <col min="22" max="22" width="10.73046875" style="25" customWidth="1"/>
-    <col min="23" max="23" width="13.1328125" style="25" customWidth="1"/>
-    <col min="24" max="259" width="11.3984375" style="25" customWidth="1"/>
-    <col min="260" max="16384" width="9.1328125" style="25"/>
+    <col min="21" max="21" width="11.7272727272727" style="25" customWidth="1"/>
+    <col min="22" max="22" width="10.7272727272727" style="25" customWidth="1"/>
+    <col min="23" max="23" width="13.1363636363636" style="25" customWidth="1"/>
+    <col min="24" max="259" width="11.4" style="25" customWidth="1"/>
+    <col min="260" max="16384" width="9.13636363636364" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="12.75">
+    <row r="1" ht="12.5" spans="1:21">
       <c r="A1"/>
       <c r="B1"/>
       <c r="C1"/>
@@ -1309,7 +1921,7 @@
       <c r="T1"/>
       <c r="U1"/>
     </row>
-    <row r="2" spans="1:27" ht="12.75">
+    <row r="2" ht="12.5" spans="1:21">
       <c r="A2"/>
       <c r="B2"/>
       <c r="C2"/>
@@ -1332,7 +1944,7 @@
       <c r="T2"/>
       <c r="U2"/>
     </row>
-    <row r="3" spans="1:27" ht="12.75">
+    <row r="3" ht="12.5" spans="1:27">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1363,7 +1975,7 @@
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
     </row>
-    <row r="4" spans="1:27" ht="12.75">
+    <row r="4" ht="12.5" spans="1:27">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1396,7 +2008,7 @@
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
     </row>
-    <row r="5" spans="1:27" ht="12.75">
+    <row r="5" ht="12.5" spans="1:27">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1429,7 +2041,7 @@
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
     </row>
-    <row r="6" spans="1:27" ht="12.75">
+    <row r="6" ht="12.5" spans="1:27">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1462,7 +2074,7 @@
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
     </row>
-    <row r="7" spans="1:27" ht="12.75">
+    <row r="7" ht="12.5" spans="1:27">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1495,7 +2107,7 @@
       <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
     </row>
-    <row r="8" spans="1:27" ht="12.75">
+    <row r="8" ht="12.5" spans="1:27">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1528,7 +2140,7 @@
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
     </row>
-    <row r="9" spans="1:27" ht="12.75">
+    <row r="9" ht="12.5" spans="1:27">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1561,7 +2173,7 @@
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
     </row>
-    <row r="10" spans="1:27" ht="12.75">
+    <row r="10" ht="12.5" spans="1:27">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1594,7 +2206,7 @@
       <c r="Z10" s="4"/>
       <c r="AA10" s="4"/>
     </row>
-    <row r="11" spans="1:27" ht="12.75">
+    <row r="11" ht="12.5" spans="1:27">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1627,7 +2239,7 @@
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
     </row>
-    <row r="12" spans="1:27" ht="12.75">
+    <row r="12" ht="12.5" spans="1:27">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1660,7 +2272,7 @@
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
     </row>
-    <row r="13" spans="1:27" ht="12.75">
+    <row r="13" ht="12.5" spans="1:27">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1693,7 +2305,7 @@
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
     </row>
-    <row r="14" spans="1:27" ht="12.75">
+    <row r="14" ht="12.5" spans="1:27">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1726,7 +2338,7 @@
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
     </row>
-    <row r="15" spans="1:27" ht="12.75">
+    <row r="15" ht="12.5" spans="1:27">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1759,7 +2371,7 @@
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
     </row>
-    <row r="16" spans="1:27" ht="12.75">
+    <row r="16" ht="12.5" spans="1:27">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1792,7 +2404,7 @@
       <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
     </row>
-    <row r="17" spans="1:27" ht="12.75">
+    <row r="17" ht="12.5" spans="1:27">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1825,7 +2437,7 @@
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
     </row>
-    <row r="18" spans="1:27" ht="12.75">
+    <row r="18" ht="12.5" spans="1:27">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1858,7 +2470,7 @@
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
     </row>
-    <row r="19" spans="1:27" ht="12.75">
+    <row r="19" ht="12.5" spans="1:27">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1891,7 +2503,7 @@
       <c r="Z19" s="4"/>
       <c r="AA19" s="4"/>
     </row>
-    <row r="20" spans="1:27" ht="12.75">
+    <row r="20" ht="12.5" spans="1:27">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1924,7 +2536,7 @@
       <c r="Z20" s="4"/>
       <c r="AA20" s="4"/>
     </row>
-    <row r="21" spans="1:27" ht="12.75">
+    <row r="21" ht="12.5" spans="1:27">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1957,7 +2569,7 @@
       <c r="Z21" s="4"/>
       <c r="AA21" s="4"/>
     </row>
-    <row r="22" spans="1:27" ht="12.75">
+    <row r="22" ht="12.5" spans="1:27">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1990,7 +2602,7 @@
       <c r="Z22" s="4"/>
       <c r="AA22" s="4"/>
     </row>
-    <row r="23" spans="1:27" ht="12.75">
+    <row r="23" ht="12.5" spans="1:27">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -2023,7 +2635,7 @@
       <c r="Z23" s="4"/>
       <c r="AA23" s="4"/>
     </row>
-    <row r="24" spans="1:27" ht="12.75">
+    <row r="24" ht="12.5" spans="1:27">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2056,7 +2668,7 @@
       <c r="Z24" s="4"/>
       <c r="AA24" s="4"/>
     </row>
-    <row r="25" spans="1:27" ht="12.75">
+    <row r="25" ht="12.5" spans="1:27">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -2089,7 +2701,7 @@
       <c r="Z25" s="4"/>
       <c r="AA25" s="4"/>
     </row>
-    <row r="26" spans="1:27" ht="12.75">
+    <row r="26" ht="12.5" spans="1:27">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2122,7 +2734,7 @@
       <c r="Z26" s="4"/>
       <c r="AA26" s="4"/>
     </row>
-    <row r="27" spans="1:27" ht="12.75">
+    <row r="27" ht="12.5" spans="1:27">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -2155,7 +2767,7 @@
       <c r="Z27" s="4"/>
       <c r="AA27" s="4"/>
     </row>
-    <row r="28" spans="1:27" ht="12.75">
+    <row r="28" ht="12.5" spans="1:27">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -2188,7 +2800,7 @@
       <c r="Z28" s="4"/>
       <c r="AA28" s="4"/>
     </row>
-    <row r="29" spans="1:27" ht="12.75">
+    <row r="29" ht="12.5" spans="1:27">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2221,7 +2833,7 @@
       <c r="Z29" s="4"/>
       <c r="AA29" s="4"/>
     </row>
-    <row r="30" spans="1:27" ht="12.75">
+    <row r="30" ht="12.5" spans="1:27">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -2249,7 +2861,7 @@
       <c r="Z30" s="4"/>
       <c r="AA30" s="4"/>
     </row>
-    <row r="31" spans="1:27" ht="12.75">
+    <row r="31" ht="12.5" spans="1:27">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -2277,7 +2889,7 @@
       <c r="Z31" s="4"/>
       <c r="AA31" s="4"/>
     </row>
-    <row r="32" spans="1:27" ht="12.75">
+    <row r="32" ht="12.5" spans="1:27">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -2305,7 +2917,7 @@
       <c r="Z32" s="4"/>
       <c r="AA32" s="4"/>
     </row>
-    <row r="33" spans="1:27" ht="12.75">
+    <row r="33" ht="12.5" spans="1:27">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -2333,7 +2945,7 @@
       <c r="Z33" s="4"/>
       <c r="AA33" s="4"/>
     </row>
-    <row r="34" spans="1:27" ht="12.75">
+    <row r="34" ht="12.5" spans="1:27">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -2361,7 +2973,7 @@
       <c r="Z34" s="4"/>
       <c r="AA34" s="4"/>
     </row>
-    <row r="35" spans="1:27" ht="12.75">
+    <row r="35" ht="12.5" spans="1:27">
       <c r="A35" s="25" t="s">
         <v>34</v>
       </c>
@@ -2389,7 +3001,7 @@
       <c r="Z35" s="4"/>
       <c r="AA35" s="4"/>
     </row>
-    <row r="36" spans="1:27" ht="12.75">
+    <row r="36" ht="12.5" spans="1:27">
       <c r="A36" s="25" t="s">
         <v>35</v>
       </c>
@@ -2417,7 +3029,7 @@
       <c r="Z36" s="4"/>
       <c r="AA36" s="4"/>
     </row>
-    <row r="37" spans="1:27" ht="12.75">
+    <row r="37" ht="12.5" spans="1:27">
       <c r="A37" s="25" t="s">
         <v>36</v>
       </c>
@@ -2445,7 +3057,7 @@
       <c r="Z37" s="4"/>
       <c r="AA37" s="4"/>
     </row>
-    <row r="38" spans="1:27" ht="12.75">
+    <row r="38" ht="12.5" spans="1:27">
       <c r="A38" s="25" t="s">
         <v>37</v>
       </c>
@@ -2473,7 +3085,7 @@
       <c r="Z38" s="4"/>
       <c r="AA38" s="4"/>
     </row>
-    <row r="39" spans="1:27" ht="12.75">
+    <row r="39" ht="12.5" spans="1:27">
       <c r="A39" s="25" t="s">
         <v>38</v>
       </c>
@@ -2501,7 +3113,7 @@
       <c r="Z39" s="4"/>
       <c r="AA39" s="4"/>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="8:27">
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -2523,7 +3135,7 @@
       <c r="Z40" s="4"/>
       <c r="AA40" s="4"/>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="8:27">
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
@@ -2545,7 +3157,7 @@
       <c r="Z41" s="4"/>
       <c r="AA41" s="4"/>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="8:27">
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -2567,7 +3179,7 @@
       <c r="Z42" s="4"/>
       <c r="AA42" s="4"/>
     </row>
-    <row r="43" spans="1:27">
+    <row r="43" spans="8:27">
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
@@ -2589,7 +3201,7 @@
       <c r="Z43" s="4"/>
       <c r="AA43" s="4"/>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="8:27">
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -2611,7 +3223,7 @@
       <c r="Z44" s="4"/>
       <c r="AA44" s="4"/>
     </row>
-    <row r="45" spans="1:27">
+    <row r="45" spans="8:27">
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
@@ -2633,7 +3245,7 @@
       <c r="Z45" s="4"/>
       <c r="AA45" s="4"/>
     </row>
-    <row r="46" spans="1:27">
+    <row r="46" spans="8:27">
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -2655,7 +3267,7 @@
       <c r="Z46" s="4"/>
       <c r="AA46" s="4"/>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="8:27">
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
@@ -2677,7 +3289,7 @@
       <c r="Z47" s="4"/>
       <c r="AA47" s="4"/>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="8:27">
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
@@ -7827,47 +8439,48 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A2:DB124"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
-    <col min="2" max="2" width="21.3984375" customWidth="1"/>
-    <col min="3" max="3" width="12.73046875" customWidth="1"/>
-    <col min="4" max="5" width="22.06640625" customWidth="1"/>
+    <col min="2" max="2" width="21.4" customWidth="1"/>
+    <col min="3" max="3" width="12.7272727272727" customWidth="1"/>
+    <col min="4" max="5" width="22.0636363636364" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="9" width="7.1328125" customWidth="1"/>
-    <col min="10" max="10" width="10.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.265625" customWidth="1"/>
-    <col min="12" max="12" width="15.53125" customWidth="1"/>
-    <col min="13" max="18" width="7.1328125" customWidth="1"/>
-    <col min="19" max="19" width="12.73046875" customWidth="1"/>
-    <col min="20" max="20" width="8.59765625" customWidth="1"/>
-    <col min="21" max="21" width="7.796875" customWidth="1"/>
-    <col min="22" max="24" width="7.1328125" customWidth="1"/>
-    <col min="25" max="25" width="9.53125" customWidth="1"/>
-    <col min="26" max="26" width="17.9296875" customWidth="1"/>
-    <col min="27" max="27" width="9.9296875" customWidth="1"/>
-    <col min="28" max="33" width="7.1328125" customWidth="1"/>
+    <col min="8" max="9" width="7.13636363636364" customWidth="1"/>
+    <col min="10" max="10" width="10.6" customWidth="1"/>
+    <col min="11" max="11" width="11.2636363636364" customWidth="1"/>
+    <col min="12" max="12" width="15.5272727272727" customWidth="1"/>
+    <col min="13" max="18" width="7.13636363636364" customWidth="1"/>
+    <col min="19" max="19" width="12.7272727272727" customWidth="1"/>
+    <col min="20" max="20" width="8.6" customWidth="1"/>
+    <col min="21" max="21" width="7.8" customWidth="1"/>
+    <col min="22" max="24" width="7.13636363636364" customWidth="1"/>
+    <col min="25" max="25" width="9.52727272727273" customWidth="1"/>
+    <col min="26" max="26" width="17.9272727272727" customWidth="1"/>
+    <col min="27" max="27" width="9.92727272727273" customWidth="1"/>
+    <col min="28" max="33" width="7.13636363636364" customWidth="1"/>
     <col min="34" max="37" width="6" customWidth="1"/>
-    <col min="38" max="39" width="15.53125" customWidth="1"/>
-    <col min="40" max="40" width="22.59765625" customWidth="1"/>
-    <col min="41" max="41" width="13.59765625" customWidth="1"/>
+    <col min="38" max="39" width="15.5272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22.6" customWidth="1"/>
+    <col min="41" max="41" width="13.6" customWidth="1"/>
     <col min="42" max="43" width="6" customWidth="1"/>
-    <col min="44" max="44" width="8.46484375" customWidth="1"/>
-    <col min="45" max="45" width="10.33203125" customWidth="1"/>
+    <col min="44" max="44" width="8.46363636363636" customWidth="1"/>
+    <col min="45" max="45" width="10.3363636363636" customWidth="1"/>
     <col min="46" max="49" width="6" customWidth="1"/>
-    <col min="50" max="50" width="12.265625" customWidth="1"/>
-    <col min="51" max="51" width="13.59765625" customWidth="1"/>
+    <col min="50" max="50" width="12.2636363636364" customWidth="1"/>
+    <col min="51" max="51" width="13.6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23">
+    <row r="2" spans="2:11">
       <c r="B2" s="4" t="s">
         <v>39</v>
       </c>
@@ -7878,7 +8491,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="2:23">
+    <row r="3" spans="2:18">
       <c r="B3" s="5" t="s">
         <v>41</v>
       </c>
@@ -7986,7 +8599,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="2:23">
+    <row r="6" spans="11:13">
       <c r="K6" t="s">
         <v>69</v>
       </c>
@@ -7997,7 +8610,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="2:23">
+    <row r="7" spans="11:13">
       <c r="K7" t="s">
         <v>71</v>
       </c>
@@ -8008,7 +8621,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="2:23">
+    <row r="8" spans="2:13">
       <c r="B8" t="s">
         <v>73</v>
       </c>
@@ -8022,7 +8635,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="2:23">
+    <row r="9" spans="2:13">
       <c r="B9" t="s">
         <v>56</v>
       </c>
@@ -8054,7 +8667,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="2:23">
+    <row r="10" spans="2:13">
       <c r="B10" t="s">
         <v>81</v>
       </c>
@@ -8080,7 +8693,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="2:23">
+    <row r="11" spans="2:8">
       <c r="B11" t="s">
         <v>81</v>
       </c>
@@ -8100,7 +8713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:23">
+    <row r="12" spans="2:11">
       <c r="B12" t="s">
         <v>84</v>
       </c>
@@ -8117,7 +8730,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="2:23">
+    <row r="13" spans="2:14">
       <c r="B13" t="s">
         <v>88</v>
       </c>
@@ -8140,7 +8753,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="2:23">
+    <row r="14" spans="2:14">
       <c r="B14" t="s">
         <v>91</v>
       </c>
@@ -8166,7 +8779,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="2:23">
+    <row r="15" spans="11:14">
       <c r="K15" t="s">
         <v>93</v>
       </c>
@@ -8180,12 +8793,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="2:23">
+    <row r="16" spans="2:2">
       <c r="B16" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="2:50">
+    <row r="17" spans="2:7">
       <c r="B17" t="s">
         <v>57</v>
       </c>
@@ -8205,7 +8818,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="2:50">
+    <row r="18" spans="2:7">
       <c r="B18" s="26" t="s">
         <v>92</v>
       </c>
@@ -8225,12 +8838,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="2:50">
+    <row r="21" spans="3:3">
       <c r="C21" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="2:50">
+    <row r="22" spans="3:50">
       <c r="C22" t="s">
         <v>56</v>
       </c>
@@ -8422,7 +9035,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="2:50">
+    <row r="23" spans="3:50">
       <c r="C23" t="s">
         <v>50</v>
       </c>
@@ -8614,7 +9227,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="2:50">
+    <row r="24" spans="3:50">
       <c r="C24" t="s">
         <v>50</v>
       </c>
@@ -8806,7 +9419,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="2:50">
+    <row r="25" spans="3:50">
       <c r="C25" t="s">
         <v>50</v>
       </c>
@@ -8998,7 +9611,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="2:50">
+    <row r="26" spans="3:50">
       <c r="C26" t="s">
         <v>50</v>
       </c>
@@ -9190,7 +9803,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="2:50">
+    <row r="27" spans="3:50">
       <c r="C27" t="s">
         <v>50</v>
       </c>
@@ -9382,7 +9995,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="28" spans="2:50">
+    <row r="28" spans="3:50">
       <c r="C28" t="s">
         <v>50</v>
       </c>
@@ -9574,12 +10187,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="31" spans="2:50">
+    <row r="31" spans="3:3">
       <c r="C31" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="2:50">
+    <row r="32" spans="3:50">
       <c r="C32" t="s">
         <v>56</v>
       </c>
@@ -9771,7 +10384,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="2:53">
+    <row r="33" spans="3:53">
       <c r="C33" t="s">
         <v>61</v>
       </c>
@@ -9971,7 +10584,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="2:53">
+    <row r="34" spans="3:53">
       <c r="C34" t="s">
         <v>61</v>
       </c>
@@ -10171,7 +10784,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="35" spans="2:53">
+    <row r="35" spans="3:53">
       <c r="C35" t="s">
         <v>61</v>
       </c>
@@ -10371,7 +10984,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="2:53">
+    <row r="36" spans="3:53">
       <c r="C36" t="s">
         <v>61</v>
       </c>
@@ -10571,7 +11184,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="37" spans="2:53">
+    <row r="37" spans="3:53">
       <c r="C37" t="s">
         <v>61</v>
       </c>
@@ -10771,7 +11384,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="38" spans="2:53">
+    <row r="38" spans="3:53">
       <c r="C38" t="s">
         <v>61</v>
       </c>
@@ -10971,15 +11584,15 @@
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="2:53">
-      <c r="E45" s="27"/>
-    </row>
-    <row r="48" spans="2:53">
+    <row r="45" spans="5:5">
+      <c r="E45" s="7"/>
+    </row>
+    <row r="48" spans="2:2">
       <c r="B48" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="2:53">
+    <row r="49" spans="2:9">
       <c r="B49" t="s">
         <v>56</v>
       </c>
@@ -10993,29 +11606,29 @@
         <v>58</v>
       </c>
       <c r="I49" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="50" spans="2:53">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5">
       <c r="B50" t="s">
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D50" t="s">
         <v>66</v>
       </c>
       <c r="E50" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="53" spans="2:53">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
       <c r="B53" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="2:53">
+    <row r="54" spans="2:8">
       <c r="B54" t="s">
         <v>56</v>
       </c>
@@ -11023,7 +11636,7 @@
         <v>78</v>
       </c>
       <c r="D54" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E54" t="s">
         <v>98</v>
@@ -11032,13 +11645,13 @@
         <v>59</v>
       </c>
       <c r="G54" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H54" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="2:53">
+    <row r="55" spans="2:5">
       <c r="B55" t="s">
         <v>93</v>
       </c>
@@ -11046,21 +11659,21 @@
         <v>10</v>
       </c>
       <c r="D55" t="s">
+        <v>120</v>
+      </c>
+      <c r="E55" s="26" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8">
+      <c r="B56" t="s">
         <v>122</v>
-      </c>
-      <c r="E55" s="26" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="56" spans="2:53">
-      <c r="B56" t="s">
-        <v>124</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G56" t="s">
         <v>65</v>
@@ -11070,21 +11683,21 @@
         <v>AuxStoIN</v>
       </c>
     </row>
-    <row r="62" spans="2:53">
+    <row r="62" spans="8:8">
       <c r="H62" s="3"/>
     </row>
-    <row r="63" spans="2:53">
+    <row r="63" spans="8:53">
       <c r="H63" s="3"/>
       <c r="BA63" s="2"/>
     </row>
-    <row r="65" spans="1:106" s="1" customFormat="1">
+    <row r="65" s="1" customFormat="1" spans="1:106">
       <c r="A65" s="2"/>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C65" s="8"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -11147,17 +11760,17 @@
       <c r="DA65" s="3"/>
       <c r="DB65" s="3"/>
     </row>
-    <row r="66" spans="1:106" s="2" customFormat="1">
-      <c r="B66" s="7" t="s">
+    <row r="66" s="2" customFormat="1" spans="2:106">
+      <c r="B66" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="D66" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E66" s="9" t="s">
+      <c r="E66" s="8" t="s">
         <v>59</v>
       </c>
       <c r="F66" s="2" t="s">
@@ -11239,7 +11852,7 @@
         <v>29</v>
       </c>
       <c r="AF66" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AG66" s="2" t="s">
         <v>31</v>
@@ -11285,18 +11898,18 @@
         <v>44</v>
       </c>
     </row>
-    <row r="67" spans="1:106" s="2" customFormat="1" ht="14.25">
+    <row r="67" s="2" customFormat="1" ht="14.5" spans="2:106">
       <c r="B67" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E67" s="9" t="s">
         <v>127</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D67" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>129</v>
       </c>
       <c r="F67" s="2">
         <f t="shared" ref="F67:L67" si="2">D77/1000</f>
@@ -11438,16 +12051,16 @@
       <c r="CT67" s="20"/>
       <c r="CU67" s="20"/>
       <c r="CW67" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="CX67" t="s">
         <v>68</v>
       </c>
       <c r="CY67" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="CZ67" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="DA67" s="24">
         <v>0</v>
@@ -11456,18 +12069,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:106" s="2" customFormat="1" ht="14.25">
+    <row r="68" s="2" customFormat="1" ht="14.5" spans="2:106">
       <c r="B68" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C68" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C68" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D68" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E68" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>130</v>
       </c>
       <c r="F68" s="2">
         <f t="shared" ref="F68:M68" si="4">D78/1000</f>
@@ -11610,16 +12223,16 @@
       <c r="CT68" s="20"/>
       <c r="CU68" s="20"/>
       <c r="CW68" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="CX68" t="s">
         <v>68</v>
       </c>
       <c r="CY68" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="CZ68" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="CZ68" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="DA68" s="24">
         <v>0</v>
@@ -11628,18 +12241,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:106" s="2" customFormat="1" ht="14.25">
+    <row r="69" s="2" customFormat="1" ht="14.5" spans="2:106">
       <c r="B69" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C69" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C69" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D69" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>131</v>
+      <c r="D69" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="F69" s="2">
         <f t="shared" ref="F69:M69" si="6">D79/1000</f>
@@ -11782,16 +12395,16 @@
       <c r="CT69" s="20"/>
       <c r="CU69" s="20"/>
       <c r="CW69" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="CX69" t="s">
         <v>68</v>
       </c>
       <c r="CY69" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="CZ69" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="DA69" s="24">
         <v>0</v>
@@ -11800,18 +12413,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:106" s="2" customFormat="1" ht="14.25">
+    <row r="70" s="2" customFormat="1" ht="14.5" spans="2:106">
       <c r="B70" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C70" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C70" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="8" t="s">
-        <v>128</v>
+      <c r="D70" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F70" s="12">
         <f t="shared" ref="F70:M70" si="8">D80/1000</f>
@@ -11953,16 +12566,16 @@
       <c r="CT70" s="20"/>
       <c r="CU70" s="20"/>
       <c r="CW70" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="CX70" t="s">
         <v>68</v>
       </c>
       <c r="CY70" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="CZ70" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="DA70" s="24">
         <v>0</v>
@@ -11971,18 +12584,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:106" s="2" customFormat="1" ht="14.25">
+    <row r="71" s="2" customFormat="1" ht="14.5" spans="2:106">
       <c r="B71" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C71" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C71" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D71" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>133</v>
+      <c r="D71" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>131</v>
       </c>
       <c r="F71" s="2">
         <f t="shared" ref="F71:L71" si="10">D81/1000</f>
@@ -12012,9 +12625,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M71" s="17">
-        <v>100</v>
-      </c>
+      <c r="M71" s="17"/>
       <c r="N71" s="2">
         <f t="shared" ref="N71:AM71" si="11">L81/1000</f>
         <v>0</v>
@@ -12067,9 +12678,7 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AA71" s="17">
-        <v>100</v>
-      </c>
+      <c r="AA71" s="17"/>
       <c r="AB71" s="2">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -12123,16 +12732,16 @@
       <c r="CT71" s="20"/>
       <c r="CU71" s="20"/>
       <c r="CW71" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="CX71" t="s">
         <v>68</v>
       </c>
       <c r="CY71" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="CZ71" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="DA71" s="24">
         <v>0</v>
@@ -12141,18 +12750,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:106" s="2" customFormat="1" ht="14.25">
+    <row r="72" s="2" customFormat="1" ht="14.5" spans="2:106">
       <c r="B72" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C72" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C72" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D72" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>134</v>
+      <c r="D72" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>132</v>
       </c>
       <c r="F72" s="2">
         <f t="shared" ref="F72:M72" si="12">D82/1000</f>
@@ -12295,16 +12904,16 @@
       <c r="CT72" s="20"/>
       <c r="CU72" s="20"/>
       <c r="CW72" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="CX72" t="s">
         <v>68</v>
       </c>
       <c r="CY72" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="CZ72" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="DA72" s="24">
         <v>0</v>
@@ -12313,19 +12922,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:106" s="1" customFormat="1" ht="14.25">
+    <row r="73" s="1" customFormat="1" ht="14.5" spans="1:106">
       <c r="A73" s="2"/>
       <c r="B73" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C73" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C73" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D73" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>135</v>
+      <c r="D73" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="F73" s="2">
         <f t="shared" ref="F73:M73" si="14">D83/1000</f>
@@ -12470,16 +13079,16 @@
       <c r="CT73" s="19"/>
       <c r="CU73" s="19"/>
       <c r="CW73" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="CX73" t="s">
         <v>68</v>
       </c>
       <c r="CY73" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="CZ73" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="DA73" s="24">
         <v>0</v>
@@ -12488,14 +13097,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:106" s="3" customFormat="1"/>
-    <row r="75" spans="1:106" s="3" customFormat="1">
+    <row r="74" s="3" customFormat="1"/>
+    <row r="75" s="3" customFormat="1" spans="5:5">
       <c r="E75" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="76" spans="1:106" s="3" customFormat="1"/>
-    <row r="77" spans="1:106" s="3" customFormat="1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="76" s="3" customFormat="1"/>
+    <row r="77" s="3" customFormat="1" spans="4:37">
       <c r="D77" s="13">
         <v>0</v>
       </c>
@@ -12583,7 +13192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:106" s="3" customFormat="1">
+    <row r="78" s="3" customFormat="1" spans="4:37">
       <c r="D78" s="13">
         <v>0</v>
       </c>
@@ -12671,7 +13280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:106" s="3" customFormat="1">
+    <row r="79" s="3" customFormat="1" spans="4:37">
       <c r="D79" s="13">
         <v>13000</v>
       </c>
@@ -12759,7 +13368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:106" s="3" customFormat="1">
+    <row r="80" s="3" customFormat="1" spans="4:37">
       <c r="D80" s="13">
         <v>0</v>
       </c>
@@ -12847,7 +13456,7 @@
         <v>140000000</v>
       </c>
     </row>
-    <row r="81" spans="2:37" s="3" customFormat="1">
+    <row r="81" s="3" customFormat="1" spans="4:37">
       <c r="D81" s="13"/>
       <c r="E81" s="13"/>
       <c r="F81" s="13"/>
@@ -12885,7 +13494,7 @@
       <c r="AJ81" s="13"/>
       <c r="AK81" s="13"/>
     </row>
-    <row r="82" spans="2:37" s="3" customFormat="1">
+    <row r="82" s="3" customFormat="1" spans="4:37">
       <c r="D82" s="13">
         <v>0</v>
       </c>
@@ -12973,7 +13582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:37" s="3" customFormat="1">
+    <row r="83" s="3" customFormat="1" spans="4:37">
       <c r="D83" s="13">
         <v>0</v>
       </c>
@@ -13061,20 +13670,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:37" s="3" customFormat="1"/>
-    <row r="88" spans="2:37">
+    <row r="84" s="3" customFormat="1"/>
+    <row r="88" spans="2:2">
       <c r="B88" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="91" spans="2:37">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="91" spans="8:12">
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
       <c r="L91" s="3"/>
     </row>
-    <row r="92" spans="2:37">
+    <row r="92" spans="4:12">
       <c r="D92" s="3"/>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
@@ -13082,7 +13691,7 @@
       <c r="K92" s="3"/>
       <c r="L92" s="3"/>
     </row>
-    <row r="93" spans="2:37">
+    <row r="93" spans="3:12">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="F93" s="3"/>
@@ -13092,7 +13701,7 @@
       <c r="K93" s="3"/>
       <c r="L93" s="3"/>
     </row>
-    <row r="94" spans="2:37">
+    <row r="94" spans="3:12">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="H94" s="3"/>
@@ -13101,7 +13710,7 @@
       <c r="K94" s="3"/>
       <c r="L94" s="3"/>
     </row>
-    <row r="95" spans="2:37">
+    <row r="95" spans="3:12">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="F95" s="3"/>
@@ -13111,7 +13720,7 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
     </row>
-    <row r="96" spans="2:37">
+    <row r="96" spans="3:12">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="H96" s="3"/>
@@ -13120,7 +13729,7 @@
       <c r="K96" s="3"/>
       <c r="L96" s="3"/>
     </row>
-    <row r="97" spans="3:29">
+    <row r="97" spans="3:12">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="F97" s="3"/>
@@ -13130,7 +13739,7 @@
       <c r="K97" s="3"/>
       <c r="L97" s="3"/>
     </row>
-    <row r="98" spans="3:29">
+    <row r="98" spans="3:12">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="H98" s="3"/>
@@ -13139,22 +13748,22 @@
       <c r="K98" s="3"/>
       <c r="L98" s="3"/>
     </row>
-    <row r="99" spans="3:29">
+    <row r="99" spans="3:6">
       <c r="C99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="3:29">
+    <row r="100" spans="3:4">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
     </row>
-    <row r="101" spans="3:29">
+    <row r="101" spans="3:7">
       <c r="C101" s="3"/>
       <c r="D101" s="14"/>
       <c r="E101" s="14"/>
       <c r="F101" s="14"/>
       <c r="G101" s="14"/>
     </row>
-    <row r="102" spans="3:29">
+    <row r="102" spans="3:26">
       <c r="C102" s="3"/>
       <c r="D102" t="s">
         <v>73</v>
@@ -13223,36 +13832,36 @@
     </row>
     <row r="104" spans="3:29">
       <c r="C104" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E104" s="14">
-        <v>7.1138439695406497</v>
+        <v>7.11384396954065</v>
       </c>
       <c r="F104" s="15">
-        <v>5.4017985261606496</v>
+        <v>5.40179852616065</v>
       </c>
       <c r="G104" s="15">
-        <v>8.8554074428887208</v>
+        <v>8.85540744288872</v>
       </c>
       <c r="L104">
         <v>2050</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N104" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O104" s="14">
         <f>E104*0.313</f>
-        <v>2.2266331624662201</v>
+        <v>2.22663316246622</v>
       </c>
       <c r="P104" s="14">
         <f>F104*0.313</f>
-        <v>1.6907629386882801</v>
+        <v>1.69076293868828</v>
       </c>
       <c r="Q104" s="14">
         <f>G104*0.313</f>
@@ -13262,10 +13871,10 @@
         <v>0</v>
       </c>
       <c r="Y104" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z104" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AA104" s="14">
         <v>5</v>
@@ -13279,36 +13888,36 @@
     </row>
     <row r="105" spans="3:29">
       <c r="C105" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E105" s="14">
-        <v>7.1138439695406497</v>
+        <v>7.11384396954065</v>
       </c>
       <c r="F105" s="15">
-        <v>5.4017985261606496</v>
+        <v>5.40179852616065</v>
       </c>
       <c r="G105" s="15">
-        <v>8.8554074428887208</v>
+        <v>8.85540744288872</v>
       </c>
       <c r="L105">
         <v>2050</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N105" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O105" s="14">
         <f t="shared" ref="O105:O124" si="16">E105*0.313</f>
-        <v>2.2266331624662201</v>
+        <v>2.22663316246622</v>
       </c>
       <c r="P105" s="14">
         <f t="shared" ref="P105:P124" si="17">F105*0.313</f>
-        <v>1.6907629386882801</v>
+        <v>1.69076293868828</v>
       </c>
       <c r="Q105" s="14">
         <f t="shared" ref="Q105:Q124" si="18">G105*0.313</f>
@@ -13318,10 +13927,10 @@
         <v>0</v>
       </c>
       <c r="Y105" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z105" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AA105" s="14">
         <v>5</v>
@@ -13335,32 +13944,32 @@
     </row>
     <row r="106" spans="3:29">
       <c r="C106" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E106" s="14">
-        <v>7.6297544583640402</v>
+        <v>7.62975445836404</v>
       </c>
       <c r="F106" s="15">
-        <v>5.7935479734708899</v>
+        <v>5.79354797347089</v>
       </c>
       <c r="G106" s="15">
-        <v>9.4976196757553399</v>
+        <v>9.49761967575534</v>
       </c>
       <c r="L106">
         <v>2050</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N106" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O106" s="14">
         <f t="shared" si="16"/>
-        <v>2.3881131454679401</v>
+        <v>2.38811314546794</v>
       </c>
       <c r="P106" s="14">
         <f t="shared" si="17"/>
@@ -13368,16 +13977,16 @@
       </c>
       <c r="Q106" s="14">
         <f t="shared" si="18"/>
-        <v>2.9727549585114201</v>
+        <v>2.97275495851142</v>
       </c>
       <c r="X106">
         <v>0</v>
       </c>
       <c r="Y106" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z106" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AA106" s="14">
         <v>5</v>
@@ -13391,32 +14000,32 @@
     </row>
     <row r="107" spans="3:29">
       <c r="C107" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E107" s="14">
-        <v>7.4709708179808398</v>
+        <v>7.47097081798084</v>
       </c>
       <c r="F107" s="15">
-        <v>5.6729778187177597</v>
+        <v>5.67297781871776</v>
       </c>
       <c r="G107" s="15">
-        <v>9.2999636698599897</v>
+        <v>9.29996366985999</v>
       </c>
       <c r="L107">
         <v>2050</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N107" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O107" s="14">
         <f t="shared" si="16"/>
-        <v>2.3384138660280001</v>
+        <v>2.338413866028</v>
       </c>
       <c r="P107" s="14">
         <f t="shared" si="17"/>
@@ -13424,16 +14033,16 @@
       </c>
       <c r="Q107" s="14">
         <f t="shared" si="18"/>
-        <v>2.9108886286661799</v>
+        <v>2.91088862866618</v>
       </c>
       <c r="X107">
         <v>0</v>
       </c>
       <c r="Y107" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z107" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AA107" s="14">
         <v>5</v>
@@ -13447,49 +14056,49 @@
     </row>
     <row r="108" spans="3:29">
       <c r="C108" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E108" s="14">
-        <v>7.5164352001965096</v>
+        <v>7.51643520019651</v>
       </c>
       <c r="F108" s="15">
-        <v>5.7075005895357398</v>
+        <v>5.70750058953574</v>
       </c>
       <c r="G108" s="15">
-        <v>9.3565583640383192</v>
+        <v>9.35655836403832</v>
       </c>
       <c r="L108">
         <v>2050</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N108" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O108" s="14">
         <f t="shared" si="16"/>
-        <v>2.3526442176615099</v>
+        <v>2.35264421766151</v>
       </c>
       <c r="P108" s="14">
         <f t="shared" si="17"/>
-        <v>1.7864476845246899</v>
+        <v>1.78644768452469</v>
       </c>
       <c r="Q108" s="14">
         <f t="shared" si="18"/>
-        <v>2.9286027679439899</v>
+        <v>2.92860276794399</v>
       </c>
       <c r="X108">
         <v>0</v>
       </c>
       <c r="Y108" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z108" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AA108" s="14">
         <v>5</v>
@@ -13503,36 +14112,36 @@
     </row>
     <row r="109" spans="3:29">
       <c r="C109" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E109" s="14">
         <v>7.55036263817244</v>
       </c>
       <c r="F109" s="15">
-        <v>5.7332629329403098</v>
+        <v>5.73326293294031</v>
       </c>
       <c r="G109" s="15">
-        <v>9.3987916728076595</v>
+        <v>9.39879167280766</v>
       </c>
       <c r="L109">
         <v>2050</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N109" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O109" s="14">
         <f t="shared" si="16"/>
-        <v>2.3632635057479701</v>
+        <v>2.36326350574797</v>
       </c>
       <c r="P109" s="14">
         <f t="shared" si="17"/>
-        <v>1.7945112980103199</v>
+        <v>1.79451129801032</v>
       </c>
       <c r="Q109" s="14">
         <f t="shared" si="18"/>
@@ -13542,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="Y109" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z109" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AA109" s="14">
         <v>5</v>
@@ -13559,32 +14168,32 @@
     </row>
     <row r="110" spans="3:29">
       <c r="C110" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E110" s="14">
-        <v>7.6297544583640402</v>
+        <v>7.62975445836404</v>
       </c>
       <c r="F110" s="15">
-        <v>5.7935479734708899</v>
+        <v>5.79354797347089</v>
       </c>
       <c r="G110" s="15">
-        <v>9.4976196757553399</v>
+        <v>9.49761967575534</v>
       </c>
       <c r="L110">
         <v>2050</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N110" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O110" s="14">
         <f t="shared" si="16"/>
-        <v>2.3881131454679401</v>
+        <v>2.38811314546794</v>
       </c>
       <c r="P110" s="14">
         <f t="shared" si="17"/>
@@ -13592,16 +14201,16 @@
       </c>
       <c r="Q110" s="14">
         <f t="shared" si="18"/>
-        <v>2.9727549585114201</v>
+        <v>2.97275495851142</v>
       </c>
       <c r="X110">
         <v>0</v>
       </c>
       <c r="Y110" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z110" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AA110" s="14">
         <v>5</v>
@@ -13615,28 +14224,28 @@
     </row>
     <row r="111" spans="3:29">
       <c r="C111" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E111" s="14">
-        <v>4.1838460083517601</v>
+        <v>4.18384600835176</v>
       </c>
       <c r="F111" s="15">
-        <v>3.1769453205600602</v>
+        <v>3.17694532056006</v>
       </c>
       <c r="G111" s="15">
-        <v>5.2081070744288898</v>
+        <v>5.20810707442889</v>
       </c>
       <c r="L111">
         <v>2050</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N111" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O111" s="14">
         <f t="shared" si="16"/>
@@ -13644,7 +14253,7 @@
       </c>
       <c r="P111" s="14">
         <f t="shared" si="17"/>
-        <v>0.99438388533529898</v>
+        <v>0.994383885335299</v>
       </c>
       <c r="Q111" s="14">
         <f t="shared" si="18"/>
@@ -13654,10 +14263,10 @@
         <v>0</v>
       </c>
       <c r="Y111" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z111" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AA111" s="14">
         <v>5</v>
@@ -13671,28 +14280,28 @@
     </row>
     <row r="112" spans="3:29">
       <c r="C112" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E112" s="14">
-        <v>4.1838460083517601</v>
+        <v>4.18384600835176</v>
       </c>
       <c r="F112" s="15">
-        <v>3.1769453205600602</v>
+        <v>3.17694532056006</v>
       </c>
       <c r="G112" s="15">
-        <v>5.2081070744288898</v>
+        <v>5.20810707442889</v>
       </c>
       <c r="L112">
         <v>2050</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N112" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O112" s="14">
         <f t="shared" si="16"/>
@@ -13700,7 +14309,7 @@
       </c>
       <c r="P112" s="14">
         <f t="shared" si="17"/>
-        <v>0.99438388533529898</v>
+        <v>0.994383885335299</v>
       </c>
       <c r="Q112" s="14">
         <f t="shared" si="18"/>
@@ -13710,10 +14319,10 @@
         <v>0</v>
       </c>
       <c r="Y112" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z112" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AA112" s="14">
         <v>5</v>
@@ -13727,28 +14336,28 @@
     </row>
     <row r="113" spans="3:29">
       <c r="C113" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E113" s="14">
-        <v>4.1838460083517601</v>
+        <v>4.18384600835176</v>
       </c>
       <c r="F113" s="15">
-        <v>3.1769453205600602</v>
+        <v>3.17694532056006</v>
       </c>
       <c r="G113" s="15">
-        <v>5.2081070744288898</v>
+        <v>5.20810707442889</v>
       </c>
       <c r="L113">
         <v>2050</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N113" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O113" s="14">
         <f t="shared" si="16"/>
@@ -13756,7 +14365,7 @@
       </c>
       <c r="P113" s="14">
         <f t="shared" si="17"/>
-        <v>0.99438388533529898</v>
+        <v>0.994383885335299</v>
       </c>
       <c r="Q113" s="14">
         <f t="shared" si="18"/>
@@ -13766,10 +14375,10 @@
         <v>0</v>
       </c>
       <c r="Y113" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z113" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AA113" s="14">
         <v>5</v>
@@ -13783,28 +14392,28 @@
     </row>
     <row r="114" spans="3:29">
       <c r="C114" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E114" s="14">
-        <v>4.1838460083517601</v>
+        <v>4.18384600835176</v>
       </c>
       <c r="F114" s="15">
-        <v>3.1769453205600602</v>
+        <v>3.17694532056006</v>
       </c>
       <c r="G114" s="15">
-        <v>5.2081070744288898</v>
+        <v>5.20810707442889</v>
       </c>
       <c r="L114">
         <v>2050</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N114" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O114" s="14">
         <f t="shared" si="16"/>
@@ -13812,7 +14421,7 @@
       </c>
       <c r="P114" s="14">
         <f t="shared" si="17"/>
-        <v>0.99438388533529898</v>
+        <v>0.994383885335299</v>
       </c>
       <c r="Q114" s="14">
         <f t="shared" si="18"/>
@@ -13822,10 +14431,10 @@
         <v>0</v>
       </c>
       <c r="Y114" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z114" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AA114" s="14">
         <v>5</v>
@@ -13839,28 +14448,28 @@
     </row>
     <row r="115" spans="3:29">
       <c r="C115" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E115" s="14">
-        <v>4.1838460083517601</v>
+        <v>4.18384600835176</v>
       </c>
       <c r="F115" s="15">
-        <v>3.1769453205600602</v>
+        <v>3.17694532056006</v>
       </c>
       <c r="G115" s="15">
-        <v>5.2081070744288898</v>
+        <v>5.20810707442889</v>
       </c>
       <c r="L115">
         <v>2050</v>
       </c>
       <c r="M115" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N115" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O115" s="14">
         <f t="shared" si="16"/>
@@ -13868,7 +14477,7 @@
       </c>
       <c r="P115" s="14">
         <f t="shared" si="17"/>
-        <v>0.99438388533529898</v>
+        <v>0.994383885335299</v>
       </c>
       <c r="Q115" s="14">
         <f t="shared" si="18"/>
@@ -13878,10 +14487,10 @@
         <v>0</v>
       </c>
       <c r="Y115" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z115" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA115" s="14">
         <v>5</v>
@@ -13895,28 +14504,28 @@
     </row>
     <row r="116" spans="3:29">
       <c r="C116" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E116" s="14">
-        <v>4.1838460083517601</v>
+        <v>4.18384600835176</v>
       </c>
       <c r="F116" s="15">
-        <v>3.1769453205600602</v>
+        <v>3.17694532056006</v>
       </c>
       <c r="G116" s="15">
-        <v>5.2081070744288898</v>
+        <v>5.20810707442889</v>
       </c>
       <c r="L116">
         <v>2050</v>
       </c>
       <c r="M116" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N116" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O116" s="14">
         <f t="shared" si="16"/>
@@ -13924,7 +14533,7 @@
       </c>
       <c r="P116" s="14">
         <f t="shared" si="17"/>
-        <v>0.99438388533529898</v>
+        <v>0.994383885335299</v>
       </c>
       <c r="Q116" s="14">
         <f t="shared" si="18"/>
@@ -13934,10 +14543,10 @@
         <v>0</v>
       </c>
       <c r="Y116" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z116" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AA116" s="14">
         <v>5</v>
@@ -13951,28 +14560,28 @@
     </row>
     <row r="117" spans="3:29">
       <c r="C117" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D117" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E117" s="14">
-        <v>4.1838460083517601</v>
+        <v>4.18384600835176</v>
       </c>
       <c r="F117" s="15">
-        <v>3.1769453205600602</v>
+        <v>3.17694532056006</v>
       </c>
       <c r="G117" s="15">
-        <v>5.2081070744288898</v>
+        <v>5.20810707442889</v>
       </c>
       <c r="L117">
         <v>2050</v>
       </c>
       <c r="M117" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N117" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O117" s="14">
         <f t="shared" si="16"/>
@@ -13980,7 +14589,7 @@
       </c>
       <c r="P117" s="14">
         <f t="shared" si="17"/>
-        <v>0.99438388533529898</v>
+        <v>0.994383885335299</v>
       </c>
       <c r="Q117" s="14">
         <f t="shared" si="18"/>
@@ -13990,10 +14599,10 @@
         <v>0</v>
       </c>
       <c r="Y117" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z117" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AA117" s="14">
         <v>5</v>
@@ -14007,49 +14616,49 @@
     </row>
     <row r="118" spans="3:29">
       <c r="C118" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D118" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E118" s="14">
-        <v>3.5655626627364301</v>
+        <v>3.56556266273643</v>
       </c>
       <c r="F118" s="15">
-        <v>2.7074604274134102</v>
+        <v>2.70746042741341</v>
       </c>
       <c r="G118" s="15">
-        <v>4.4384597641857004</v>
+        <v>4.4384597641857</v>
       </c>
       <c r="L118">
         <v>2050</v>
       </c>
       <c r="M118" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N118" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O118" s="14">
         <f t="shared" si="16"/>
-        <v>1.1160211134364999</v>
+        <v>1.1160211134365</v>
       </c>
       <c r="P118" s="14">
         <f t="shared" si="17"/>
-        <v>0.84743511378039704</v>
+        <v>0.847435113780397</v>
       </c>
       <c r="Q118" s="14">
         <f t="shared" si="18"/>
-        <v>1.3892379061901201</v>
+        <v>1.38923790619012</v>
       </c>
       <c r="X118">
         <v>0</v>
       </c>
       <c r="Y118" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z118" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AA118" s="14">
         <v>5</v>
@@ -14063,36 +14672,36 @@
     </row>
     <row r="119" spans="3:29">
       <c r="C119" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E119" s="14">
-        <v>3.6008770817980902</v>
+        <v>3.60087708179809</v>
       </c>
       <c r="F119" s="15">
-        <v>2.7342759764185698</v>
+        <v>2.73427597641857</v>
       </c>
       <c r="G119" s="15">
-        <v>4.4824196020633797</v>
+        <v>4.48241960206338</v>
       </c>
       <c r="L119">
         <v>2050</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N119" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O119" s="14">
         <f t="shared" si="16"/>
-        <v>1.1270745266027999</v>
+        <v>1.1270745266028</v>
       </c>
       <c r="P119" s="14">
         <f t="shared" si="17"/>
-        <v>0.85582838061901201</v>
+        <v>0.855828380619012</v>
       </c>
       <c r="Q119" s="14">
         <f t="shared" si="18"/>
@@ -14102,10 +14711,10 @@
         <v>0</v>
       </c>
       <c r="Y119" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z119" s="14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AA119" s="14">
         <v>5</v>
@@ -14119,49 +14728,49 @@
     </row>
     <row r="120" spans="3:29">
       <c r="C120" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E120" s="14">
-        <v>3.5655626627364301</v>
+        <v>3.56556266273643</v>
       </c>
       <c r="F120" s="15">
-        <v>2.7074604274134102</v>
+        <v>2.70746042741341</v>
       </c>
       <c r="G120" s="15">
-        <v>4.4384597641857004</v>
+        <v>4.4384597641857</v>
       </c>
       <c r="L120">
         <v>2050</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N120" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O120" s="14">
         <f t="shared" si="16"/>
-        <v>1.1160211134364999</v>
+        <v>1.1160211134365</v>
       </c>
       <c r="P120" s="14">
         <f t="shared" si="17"/>
-        <v>0.84743511378039704</v>
+        <v>0.847435113780397</v>
       </c>
       <c r="Q120" s="14">
         <f t="shared" si="18"/>
-        <v>1.3892379061901201</v>
+        <v>1.38923790619012</v>
       </c>
       <c r="X120">
         <v>0</v>
       </c>
       <c r="Y120" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z120" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AA120" s="14">
         <v>5</v>
@@ -14175,10 +14784,10 @@
     </row>
     <row r="121" spans="3:29">
       <c r="C121" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D121" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E121" s="14">
         <v>3.56645369688037</v>
@@ -14187,16 +14796,16 @@
         <v>2.70813706705969</v>
       </c>
       <c r="G121" s="15">
-        <v>4.4395689019896798</v>
+        <v>4.43956890198968</v>
       </c>
       <c r="L121">
         <v>2050</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N121" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O121" s="14">
         <f t="shared" si="16"/>
@@ -14204,7 +14813,7 @@
       </c>
       <c r="P121" s="14">
         <f t="shared" si="17"/>
-        <v>0.84764690198968295</v>
+        <v>0.847646901989683</v>
       </c>
       <c r="Q121" s="14">
         <f t="shared" si="18"/>
@@ -14214,10 +14823,10 @@
         <v>0</v>
       </c>
       <c r="Y121" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z121" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AA121" s="14">
         <v>5</v>
@@ -14231,49 +14840,49 @@
     </row>
     <row r="122" spans="3:29">
       <c r="C122" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E122" s="14">
-        <v>3.5658596168017702</v>
+        <v>3.56585961680177</v>
       </c>
       <c r="F122" s="15">
-        <v>2.7076859248341898</v>
+        <v>2.70768592483419</v>
       </c>
       <c r="G122" s="15">
-        <v>4.4388294030950597</v>
+        <v>4.43882940309506</v>
       </c>
       <c r="L122">
         <v>2050</v>
       </c>
       <c r="M122" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N122" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O122" s="14">
         <f t="shared" si="16"/>
-        <v>1.1161140600589501</v>
+        <v>1.11611406005895</v>
       </c>
       <c r="P122" s="14">
         <f t="shared" si="17"/>
-        <v>0.84750569447310098</v>
+        <v>0.847505694473101</v>
       </c>
       <c r="Q122" s="14">
         <f t="shared" si="18"/>
-        <v>1.3893536031687499</v>
+        <v>1.38935360316875</v>
       </c>
       <c r="X122">
         <v>0</v>
       </c>
       <c r="Y122" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z122" s="14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AA122" s="14">
         <v>5</v>
@@ -14287,49 +14896,49 @@
     </row>
     <row r="123" spans="3:29">
       <c r="C123" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D123" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E123" s="14">
-        <v>3.5655626627364301</v>
+        <v>3.56556266273643</v>
       </c>
       <c r="F123" s="15">
-        <v>2.7074604274134102</v>
+        <v>2.70746042741341</v>
       </c>
       <c r="G123" s="15">
-        <v>4.4384597641857004</v>
+        <v>4.4384597641857</v>
       </c>
       <c r="L123">
         <v>2050</v>
       </c>
       <c r="M123" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N123" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O123" s="14">
         <f t="shared" si="16"/>
-        <v>1.1160211134364999</v>
+        <v>1.1160211134365</v>
       </c>
       <c r="P123" s="14">
         <f t="shared" si="17"/>
-        <v>0.84743511378039704</v>
+        <v>0.847435113780397</v>
       </c>
       <c r="Q123" s="14">
         <f t="shared" si="18"/>
-        <v>1.3892379061901201</v>
+        <v>1.38923790619012</v>
       </c>
       <c r="X123">
         <v>0</v>
       </c>
       <c r="Y123" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z123" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AA123" s="14">
         <v>5</v>
@@ -14343,28 +14952,28 @@
     </row>
     <row r="124" spans="3:29">
       <c r="C124" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D124" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E124" s="14">
-        <v>3.5649689019896802</v>
+        <v>3.56496890198968</v>
       </c>
       <c r="F124" s="15">
-        <v>2.7070095799557801</v>
+        <v>2.70700957995578</v>
       </c>
       <c r="G124" s="15">
-        <v>4.4377206337509199</v>
+        <v>4.43772063375092</v>
       </c>
       <c r="L124">
         <v>2050</v>
       </c>
       <c r="M124" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="N124" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O124" s="14">
         <f t="shared" si="16"/>
@@ -14372,20 +14981,20 @@
       </c>
       <c r="P124" s="14">
         <f t="shared" si="17"/>
-        <v>0.84729399852615905</v>
+        <v>0.847293998526159</v>
       </c>
       <c r="Q124" s="14">
         <f t="shared" si="18"/>
-        <v>1.3890065583640401</v>
+        <v>1.38900655836404</v>
       </c>
       <c r="X124">
         <v>0</v>
       </c>
       <c r="Y124" s="3" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="Z124" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AA124" s="14">
         <v>5</v>
@@ -14398,26 +15007,28 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AZ33:BA38">
+  <sortState ref="AZ33:BA38">
     <sortCondition ref="AZ33:AZ38"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AU55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
-    <col min="3" max="3" width="11.59765625" customWidth="1"/>
-    <col min="12" max="28" width="5.265625" customWidth="1"/>
+    <col min="3" max="3" width="11.6" customWidth="1"/>
+    <col min="12" max="28" width="5.26363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:47">
       <c r="A1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -14429,25 +15040,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" t="s">
         <v>160</v>
-      </c>
-      <c r="F1" t="s">
-        <v>161</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I1" t="s">
         <v>162</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>163</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>164</v>
-      </c>
-      <c r="K1" t="s">
-        <v>165</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -14555,7 +15166,7 @@
         <v>38</v>
       </c>
       <c r="AU1" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:47">
@@ -18597,109 +19208,109 @@
         <v>166</v>
       </c>
       <c r="L30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="M30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="N30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="O30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="P30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="Q30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="R30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="S30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="T30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="U30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="V30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="W30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="X30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="Y30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="Z30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AA30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AB30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AC30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AD30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AE30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AF30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AG30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AH30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AI30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AJ30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AK30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AL30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AM30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AN30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AO30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AP30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AQ30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AR30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AS30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AT30">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AU30" t="s">
         <v>166</v>
@@ -18740,109 +19351,109 @@
         <v>166</v>
       </c>
       <c r="L31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="M31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="N31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="O31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="P31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="Q31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="R31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="S31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="T31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="U31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="V31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="W31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="X31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="Y31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="Z31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AA31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AB31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AC31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AD31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AE31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AF31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AG31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AH31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AI31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AJ31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AK31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AL31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AM31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AN31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AO31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AP31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AQ31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AR31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AS31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AT31">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AU31" t="s">
         <v>166</v>
@@ -18883,109 +19494,109 @@
         <v>166</v>
       </c>
       <c r="L32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="M32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="N32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="O32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="P32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="Q32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="R32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="S32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="T32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="U32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="V32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="W32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="X32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="Y32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="Z32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AA32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AB32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AC32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AD32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AE32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AF32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AG32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AH32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AI32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AJ32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AK32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AL32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AM32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AN32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AO32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AP32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AQ32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AR32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AS32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AT32">
-        <v>0.58696999999999999</v>
+        <v>0.58697</v>
       </c>
       <c r="AU32" t="s">
         <v>166</v>
@@ -19026,109 +19637,109 @@
         <v>166</v>
       </c>
       <c r="L33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="M33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="N33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="O33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="P33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="Q33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="R33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="S33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="T33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="U33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="V33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="W33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="X33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="Y33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="Z33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AA33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AB33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AC33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AD33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AE33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AF33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AG33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AH33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AI33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AJ33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AK33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AL33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AM33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AN33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AO33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AP33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AQ33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AR33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AS33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AT33">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AU33" t="s">
         <v>166</v>
@@ -19169,109 +19780,109 @@
         <v>166</v>
       </c>
       <c r="L34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="M34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="N34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="O34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="P34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="Q34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="R34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="S34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="T34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="U34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="V34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="W34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="X34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="Y34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="Z34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AA34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AB34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AC34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AD34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AE34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AF34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AG34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AH34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AI34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AJ34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AK34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AL34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AM34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AN34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AO34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AP34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AQ34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AR34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AS34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AT34">
-        <v>7.2069999999999995E-2</v>
+        <v>0.07207</v>
       </c>
       <c r="AU34" t="s">
         <v>166</v>
@@ -19741,109 +20352,109 @@
         <v>166</v>
       </c>
       <c r="L38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="M38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="N38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="O38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="P38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="Q38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="R38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="S38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="T38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="U38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="V38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="W38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="X38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="Y38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="Z38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AA38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AB38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AC38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AD38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AE38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AF38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AG38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AH38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AI38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AJ38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AK38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AL38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AM38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AN38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AO38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AP38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AQ38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AR38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AS38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AT38">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AU38" t="s">
         <v>166</v>
@@ -19884,109 +20495,109 @@
         <v>166</v>
       </c>
       <c r="L39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="M39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="N39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="O39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="P39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="Q39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="R39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="S39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="T39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="U39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="V39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="W39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="X39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="Y39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="Z39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AA39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AB39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AC39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AD39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AE39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AF39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AG39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AH39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AI39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AJ39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AK39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AL39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AM39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AN39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AO39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AP39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AQ39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AR39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AS39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AT39">
-        <v>6.1199999999999997E-2</v>
+        <v>0.0612</v>
       </c>
       <c r="AU39" t="s">
         <v>166</v>
@@ -20027,109 +20638,109 @@
         <v>166</v>
       </c>
       <c r="L40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="M40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="N40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="O40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="P40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="Q40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="R40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="S40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="T40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="U40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="V40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="W40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="X40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="Y40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="Z40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AA40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AB40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AC40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AD40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AE40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AF40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AG40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AH40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AI40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AJ40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AK40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AL40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AM40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AN40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AO40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AP40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AQ40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AR40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AS40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AT40">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AU40" t="s">
         <v>166</v>
@@ -20170,109 +20781,109 @@
         <v>166</v>
       </c>
       <c r="L41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="M41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="N41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="O41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="P41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="Q41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="R41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="S41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="T41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="U41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="V41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="W41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="X41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="Y41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="Z41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AA41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AB41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AC41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AD41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AE41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AF41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AG41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AH41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AI41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AJ41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AK41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AL41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AM41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AN41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AO41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AP41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AQ41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AR41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AS41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AT41">
-        <v>0.52772280688712803</v>
+        <v>0.527722806887128</v>
       </c>
       <c r="AU41" t="s">
         <v>166</v>
@@ -20313,109 +20924,109 @@
         <v>166</v>
       </c>
       <c r="L42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="M42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="N42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="O42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="P42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="Q42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="R42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="S42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="T42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="U42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="V42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="W42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="X42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="Y42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="Z42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AA42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AB42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AC42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AD42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AE42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AF42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AG42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AH42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AI42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AJ42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AK42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AL42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AM42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AN42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AO42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AP42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AQ42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AR42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AS42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AT42">
-        <v>1.1651321700288899</v>
+        <v>1.16513217002889</v>
       </c>
       <c r="AU42" t="s">
         <v>166</v>
@@ -20456,109 +21067,109 @@
         <v>166</v>
       </c>
       <c r="L43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="M43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="N43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="O43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="P43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="Q43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="R43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="S43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="T43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="U43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="V43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="W43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="X43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="Y43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="Z43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AA43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AB43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AC43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AD43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AE43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AF43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AG43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AH43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AI43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AJ43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AK43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AL43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AM43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AN43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AO43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AP43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AQ43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AR43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AS43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AT43">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AU43" t="s">
         <v>166</v>
@@ -20599,109 +21210,109 @@
         <v>166</v>
       </c>
       <c r="L44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="M44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="N44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="O44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="P44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="Q44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="R44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="S44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="T44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="U44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="V44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="W44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="X44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="Y44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="Z44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AA44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AB44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AC44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AD44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AE44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AF44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AG44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AH44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AI44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AJ44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AK44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AL44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AM44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AN44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AO44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AP44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AQ44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AR44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AS44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AT44">
-        <v>0.46605286801155599</v>
+        <v>0.466052868011556</v>
       </c>
       <c r="AU44" t="s">
         <v>166</v>
@@ -20742,109 +21353,109 @@
         <v>166</v>
       </c>
       <c r="L45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="M45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="N45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="O45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="P45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="Q45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="R45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="S45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="T45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="U45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="V45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="W45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="X45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="Y45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="Z45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AA45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AB45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AC45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AD45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AE45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AF45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AG45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AH45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AI45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AJ45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AK45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AL45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AM45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AN45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AO45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AP45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AQ45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AR45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AS45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AT45">
-        <v>0.47553149117899501</v>
+        <v>0.475531491178995</v>
       </c>
       <c r="AU45" t="s">
         <v>166</v>
@@ -21743,109 +22354,109 @@
         <v>166</v>
       </c>
       <c r="L52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="M52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="N52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="O52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="P52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="Q52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="R52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="S52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="T52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="U52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="V52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="W52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="X52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="Y52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="Z52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AA52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AB52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AC52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AD52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AE52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AF52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AG52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AH52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AI52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AJ52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AK52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AL52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AM52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AN52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AO52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AP52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AQ52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AR52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AS52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AT52">
-        <v>0.74542647386440897</v>
+        <v>0.745426473864409</v>
       </c>
       <c r="AU52" t="s">
         <v>166</v>
@@ -21886,109 +22497,109 @@
         <v>166</v>
       </c>
       <c r="L53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="M53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="N53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="O53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="P53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="Q53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="R53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="S53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="T53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="U53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="V53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="W53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="X53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="Y53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="Z53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AA53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AB53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AC53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AD53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AE53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AF53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AG53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AH53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AI53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AJ53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AK53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AL53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AM53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AN53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AO53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AP53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AQ53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AR53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AS53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AT53">
-        <v>0.37271323693220398</v>
+        <v>0.372713236932204</v>
       </c>
       <c r="AU53" t="s">
         <v>166</v>
@@ -22029,109 +22640,109 @@
         <v>166</v>
       </c>
       <c r="L54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="M54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="N54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="O54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="P54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="Q54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="R54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="S54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="T54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="U54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="V54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="W54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="X54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="Y54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="Z54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AA54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AB54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AC54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AD54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AE54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AF54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AG54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AH54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AI54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AJ54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AK54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AL54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AM54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AN54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AO54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AP54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AQ54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AR54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AS54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AT54">
-        <v>0.44075733528719402</v>
+        <v>0.440757335287194</v>
       </c>
       <c r="AU54" t="s">
         <v>166</v>
@@ -22172,109 +22783,109 @@
         <v>166</v>
       </c>
       <c r="L55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="M55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="N55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="O55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="P55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="Q55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="R55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="S55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="T55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="U55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="V55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="W55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="X55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="Y55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="Z55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AA55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AB55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AC55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AD55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AE55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AF55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AG55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AH55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AI55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AJ55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AK55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AL55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AM55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AN55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AO55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AP55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AQ55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AR55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AS55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AT55">
-        <v>0.32948443032272601</v>
+        <v>0.329484430322726</v>
       </c>
       <c r="AU55" t="s">
         <v>166</v>
@@ -22282,5 +22893,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -42,6 +42,50 @@
     <author>xli9</author>
   </authors>
   <commentList>
+    <comment ref="M71" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+https://www.lightmetalage.com/news/industry-news/smelting/decline-of-u-s-primary-aluminum-production-and-the-growth-of-secondary-aluminum/?utm_source=chatgpt.com</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA71" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t>xli9:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Times New Roman"/>
+            <charset val="0"/>
+          </rPr>
+          <t xml:space="preserve">
+US750 ktonne, CAN 2.9 Mtonne: https://en.wikipedia.org/wiki/Aluminum_industry_in_the_United_States?utm_source=chatgpt.com; https://www.statista.com/statistics/312839/primary-aluminum-production-in-the-united-states/?utm_source=chatgpt.com</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D101" authorId="0">
       <text>
         <r>
@@ -653,7 +697,7 @@
     <numFmt numFmtId="178" formatCode="0.0"/>
     <numFmt numFmtId="179" formatCode="0.000"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -845,6 +889,17 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
     </font>
     <font>
       <b/>
@@ -12625,7 +12680,9 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="M71" s="17"/>
+      <c r="M71" s="17">
+        <v>41500</v>
+      </c>
       <c r="N71" s="2">
         <f t="shared" ref="N71:AM71" si="11">L81/1000</f>
         <v>0</v>
@@ -12678,7 +12735,9 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AA71" s="17"/>
+      <c r="AA71" s="17">
+        <v>3650</v>
+      </c>
       <c r="AB71" s="2">
         <f t="shared" si="11"/>
         <v>0</v>

--- a/SubRes_Tmpl/SubRES_Transport_trans.xlsx
+++ b/SubRes_Tmpl/SubRES_Transport_trans.xlsx
@@ -623,100 +623,100 @@
     <t>NCAP_COST</t>
   </si>
   <si>
+    <t>commodity_group</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>stage</t>
+  </si>
+  <si>
+    <t>sow</t>
+  </si>
+  <si>
+    <t>year2</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>ANNUAL</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
     <t>Trd_lcv_nga</t>
+  </si>
+  <si>
+    <t>Trd_lcv_gsl</t>
   </si>
   <si>
     <t>Trd_lcv_lpg</t>
   </si>
   <si>
-    <t>Trd_lcv_gsl</t>
+    <t>Trd_3w_bdl</t>
   </si>
   <si>
-    <t>Trd_lcv_elc</t>
+    <t>Trd_3w_dsl</t>
+  </si>
+  <si>
+    <t>Trd_bus_bdl</t>
+  </si>
+  <si>
+    <t>Trd_bus_elc</t>
+  </si>
+  <si>
+    <t>Trd_bus_eth</t>
+  </si>
+  <si>
+    <t>Trd_bus_gsl</t>
+  </si>
+  <si>
+    <t>Trd_bus_lpg</t>
+  </si>
+  <si>
+    <t>Trd_bus_nga</t>
+  </si>
+  <si>
+    <t>Trd_car_bdl</t>
+  </si>
+  <si>
+    <t>Trd_car_dsl</t>
+  </si>
+  <si>
+    <t>Trd_car_elc</t>
+  </si>
+  <si>
+    <t>Trd_car_eth</t>
+  </si>
+  <si>
+    <t>Trd_car_lpg</t>
+  </si>
+  <si>
+    <t>lim_type</t>
+  </si>
+  <si>
+    <t>time_slice</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>Trd_car_nga</t>
+  </si>
+  <si>
+    <t>Trd_hdt_bdl</t>
+  </si>
+  <si>
+    <t>Trd_hdt_gsl</t>
   </si>
   <si>
     <t>Trd_lcv_bdl</t>
   </si>
   <si>
-    <t>Trd_hdt_gsl</t>
-  </si>
-  <si>
-    <t>Trd_hdt_bdl</t>
-  </si>
-  <si>
-    <t>Trd_car_nga</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>time_slice</t>
-  </si>
-  <si>
-    <t>lim_type</t>
-  </si>
-  <si>
-    <t>Trd_car_lpg</t>
-  </si>
-  <si>
-    <t>Trd_car_eth</t>
-  </si>
-  <si>
-    <t>Trd_car_elc</t>
-  </si>
-  <si>
-    <t>Trd_car_dsl</t>
-  </si>
-  <si>
-    <t>Trd_car_bdl</t>
-  </si>
-  <si>
-    <t>Trd_bus_nga</t>
-  </si>
-  <si>
-    <t>Trd_bus_lpg</t>
-  </si>
-  <si>
-    <t>Trd_bus_gsl</t>
-  </si>
-  <si>
-    <t>Trd_bus_eth</t>
-  </si>
-  <si>
-    <t>Trd_bus_elc</t>
-  </si>
-  <si>
-    <t>Trd_bus_bdl</t>
-  </si>
-  <si>
-    <t>Trd_3w_dsl</t>
-  </si>
-  <si>
-    <t>Trd_3w_bdl</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>ANNUAL</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>year2</t>
-  </si>
-  <si>
-    <t>sow</t>
-  </si>
-  <si>
-    <t>stage</t>
-  </si>
-  <si>
-    <t>currency</t>
-  </si>
-  <si>
-    <t>commodity_group</t>
+    <t>Trd_lcv_elc</t>
   </si>
 </sst>
 </file>
@@ -11265,7 +11265,7 @@
       </c>
       <c r="K36" t="str">
         <f>"*"&amp;ROUND(SUMIFS(RoadTra_BY!S$2:S$79,RoadTra_BY!$B$2:$B$79,'Road transport'!$C36,RoadTra_BY!$C$2:$C$79,'Road transport'!$BA36),3)</f>
-        <v>*0.699</v>
+        <v>*0.466</v>
       </c>
       <c r="L36" t="str">
         <f>"*"&amp;ROUND(SUMIFS(RoadTra_BY!T$2:T$79,RoadTra_BY!$B$2:$B$79,'Road transport'!$C36,RoadTra_BY!$C$2:$C$79,'Road transport'!$BA36),3)</f>
@@ -16147,7 +16147,7 @@
   <sheetData>
     <row r="1" spans="1:47" ht="12.5">
       <c r="A1" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B1" t="s">
         <v>56</v>
@@ -16159,25 +16159,25 @@
         <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="F1" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="G1" t="s">
         <v>79</v>
       </c>
       <c r="H1" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="I1" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="J1" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="K1" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="L1" t="s">
         <v>3</v>
@@ -16285,7 +16285,7 @@
         <v>38</v>
       </c>
       <c r="AU1" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:47" ht="12.5">
@@ -16299,28 +16299,28 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
         <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G2" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H2" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I2" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J2" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K2" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L2">
         <v>7</v>
@@ -16428,7 +16428,7 @@
         <v>4</v>
       </c>
       <c r="AU2" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:47" ht="12.5">
@@ -16439,31 +16439,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D3" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E3" t="s">
         <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G3" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H3" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I3" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J3" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K3" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L3">
         <v>15</v>
@@ -16571,7 +16571,7 @@
         <v>15</v>
       </c>
       <c r="AU3" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:47" ht="12.5">
@@ -16582,31 +16582,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E4" t="s">
         <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G4" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H4" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I4" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J4" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K4" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L4">
         <v>15</v>
@@ -16714,7 +16714,7 @@
         <v>15</v>
       </c>
       <c r="AU4" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:47" ht="12.5">
@@ -16728,28 +16728,28 @@
         <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E5" t="s">
         <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G5" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H5" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I5" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J5" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K5" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L5">
         <v>15</v>
@@ -16857,7 +16857,7 @@
         <v>15</v>
       </c>
       <c r="AU5" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:47" ht="12.5">
@@ -16868,31 +16868,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D6" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E6" t="s">
         <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G6" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I6" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J6" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K6" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L6">
         <v>35</v>
@@ -17000,7 +17000,7 @@
         <v>20</v>
       </c>
       <c r="AU6" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:47" ht="12.5">
@@ -17014,28 +17014,28 @@
         <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E7" t="s">
         <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G7" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H7" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I7" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J7" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K7" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L7">
         <v>35</v>
@@ -17143,7 +17143,7 @@
         <v>20</v>
       </c>
       <c r="AU7" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:47" ht="12.5">
@@ -17154,31 +17154,31 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D8" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E8" t="s">
         <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G8" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H8" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I8" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J8" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K8" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L8">
         <v>35</v>
@@ -17286,7 +17286,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:47" ht="12.5">
@@ -17297,31 +17297,31 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E9" t="s">
         <v>68</v>
       </c>
       <c r="F9" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G9" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H9" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I9" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J9" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K9" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L9">
         <v>35</v>
@@ -17429,7 +17429,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:47" ht="12.5">
@@ -17440,31 +17440,31 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D10" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E10" t="s">
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G10" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H10" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I10" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J10" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K10" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L10">
         <v>35</v>
@@ -17572,7 +17572,7 @@
         <v>20</v>
       </c>
       <c r="AU10" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:47" ht="12.5">
@@ -17586,28 +17586,28 @@
         <v>176</v>
       </c>
       <c r="D11" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E11" t="s">
         <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G11" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H11" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I11" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J11" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K11" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L11">
         <v>35</v>
@@ -17715,7 +17715,7 @@
         <v>20</v>
       </c>
       <c r="AU11" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:47" ht="12.5">
@@ -17726,31 +17726,31 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D12" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E12" t="s">
         <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G12" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H12" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I12" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J12" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K12" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L12">
         <v>35</v>
@@ -17858,7 +17858,7 @@
         <v>20</v>
       </c>
       <c r="AU12" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:47" ht="12.5">
@@ -17869,31 +17869,31 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D13" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G13" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H13" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I13" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J13" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K13" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -18001,7 +18001,7 @@
         <v>12</v>
       </c>
       <c r="AU13" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:47" ht="12.5">
@@ -18012,31 +18012,31 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D14" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E14" t="s">
         <v>68</v>
       </c>
       <c r="F14" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G14" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H14" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I14" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J14" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K14" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -18144,7 +18144,7 @@
         <v>12</v>
       </c>
       <c r="AU14" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:47" ht="12.5">
@@ -18155,31 +18155,31 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D15" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E15" t="s">
         <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G15" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H15" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I15" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J15" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K15" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -18287,7 +18287,7 @@
         <v>12</v>
       </c>
       <c r="AU15" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:47" ht="12.5">
@@ -18298,31 +18298,31 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D16" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E16" t="s">
         <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G16" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H16" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I16" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J16" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K16" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -18430,7 +18430,7 @@
         <v>12</v>
       </c>
       <c r="AU16" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:47" ht="12.5">
@@ -18444,28 +18444,28 @@
         <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E17" t="s">
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G17" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H17" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I17" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J17" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K17" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -18573,7 +18573,7 @@
         <v>12</v>
       </c>
       <c r="AU17" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:47" ht="12.5">
@@ -18584,31 +18584,31 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D18" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E18" t="s">
         <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G18" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H18" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I18" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J18" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K18" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -18716,7 +18716,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:47" ht="12.5">
@@ -18727,31 +18727,31 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="D19" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E19" t="s">
         <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G19" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H19" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I19" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J19" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K19" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -18859,7 +18859,7 @@
         <v>12</v>
       </c>
       <c r="AU19" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:47" ht="12.5">
@@ -18870,31 +18870,31 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="D20" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E20" t="s">
         <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G20" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H20" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I20" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J20" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K20" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -19002,7 +19002,7 @@
         <v>35</v>
       </c>
       <c r="AU20" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:47" ht="12.5">
@@ -19016,28 +19016,28 @@
         <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E21" t="s">
         <v>68</v>
       </c>
       <c r="F21" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G21" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H21" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I21" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J21" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K21" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -19145,7 +19145,7 @@
         <v>35</v>
       </c>
       <c r="AU21" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:47" ht="12.5">
@@ -19156,31 +19156,31 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="D22" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E22" t="s">
         <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G22" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H22" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I22" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J22" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K22" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -19288,7 +19288,7 @@
         <v>35</v>
       </c>
       <c r="AU22" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:47" ht="12.5">
@@ -19299,31 +19299,31 @@
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="D23" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E23" t="s">
         <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G23" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H23" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I23" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J23" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K23" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L23">
         <v>40</v>
@@ -19431,7 +19431,7 @@
         <v>15</v>
       </c>
       <c r="AU23" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:47" ht="12.5">
@@ -19445,28 +19445,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E24" t="s">
         <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G24" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H24" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I24" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J24" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K24" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L24">
         <v>40</v>
@@ -19574,7 +19574,7 @@
         <v>15</v>
       </c>
       <c r="AU24" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:47" ht="12.5">
@@ -19585,31 +19585,31 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="D25" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E25" t="s">
         <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G25" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H25" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I25" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J25" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K25" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L25">
         <v>40</v>
@@ -19717,7 +19717,7 @@
         <v>15</v>
       </c>
       <c r="AU25" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:47" ht="12.5">
@@ -19728,31 +19728,31 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D26" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E26" t="s">
         <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G26" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H26" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I26" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J26" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K26" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L26">
         <v>40</v>
@@ -19860,7 +19860,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:47" ht="12.5">
@@ -19871,31 +19871,31 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D27" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E27" t="s">
         <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G27" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H27" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I27" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J27" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K27" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L27">
         <v>40</v>
@@ -20003,7 +20003,7 @@
         <v>15</v>
       </c>
       <c r="AU27" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:47" ht="12.5">
@@ -20014,31 +20014,31 @@
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E28" t="s">
         <v>68</v>
       </c>
       <c r="F28" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G28" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H28" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I28" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J28" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K28" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L28">
         <v>40</v>
@@ -20146,7 +20146,7 @@
         <v>15</v>
       </c>
       <c r="AU28" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:47" ht="12.5">
@@ -20160,28 +20160,28 @@
         <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E29" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F29" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G29" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H29" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I29" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J29" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K29" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L29">
         <v>0.98999999999999999</v>
@@ -20289,7 +20289,7 @@
         <v>0.98999999999999999</v>
       </c>
       <c r="AU29" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:47" ht="12.5">
@@ -20300,31 +20300,31 @@
         <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D30" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E30" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F30" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G30" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H30" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I30" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J30" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K30" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L30">
         <v>0.58696999999999999</v>
@@ -20432,7 +20432,7 @@
         <v>0.58696999999999999</v>
       </c>
       <c r="AU30" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:47" ht="12.5">
@@ -20443,31 +20443,31 @@
         <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D31" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E31" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F31" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G31" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H31" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I31" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J31" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K31" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L31">
         <v>0.58696999999999999</v>
@@ -20575,7 +20575,7 @@
         <v>0.58696999999999999</v>
       </c>
       <c r="AU31" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:47" ht="12.5">
@@ -20589,28 +20589,28 @@
         <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E32" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F32" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G32" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H32" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I32" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J32" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K32" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L32">
         <v>0.58696999999999999</v>
@@ -20718,7 +20718,7 @@
         <v>0.58696999999999999</v>
       </c>
       <c r="AU32" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:47" ht="12.5">
@@ -20729,31 +20729,31 @@
         <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D33" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E33" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F33" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G33" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H33" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I33" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J33" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K33" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L33">
         <v>0.072069999999999995</v>
@@ -20861,7 +20861,7 @@
         <v>0.072069999999999995</v>
       </c>
       <c r="AU33" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:47" ht="12.5">
@@ -20875,28 +20875,28 @@
         <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E34" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F34" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G34" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H34" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I34" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J34" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K34" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L34">
         <v>0.072069999999999995</v>
@@ -21004,7 +21004,7 @@
         <v>0.072069999999999995</v>
       </c>
       <c r="AU34" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:47" ht="12.5">
@@ -21015,31 +21015,31 @@
         <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D35" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E35" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F35" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G35" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H35" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I35" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J35" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K35" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L35">
         <v>0.313</v>
@@ -21147,7 +21147,7 @@
         <v>0.313</v>
       </c>
       <c r="AU35" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="36" spans="1:47" ht="12.5">
@@ -21158,31 +21158,31 @@
         <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D36" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E36" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F36" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G36" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H36" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I36" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J36" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K36" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L36">
         <v>0.080000000000000002</v>
@@ -21290,7 +21290,7 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="AU36" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="37" spans="1:47" ht="12.5">
@@ -21301,31 +21301,31 @@
         <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D37" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E37" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F37" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G37" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H37" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I37" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J37" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K37" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L37">
         <v>0.080000000000000002</v>
@@ -21433,7 +21433,7 @@
         <v>0.080000000000000002</v>
       </c>
       <c r="AU37" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:47" ht="12.5">
@@ -21447,28 +21447,28 @@
         <v>176</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E38" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F38" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G38" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H38" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I38" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J38" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K38" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L38">
         <v>0.075999999999999998</v>
@@ -21576,7 +21576,7 @@
         <v>0.075999999999999998</v>
       </c>
       <c r="AU38" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:47" ht="12.5">
@@ -21587,31 +21587,31 @@
         <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E39" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F39" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G39" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H39" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I39" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J39" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K39" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L39">
         <v>0.061199999999999997</v>
@@ -21719,7 +21719,7 @@
         <v>0.061199999999999997</v>
       </c>
       <c r="AU39" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="40" spans="1:47" ht="12.5">
@@ -21730,31 +21730,31 @@
         <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D40" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E40" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F40" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G40" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H40" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I40" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J40" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K40" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L40">
         <v>0.52772280688712803</v>
@@ -21778,7 +21778,7 @@
         <v>0.52772280688712803</v>
       </c>
       <c r="S40">
-        <v>0.79158421033069304</v>
+        <v>0.52772280688712803</v>
       </c>
       <c r="T40">
         <v>0.52772280688712803</v>
@@ -21862,7 +21862,7 @@
         <v>0.52772280688712803</v>
       </c>
       <c r="AU40" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:47" ht="12.5">
@@ -21873,31 +21873,31 @@
         <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D41" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E41" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F41" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G41" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H41" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I41" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J41" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K41" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L41">
         <v>0.52772280688712803</v>
@@ -21921,7 +21921,7 @@
         <v>0.52772280688712803</v>
       </c>
       <c r="S41">
-        <v>0.79158421033069304</v>
+        <v>0.52772280688712803</v>
       </c>
       <c r="T41">
         <v>0.52772280688712803</v>
@@ -22005,7 +22005,7 @@
         <v>0.52772280688712803</v>
       </c>
       <c r="AU41" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:47" ht="12.5">
@@ -22016,139 +22016,139 @@
         <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D42" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E42" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F42" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G42" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H42" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I42" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J42" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K42" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="M42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="N42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="O42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="P42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="Q42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="R42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="S42">
-        <v>1.74769825504333</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="T42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="U42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="V42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="W42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="X42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="Y42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="Z42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AA42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AB42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AC42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AD42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AE42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AF42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AG42">
-        <v>0.69907930201733304</v>
+        <v>0.55926344161386699</v>
       </c>
       <c r="AH42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AI42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AJ42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AK42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AL42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AM42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AN42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AO42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AP42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AQ42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AR42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AS42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AT42">
-        <v>1.1651321700288899</v>
+        <v>0.93210573602311098</v>
       </c>
       <c r="AU42" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:47" ht="12.5">
@@ -22159,31 +22159,31 @@
         <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E43" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F43" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G43" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H43" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I43" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J43" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K43" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L43">
         <v>0.46605286801155599</v>
@@ -22207,7 +22207,7 @@
         <v>0.46605286801155599</v>
       </c>
       <c r="S43">
-        <v>0.69907930201733304</v>
+        <v>0.46605286801155599</v>
       </c>
       <c r="T43">
         <v>0.46605286801155599</v>
@@ -22291,7 +22291,7 @@
         <v>0.46605286801155599</v>
       </c>
       <c r="AU43" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="44" spans="1:47" ht="12.5">
@@ -22305,28 +22305,28 @@
         <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E44" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F44" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G44" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H44" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I44" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J44" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K44" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L44">
         <v>0.46605286801155599</v>
@@ -22350,7 +22350,7 @@
         <v>0.46605286801155599</v>
       </c>
       <c r="S44">
-        <v>0.69907930201733304</v>
+        <v>0.46605286801155599</v>
       </c>
       <c r="T44">
         <v>0.46605286801155599</v>
@@ -22434,7 +22434,7 @@
         <v>0.46605286801155599</v>
       </c>
       <c r="AU44" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:47" ht="12.5">
@@ -22445,31 +22445,31 @@
         <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D45" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E45" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F45" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G45" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H45" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I45" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J45" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K45" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L45">
         <v>0.47553149117899501</v>
@@ -22493,7 +22493,7 @@
         <v>0.47553149117899501</v>
       </c>
       <c r="S45">
-        <v>0.71329723676849299</v>
+        <v>0.47553149117899501</v>
       </c>
       <c r="T45">
         <v>0.47553149117899501</v>
@@ -22577,7 +22577,7 @@
         <v>0.47553149117899501</v>
       </c>
       <c r="AU45" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:47" ht="12.5">
@@ -22588,31 +22588,31 @@
         <v>61</v>
       </c>
       <c r="C46" t="s">
+        <v>186</v>
+      </c>
+      <c r="D46" t="s">
+        <v>164</v>
+      </c>
+      <c r="E46" t="s">
+        <v>164</v>
+      </c>
+      <c r="F46" t="s">
+        <v>165</v>
+      </c>
+      <c r="G46" t="s">
         <v>166</v>
       </c>
-      <c r="D46" t="s">
-        <v>185</v>
-      </c>
-      <c r="E46" t="s">
-        <v>185</v>
-      </c>
-      <c r="F46" t="s">
-        <v>184</v>
-      </c>
-      <c r="G46" t="s">
-        <v>183</v>
-      </c>
       <c r="H46" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I46" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J46" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K46" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L46">
         <v>0.429345439465179</v>
@@ -22636,7 +22636,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="S46">
-        <v>0.64401815919776795</v>
+        <v>0.429345439465179</v>
       </c>
       <c r="T46">
         <v>0.429345439465179</v>
@@ -22720,7 +22720,7 @@
         <v>0.429345439465179</v>
       </c>
       <c r="AU46" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:47" ht="12.5">
@@ -22731,31 +22731,31 @@
         <v>61</v>
       </c>
       <c r="C47" t="s">
+        <v>187</v>
+      </c>
+      <c r="D47" t="s">
+        <v>164</v>
+      </c>
+      <c r="E47" t="s">
+        <v>164</v>
+      </c>
+      <c r="F47" t="s">
         <v>165</v>
       </c>
-      <c r="D47" t="s">
-        <v>185</v>
-      </c>
-      <c r="E47" t="s">
-        <v>185</v>
-      </c>
-      <c r="F47" t="s">
-        <v>184</v>
-      </c>
       <c r="G47" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H47" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I47" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J47" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K47" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L47">
         <v>0.139365903767697</v>
@@ -22863,7 +22863,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU47" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="48" spans="1:47" ht="12.5">
@@ -22877,28 +22877,28 @@
         <v>113</v>
       </c>
       <c r="D48" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E48" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F48" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G48" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H48" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I48" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J48" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K48" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L48">
         <v>0.139365903767697</v>
@@ -23006,7 +23006,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU48" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:47" ht="12.5">
@@ -23017,31 +23017,31 @@
         <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="D49" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E49" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F49" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G49" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H49" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I49" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J49" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K49" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L49">
         <v>0.139365903767697</v>
@@ -23149,7 +23149,7 @@
         <v>0.139365903767697</v>
       </c>
       <c r="AU49" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:47" ht="12.5">
@@ -23160,31 +23160,31 @@
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="D50" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E50" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F50" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G50" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H50" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I50" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J50" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K50" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L50">
         <v>0.379626024625345</v>
@@ -23292,7 +23292,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU50" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:47" ht="12.5">
@@ -23306,28 +23306,28 @@
         <v>114</v>
       </c>
       <c r="D51" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E51" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F51" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G51" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H51" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I51" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J51" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K51" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L51">
         <v>0.379626024625345</v>
@@ -23435,7 +23435,7 @@
         <v>0.379626024625345</v>
       </c>
       <c r="AU51" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52" spans="1:47" ht="12.5">
@@ -23446,31 +23446,31 @@
         <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="D52" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E52" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F52" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G52" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H52" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I52" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J52" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K52" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L52">
         <v>0.74542647386440897</v>
@@ -23578,7 +23578,7 @@
         <v>0.74542647386440897</v>
       </c>
       <c r="AU52" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:47" ht="12.5">
@@ -23589,31 +23589,31 @@
         <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="D53" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E53" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F53" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G53" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H53" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I53" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J53" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K53" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L53">
         <v>0.37271323693220398</v>
@@ -23721,7 +23721,7 @@
         <v>0.37271323693220398</v>
       </c>
       <c r="AU53" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:47" ht="12.5">
@@ -23732,31 +23732,31 @@
         <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="D54" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E54" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F54" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G54" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H54" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I54" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J54" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K54" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L54">
         <v>0.44075733528719402</v>
@@ -23864,7 +23864,7 @@
         <v>0.44075733528719402</v>
       </c>
       <c r="AU54" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="1:47" ht="12.5">
@@ -23875,31 +23875,31 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D55" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="E55" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="F55" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G55" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="H55" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="I55" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J55" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="K55" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="L55">
         <v>0.32948443032272601</v>
@@ -24007,7 +24007,7 @@
         <v>0.32948443032272601</v>
       </c>
       <c r="AU55" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
